--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,195 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>UEFA Champions League</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Portuguese Primeira Liga</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>02:30:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Minnesota Utd</t>
+  </si>
+  <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Boyaca Chico</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>PSV</t>
+  </si>
+  <si>
+    <t>Fenerbahce</t>
+  </si>
+  <si>
+    <t>Falkenbergs</t>
+  </si>
+  <si>
+    <t>Varbergs BoIS</t>
+  </si>
+  <si>
+    <t>Sundsvall</t>
+  </si>
+  <si>
+    <t>Ostersunds FK</t>
+  </si>
+  <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>Slavia Prague</t>
+  </si>
+  <si>
+    <t>Man Utd</t>
+  </si>
+  <si>
+    <t>Club Football Estrela</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes</t>
+  </si>
+  <si>
+    <t>St Louis City SC</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Shakhtar</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Osters</t>
+  </si>
+  <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>IK Brage</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>FC Sabah</t>
+  </si>
+  <si>
+    <t>Braga</t>
+  </si>
+  <si>
+    <t>2026-09-08 01:56:41</t>
   </si>
 </sst>
 </file>
@@ -585,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1017,5572 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2">
+        <v>2.28</v>
+      </c>
+      <c r="G2">
+        <v>2.36</v>
+      </c>
+      <c r="H2">
+        <v>3.15</v>
+      </c>
+      <c r="I2">
+        <v>3.25</v>
+      </c>
+      <c r="J2">
+        <v>3.75</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>1.33</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>4.9</v>
+      </c>
+      <c r="O2">
+        <v>1.24</v>
+      </c>
+      <c r="P2">
+        <v>2.3</v>
+      </c>
+      <c r="Q2">
+        <v>1.73</v>
+      </c>
+      <c r="R2">
+        <v>1.51</v>
+      </c>
+      <c r="S2">
+        <v>2.86</v>
+      </c>
+      <c r="T2">
+        <v>1.61</v>
+      </c>
+      <c r="U2">
+        <v>2.46</v>
+      </c>
+      <c r="V2">
+        <v>1.45</v>
+      </c>
+      <c r="W2">
+        <v>1.73</v>
+      </c>
+      <c r="X2">
+        <v>24</v>
+      </c>
+      <c r="Y2">
+        <v>17.5</v>
+      </c>
+      <c r="Z2">
+        <v>25</v>
+      </c>
+      <c r="AA2">
+        <v>260</v>
+      </c>
+      <c r="AB2">
+        <v>13.5</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>14</v>
+      </c>
+      <c r="AE2">
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <v>18</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>16.5</v>
+      </c>
+      <c r="AI2">
+        <v>44</v>
+      </c>
+      <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>24</v>
+      </c>
+      <c r="AL2">
+        <v>40</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>14.5</v>
+      </c>
+      <c r="AO2">
+        <v>26</v>
+      </c>
+      <c r="AP2">
+        <v>17</v>
+      </c>
+      <c r="AQ2">
+        <v>13.5</v>
+      </c>
+      <c r="AR2">
+        <v>17.5</v>
+      </c>
+      <c r="AS2">
+        <v>36</v>
+      </c>
+      <c r="AT2">
+        <v>11.5</v>
+      </c>
+      <c r="AU2">
+        <v>8</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>22</v>
+      </c>
+      <c r="AX2">
+        <v>13</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>13.5</v>
+      </c>
+      <c r="BA2">
+        <v>23</v>
+      </c>
+      <c r="BB2">
+        <v>20</v>
+      </c>
+      <c r="BC2">
+        <v>15.5</v>
+      </c>
+      <c r="BD2">
+        <v>20</v>
+      </c>
+      <c r="BE2">
+        <v>32</v>
+      </c>
+      <c r="BF2">
+        <v>11.5</v>
+      </c>
+      <c r="BG2">
+        <v>16.5</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>3.3</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>6.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>6.6</v>
+      </c>
+      <c r="BO2">
+        <v>4.3</v>
+      </c>
+      <c r="BP2">
+        <v>23</v>
+      </c>
+      <c r="BQ2">
+        <v>10</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>5</v>
+      </c>
+      <c r="BV2">
+        <v>34</v>
+      </c>
+      <c r="BW2">
+        <v>14</v>
+      </c>
+      <c r="BX2">
+        <v>46</v>
+      </c>
+      <c r="BY2">
+        <v>18.5</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <v>1.87</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>4.8</v>
+      </c>
+      <c r="I3">
+        <v>5.8</v>
+      </c>
+      <c r="J3">
+        <v>3.4</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.45</v>
+      </c>
+      <c r="M3">
+        <v>1.1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>1.45</v>
+      </c>
+      <c r="P3">
+        <v>1.67</v>
+      </c>
+      <c r="Q3">
+        <v>2.18</v>
+      </c>
+      <c r="R3">
+        <v>1.23</v>
+      </c>
+      <c r="S3">
+        <v>4.3</v>
+      </c>
+      <c r="T3">
+        <v>1.95</v>
+      </c>
+      <c r="U3">
+        <v>1.86</v>
+      </c>
+      <c r="V3">
+        <v>1.21</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3">
+        <v>970</v>
+      </c>
+      <c r="Y3">
+        <v>16.5</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>970</v>
+      </c>
+      <c r="AC3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>970</v>
+      </c>
+      <c r="AG3">
+        <v>970</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.65</v>
+      </c>
+      <c r="AQ3">
+        <v>1.63</v>
+      </c>
+      <c r="AR3">
+        <v>1.81</v>
+      </c>
+      <c r="AS3">
+        <v>1.81</v>
+      </c>
+      <c r="AT3">
+        <v>6.4</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>1.81</v>
+      </c>
+      <c r="AW3">
+        <v>1.81</v>
+      </c>
+      <c r="AX3">
+        <v>1.65</v>
+      </c>
+      <c r="AY3">
+        <v>1.65</v>
+      </c>
+      <c r="AZ3">
+        <v>1.81</v>
+      </c>
+      <c r="BA3">
+        <v>1.81</v>
+      </c>
+      <c r="BB3">
+        <v>1.81</v>
+      </c>
+      <c r="BC3">
+        <v>1.81</v>
+      </c>
+      <c r="BD3">
+        <v>1.75</v>
+      </c>
+      <c r="BE3">
+        <v>1.81</v>
+      </c>
+      <c r="BF3">
+        <v>1.81</v>
+      </c>
+      <c r="BG3">
+        <v>1.81</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.47</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4">
+        <v>2.28</v>
+      </c>
+      <c r="G4">
+        <v>2.46</v>
+      </c>
+      <c r="H4">
+        <v>3.9</v>
+      </c>
+      <c r="I4">
+        <v>4.3</v>
+      </c>
+      <c r="J4">
+        <v>2.9</v>
+      </c>
+      <c r="K4">
+        <v>3.1</v>
+      </c>
+      <c r="L4">
+        <v>1.62</v>
+      </c>
+      <c r="M4">
+        <v>1.16</v>
+      </c>
+      <c r="N4">
+        <v>2.34</v>
+      </c>
+      <c r="O4">
+        <v>1.67</v>
+      </c>
+      <c r="P4">
+        <v>1.43</v>
+      </c>
+      <c r="Q4">
+        <v>3.1</v>
+      </c>
+      <c r="R4">
+        <v>1.15</v>
+      </c>
+      <c r="S4">
+        <v>6.8</v>
+      </c>
+      <c r="T4">
+        <v>2.34</v>
+      </c>
+      <c r="U4">
+        <v>1.65</v>
+      </c>
+      <c r="V4">
+        <v>1.3</v>
+      </c>
+      <c r="W4">
+        <v>1.68</v>
+      </c>
+      <c r="X4">
+        <v>9.4</v>
+      </c>
+      <c r="Y4">
+        <v>13</v>
+      </c>
+      <c r="Z4">
+        <v>38</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC4">
+        <v>9.4</v>
+      </c>
+      <c r="AD4">
+        <v>26</v>
+      </c>
+      <c r="AE4">
+        <v>100</v>
+      </c>
+      <c r="AF4">
+        <v>18.5</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>50</v>
+      </c>
+      <c r="AK4">
+        <v>55</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>65</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>5.3</v>
+      </c>
+      <c r="AQ4">
+        <v>7.8</v>
+      </c>
+      <c r="AR4">
+        <v>18</v>
+      </c>
+      <c r="AS4">
+        <v>3.3</v>
+      </c>
+      <c r="AT4">
+        <v>5.1</v>
+      </c>
+      <c r="AU4">
+        <v>5.5</v>
+      </c>
+      <c r="AV4">
+        <v>2.92</v>
+      </c>
+      <c r="AW4">
+        <v>3.2</v>
+      </c>
+      <c r="AX4">
+        <v>9.4</v>
+      </c>
+      <c r="AY4">
+        <v>2.78</v>
+      </c>
+      <c r="AZ4">
+        <v>3.05</v>
+      </c>
+      <c r="BA4">
+        <v>3.3</v>
+      </c>
+      <c r="BB4">
+        <v>26</v>
+      </c>
+      <c r="BC4">
+        <v>3.1</v>
+      </c>
+      <c r="BD4">
+        <v>3.2</v>
+      </c>
+      <c r="BE4">
+        <v>3.3</v>
+      </c>
+      <c r="BF4">
+        <v>3.15</v>
+      </c>
+      <c r="BG4">
+        <v>3.3</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>2.12</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.64</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.64</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.65</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.64</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.64</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.64</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.64</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.64</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.64</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5">
+        <v>1.92</v>
+      </c>
+      <c r="G5">
+        <v>1.98</v>
+      </c>
+      <c r="H5">
+        <v>3.85</v>
+      </c>
+      <c r="I5">
+        <v>4.1</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4.4</v>
+      </c>
+      <c r="L5">
+        <v>1.29</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>5.8</v>
+      </c>
+      <c r="O5">
+        <v>1.2</v>
+      </c>
+      <c r="P5">
+        <v>2.56</v>
+      </c>
+      <c r="Q5">
+        <v>1.6</v>
+      </c>
+      <c r="R5">
+        <v>1.65</v>
+      </c>
+      <c r="S5">
+        <v>2.44</v>
+      </c>
+      <c r="T5">
+        <v>1.59</v>
+      </c>
+      <c r="U5">
+        <v>2.62</v>
+      </c>
+      <c r="V5">
+        <v>1.32</v>
+      </c>
+      <c r="W5">
+        <v>2.02</v>
+      </c>
+      <c r="X5">
+        <v>40</v>
+      </c>
+      <c r="Y5">
+        <v>22</v>
+      </c>
+      <c r="Z5">
+        <v>34</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>13.5</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>46</v>
+      </c>
+      <c r="AF5">
+        <v>15</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
+        <v>16.5</v>
+      </c>
+      <c r="AI5">
+        <v>46</v>
+      </c>
+      <c r="AJ5">
+        <v>25</v>
+      </c>
+      <c r="AK5">
+        <v>17.5</v>
+      </c>
+      <c r="AL5">
+        <v>28</v>
+      </c>
+      <c r="AM5">
+        <v>580</v>
+      </c>
+      <c r="AN5">
+        <v>8.6</v>
+      </c>
+      <c r="AO5">
+        <v>29</v>
+      </c>
+      <c r="AP5">
+        <v>20</v>
+      </c>
+      <c r="AQ5">
+        <v>18</v>
+      </c>
+      <c r="AR5">
+        <v>21</v>
+      </c>
+      <c r="AS5">
+        <v>34</v>
+      </c>
+      <c r="AT5">
+        <v>12</v>
+      </c>
+      <c r="AU5">
+        <v>9</v>
+      </c>
+      <c r="AV5">
+        <v>15</v>
+      </c>
+      <c r="AW5">
+        <v>23</v>
+      </c>
+      <c r="AX5">
+        <v>13</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>14</v>
+      </c>
+      <c r="BA5">
+        <v>24</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5">
+        <v>15</v>
+      </c>
+      <c r="BD5">
+        <v>18</v>
+      </c>
+      <c r="BE5">
+        <v>30</v>
+      </c>
+      <c r="BF5">
+        <v>8</v>
+      </c>
+      <c r="BG5">
+        <v>19</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>3.65</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>5.6</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>4.1</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>7.2</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>12</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>5.1</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6">
+        <v>2.6</v>
+      </c>
+      <c r="G6">
+        <v>2.7</v>
+      </c>
+      <c r="H6">
+        <v>2.8</v>
+      </c>
+      <c r="I6">
+        <v>2.92</v>
+      </c>
+      <c r="J6">
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <v>3.75</v>
+      </c>
+      <c r="L6">
+        <v>1.4</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>4.1</v>
+      </c>
+      <c r="O6">
+        <v>1.3</v>
+      </c>
+      <c r="P6">
+        <v>2.04</v>
+      </c>
+      <c r="Q6">
+        <v>1.92</v>
+      </c>
+      <c r="R6">
+        <v>1.4</v>
+      </c>
+      <c r="S6">
+        <v>3.35</v>
+      </c>
+      <c r="T6">
+        <v>1.73</v>
+      </c>
+      <c r="U6">
+        <v>2.26</v>
+      </c>
+      <c r="V6">
+        <v>1.52</v>
+      </c>
+      <c r="W6">
+        <v>1.58</v>
+      </c>
+      <c r="X6">
+        <v>17</v>
+      </c>
+      <c r="Y6">
+        <v>14.5</v>
+      </c>
+      <c r="Z6">
+        <v>19.5</v>
+      </c>
+      <c r="AA6">
+        <v>60</v>
+      </c>
+      <c r="AB6">
+        <v>13</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>13.5</v>
+      </c>
+      <c r="AE6">
+        <v>36</v>
+      </c>
+      <c r="AF6">
+        <v>18.5</v>
+      </c>
+      <c r="AG6">
+        <v>13.5</v>
+      </c>
+      <c r="AH6">
+        <v>18.5</v>
+      </c>
+      <c r="AI6">
+        <v>50</v>
+      </c>
+      <c r="AJ6">
+        <v>48</v>
+      </c>
+      <c r="AK6">
+        <v>32</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>23</v>
+      </c>
+      <c r="AO6">
+        <v>30</v>
+      </c>
+      <c r="AP6">
+        <v>14</v>
+      </c>
+      <c r="AQ6">
+        <v>11</v>
+      </c>
+      <c r="AR6">
+        <v>15</v>
+      </c>
+      <c r="AS6">
+        <v>25</v>
+      </c>
+      <c r="AT6">
+        <v>10</v>
+      </c>
+      <c r="AU6">
+        <v>7.4</v>
+      </c>
+      <c r="AV6">
+        <v>11.5</v>
+      </c>
+      <c r="AW6">
+        <v>24</v>
+      </c>
+      <c r="AX6">
+        <v>14</v>
+      </c>
+      <c r="AY6">
+        <v>11</v>
+      </c>
+      <c r="AZ6">
+        <v>14.5</v>
+      </c>
+      <c r="BA6">
+        <v>32</v>
+      </c>
+      <c r="BB6">
+        <v>29</v>
+      </c>
+      <c r="BC6">
+        <v>19.5</v>
+      </c>
+      <c r="BD6">
+        <v>24</v>
+      </c>
+      <c r="BE6">
+        <v>36</v>
+      </c>
+      <c r="BF6">
+        <v>18</v>
+      </c>
+      <c r="BG6">
+        <v>17.5</v>
+      </c>
+      <c r="BH6">
+        <v>4</v>
+      </c>
+      <c r="BI6">
+        <v>2.84</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>6.2</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>2.1</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>4</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>2.16</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>2.1</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>4.6</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>2.16</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>2.1</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>2.1</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7">
+        <v>1.8</v>
+      </c>
+      <c r="G7">
+        <v>1.85</v>
+      </c>
+      <c r="H7">
+        <v>4.5</v>
+      </c>
+      <c r="I7">
+        <v>4.9</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>4.4</v>
+      </c>
+      <c r="L7">
+        <v>1.34</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.9</v>
+      </c>
+      <c r="O7">
+        <v>1.23</v>
+      </c>
+      <c r="P7">
+        <v>2.3</v>
+      </c>
+      <c r="Q7">
+        <v>1.72</v>
+      </c>
+      <c r="R7">
+        <v>1.51</v>
+      </c>
+      <c r="S7">
+        <v>2.84</v>
+      </c>
+      <c r="T7">
+        <v>1.68</v>
+      </c>
+      <c r="U7">
+        <v>2.34</v>
+      </c>
+      <c r="V7">
+        <v>1.26</v>
+      </c>
+      <c r="W7">
+        <v>2.16</v>
+      </c>
+      <c r="X7">
+        <v>29</v>
+      </c>
+      <c r="Y7">
+        <v>21</v>
+      </c>
+      <c r="Z7">
+        <v>40</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>12</v>
+      </c>
+      <c r="AC7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>19.5</v>
+      </c>
+      <c r="AE7">
+        <v>220</v>
+      </c>
+      <c r="AF7">
+        <v>12.5</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>18.5</v>
+      </c>
+      <c r="AI7">
+        <v>290</v>
+      </c>
+      <c r="AJ7">
+        <v>22</v>
+      </c>
+      <c r="AK7">
+        <v>18.5</v>
+      </c>
+      <c r="AL7">
+        <v>50</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>9.4</v>
+      </c>
+      <c r="AO7">
+        <v>160</v>
+      </c>
+      <c r="AP7">
+        <v>18</v>
+      </c>
+      <c r="AQ7">
+        <v>14.5</v>
+      </c>
+      <c r="AR7">
+        <v>22</v>
+      </c>
+      <c r="AS7">
+        <v>42</v>
+      </c>
+      <c r="AT7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU7">
+        <v>7.8</v>
+      </c>
+      <c r="AV7">
+        <v>16</v>
+      </c>
+      <c r="AW7">
+        <v>34</v>
+      </c>
+      <c r="AX7">
+        <v>10.5</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>36</v>
+      </c>
+      <c r="BB7">
+        <v>15.5</v>
+      </c>
+      <c r="BC7">
+        <v>15</v>
+      </c>
+      <c r="BD7">
+        <v>19.5</v>
+      </c>
+      <c r="BE7">
+        <v>42</v>
+      </c>
+      <c r="BF7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG7">
+        <v>34</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>3.3</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>6.6</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>3.75</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>7</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>5.4</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8">
+        <v>2.2</v>
+      </c>
+      <c r="G8">
+        <v>2.26</v>
+      </c>
+      <c r="H8">
+        <v>2.96</v>
+      </c>
+      <c r="I8">
+        <v>3.1</v>
+      </c>
+      <c r="J8">
+        <v>4.4</v>
+      </c>
+      <c r="K8">
+        <v>4.7</v>
+      </c>
+      <c r="L8">
+        <v>1.18</v>
+      </c>
+      <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
+        <v>10.5</v>
+      </c>
+      <c r="O8">
+        <v>1.09</v>
+      </c>
+      <c r="P8">
+        <v>4.2</v>
+      </c>
+      <c r="Q8">
+        <v>1.29</v>
+      </c>
+      <c r="R8">
+        <v>2.32</v>
+      </c>
+      <c r="S8">
+        <v>1.72</v>
+      </c>
+      <c r="T8">
+        <v>1.32</v>
+      </c>
+      <c r="U8">
+        <v>3.8</v>
+      </c>
+      <c r="V8">
+        <v>1.48</v>
+      </c>
+      <c r="W8">
+        <v>1.79</v>
+      </c>
+      <c r="X8">
+        <v>320</v>
+      </c>
+      <c r="Y8">
+        <v>60</v>
+      </c>
+      <c r="Z8">
+        <v>70</v>
+      </c>
+      <c r="AA8">
+        <v>300</v>
+      </c>
+      <c r="AB8">
+        <v>32</v>
+      </c>
+      <c r="AC8">
+        <v>14.5</v>
+      </c>
+      <c r="AD8">
+        <v>17</v>
+      </c>
+      <c r="AE8">
+        <v>29</v>
+      </c>
+      <c r="AF8">
+        <v>28</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>13.5</v>
+      </c>
+      <c r="AI8">
+        <v>24</v>
+      </c>
+      <c r="AJ8">
+        <v>38</v>
+      </c>
+      <c r="AK8">
+        <v>20</v>
+      </c>
+      <c r="AL8">
+        <v>21</v>
+      </c>
+      <c r="AM8">
+        <v>34</v>
+      </c>
+      <c r="AN8">
+        <v>6.6</v>
+      </c>
+      <c r="AO8">
+        <v>10.5</v>
+      </c>
+      <c r="AP8">
+        <v>28</v>
+      </c>
+      <c r="AQ8">
+        <v>21</v>
+      </c>
+      <c r="AR8">
+        <v>22</v>
+      </c>
+      <c r="AS8">
+        <v>40</v>
+      </c>
+      <c r="AT8">
+        <v>19</v>
+      </c>
+      <c r="AU8">
+        <v>12.5</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>22</v>
+      </c>
+      <c r="AX8">
+        <v>18</v>
+      </c>
+      <c r="AY8">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8">
+        <v>11.5</v>
+      </c>
+      <c r="BA8">
+        <v>20</v>
+      </c>
+      <c r="BB8">
+        <v>21</v>
+      </c>
+      <c r="BC8">
+        <v>17</v>
+      </c>
+      <c r="BD8">
+        <v>15</v>
+      </c>
+      <c r="BE8">
+        <v>19.5</v>
+      </c>
+      <c r="BF8">
+        <v>6</v>
+      </c>
+      <c r="BG8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>4.9</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>5.9</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>5.4</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>9</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>5.5</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9">
+        <v>1.04</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>1.63</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.26</v>
+      </c>
+      <c r="O9">
+        <v>1.3</v>
+      </c>
+      <c r="P9">
+        <v>1.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.3</v>
+      </c>
+      <c r="R9">
+        <v>1.13</v>
+      </c>
+      <c r="S9">
+        <v>1.32</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.66</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10">
+        <v>1.83</v>
+      </c>
+      <c r="G10">
+        <v>1.91</v>
+      </c>
+      <c r="H10">
+        <v>3.9</v>
+      </c>
+      <c r="I10">
+        <v>4.5</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>5.2</v>
+      </c>
+      <c r="L10">
+        <v>1.22</v>
+      </c>
+      <c r="M10">
+        <v>1.02</v>
+      </c>
+      <c r="N10">
+        <v>7</v>
+      </c>
+      <c r="O10">
+        <v>1.14</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>1.45</v>
+      </c>
+      <c r="R10">
+        <v>1.81</v>
+      </c>
+      <c r="S10">
+        <v>2.12</v>
+      </c>
+      <c r="T10">
+        <v>1.48</v>
+      </c>
+      <c r="U10">
+        <v>2.9</v>
+      </c>
+      <c r="V10">
+        <v>1.3</v>
+      </c>
+      <c r="W10">
+        <v>2.1</v>
+      </c>
+      <c r="X10">
+        <v>70</v>
+      </c>
+      <c r="Y10">
+        <v>32</v>
+      </c>
+      <c r="Z10">
+        <v>65</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>17.5</v>
+      </c>
+      <c r="AC10">
+        <v>11.5</v>
+      </c>
+      <c r="AD10">
+        <v>17.5</v>
+      </c>
+      <c r="AE10">
+        <v>85</v>
+      </c>
+      <c r="AF10">
+        <v>16.5</v>
+      </c>
+      <c r="AG10">
+        <v>11.5</v>
+      </c>
+      <c r="AH10">
+        <v>16</v>
+      </c>
+      <c r="AI10">
+        <v>70</v>
+      </c>
+      <c r="AJ10">
+        <v>25</v>
+      </c>
+      <c r="AK10">
+        <v>17.5</v>
+      </c>
+      <c r="AL10">
+        <v>26</v>
+      </c>
+      <c r="AM10">
+        <v>180</v>
+      </c>
+      <c r="AN10">
+        <v>6.8</v>
+      </c>
+      <c r="AO10">
+        <v>29</v>
+      </c>
+      <c r="AP10">
+        <v>22</v>
+      </c>
+      <c r="AQ10">
+        <v>17.5</v>
+      </c>
+      <c r="AR10">
+        <v>23</v>
+      </c>
+      <c r="AS10">
+        <v>36</v>
+      </c>
+      <c r="AT10">
+        <v>13</v>
+      </c>
+      <c r="AU10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>13</v>
+      </c>
+      <c r="AW10">
+        <v>23</v>
+      </c>
+      <c r="AX10">
+        <v>13</v>
+      </c>
+      <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>12</v>
+      </c>
+      <c r="BA10">
+        <v>22</v>
+      </c>
+      <c r="BB10">
+        <v>16</v>
+      </c>
+      <c r="BC10">
+        <v>13.5</v>
+      </c>
+      <c r="BD10">
+        <v>16.5</v>
+      </c>
+      <c r="BE10">
+        <v>34</v>
+      </c>
+      <c r="BF10">
+        <v>6.2</v>
+      </c>
+      <c r="BG10">
+        <v>17.5</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>4</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>6.2</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>4.2</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>7</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>9.6</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>6</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11">
+        <v>2.34</v>
+      </c>
+      <c r="G11">
+        <v>2.42</v>
+      </c>
+      <c r="H11">
+        <v>2.96</v>
+      </c>
+      <c r="I11">
+        <v>3.05</v>
+      </c>
+      <c r="J11">
+        <v>3.9</v>
+      </c>
+      <c r="K11">
+        <v>4.3</v>
+      </c>
+      <c r="L11">
+        <v>1.25</v>
+      </c>
+      <c r="M11">
+        <v>1.03</v>
+      </c>
+      <c r="N11">
+        <v>5.8</v>
+      </c>
+      <c r="O11">
+        <v>1.18</v>
+      </c>
+      <c r="P11">
+        <v>2.62</v>
+      </c>
+      <c r="Q11">
+        <v>1.55</v>
+      </c>
+      <c r="R11">
+        <v>1.67</v>
+      </c>
+      <c r="S11">
+        <v>2.36</v>
+      </c>
+      <c r="T11">
+        <v>1.52</v>
+      </c>
+      <c r="U11">
+        <v>2.74</v>
+      </c>
+      <c r="V11">
+        <v>1.48</v>
+      </c>
+      <c r="W11">
+        <v>1.7</v>
+      </c>
+      <c r="X11">
+        <v>27</v>
+      </c>
+      <c r="Y11">
+        <v>18.5</v>
+      </c>
+      <c r="Z11">
+        <v>25</v>
+      </c>
+      <c r="AA11">
+        <v>50</v>
+      </c>
+      <c r="AB11">
+        <v>16</v>
+      </c>
+      <c r="AC11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11">
+        <v>29</v>
+      </c>
+      <c r="AF11">
+        <v>19.5</v>
+      </c>
+      <c r="AG11">
+        <v>12.5</v>
+      </c>
+      <c r="AH11">
+        <v>15</v>
+      </c>
+      <c r="AI11">
+        <v>32</v>
+      </c>
+      <c r="AJ11">
+        <v>32</v>
+      </c>
+      <c r="AK11">
+        <v>22</v>
+      </c>
+      <c r="AL11">
+        <v>28</v>
+      </c>
+      <c r="AM11">
+        <v>55</v>
+      </c>
+      <c r="AN11">
+        <v>11.5</v>
+      </c>
+      <c r="AO11">
+        <v>17.5</v>
+      </c>
+      <c r="AP11">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11">
+        <v>16</v>
+      </c>
+      <c r="AR11">
+        <v>21</v>
+      </c>
+      <c r="AS11">
+        <v>38</v>
+      </c>
+      <c r="AT11">
+        <v>14.5</v>
+      </c>
+      <c r="AU11">
+        <v>9</v>
+      </c>
+      <c r="AV11">
+        <v>12</v>
+      </c>
+      <c r="AW11">
+        <v>22</v>
+      </c>
+      <c r="AX11">
+        <v>16.5</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>13</v>
+      </c>
+      <c r="BA11">
+        <v>19.5</v>
+      </c>
+      <c r="BB11">
+        <v>21</v>
+      </c>
+      <c r="BC11">
+        <v>19</v>
+      </c>
+      <c r="BD11">
+        <v>22</v>
+      </c>
+      <c r="BE11">
+        <v>26</v>
+      </c>
+      <c r="BF11">
+        <v>10.5</v>
+      </c>
+      <c r="BG11">
+        <v>15</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>3.65</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>6.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>4.7</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>10</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>5.2</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>13</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12">
+        <v>1.44</v>
+      </c>
+      <c r="G12">
+        <v>1.47</v>
+      </c>
+      <c r="H12">
+        <v>6.8</v>
+      </c>
+      <c r="I12">
+        <v>7.6</v>
+      </c>
+      <c r="J12">
+        <v>5.4</v>
+      </c>
+      <c r="K12">
+        <v>5.9</v>
+      </c>
+      <c r="L12">
+        <v>1.2</v>
+      </c>
+      <c r="M12">
+        <v>1.02</v>
+      </c>
+      <c r="N12">
+        <v>7.6</v>
+      </c>
+      <c r="O12">
+        <v>1.13</v>
+      </c>
+      <c r="P12">
+        <v>3.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.4</v>
+      </c>
+      <c r="R12">
+        <v>1.92</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
+        <v>1.58</v>
+      </c>
+      <c r="U12">
+        <v>2.5</v>
+      </c>
+      <c r="V12">
+        <v>1.15</v>
+      </c>
+      <c r="W12">
+        <v>3.1</v>
+      </c>
+      <c r="X12">
+        <v>110</v>
+      </c>
+      <c r="Y12">
+        <v>90</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>17.5</v>
+      </c>
+      <c r="AC12">
+        <v>14.5</v>
+      </c>
+      <c r="AD12">
+        <v>32</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>13</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>21</v>
+      </c>
+      <c r="AI12">
+        <v>80</v>
+      </c>
+      <c r="AJ12">
+        <v>15</v>
+      </c>
+      <c r="AK12">
+        <v>14</v>
+      </c>
+      <c r="AL12">
+        <v>27</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>4.3</v>
+      </c>
+      <c r="AO12">
+        <v>380</v>
+      </c>
+      <c r="AP12">
+        <v>25</v>
+      </c>
+      <c r="AQ12">
+        <v>27</v>
+      </c>
+      <c r="AR12">
+        <v>44</v>
+      </c>
+      <c r="AS12">
+        <v>90</v>
+      </c>
+      <c r="AT12">
+        <v>13</v>
+      </c>
+      <c r="AU12">
+        <v>12</v>
+      </c>
+      <c r="AV12">
+        <v>18.5</v>
+      </c>
+      <c r="AW12">
+        <v>48</v>
+      </c>
+      <c r="AX12">
+        <v>10.5</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>16</v>
+      </c>
+      <c r="BA12">
+        <v>38</v>
+      </c>
+      <c r="BB12">
+        <v>12</v>
+      </c>
+      <c r="BC12">
+        <v>11</v>
+      </c>
+      <c r="BD12">
+        <v>19.5</v>
+      </c>
+      <c r="BE12">
+        <v>42</v>
+      </c>
+      <c r="BF12">
+        <v>4</v>
+      </c>
+      <c r="BG12">
+        <v>34</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>6</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>6</v>
+      </c>
+      <c r="BO12">
+        <v>3.3</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>5.3</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>7.8</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>6.8</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13">
+        <v>1.35</v>
+      </c>
+      <c r="G13">
+        <v>1.38</v>
+      </c>
+      <c r="H13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>6.6</v>
+      </c>
+      <c r="L13">
+        <v>1.18</v>
+      </c>
+      <c r="M13">
+        <v>1.02</v>
+      </c>
+      <c r="N13">
+        <v>7.6</v>
+      </c>
+      <c r="O13">
+        <v>1.13</v>
+      </c>
+      <c r="P13">
+        <v>3.3</v>
+      </c>
+      <c r="Q13">
+        <v>1.4</v>
+      </c>
+      <c r="R13">
+        <v>1.94</v>
+      </c>
+      <c r="S13">
+        <v>1.98</v>
+      </c>
+      <c r="T13">
+        <v>1.7</v>
+      </c>
+      <c r="U13">
+        <v>2.34</v>
+      </c>
+      <c r="V13">
+        <v>1.11</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>110</v>
+      </c>
+      <c r="Y13">
+        <v>120</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>310</v>
+      </c>
+      <c r="AB13">
+        <v>14.5</v>
+      </c>
+      <c r="AC13">
+        <v>19</v>
+      </c>
+      <c r="AD13">
+        <v>38</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>11.5</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>32</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>13</v>
+      </c>
+      <c r="AK13">
+        <v>13.5</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>3.75</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>34</v>
+      </c>
+      <c r="AQ13">
+        <v>25</v>
+      </c>
+      <c r="AR13">
+        <v>36</v>
+      </c>
+      <c r="AS13">
+        <v>95</v>
+      </c>
+      <c r="AT13">
+        <v>13</v>
+      </c>
+      <c r="AU13">
+        <v>13</v>
+      </c>
+      <c r="AV13">
+        <v>30</v>
+      </c>
+      <c r="AW13">
+        <v>38</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>19.5</v>
+      </c>
+      <c r="BA13">
+        <v>34</v>
+      </c>
+      <c r="BB13">
+        <v>11.5</v>
+      </c>
+      <c r="BC13">
+        <v>12</v>
+      </c>
+      <c r="BD13">
+        <v>18</v>
+      </c>
+      <c r="BE13">
+        <v>36</v>
+      </c>
+      <c r="BF13">
+        <v>3.6</v>
+      </c>
+      <c r="BG13">
+        <v>36</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>4.2</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>7.2</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>3.55</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>5.6</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>8.6</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14">
+        <v>1.46</v>
+      </c>
+      <c r="G14">
+        <v>1.47</v>
+      </c>
+      <c r="H14">
+        <v>7.2</v>
+      </c>
+      <c r="I14">
+        <v>7.6</v>
+      </c>
+      <c r="J14">
+        <v>5.4</v>
+      </c>
+      <c r="K14">
+        <v>5.7</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>6.8</v>
+      </c>
+      <c r="O14">
+        <v>1.15</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>1.46</v>
+      </c>
+      <c r="R14">
+        <v>1.8</v>
+      </c>
+      <c r="S14">
+        <v>2.14</v>
+      </c>
+      <c r="T14">
+        <v>1.69</v>
+      </c>
+      <c r="U14">
+        <v>2.36</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>36</v>
+      </c>
+      <c r="Y14">
+        <v>36</v>
+      </c>
+      <c r="Z14">
+        <v>85</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>13.5</v>
+      </c>
+      <c r="AC14">
+        <v>13.5</v>
+      </c>
+      <c r="AD14">
+        <v>29</v>
+      </c>
+      <c r="AE14">
+        <v>100</v>
+      </c>
+      <c r="AF14">
+        <v>11.5</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>21</v>
+      </c>
+      <c r="AI14">
+        <v>70</v>
+      </c>
+      <c r="AJ14">
+        <v>13.5</v>
+      </c>
+      <c r="AK14">
+        <v>13.5</v>
+      </c>
+      <c r="AL14">
+        <v>26</v>
+      </c>
+      <c r="AM14">
+        <v>95</v>
+      </c>
+      <c r="AN14">
+        <v>4.6</v>
+      </c>
+      <c r="AO14">
+        <v>85</v>
+      </c>
+      <c r="AP14">
+        <v>22</v>
+      </c>
+      <c r="AQ14">
+        <v>22</v>
+      </c>
+      <c r="AR14">
+        <v>32</v>
+      </c>
+      <c r="AS14">
+        <v>46</v>
+      </c>
+      <c r="AT14">
+        <v>12</v>
+      </c>
+      <c r="AU14">
+        <v>12</v>
+      </c>
+      <c r="AV14">
+        <v>18</v>
+      </c>
+      <c r="AW14">
+        <v>34</v>
+      </c>
+      <c r="AX14">
+        <v>10.5</v>
+      </c>
+      <c r="AY14">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14">
+        <v>17.5</v>
+      </c>
+      <c r="BA14">
+        <v>32</v>
+      </c>
+      <c r="BB14">
+        <v>12</v>
+      </c>
+      <c r="BC14">
+        <v>12.5</v>
+      </c>
+      <c r="BD14">
+        <v>21</v>
+      </c>
+      <c r="BE14">
+        <v>34</v>
+      </c>
+      <c r="BF14">
+        <v>4.3</v>
+      </c>
+      <c r="BG14">
+        <v>32</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>3.9</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>7.6</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15">
+        <v>3.55</v>
+      </c>
+      <c r="G15">
+        <v>3.6</v>
+      </c>
+      <c r="H15">
+        <v>2.24</v>
+      </c>
+      <c r="I15">
+        <v>2.26</v>
+      </c>
+      <c r="J15">
+        <v>3.6</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>4.4</v>
+      </c>
+      <c r="O15">
+        <v>1.26</v>
+      </c>
+      <c r="P15">
+        <v>2.22</v>
+      </c>
+      <c r="Q15">
+        <v>1.79</v>
+      </c>
+      <c r="R15">
+        <v>1.47</v>
+      </c>
+      <c r="S15">
+        <v>2.96</v>
+      </c>
+      <c r="T15">
+        <v>1.66</v>
+      </c>
+      <c r="U15">
+        <v>2.38</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>17.5</v>
+      </c>
+      <c r="Y15">
+        <v>12</v>
+      </c>
+      <c r="Z15">
+        <v>16</v>
+      </c>
+      <c r="AA15">
+        <v>29</v>
+      </c>
+      <c r="AB15">
+        <v>16</v>
+      </c>
+      <c r="AC15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>23</v>
+      </c>
+      <c r="AF15">
+        <v>27</v>
+      </c>
+      <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>15.5</v>
+      </c>
+      <c r="AI15">
+        <v>34</v>
+      </c>
+      <c r="AJ15">
+        <v>65</v>
+      </c>
+      <c r="AK15">
+        <v>38</v>
+      </c>
+      <c r="AL15">
+        <v>44</v>
+      </c>
+      <c r="AM15">
+        <v>90</v>
+      </c>
+      <c r="AN15">
+        <v>32</v>
+      </c>
+      <c r="AO15">
+        <v>14</v>
+      </c>
+      <c r="AP15">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15">
+        <v>10.5</v>
+      </c>
+      <c r="AR15">
+        <v>14</v>
+      </c>
+      <c r="AS15">
+        <v>25</v>
+      </c>
+      <c r="AT15">
+        <v>14</v>
+      </c>
+      <c r="AU15">
+        <v>7.6</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>19.5</v>
+      </c>
+      <c r="AX15">
+        <v>18</v>
+      </c>
+      <c r="AY15">
+        <v>13</v>
+      </c>
+      <c r="AZ15">
+        <v>13.5</v>
+      </c>
+      <c r="BA15">
+        <v>27</v>
+      </c>
+      <c r="BB15">
+        <v>30</v>
+      </c>
+      <c r="BC15">
+        <v>30</v>
+      </c>
+      <c r="BD15">
+        <v>32</v>
+      </c>
+      <c r="BE15">
+        <v>32</v>
+      </c>
+      <c r="BF15">
+        <v>24</v>
+      </c>
+      <c r="BG15">
+        <v>13</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>2.96</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>6.4</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>5.2</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>4.2</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>10</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16">
+        <v>1.86</v>
+      </c>
+      <c r="G16">
+        <v>2.04</v>
+      </c>
+      <c r="H16">
+        <v>3.75</v>
+      </c>
+      <c r="I16">
+        <v>4.3</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>4.5</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>2.36</v>
+      </c>
+      <c r="Q16">
+        <v>1.56</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17">
+        <v>3.25</v>
+      </c>
+      <c r="G17">
+        <v>3.8</v>
+      </c>
+      <c r="H17">
+        <v>2.1</v>
+      </c>
+      <c r="I17">
+        <v>2.42</v>
+      </c>
+      <c r="J17">
+        <v>3.55</v>
+      </c>
+      <c r="K17">
+        <v>4.4</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.12</v>
+      </c>
+      <c r="Q17">
+        <v>1.7</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18">
+        <v>3.95</v>
+      </c>
+      <c r="G18">
+        <v>4.7</v>
+      </c>
+      <c r="H18">
+        <v>1.86</v>
+      </c>
+      <c r="I18">
+        <v>2.06</v>
+      </c>
+      <c r="J18">
+        <v>3.8</v>
+      </c>
+      <c r="K18">
+        <v>4.3</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18">
+        <v>1.68</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19">
+        <v>1.66</v>
+      </c>
+      <c r="G19">
+        <v>2.16</v>
+      </c>
+      <c r="H19">
+        <v>3.8</v>
+      </c>
+      <c r="I19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J19">
+        <v>3.65</v>
+      </c>
+      <c r="K19">
+        <v>7.6</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.83</v>
+      </c>
+      <c r="Q19">
+        <v>1.7</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20">
+        <v>1.9</v>
+      </c>
+      <c r="G20">
+        <v>1.91</v>
+      </c>
+      <c r="H20">
+        <v>4.2</v>
+      </c>
+      <c r="I20">
+        <v>4.4</v>
+      </c>
+      <c r="J20">
+        <v>4.1</v>
+      </c>
+      <c r="K20">
+        <v>4.2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>5.5</v>
+      </c>
+      <c r="O20">
+        <v>1.2</v>
+      </c>
+      <c r="P20">
+        <v>2.54</v>
+      </c>
+      <c r="Q20">
+        <v>1.62</v>
+      </c>
+      <c r="R20">
+        <v>1.62</v>
+      </c>
+      <c r="S20">
+        <v>2.5</v>
+      </c>
+      <c r="T20">
+        <v>1.59</v>
+      </c>
+      <c r="U20">
+        <v>2.6</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>25</v>
+      </c>
+      <c r="Y20">
+        <v>22</v>
+      </c>
+      <c r="Z20">
+        <v>36</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>13.5</v>
+      </c>
+      <c r="AC20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD20">
+        <v>17.5</v>
+      </c>
+      <c r="AE20">
+        <v>46</v>
+      </c>
+      <c r="AF20">
+        <v>14.5</v>
+      </c>
+      <c r="AG20">
+        <v>10.5</v>
+      </c>
+      <c r="AH20">
+        <v>16</v>
+      </c>
+      <c r="AI20">
+        <v>46</v>
+      </c>
+      <c r="AJ20">
+        <v>23</v>
+      </c>
+      <c r="AK20">
+        <v>18</v>
+      </c>
+      <c r="AL20">
+        <v>28</v>
+      </c>
+      <c r="AM20">
+        <v>65</v>
+      </c>
+      <c r="AN20">
+        <v>8.6</v>
+      </c>
+      <c r="AO20">
+        <v>34</v>
+      </c>
+      <c r="AP20">
+        <v>21</v>
+      </c>
+      <c r="AQ20">
+        <v>18.5</v>
+      </c>
+      <c r="AR20">
+        <v>28</v>
+      </c>
+      <c r="AS20">
+        <v>36</v>
+      </c>
+      <c r="AT20">
+        <v>11.5</v>
+      </c>
+      <c r="AU20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20">
+        <v>15</v>
+      </c>
+      <c r="AW20">
+        <v>34</v>
+      </c>
+      <c r="AX20">
+        <v>12.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>13.5</v>
+      </c>
+      <c r="BA20">
+        <v>34</v>
+      </c>
+      <c r="BB20">
+        <v>19</v>
+      </c>
+      <c r="BC20">
+        <v>15</v>
+      </c>
+      <c r="BD20">
+        <v>18</v>
+      </c>
+      <c r="BE20">
+        <v>30</v>
+      </c>
+      <c r="BF20">
+        <v>7.8</v>
+      </c>
+      <c r="BG20">
+        <v>24</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>3.35</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>6.4</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>4</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>8.4</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>5.7</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21">
+        <v>1.13</v>
+      </c>
+      <c r="G21">
+        <v>1.14</v>
+      </c>
+      <c r="H21">
+        <v>23</v>
+      </c>
+      <c r="I21">
+        <v>25</v>
+      </c>
+      <c r="J21">
+        <v>13</v>
+      </c>
+      <c r="K21">
+        <v>14</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>17.5</v>
+      </c>
+      <c r="O21">
+        <v>1.05</v>
+      </c>
+      <c r="P21">
+        <v>6.4</v>
+      </c>
+      <c r="Q21">
+        <v>1.16</v>
+      </c>
+      <c r="R21">
+        <v>3.1</v>
+      </c>
+      <c r="S21">
+        <v>1.42</v>
+      </c>
+      <c r="T21">
+        <v>1.73</v>
+      </c>
+      <c r="U21">
+        <v>2.28</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>340</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>34</v>
+      </c>
+      <c r="AC21">
+        <v>46</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>290</v>
+      </c>
+      <c r="AF21">
+        <v>18</v>
+      </c>
+      <c r="AG21">
+        <v>18</v>
+      </c>
+      <c r="AH21">
+        <v>50</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>11.5</v>
+      </c>
+      <c r="AK21">
+        <v>15</v>
+      </c>
+      <c r="AL21">
+        <v>38</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1.94</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>40</v>
+      </c>
+      <c r="AQ21">
+        <v>40</v>
+      </c>
+      <c r="AR21">
+        <v>18.5</v>
+      </c>
+      <c r="AS21">
+        <v>60</v>
+      </c>
+      <c r="AT21">
+        <v>20</v>
+      </c>
+      <c r="AU21">
+        <v>23</v>
+      </c>
+      <c r="AV21">
+        <v>36</v>
+      </c>
+      <c r="AW21">
+        <v>18.5</v>
+      </c>
+      <c r="AX21">
+        <v>15</v>
+      </c>
+      <c r="AY21">
+        <v>16</v>
+      </c>
+      <c r="AZ21">
+        <v>25</v>
+      </c>
+      <c r="BA21">
+        <v>44</v>
+      </c>
+      <c r="BB21">
+        <v>10</v>
+      </c>
+      <c r="BC21">
+        <v>13</v>
+      </c>
+      <c r="BD21">
+        <v>21</v>
+      </c>
+      <c r="BE21">
+        <v>40</v>
+      </c>
+      <c r="BF21">
+        <v>1.84</v>
+      </c>
+      <c r="BG21">
+        <v>85</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>6.6</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>4</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>4.5</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22">
+        <v>2.62</v>
+      </c>
+      <c r="G22">
+        <v>2.64</v>
+      </c>
+      <c r="H22">
+        <v>2.92</v>
+      </c>
+      <c r="I22">
+        <v>2.94</v>
+      </c>
+      <c r="J22">
+        <v>3.55</v>
+      </c>
+      <c r="K22">
+        <v>3.6</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1.06</v>
+      </c>
+      <c r="N22">
+        <v>4.3</v>
+      </c>
+      <c r="O22">
+        <v>1.28</v>
+      </c>
+      <c r="P22">
+        <v>2.12</v>
+      </c>
+      <c r="Q22">
+        <v>1.84</v>
+      </c>
+      <c r="R22">
+        <v>1.44</v>
+      </c>
+      <c r="S22">
+        <v>3.05</v>
+      </c>
+      <c r="T22">
+        <v>1.68</v>
+      </c>
+      <c r="U22">
+        <v>2.38</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>17</v>
+      </c>
+      <c r="Y22">
+        <v>13.5</v>
+      </c>
+      <c r="Z22">
+        <v>21</v>
+      </c>
+      <c r="AA22">
+        <v>120</v>
+      </c>
+      <c r="AB22">
+        <v>13</v>
+      </c>
+      <c r="AC22">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>13</v>
+      </c>
+      <c r="AE22">
+        <v>32</v>
+      </c>
+      <c r="AF22">
+        <v>18.5</v>
+      </c>
+      <c r="AG22">
+        <v>12.5</v>
+      </c>
+      <c r="AH22">
+        <v>15.5</v>
+      </c>
+      <c r="AI22">
+        <v>40</v>
+      </c>
+      <c r="AJ22">
+        <v>38</v>
+      </c>
+      <c r="AK22">
+        <v>27</v>
+      </c>
+      <c r="AL22">
+        <v>36</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>19.5</v>
+      </c>
+      <c r="AO22">
+        <v>23</v>
+      </c>
+      <c r="AP22">
+        <v>15</v>
+      </c>
+      <c r="AQ22">
+        <v>12</v>
+      </c>
+      <c r="AR22">
+        <v>18</v>
+      </c>
+      <c r="AS22">
+        <v>25</v>
+      </c>
+      <c r="AT22">
+        <v>11</v>
+      </c>
+      <c r="AU22">
+        <v>7.4</v>
+      </c>
+      <c r="AV22">
+        <v>11.5</v>
+      </c>
+      <c r="AW22">
+        <v>19</v>
+      </c>
+      <c r="AX22">
+        <v>16</v>
+      </c>
+      <c r="AY22">
+        <v>11</v>
+      </c>
+      <c r="AZ22">
+        <v>14</v>
+      </c>
+      <c r="BA22">
+        <v>24</v>
+      </c>
+      <c r="BB22">
+        <v>23</v>
+      </c>
+      <c r="BC22">
+        <v>17.5</v>
+      </c>
+      <c r="BD22">
+        <v>23</v>
+      </c>
+      <c r="BE22">
+        <v>34</v>
+      </c>
+      <c r="BF22">
+        <v>17.5</v>
+      </c>
+      <c r="BG22">
+        <v>20</v>
+      </c>
+      <c r="BH22">
+        <v>3.65</v>
+      </c>
+      <c r="BI22">
+        <v>3.35</v>
+      </c>
+      <c r="BJ22">
+        <v>9</v>
+      </c>
+      <c r="BK22">
+        <v>8</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>65</v>
+      </c>
+      <c r="BN22">
+        <v>5.6</v>
+      </c>
+      <c r="BO22">
+        <v>5.2</v>
+      </c>
+      <c r="BP22">
+        <v>18.5</v>
+      </c>
+      <c r="BQ22">
+        <v>13.5</v>
+      </c>
+      <c r="BR22">
+        <v>29</v>
+      </c>
+      <c r="BS22">
+        <v>20</v>
+      </c>
+      <c r="BT22">
+        <v>6.2</v>
+      </c>
+      <c r="BU22">
+        <v>5.5</v>
+      </c>
+      <c r="BV22">
+        <v>21</v>
+      </c>
+      <c r="BW22">
+        <v>15</v>
+      </c>
+      <c r="BX22">
+        <v>30</v>
+      </c>
+      <c r="BY22">
+        <v>22</v>
+      </c>
+      <c r="BZ22">
+        <v>22</v>
+      </c>
+      <c r="CA22">
+        <v>16</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23">
+        <v>1.14</v>
+      </c>
+      <c r="G23">
+        <v>1.15</v>
+      </c>
+      <c r="H23">
+        <v>28</v>
+      </c>
+      <c r="I23">
+        <v>32</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23">
+        <v>11</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>10.5</v>
+      </c>
+      <c r="O23">
+        <v>1.09</v>
+      </c>
+      <c r="P23">
+        <v>4.1</v>
+      </c>
+      <c r="Q23">
+        <v>1.28</v>
+      </c>
+      <c r="R23">
+        <v>2.3</v>
+      </c>
+      <c r="S23">
+        <v>1.7</v>
+      </c>
+      <c r="T23">
+        <v>2.1</v>
+      </c>
+      <c r="U23">
+        <v>1.85</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>60</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>380</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>18.5</v>
+      </c>
+      <c r="AC23">
+        <v>26</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>450</v>
+      </c>
+      <c r="AF23">
+        <v>11</v>
+      </c>
+      <c r="AG23">
+        <v>16.5</v>
+      </c>
+      <c r="AH23">
+        <v>120</v>
+      </c>
+      <c r="AI23">
+        <v>280</v>
+      </c>
+      <c r="AJ23">
+        <v>9.4</v>
+      </c>
+      <c r="AK23">
+        <v>14.5</v>
+      </c>
+      <c r="AL23">
+        <v>44</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>2.32</v>
+      </c>
+      <c r="AO23">
+        <v>450</v>
+      </c>
+      <c r="AP23">
+        <v>29</v>
+      </c>
+      <c r="AQ23">
+        <v>40</v>
+      </c>
+      <c r="AR23">
+        <v>65</v>
+      </c>
+      <c r="AS23">
+        <v>18</v>
+      </c>
+      <c r="AT23">
+        <v>15.5</v>
+      </c>
+      <c r="AU23">
+        <v>21</v>
+      </c>
+      <c r="AV23">
+        <v>38</v>
+      </c>
+      <c r="AW23">
+        <v>55</v>
+      </c>
+      <c r="AX23">
+        <v>10</v>
+      </c>
+      <c r="AY23">
+        <v>13.5</v>
+      </c>
+      <c r="AZ23">
+        <v>25</v>
+      </c>
+      <c r="BA23">
+        <v>50</v>
+      </c>
+      <c r="BB23">
+        <v>8.6</v>
+      </c>
+      <c r="BC23">
+        <v>12.5</v>
+      </c>
+      <c r="BD23">
+        <v>25</v>
+      </c>
+      <c r="BE23">
+        <v>46</v>
+      </c>
+      <c r="BF23">
+        <v>2.24</v>
+      </c>
+      <c r="BG23">
+        <v>65</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>5</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>3.45</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>4.2</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>5.7</v>
+      </c>
+      <c r="H24">
+        <v>1.76</v>
+      </c>
+      <c r="I24">
+        <v>1.83</v>
+      </c>
+      <c r="J24">
+        <v>3.8</v>
+      </c>
+      <c r="K24">
+        <v>4.1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.84</v>
+      </c>
+      <c r="Q24">
+        <v>1.99</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -442,7 +442,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 01:56:41</t>
+    <t>2026-09-08 04:08:25</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1045,7 @@
         <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
         <v>3.75</v>
@@ -1054,19 +1054,19 @@
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
         <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q2">
         <v>1.73</v>
@@ -1078,7 +1078,7 @@
         <v>2.86</v>
       </c>
       <c r="T2">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U2">
         <v>2.46</v>
@@ -1090,19 +1090,19 @@
         <v>1.73</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
@@ -1114,31 +1114,31 @@
         <v>36</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2">
         <v>44</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>24</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO2">
         <v>26</v>
@@ -1150,10 +1150,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
@@ -1162,13 +1162,13 @@
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1180,10 +1180,10 @@
         <v>23</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
         <v>20</v>
@@ -1192,70 +1192,70 @@
         <v>32</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG2">
+        <v>21</v>
+      </c>
+      <c r="BH2">
+        <v>3.95</v>
+      </c>
+      <c r="BI2">
+        <v>3.55</v>
+      </c>
+      <c r="BJ2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK2">
+        <v>7.8</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>21</v>
+      </c>
+      <c r="BN2">
+        <v>5.4</v>
+      </c>
+      <c r="BO2">
+        <v>4.8</v>
+      </c>
+      <c r="BP2">
         <v>16.5</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>3.3</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>6.4</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>6.6</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>23</v>
       </c>
       <c r="BQ2">
         <v>10</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BW2">
         <v>14</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BY2">
         <v>18.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>142</v>
@@ -1278,7 +1278,7 @@
         <v>120</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1287,7 +1287,7 @@
         <v>4.8</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
         <v>3.4</v>
@@ -1296,208 +1296,208 @@
         <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
+        <v>1.26</v>
+      </c>
+      <c r="S3">
+        <v>4.4</v>
+      </c>
+      <c r="T3">
+        <v>2.04</v>
+      </c>
+      <c r="U3">
+        <v>1.88</v>
+      </c>
+      <c r="V3">
         <v>1.23</v>
-      </c>
-      <c r="S3">
-        <v>4.3</v>
-      </c>
-      <c r="T3">
-        <v>1.95</v>
-      </c>
-      <c r="U3">
-        <v>1.86</v>
-      </c>
-      <c r="V3">
-        <v>1.21</v>
       </c>
       <c r="W3">
         <v>2</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
+        <v>14.5</v>
+      </c>
+      <c r="Z3">
+        <v>44</v>
+      </c>
+      <c r="AA3">
+        <v>160</v>
+      </c>
+      <c r="AB3">
+        <v>7.4</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>24</v>
+      </c>
+      <c r="AE3">
+        <v>95</v>
+      </c>
+      <c r="AF3">
+        <v>13.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>27</v>
+      </c>
+      <c r="AI3">
+        <v>110</v>
+      </c>
+      <c r="AJ3">
+        <v>28</v>
+      </c>
+      <c r="AK3">
+        <v>29</v>
+      </c>
+      <c r="AL3">
+        <v>48</v>
+      </c>
+      <c r="AM3">
+        <v>200</v>
+      </c>
+      <c r="AN3">
+        <v>24</v>
+      </c>
+      <c r="AO3">
+        <v>140</v>
+      </c>
+      <c r="AP3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ3">
+        <v>12.5</v>
+      </c>
+      <c r="AR3">
+        <v>5.5</v>
+      </c>
+      <c r="AS3">
+        <v>6</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>17</v>
+      </c>
+      <c r="AW3">
+        <v>5.9</v>
+      </c>
+      <c r="AX3">
+        <v>9.6</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>5.1</v>
+      </c>
+      <c r="BA3">
+        <v>5.9</v>
+      </c>
+      <c r="BB3">
+        <v>5.1</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
+        <v>38</v>
+      </c>
+      <c r="BE3">
+        <v>6</v>
+      </c>
+      <c r="BF3">
         <v>16.5</v>
       </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>970</v>
-      </c>
-      <c r="AC3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>970</v>
-      </c>
-      <c r="AG3">
-        <v>970</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>50</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.65</v>
-      </c>
-      <c r="AQ3">
-        <v>1.63</v>
-      </c>
-      <c r="AR3">
-        <v>1.81</v>
-      </c>
-      <c r="AS3">
-        <v>1.81</v>
-      </c>
-      <c r="AT3">
-        <v>6.4</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>1.81</v>
-      </c>
-      <c r="AW3">
-        <v>1.81</v>
-      </c>
-      <c r="AX3">
-        <v>1.65</v>
-      </c>
-      <c r="AY3">
-        <v>1.65</v>
-      </c>
-      <c r="AZ3">
-        <v>1.81</v>
-      </c>
-      <c r="BA3">
-        <v>1.81</v>
-      </c>
-      <c r="BB3">
-        <v>1.81</v>
-      </c>
-      <c r="BC3">
-        <v>1.81</v>
-      </c>
-      <c r="BD3">
-        <v>1.75</v>
-      </c>
-      <c r="BE3">
-        <v>1.81</v>
-      </c>
-      <c r="BF3">
-        <v>1.81</v>
-      </c>
       <c r="BG3">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="CB3" t="s">
         <v>142</v>
@@ -1520,7 +1520,7 @@
         <v>121</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
         <v>2.46</v>
@@ -1529,13 +1529,13 @@
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
         <v>2.9</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
         <v>1.62</v>
@@ -1544,10 +1544,10 @@
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P4">
         <v>1.43</v>
@@ -1562,52 +1562,52 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
         <v>1.68</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE4">
         <v>100</v>
       </c>
       <c r="AF4">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AG4">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
         <v>50</v>
@@ -1619,67 +1619,67 @@
         <v>100</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN4">
         <v>65</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS4">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="AT4">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>2.92</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="AX4">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>2.78</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>3.05</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>3.3</v>
+        <v>14.5</v>
       </c>
       <c r="BB4">
         <v>26</v>
       </c>
       <c r="BC4">
-        <v>3.1</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>3.2</v>
+        <v>13.5</v>
       </c>
       <c r="BE4">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="BF4">
-        <v>3.15</v>
+        <v>28</v>
       </c>
       <c r="BG4">
-        <v>3.3</v>
+        <v>14.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1765,7 +1765,7 @@
         <v>1.92</v>
       </c>
       <c r="G5">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H5">
         <v>3.85</v>
@@ -1774,7 +1774,7 @@
         <v>4.1</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.4</v>
@@ -1792,7 +1792,7 @@
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
@@ -1801,22 +1801,22 @@
         <v>1.65</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T5">
         <v>1.59</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V5">
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X5">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>22</v>
@@ -1831,10 +1831,10 @@
         <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE5">
         <v>46</v>
@@ -1849,19 +1849,19 @@
         <v>16.5</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ5">
         <v>25</v>
       </c>
       <c r="AK5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
         <v>28</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>790</v>
       </c>
       <c r="AN5">
         <v>8.6</v>
@@ -1870,10 +1870,10 @@
         <v>29</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR5">
         <v>21</v>
@@ -1921,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="BG5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1957,13 +1957,13 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2004,10 +2004,10 @@
         <v>123</v>
       </c>
       <c r="F6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H6">
         <v>2.8</v>
@@ -2019,25 +2019,25 @@
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
         <v>1.4</v>
@@ -2046,7 +2046,7 @@
         <v>3.35</v>
       </c>
       <c r="T6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
         <v>2.26</v>
@@ -2058,10 +2058,10 @@
         <v>1.58</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
         <v>19.5</v>
@@ -2070,37 +2070,37 @@
         <v>60</v>
       </c>
       <c r="AB6">
+        <v>12</v>
+      </c>
+      <c r="AC6">
+        <v>8</v>
+      </c>
+      <c r="AD6">
         <v>13</v>
       </c>
-      <c r="AC6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD6">
-        <v>13.5</v>
-      </c>
       <c r="AE6">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AF6">
         <v>18.5</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI6">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2109,34 +2109,34 @@
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
         <v>11</v>
       </c>
       <c r="AR6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS6">
         <v>25</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AX6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY6">
         <v>11</v>
@@ -2145,13 +2145,13 @@
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD6">
         <v>24</v>
@@ -2160,19 +2160,19 @@
         <v>36</v>
       </c>
       <c r="BF6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH6">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
         <v>6.2</v>
@@ -2181,49 +2181,49 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW6">
-        <v>2.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>142</v>
@@ -2261,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2273,13 +2273,13 @@
         <v>4.9</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
         <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
         <v>1.51</v>
@@ -2288,7 +2288,7 @@
         <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
         <v>2.34</v>
@@ -2300,7 +2300,7 @@
         <v>2.16</v>
       </c>
       <c r="X7">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Y7">
         <v>21</v>
@@ -2312,13 +2312,13 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC7">
         <v>9.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7">
         <v>220</v>
@@ -2330,19 +2330,19 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI7">
         <v>290</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2354,58 +2354,58 @@
         <v>160</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR7">
         <v>22</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT7">
         <v>9.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV7">
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BB7">
+        <v>16.5</v>
+      </c>
+      <c r="BC7">
         <v>15.5</v>
-      </c>
-      <c r="BC7">
-        <v>15</v>
       </c>
       <c r="BD7">
         <v>19.5</v>
       </c>
       <c r="BE7">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2491,7 +2491,7 @@
         <v>2.2</v>
       </c>
       <c r="G8">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H8">
         <v>2.96</v>
@@ -2524,7 +2524,7 @@
         <v>1.29</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.72</v>
@@ -2533,13 +2533,13 @@
         <v>1.32</v>
       </c>
       <c r="U8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="V8">
         <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X8">
         <v>320</v>
@@ -2569,7 +2569,7 @@
         <v>28</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
@@ -2590,7 +2590,7 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO8">
         <v>10.5</v>
@@ -2614,10 +2614,10 @@
         <v>12.5</v>
       </c>
       <c r="AV8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX8">
         <v>18</v>
@@ -2638,76 +2638,76 @@
         <v>17</v>
       </c>
       <c r="BD8">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BE8">
         <v>19.5</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG8">
         <v>9.199999999999999</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI8">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK8">
+        <v>6.8</v>
+      </c>
+      <c r="BL8">
+        <v>65</v>
+      </c>
+      <c r="BM8">
+        <v>21</v>
+      </c>
+      <c r="BN8">
+        <v>6.8</v>
+      </c>
+      <c r="BO8">
         <v>5.9</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>5.4</v>
-      </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>142</v>
@@ -2778,7 +2778,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -2975,64 +2975,64 @@
         <v>1.83</v>
       </c>
       <c r="G10">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M10">
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
         <v>1.45</v>
       </c>
       <c r="R10">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S10">
         <v>2.12</v>
       </c>
       <c r="T10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U10">
         <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X10">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Y10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3044,10 +3044,10 @@
         <v>11.5</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE10">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AF10">
         <v>16.5</v>
@@ -3059,31 +3059,31 @@
         <v>16</v>
       </c>
       <c r="AI10">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
+        <v>23</v>
+      </c>
+      <c r="AK10">
+        <v>16.5</v>
+      </c>
+      <c r="AL10">
         <v>25</v>
       </c>
-      <c r="AK10">
-        <v>17.5</v>
-      </c>
-      <c r="AL10">
-        <v>26</v>
-      </c>
       <c r="AM10">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AN10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AP10">
         <v>22</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR10">
         <v>23</v>
@@ -3092,58 +3092,58 @@
         <v>36</v>
       </c>
       <c r="AT10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW10">
         <v>23</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY10">
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA10">
         <v>22</v>
       </c>
       <c r="BB10">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD10">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE10">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BF10">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG10">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3155,19 +3155,19 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT10">
         <v>1000</v>
@@ -3214,13 +3214,13 @@
         <v>128</v>
       </c>
       <c r="F11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G11">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H11">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="I11">
         <v>3.05</v>
@@ -3229,43 +3229,43 @@
         <v>3.9</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R11">
         <v>1.67</v>
       </c>
       <c r="S11">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U11">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X11">
         <v>27</v>
@@ -3274,10 +3274,10 @@
         <v>18.5</v>
       </c>
       <c r="Z11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB11">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         <v>14</v>
       </c>
       <c r="AE11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF11">
         <v>19.5</v>
@@ -3304,7 +3304,7 @@
         <v>32</v>
       </c>
       <c r="AJ11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK11">
         <v>22</v>
@@ -3316,10 +3316,10 @@
         <v>55</v>
       </c>
       <c r="AN11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO11">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP11">
         <v>18.5</v>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT11">
         <v>14.5</v>
@@ -3343,7 +3343,7 @@
         <v>12</v>
       </c>
       <c r="AW11">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX11">
         <v>16.5</v>
@@ -3355,7 +3355,7 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB11">
         <v>21</v>
@@ -3364,7 +3364,7 @@
         <v>19</v>
       </c>
       <c r="BD11">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BE11">
         <v>26</v>
@@ -3373,16 +3373,16 @@
         <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK11">
         <v>6.2</v>
@@ -3391,49 +3391,49 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11">
         <v>10</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="s">
         <v>142</v>
@@ -3456,25 +3456,25 @@
         <v>129</v>
       </c>
       <c r="F12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I12">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>5.4</v>
       </c>
       <c r="K12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L12">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M12">
         <v>1.02</v>
@@ -3486,49 +3486,49 @@
         <v>1.13</v>
       </c>
       <c r="P12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S12">
         <v>2</v>
       </c>
       <c r="T12">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X12">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="Y12">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD12">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3537,145 +3537,145 @@
         <v>13</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI12">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK12">
         <v>14</v>
       </c>
       <c r="AL12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AO12">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AP12">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AQ12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR12">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AS12">
         <v>90</v>
       </c>
       <c r="AT12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU12">
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW12">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BB12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC12">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE12">
         <v>42</v>
       </c>
       <c r="BF12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG12">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN12">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO12">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ12">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS12">
         <v>7.8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU12">
         <v>6.8</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB12" t="s">
         <v>142</v>
@@ -3707,7 +3707,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -3716,28 +3716,28 @@
         <v>6.6</v>
       </c>
       <c r="L13">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
         <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T13">
         <v>1.7</v>
@@ -3746,16 +3746,16 @@
         <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Y13">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3767,7 +3767,7 @@
         <v>14.5</v>
       </c>
       <c r="AC13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AD13">
         <v>38</v>
@@ -3779,10 +3779,10 @@
         <v>11.5</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI13">
         <v>1000</v>
@@ -3800,7 +3800,7 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AO13">
         <v>1000</v>
@@ -3818,7 +3818,7 @@
         <v>95</v>
       </c>
       <c r="AT13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
         <v>13</v>
@@ -3854,70 +3854,70 @@
         <v>36</v>
       </c>
       <c r="BF13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG13">
         <v>36</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI13">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
+        <v>9</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>21</v>
+      </c>
+      <c r="BN13">
+        <v>4.5</v>
+      </c>
+      <c r="BO13">
+        <v>4</v>
+      </c>
+      <c r="BP13">
+        <v>7.6</v>
+      </c>
+      <c r="BQ13">
+        <v>6.6</v>
+      </c>
+      <c r="BR13">
+        <v>17.5</v>
+      </c>
+      <c r="BS13">
+        <v>15</v>
+      </c>
+      <c r="BT13">
+        <v>12.5</v>
+      </c>
+      <c r="BU13">
+        <v>11</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>50</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>40</v>
+      </c>
+      <c r="BZ13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CA13">
         <v>7.2</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>3.55</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>5.6</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.01</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>8.6</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.01</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.01</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
-      <c r="CA13">
-        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>142</v>
@@ -3961,31 +3961,31 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O14">
         <v>1.15</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R14">
         <v>1.8</v>
       </c>
       <c r="S14">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>36</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA14">
         <v>1000</v>
@@ -4015,7 +4015,7 @@
         <v>29</v>
       </c>
       <c r="AE14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF14">
         <v>11.5</v>
@@ -4030,13 +4030,13 @@
         <v>70</v>
       </c>
       <c r="AJ14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK14">
         <v>13.5</v>
       </c>
       <c r="AL14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM14">
         <v>95</v>
@@ -4048,10 +4048,10 @@
         <v>85</v>
       </c>
       <c r="AP14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AR14">
         <v>32</v>
@@ -4066,7 +4066,7 @@
         <v>12</v>
       </c>
       <c r="AV14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW14">
         <v>34</v>
@@ -4102,64 +4102,64 @@
         <v>32</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI14">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU14">
+        <v>9.4</v>
+      </c>
+      <c r="BV14">
+        <v>60</v>
+      </c>
+      <c r="BW14">
+        <v>34</v>
+      </c>
+      <c r="BX14">
+        <v>55</v>
+      </c>
+      <c r="BY14">
+        <v>32</v>
+      </c>
+      <c r="BZ14">
+        <v>12.5</v>
+      </c>
+      <c r="CA14">
         <v>7.6</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.01</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.01</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>142</v>
@@ -4215,7 +4215,7 @@
         <v>2.22</v>
       </c>
       <c r="Q15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
         <v>1.47</v>
@@ -4227,7 +4227,7 @@
         <v>1.66</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BB15">
         <v>30</v>
@@ -4427,10 +4427,10 @@
         <v>1.86</v>
       </c>
       <c r="G16">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H16">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I16">
         <v>4.3</v>
@@ -4439,7 +4439,7 @@
         <v>4</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4666,22 +4666,22 @@
         <v>134</v>
       </c>
       <c r="F17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G17">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="H17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I17">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4908,22 +4908,22 @@
         <v>135</v>
       </c>
       <c r="F18">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H18">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="I18">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q18">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5153,19 +5153,19 @@
         <v>1.66</v>
       </c>
       <c r="G19">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="H19">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I19">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="J19">
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5392,13 +5392,13 @@
         <v>137</v>
       </c>
       <c r="F20">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G20">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I20">
         <v>4.4</v>
@@ -5422,7 +5422,7 @@
         <v>1.2</v>
       </c>
       <c r="P20">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q20">
         <v>1.62</v>
@@ -5434,7 +5434,7 @@
         <v>2.5</v>
       </c>
       <c r="T20">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U20">
         <v>2.6</v>
@@ -5494,13 +5494,13 @@
         <v>65</v>
       </c>
       <c r="AN20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO20">
         <v>34</v>
       </c>
       <c r="AP20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ20">
         <v>18.5</v>
@@ -5548,7 +5548,7 @@
         <v>30</v>
       </c>
       <c r="BF20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG20">
         <v>24</v>
@@ -5640,10 +5640,10 @@
         <v>1.14</v>
       </c>
       <c r="H21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21">
         <v>13</v>
@@ -5673,10 +5673,10 @@
         <v>3.1</v>
       </c>
       <c r="S21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U21">
         <v>2.28</v>
@@ -5712,13 +5712,13 @@
         <v>290</v>
       </c>
       <c r="AF21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21">
         <v>18</v>
       </c>
       <c r="AH21">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AI21">
         <v>1000</v>
@@ -5727,7 +5727,7 @@
         <v>11.5</v>
       </c>
       <c r="AK21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL21">
         <v>38</v>
@@ -5748,13 +5748,13 @@
         <v>40</v>
       </c>
       <c r="AR21">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS21">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AT21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU21">
         <v>23</v>
@@ -5763,7 +5763,7 @@
         <v>36</v>
       </c>
       <c r="AW21">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX21">
         <v>15</v>
@@ -5790,7 +5790,7 @@
         <v>40</v>
       </c>
       <c r="BF21">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="BG21">
         <v>85</v>
@@ -5799,7 +5799,7 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -5912,7 +5912,7 @@
         <v>1.84</v>
       </c>
       <c r="R22">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S22">
         <v>3.05</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y22">
         <v>13.5</v>
@@ -5939,7 +5939,7 @@
         <v>21</v>
       </c>
       <c r="AA22">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AB22">
         <v>13</v>
@@ -5996,10 +5996,10 @@
         <v>25</v>
       </c>
       <c r="AT22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6038,7 +6038,7 @@
         <v>20</v>
       </c>
       <c r="BH22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI22">
         <v>3.35</v>
@@ -6148,19 +6148,19 @@
         <v>1.09</v>
       </c>
       <c r="P23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
         <v>1.28</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S23">
         <v>1.7</v>
       </c>
       <c r="T23">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U23">
         <v>1.85</v>
@@ -6232,13 +6232,13 @@
         <v>40</v>
       </c>
       <c r="AR23">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="AS23">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="AT23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU23">
         <v>21</v>
@@ -6253,13 +6253,13 @@
         <v>10</v>
       </c>
       <c r="AY23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ23">
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="BB23">
         <v>8.6</v>
@@ -6280,16 +6280,16 @@
         <v>65</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6298,28 +6298,28 @@
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO23">
         <v>3.45</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BQ23">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BV23">
         <v>1000</v>
@@ -6328,16 +6328,16 @@
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB23" t="s">
         <v>142</v>
@@ -6360,7 +6360,7 @@
         <v>141</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G24">
         <v>5.7</v>
@@ -6375,7 +6375,7 @@
         <v>3.8</v>
       </c>
       <c r="K24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q24">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -442,7 +442,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 04:08:25</t>
+    <t>2026-09-08 06:20:18</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1138,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>26</v>
@@ -1180,7 +1180,7 @@
         <v>23</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BC2">
         <v>18.5</v>
@@ -1204,7 +1204,7 @@
         <v>3.55</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
         <v>7.8</v>
@@ -1222,7 +1222,7 @@
         <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
         <v>10</v>
@@ -1240,13 +1240,13 @@
         <v>5.9</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW2">
         <v>14</v>
       </c>
       <c r="BX2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY2">
         <v>18.5</v>
@@ -1308,10 +1308,10 @@
         <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
         <v>1.26</v>
@@ -1371,7 +1371,7 @@
         <v>28</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL3">
         <v>48</v>
@@ -1392,10 +1392,10 @@
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1407,7 +1407,7 @@
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
         <v>9.6</v>
@@ -1416,13 +1416,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BC3">
         <v>20</v>
@@ -1431,13 +1431,13 @@
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1449,13 +1449,13 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>1000</v>
@@ -1467,37 +1467,37 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>142</v>
@@ -1520,7 +1520,7 @@
         <v>121</v>
       </c>
       <c r="F4">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
         <v>2.46</v>
@@ -1529,7 +1529,7 @@
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>2.9</v>
@@ -1568,13 +1568,13 @@
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y4">
         <v>9.6</v>
@@ -1634,10 +1634,10 @@
         <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AS4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT4">
         <v>5.9</v>
@@ -1661,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="BA4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB4">
         <v>26</v>
@@ -1673,13 +1673,13 @@
         <v>13.5</v>
       </c>
       <c r="BE4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF4">
         <v>28</v>
       </c>
       <c r="BG4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1762,22 +1762,22 @@
         <v>122</v>
       </c>
       <c r="F5">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G5">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.29</v>
@@ -1786,34 +1786,34 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W5">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="X5">
         <v>26</v>
@@ -1822,7 +1822,7 @@
         <v>22</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1831,10 +1831,10 @@
         <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE5">
         <v>46</v>
@@ -1846,7 +1846,7 @@
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5">
         <v>48</v>
@@ -1858,34 +1858,34 @@
         <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM5">
-        <v>790</v>
+        <v>440</v>
       </c>
       <c r="AN5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5">
         <v>29</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR5">
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT5">
         <v>12</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
         <v>15</v>
@@ -1894,13 +1894,13 @@
         <v>23</v>
       </c>
       <c r="AX5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
         <v>24</v>
@@ -1912,16 +1912,16 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF5">
         <v>8</v>
       </c>
       <c r="BG5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1951,13 +1951,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT5">
         <v>1000</v>
@@ -2013,7 +2013,7 @@
         <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -2109,7 +2109,7 @@
         <v>23</v>
       </c>
       <c r="AO6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
@@ -2249,13 +2249,13 @@
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H7">
         <v>4.5</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2291,7 +2291,7 @@
         <v>1.71</v>
       </c>
       <c r="U7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V7">
         <v>1.26</v>
@@ -2306,7 +2306,7 @@
         <v>21</v>
       </c>
       <c r="Z7">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2333,7 +2333,7 @@
         <v>18</v>
       </c>
       <c r="AI7">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2354,10 +2354,10 @@
         <v>160</v>
       </c>
       <c r="AP7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR7">
         <v>22</v>
@@ -2366,7 +2366,7 @@
         <v>38</v>
       </c>
       <c r="AT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7">
         <v>8.6</v>
@@ -2390,7 +2390,7 @@
         <v>28</v>
       </c>
       <c r="BB7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC7">
         <v>15.5</v>
@@ -2435,7 +2435,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2494,10 +2494,10 @@
         <v>2.28</v>
       </c>
       <c r="H8">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8">
         <v>4.4</v>
@@ -2605,7 +2605,7 @@
         <v>22</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AT8">
         <v>19</v>
@@ -2614,7 +2614,7 @@
         <v>12.5</v>
       </c>
       <c r="AV8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW8">
         <v>18</v>
@@ -2656,7 +2656,7 @@
         <v>5.8</v>
       </c>
       <c r="BJ8">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
         <v>6.8</v>
@@ -2668,7 +2668,7 @@
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BO8">
         <v>5.9</v>
@@ -2686,7 +2686,7 @@
         <v>12</v>
       </c>
       <c r="BT8">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8">
         <v>6.6</v>
@@ -2972,16 +2972,16 @@
         <v>127</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
         <v>4.4</v>
@@ -2990,40 +2990,40 @@
         <v>4.8</v>
       </c>
       <c r="L10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M10">
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="S10">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T10">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U10">
         <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X10">
         <v>40</v>
@@ -3032,7 +3032,7 @@
         <v>28</v>
       </c>
       <c r="Z10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3050,49 +3050,49 @@
         <v>44</v>
       </c>
       <c r="AF10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG10">
         <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK10">
         <v>16.5</v>
       </c>
       <c r="AL10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM10">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
         <v>24</v>
       </c>
       <c r="AP10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU10">
         <v>10.5</v>
@@ -3128,10 +3128,10 @@
         <v>27</v>
       </c>
       <c r="BF10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3155,13 +3155,13 @@
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3226,40 +3226,40 @@
         <v>3.05</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
         <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S11">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U11">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V11">
         <v>1.49</v>
@@ -3274,16 +3274,16 @@
         <v>18.5</v>
       </c>
       <c r="Z11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA11">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AB11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD11">
         <v>14</v>
@@ -3313,10 +3313,10 @@
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO11">
         <v>16.5</v>
@@ -3325,7 +3325,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR11">
         <v>21</v>
@@ -3355,7 +3355,7 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB11">
         <v>21</v>
@@ -3367,7 +3367,7 @@
         <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BF11">
         <v>10.5</v>
@@ -3397,10 +3397,10 @@
         <v>7</v>
       </c>
       <c r="BO11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
         <v>10</v>
@@ -3412,7 +3412,7 @@
         <v>14</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU11">
         <v>4.9</v>
@@ -3609,7 +3609,7 @@
         <v>20</v>
       </c>
       <c r="BE12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF12">
         <v>4.1</v>
@@ -3698,22 +3698,22 @@
         <v>130</v>
       </c>
       <c r="F13">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="G13">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="H13">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I13">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
         <v>6</v>
       </c>
       <c r="K13">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L13">
         <v>1.22</v>
@@ -3722,52 +3722,52 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
+        <v>3.3</v>
+      </c>
+      <c r="Q13">
+        <v>1.41</v>
+      </c>
+      <c r="R13">
+        <v>1.94</v>
+      </c>
+      <c r="S13">
+        <v>2.02</v>
+      </c>
+      <c r="T13">
+        <v>1.67</v>
+      </c>
+      <c r="U13">
+        <v>2.42</v>
+      </c>
+      <c r="V13">
+        <v>1.13</v>
+      </c>
+      <c r="W13">
         <v>3.35</v>
       </c>
-      <c r="Q13">
-        <v>1.4</v>
-      </c>
-      <c r="R13">
-        <v>1.95</v>
-      </c>
-      <c r="S13">
-        <v>1.99</v>
-      </c>
-      <c r="T13">
-        <v>1.7</v>
-      </c>
-      <c r="U13">
-        <v>2.34</v>
-      </c>
-      <c r="V13">
-        <v>1.12</v>
-      </c>
-      <c r="W13">
-        <v>3.65</v>
-      </c>
       <c r="X13">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="Y13">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="Z13">
         <v>1000</v>
       </c>
       <c r="AA13">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD13">
         <v>38</v>
@@ -3776,100 +3776,100 @@
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI13">
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13">
         <v>13.5</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM13">
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
+        <v>24</v>
+      </c>
+      <c r="AQ13">
+        <v>24</v>
+      </c>
+      <c r="AR13">
         <v>34</v>
       </c>
-      <c r="AQ13">
-        <v>25</v>
-      </c>
-      <c r="AR13">
+      <c r="AS13">
+        <v>48</v>
+      </c>
+      <c r="AT13">
+        <v>13</v>
+      </c>
+      <c r="AU13">
+        <v>13.5</v>
+      </c>
+      <c r="AV13">
+        <v>20</v>
+      </c>
+      <c r="AW13">
         <v>36</v>
       </c>
-      <c r="AS13">
-        <v>95</v>
-      </c>
-      <c r="AT13">
-        <v>13.5</v>
-      </c>
-      <c r="AU13">
-        <v>13</v>
-      </c>
-      <c r="AV13">
-        <v>30</v>
-      </c>
-      <c r="AW13">
-        <v>38</v>
-      </c>
       <c r="AX13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY13">
         <v>10</v>
       </c>
       <c r="AZ13">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BA13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB13">
         <v>11.5</v>
       </c>
       <c r="BC13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF13">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BG13">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI13">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3884,37 +3884,37 @@
         <v>4</v>
       </c>
       <c r="BP13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BQ13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS13">
         <v>15</v>
       </c>
       <c r="BT13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BZ13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CA13">
         <v>7.2</v>
@@ -3967,7 +3967,7 @@
         <v>6.6</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P14">
         <v>2.96</v>
@@ -3979,7 +3979,7 @@
         <v>1.8</v>
       </c>
       <c r="S14">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T14">
         <v>1.7</v>
@@ -4033,7 +4033,7 @@
         <v>14</v>
       </c>
       <c r="AK14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL14">
         <v>27</v>
@@ -4051,7 +4051,7 @@
         <v>21</v>
       </c>
       <c r="AQ14">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AR14">
         <v>32</v>
@@ -4141,7 +4141,7 @@
         <v>13.5</v>
       </c>
       <c r="BU14">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV14">
         <v>60</v>
@@ -4206,19 +4206,19 @@
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O15">
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
         <v>2.96</v>
@@ -4227,7 +4227,7 @@
         <v>1.66</v>
       </c>
       <c r="U15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4287,13 +4287,13 @@
         <v>32</v>
       </c>
       <c r="AO15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP15">
         <v>15.5</v>
       </c>
       <c r="AQ15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR15">
         <v>14</v>
@@ -4323,7 +4323,7 @@
         <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BB15">
         <v>30</v>
@@ -4454,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q16">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         <v>134</v>
       </c>
       <c r="F17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G17">
         <v>3.65</v>
@@ -4678,7 +4678,7 @@
         <v>2.3</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K17">
         <v>4.1</v>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q17">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q19">
         <v>1.7</v>
@@ -5392,13 +5392,13 @@
         <v>137</v>
       </c>
       <c r="F20">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I20">
         <v>4.4</v>
@@ -5506,7 +5506,7 @@
         <v>18.5</v>
       </c>
       <c r="AR20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS20">
         <v>36</v>
@@ -5542,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE20">
         <v>30</v>
@@ -5551,7 +5551,7 @@
         <v>8</v>
       </c>
       <c r="BG20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5634,16 +5634,16 @@
         <v>138</v>
       </c>
       <c r="F21">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G21">
         <v>1.14</v>
       </c>
       <c r="H21">
+        <v>22</v>
+      </c>
+      <c r="I21">
         <v>24</v>
-      </c>
-      <c r="I21">
-        <v>26</v>
       </c>
       <c r="J21">
         <v>13</v>
@@ -5694,7 +5694,7 @@
         <v>1000</v>
       </c>
       <c r="Z21">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -5709,16 +5709,16 @@
         <v>1000</v>
       </c>
       <c r="AE21">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AF21">
         <v>17</v>
       </c>
       <c r="AG21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH21">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AI21">
         <v>1000</v>
@@ -5727,7 +5727,7 @@
         <v>11.5</v>
       </c>
       <c r="AK21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL21">
         <v>38</v>
@@ -5748,22 +5748,22 @@
         <v>40</v>
       </c>
       <c r="AR21">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS21">
+        <v>18.5</v>
+      </c>
+      <c r="AT21">
         <v>20</v>
       </c>
-      <c r="AT21">
-        <v>19.5</v>
-      </c>
       <c r="AU21">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AV21">
         <v>36</v>
       </c>
       <c r="AW21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX21">
         <v>15</v>
@@ -5939,7 +5939,7 @@
         <v>21</v>
       </c>
       <c r="AA22">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB22">
         <v>13</v>
@@ -5999,7 +5999,7 @@
         <v>11.5</v>
       </c>
       <c r="AU22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6017,7 +6017,7 @@
         <v>14</v>
       </c>
       <c r="BA22">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB22">
         <v>23</v>
@@ -6026,7 +6026,7 @@
         <v>17.5</v>
       </c>
       <c r="BD22">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE22">
         <v>34</v>
@@ -6118,13 +6118,13 @@
         <v>140</v>
       </c>
       <c r="F23">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23">
         <v>32</v>
@@ -6154,7 +6154,7 @@
         <v>1.28</v>
       </c>
       <c r="R23">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S23">
         <v>1.7</v>
@@ -6163,7 +6163,7 @@
         <v>2.12</v>
       </c>
       <c r="U23">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6202,10 +6202,10 @@
         <v>16.5</v>
       </c>
       <c r="AH23">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AI23">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
         <v>9.4</v>
@@ -6223,16 +6223,16 @@
         <v>2.32</v>
       </c>
       <c r="AO23">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="AP23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AR23">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AS23">
         <v>60</v>
@@ -6259,7 +6259,7 @@
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="BB23">
         <v>8.6</v>
@@ -6271,13 +6271,13 @@
         <v>25</v>
       </c>
       <c r="BE23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF23">
         <v>2.24</v>
       </c>
       <c r="BG23">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH23">
         <v>8</v>
@@ -6369,10 +6369,10 @@
         <v>1.76</v>
       </c>
       <c r="I24">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J24">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K24">
         <v>4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -442,7 +442,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 06:20:18</t>
+    <t>2026-09-08 08:32:26</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1039,7 @@
         <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>3.15</v>
@@ -1063,22 +1063,22 @@
         <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2">
         <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U2">
         <v>2.46</v>
@@ -1087,7 +1087,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
         <v>21</v>
@@ -1099,19 +1099,19 @@
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AB2">
         <v>13</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF2">
         <v>17</v>
@@ -1138,10 +1138,10 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP2">
         <v>17</v>
@@ -1153,7 +1153,7 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
@@ -1162,10 +1162,10 @@
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1177,7 +1177,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1186,10 +1186,10 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BF2">
         <v>12</v>
@@ -1225,13 +1225,13 @@
         <v>19</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BT2">
         <v>7</v>
@@ -1243,19 +1243,19 @@
         <v>29</v>
       </c>
       <c r="BW2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BZ2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>142</v>
@@ -1281,10 +1281,10 @@
         <v>1.91</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
         <v>5.3</v>
@@ -1296,7 +1296,7 @@
         <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1305,25 +1305,25 @@
         <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
         <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
         <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
         <v>1.23</v>
@@ -1335,7 +1335,7 @@
         <v>13.5</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>44</v>
@@ -1347,13 +1347,13 @@
         <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
         <v>24</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF3">
         <v>13.5</v>
@@ -1371,16 +1371,16 @@
         <v>28</v>
       </c>
       <c r="AK3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM3">
         <v>200</v>
       </c>
       <c r="AN3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3">
         <v>140</v>
@@ -1392,10 +1392,10 @@
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1407,7 +1407,7 @@
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AX3">
         <v>9.6</v>
@@ -1416,88 +1416,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA3">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BB3">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF3">
         <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI3">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>1.45</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB3" t="s">
         <v>142</v>
@@ -1520,25 +1520,25 @@
         <v>121</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="M4">
         <v>1.16</v>
@@ -1565,34 +1565,34 @@
         <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V4">
         <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>7.2</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1601,7 +1601,7 @@
         <v>13</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH4">
         <v>29</v>
@@ -1613,19 +1613,19 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AL4">
         <v>100</v>
       </c>
       <c r="AM4">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP4">
         <v>6.4</v>
@@ -1634,112 +1634,112 @@
         <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY4">
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA4">
+        <v>11.5</v>
+      </c>
+      <c r="BB4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC4">
+        <v>27</v>
+      </c>
+      <c r="BD4">
+        <v>10.5</v>
+      </c>
+      <c r="BE4">
+        <v>12</v>
+      </c>
+      <c r="BF4">
+        <v>27</v>
+      </c>
+      <c r="BG4">
+        <v>11.5</v>
+      </c>
+      <c r="BH4">
+        <v>2.44</v>
+      </c>
+      <c r="BI4">
+        <v>2.3</v>
+      </c>
+      <c r="BJ4">
+        <v>12.5</v>
+      </c>
+      <c r="BK4">
+        <v>7.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>2.14</v>
+      </c>
+      <c r="BN4">
+        <v>4.9</v>
+      </c>
+      <c r="BO4">
+        <v>4.4</v>
+      </c>
+      <c r="BP4">
+        <v>23</v>
+      </c>
+      <c r="BQ4">
+        <v>10.5</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>14</v>
+      </c>
+      <c r="BT4">
+        <v>7.2</v>
+      </c>
+      <c r="BU4">
+        <v>5.2</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>13.5</v>
       </c>
-      <c r="BB4">
-        <v>26</v>
-      </c>
-      <c r="BC4">
-        <v>28</v>
-      </c>
-      <c r="BD4">
-        <v>13.5</v>
-      </c>
-      <c r="BE4">
-        <v>14.5</v>
-      </c>
-      <c r="BF4">
-        <v>28</v>
-      </c>
-      <c r="BG4">
-        <v>14</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>2.12</v>
-      </c>
-      <c r="BJ4">
-        <v>1000</v>
-      </c>
-      <c r="BK4">
-        <v>1.64</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>1.64</v>
-      </c>
-      <c r="BN4">
-        <v>1000</v>
-      </c>
-      <c r="BO4">
-        <v>1.64</v>
-      </c>
-      <c r="BP4">
-        <v>1000</v>
-      </c>
-      <c r="BQ4">
-        <v>1.64</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>1.64</v>
-      </c>
-      <c r="BT4">
-        <v>1000</v>
-      </c>
-      <c r="BU4">
-        <v>1.64</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>1.64</v>
-      </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="CB4" t="s">
         <v>142</v>
@@ -1762,25 +1762,25 @@
         <v>122</v>
       </c>
       <c r="F5">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I5">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1792,196 +1792,196 @@
         <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X5">
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
+        <v>16</v>
+      </c>
+      <c r="AE5">
+        <v>40</v>
+      </c>
+      <c r="AF5">
         <v>17</v>
       </c>
-      <c r="AE5">
-        <v>46</v>
-      </c>
-      <c r="AF5">
-        <v>15</v>
-      </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ5">
+        <v>32</v>
+      </c>
+      <c r="AK5">
+        <v>20</v>
+      </c>
+      <c r="AL5">
+        <v>30</v>
+      </c>
+      <c r="AM5">
+        <v>340</v>
+      </c>
+      <c r="AN5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO5">
         <v>25</v>
       </c>
-      <c r="AK5">
-        <v>18.5</v>
-      </c>
-      <c r="AL5">
-        <v>29</v>
-      </c>
-      <c r="AM5">
-        <v>440</v>
-      </c>
-      <c r="AN5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO5">
-        <v>29</v>
-      </c>
       <c r="AP5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS5">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
+        <v>22</v>
+      </c>
+      <c r="AX5">
+        <v>13.5</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
+        <v>13</v>
+      </c>
+      <c r="BA5">
+        <v>22</v>
+      </c>
+      <c r="BB5">
+        <v>18</v>
+      </c>
+      <c r="BC5">
+        <v>16.5</v>
+      </c>
+      <c r="BD5">
         <v>23</v>
       </c>
-      <c r="AX5">
-        <v>12.5</v>
-      </c>
-      <c r="AY5">
-        <v>10</v>
-      </c>
-      <c r="AZ5">
-        <v>13.5</v>
-      </c>
-      <c r="BA5">
-        <v>24</v>
-      </c>
-      <c r="BB5">
+      <c r="BE5">
+        <v>34</v>
+      </c>
+      <c r="BF5">
+        <v>9</v>
+      </c>
+      <c r="BG5">
         <v>20</v>
       </c>
-      <c r="BC5">
-        <v>15</v>
-      </c>
-      <c r="BD5">
-        <v>18.5</v>
-      </c>
-      <c r="BE5">
-        <v>29</v>
-      </c>
-      <c r="BF5">
+      <c r="BH5">
+        <v>4.4</v>
+      </c>
+      <c r="BI5">
+        <v>4</v>
+      </c>
+      <c r="BJ5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5">
+        <v>7.4</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>21</v>
+      </c>
+      <c r="BN5">
+        <v>5.4</v>
+      </c>
+      <c r="BO5">
+        <v>4.9</v>
+      </c>
+      <c r="BP5">
+        <v>16</v>
+      </c>
+      <c r="BQ5">
+        <v>11.5</v>
+      </c>
+      <c r="BR5">
+        <v>25</v>
+      </c>
+      <c r="BS5">
+        <v>16.5</v>
+      </c>
+      <c r="BT5">
         <v>8</v>
       </c>
-      <c r="BG5">
+      <c r="BU5">
+        <v>6.4</v>
+      </c>
+      <c r="BV5">
+        <v>27</v>
+      </c>
+      <c r="BW5">
+        <v>17.5</v>
+      </c>
+      <c r="BX5">
+        <v>34</v>
+      </c>
+      <c r="BY5">
         <v>21</v>
       </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>3.65</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>5.6</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>4.1</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>12</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>5.8</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.01</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.01</v>
-      </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>142</v>
@@ -2037,28 +2037,28 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
         <v>1.74</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
         <v>12.5</v>
@@ -2079,10 +2079,10 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2091,13 +2091,13 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL6">
         <v>100</v>
@@ -2106,7 +2106,7 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO6">
         <v>28</v>
@@ -2121,7 +2121,7 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2166,64 +2166,64 @@
         <v>17</v>
       </c>
       <c r="BH6">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>1.39</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>1.36</v>
       </c>
       <c r="BN6">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>1.36</v>
       </c>
       <c r="BT6">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>1.69</v>
       </c>
       <c r="BV6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>1.36</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="CB6" t="s">
         <v>142</v>
@@ -2249,7 +2249,7 @@
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H7">
         <v>4.5</v>
@@ -2258,13 +2258,13 @@
         <v>4.8</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.05</v>
@@ -2291,7 +2291,7 @@
         <v>1.71</v>
       </c>
       <c r="U7">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
         <v>1.26</v>
@@ -2306,7 +2306,7 @@
         <v>21</v>
       </c>
       <c r="Z7">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2330,7 +2330,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
         <v>300</v>
@@ -2339,7 +2339,7 @@
         <v>21</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>32</v>
@@ -2357,7 +2357,7 @@
         <v>18</v>
       </c>
       <c r="AQ7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR7">
         <v>22</v>
@@ -2372,13 +2372,13 @@
         <v>8.6</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2387,13 +2387,13 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BB7">
         <v>17</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD7">
         <v>19.5</v>
@@ -2402,22 +2402,22 @@
         <v>34</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2429,13 +2429,13 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2497,16 +2497,16 @@
         <v>2.94</v>
       </c>
       <c r="I8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M8">
         <v>1.02</v>
@@ -2524,7 +2524,7 @@
         <v>1.29</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S8">
         <v>1.72</v>
@@ -2533,7 +2533,7 @@
         <v>1.32</v>
       </c>
       <c r="U8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V8">
         <v>1.48</v>
@@ -2542,31 +2542,31 @@
         <v>1.78</v>
       </c>
       <c r="X8">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="Y8">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="Z8">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AA8">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB8">
         <v>32</v>
       </c>
       <c r="AC8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8">
         <v>17</v>
       </c>
       <c r="AE8">
+        <v>27</v>
+      </c>
+      <c r="AF8">
         <v>29</v>
-      </c>
-      <c r="AF8">
-        <v>28</v>
       </c>
       <c r="AG8">
         <v>15</v>
@@ -2575,13 +2575,13 @@
         <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL8">
         <v>21</v>
@@ -2590,10 +2590,10 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP8">
         <v>28</v>
@@ -2608,19 +2608,19 @@
         <v>28</v>
       </c>
       <c r="AT8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV8">
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AX8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2644,10 +2644,10 @@
         <v>19.5</v>
       </c>
       <c r="BF8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8">
         <v>7.8</v>
@@ -2662,10 +2662,10 @@
         <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BN8">
         <v>7.8</v>
@@ -2674,40 +2674,40 @@
         <v>5.9</v>
       </c>
       <c r="BP8">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BT8">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU8">
         <v>6.6</v>
       </c>
       <c r="BV8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BW8">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BY8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="s">
         <v>142</v>
@@ -2778,7 +2778,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -2972,16 +2972,16 @@
         <v>127</v>
       </c>
       <c r="F10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
         <v>4.4</v>
@@ -2993,46 +2993,46 @@
         <v>1.24</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R10">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="S10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U10">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z10">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3047,64 +3047,64 @@
         <v>18</v>
       </c>
       <c r="AE10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI10">
         <v>40</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL10">
         <v>24</v>
       </c>
       <c r="AM10">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP10">
+        <v>22</v>
+      </c>
+      <c r="AQ10">
+        <v>18</v>
+      </c>
+      <c r="AR10">
         <v>23</v>
-      </c>
-      <c r="AQ10">
-        <v>18.5</v>
-      </c>
-      <c r="AR10">
-        <v>24</v>
       </c>
       <c r="AS10">
         <v>34</v>
       </c>
       <c r="AT10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV10">
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
         <v>10</v>
@@ -3119,79 +3119,79 @@
         <v>18.5</v>
       </c>
       <c r="BC10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE10">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BF10">
         <v>6</v>
       </c>
       <c r="BG10">
+        <v>19.5</v>
+      </c>
+      <c r="BH10">
+        <v>5.2</v>
+      </c>
+      <c r="BI10">
+        <v>4.6</v>
+      </c>
+      <c r="BJ10">
+        <v>8.6</v>
+      </c>
+      <c r="BK10">
+        <v>7.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>42</v>
+      </c>
+      <c r="BN10">
+        <v>5.4</v>
+      </c>
+      <c r="BO10">
+        <v>4.7</v>
+      </c>
+      <c r="BP10">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10">
+        <v>10</v>
+      </c>
+      <c r="BR10">
+        <v>19</v>
+      </c>
+      <c r="BS10">
+        <v>15.5</v>
+      </c>
+      <c r="BT10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU10">
+        <v>7.2</v>
+      </c>
+      <c r="BV10">
+        <v>28</v>
+      </c>
+      <c r="BW10">
+        <v>19</v>
+      </c>
+      <c r="BX10">
+        <v>29</v>
+      </c>
+      <c r="BY10">
         <v>20</v>
       </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>4.1</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>6</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>4.2</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>7.6</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>11</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>6</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>1.01</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>1.01</v>
-      </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="s">
         <v>142</v>
@@ -3214,16 +3214,16 @@
         <v>128</v>
       </c>
       <c r="F11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G11">
         <v>2.46</v>
       </c>
       <c r="H11">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>3.95</v>
@@ -3244,25 +3244,25 @@
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q11">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R11">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U11">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.68</v>
@@ -3271,28 +3271,28 @@
         <v>27</v>
       </c>
       <c r="Y11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z11">
         <v>25</v>
       </c>
       <c r="AA11">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AB11">
         <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>14</v>
       </c>
       <c r="AE11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG11">
         <v>12.5</v>
@@ -3313,7 +3313,7 @@
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN11">
         <v>11.5</v>
@@ -3322,7 +3322,7 @@
         <v>16.5</v>
       </c>
       <c r="AP11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
         <v>16.5</v>
@@ -3346,46 +3346,46 @@
         <v>18</v>
       </c>
       <c r="AX11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY11">
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC11">
         <v>19</v>
       </c>
       <c r="BD11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI11">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3394,46 +3394,46 @@
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BR11">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BS11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BT11">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU11">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BV11">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="BW11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BZ11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CA11">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>142</v>
@@ -3456,7 +3456,7 @@
         <v>129</v>
       </c>
       <c r="F12">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G12">
         <v>1.5</v>
@@ -3465,7 +3465,7 @@
         <v>6.6</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
         <v>5.4</v>
@@ -3492,10 +3492,10 @@
         <v>1.41</v>
       </c>
       <c r="R12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T12">
         <v>1.59</v>
@@ -3516,7 +3516,7 @@
         <v>40</v>
       </c>
       <c r="Z12">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
         <v>1000</v>
@@ -3543,7 +3543,7 @@
         <v>19</v>
       </c>
       <c r="AI12">
-        <v>65</v>
+        <v>360</v>
       </c>
       <c r="AJ12">
         <v>16</v>
@@ -3555,25 +3555,25 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
         <v>4.4</v>
       </c>
       <c r="AO12">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="AP12">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AQ12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR12">
         <v>32</v>
       </c>
       <c r="AS12">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AT12">
         <v>13.5</v>
@@ -3582,10 +3582,10 @@
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -3597,19 +3597,19 @@
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB12">
         <v>14</v>
       </c>
       <c r="BC12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD12">
         <v>20</v>
       </c>
       <c r="BE12">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BF12">
         <v>4.1</v>
@@ -3621,7 +3621,7 @@
         <v>5.4</v>
       </c>
       <c r="BI12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BJ12">
         <v>9.4</v>
@@ -3651,13 +3651,13 @@
         <v>17.5</v>
       </c>
       <c r="BS12">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BT12">
         <v>11</v>
       </c>
       <c r="BU12">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BV12">
         <v>44</v>
@@ -3698,22 +3698,22 @@
         <v>130</v>
       </c>
       <c r="F13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="G13">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="K13">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L13">
         <v>1.22</v>
@@ -3722,145 +3722,145 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>1.13</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="U13">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
         <v>1.13</v>
       </c>
       <c r="W13">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="X13">
+        <v>40</v>
+      </c>
+      <c r="Y13">
         <v>48</v>
       </c>
-      <c r="Y13">
-        <v>50</v>
-      </c>
       <c r="Z13">
         <v>1000</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB13">
         <v>15.5</v>
       </c>
       <c r="AC13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD13">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AJ13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK13">
         <v>13.5</v>
       </c>
       <c r="AL13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN13">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AQ13">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AR13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT13">
+        <v>13.5</v>
+      </c>
+      <c r="AU13">
         <v>13</v>
       </c>
-      <c r="AU13">
-        <v>13.5</v>
-      </c>
       <c r="AV13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AW13">
         <v>36</v>
       </c>
       <c r="AX13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC13">
         <v>11.5</v>
       </c>
       <c r="BD13">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BG13">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH13">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
         <v>4.3</v>
@@ -3869,55 +3869,55 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>5.8</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
         <v>8</v>
       </c>
-      <c r="BQ13">
-        <v>6.8</v>
-      </c>
-      <c r="BR13">
-        <v>17</v>
-      </c>
-      <c r="BS13">
-        <v>15</v>
-      </c>
-      <c r="BT13">
-        <v>12</v>
-      </c>
-      <c r="BU13">
-        <v>10.5</v>
-      </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>142</v>
@@ -3943,16 +3943,16 @@
         <v>1.46</v>
       </c>
       <c r="G14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K14">
         <v>5.7</v>
@@ -3961,13 +3961,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
         <v>2.96</v>
@@ -3979,10 +3979,10 @@
         <v>1.8</v>
       </c>
       <c r="S14">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T14">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U14">
         <v>2.34</v>
@@ -3997,28 +3997,28 @@
         <v>36</v>
       </c>
       <c r="Y14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z14">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
@@ -4027,70 +4027,70 @@
         <v>21</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM14">
         <v>95</v>
       </c>
       <c r="AN14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AR14">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AS14">
         <v>46</v>
       </c>
       <c r="AT14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU14">
         <v>12</v>
       </c>
       <c r="AV14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW14">
         <v>34</v>
       </c>
       <c r="AX14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY14">
         <v>9.6</v>
       </c>
       <c r="AZ14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA14">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BB14">
         <v>12</v>
       </c>
       <c r="BC14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD14">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BE14">
         <v>34</v>
@@ -4111,13 +4111,13 @@
         <v>12</v>
       </c>
       <c r="BK14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL14">
         <v>110</v>
       </c>
       <c r="BM14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN14">
         <v>5.2</v>
@@ -4132,10 +4132,10 @@
         <v>7.6</v>
       </c>
       <c r="BR14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT14">
         <v>13.5</v>
@@ -4159,7 +4159,7 @@
         <v>12.5</v>
       </c>
       <c r="CA14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB14" t="s">
         <v>142</v>
@@ -4206,7 +4206,7 @@
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O15">
         <v>1.26</v>
@@ -4221,13 +4221,13 @@
         <v>1.46</v>
       </c>
       <c r="S15">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T15">
         <v>1.66</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4245,7 +4245,7 @@
         <v>16</v>
       </c>
       <c r="AA15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB15">
         <v>16</v>
@@ -4272,16 +4272,16 @@
         <v>34</v>
       </c>
       <c r="AJ15">
-        <v>65</v>
+        <v>640</v>
       </c>
       <c r="AK15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL15">
         <v>44</v>
       </c>
       <c r="AM15">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN15">
         <v>32</v>
@@ -4299,19 +4299,19 @@
         <v>14</v>
       </c>
       <c r="AS15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT15">
         <v>14</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX15">
         <v>18</v>
@@ -4323,7 +4323,7 @@
         <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BB15">
         <v>30</v>
@@ -4332,76 +4332,76 @@
         <v>30</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE15">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BF15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BG15">
         <v>13</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI15">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK15">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO15">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB15" t="s">
         <v>142</v>
@@ -4427,19 +4427,19 @@
         <v>1.86</v>
       </c>
       <c r="G16">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="H16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I16">
         <v>4.3</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4454,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         <v>134</v>
       </c>
       <c r="F17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G17">
         <v>3.65</v>
@@ -4699,7 +4699,7 @@
         <v>2.28</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4908,7 +4908,7 @@
         <v>135</v>
       </c>
       <c r="F18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G18">
         <v>4.8</v>
@@ -4917,7 +4917,7 @@
         <v>1.93</v>
       </c>
       <c r="I18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J18">
         <v>3.7</v>
@@ -4938,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q18">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5150,22 +5150,22 @@
         <v>136</v>
       </c>
       <c r="F19">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G19">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H19">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J19">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5395,13 +5395,13 @@
         <v>1.89</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H20">
         <v>4.2</v>
       </c>
       <c r="I20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J20">
         <v>4.1</v>
@@ -5419,16 +5419,16 @@
         <v>5.5</v>
       </c>
       <c r="O20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P20">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R20">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S20">
         <v>2.5</v>
@@ -5449,7 +5449,7 @@
         <v>25</v>
       </c>
       <c r="Y20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z20">
         <v>36</v>
@@ -5458,7 +5458,7 @@
         <v>1000</v>
       </c>
       <c r="AB20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC20">
         <v>9.800000000000001</v>
@@ -5476,7 +5476,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI20">
         <v>46</v>
@@ -5503,10 +5503,10 @@
         <v>20</v>
       </c>
       <c r="AQ20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR20">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AS20">
         <v>36</v>
@@ -5524,7 +5524,7 @@
         <v>34</v>
       </c>
       <c r="AX20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
@@ -5533,7 +5533,7 @@
         <v>13.5</v>
       </c>
       <c r="BA20">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BB20">
         <v>19</v>
@@ -5542,76 +5542,76 @@
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BE20">
         <v>30</v>
       </c>
       <c r="BF20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG20">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI20">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK20">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ20">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU20">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="CB20" t="s">
         <v>142</v>
@@ -5640,10 +5640,10 @@
         <v>1.14</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J21">
         <v>13</v>
@@ -5664,19 +5664,19 @@
         <v>1.05</v>
       </c>
       <c r="P21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Q21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
         <v>2.28</v>
@@ -5700,10 +5700,10 @@
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AD21">
         <v>1000</v>
@@ -5712,13 +5712,13 @@
         <v>310</v>
       </c>
       <c r="AF21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG21">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH21">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AI21">
         <v>1000</v>
@@ -5736,7 +5736,7 @@
         <v>1000</v>
       </c>
       <c r="AN21">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AO21">
         <v>1000</v>
@@ -5748,37 +5748,37 @@
         <v>40</v>
       </c>
       <c r="AR21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS21">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="AT21">
         <v>20</v>
       </c>
       <c r="AU21">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AV21">
         <v>36</v>
       </c>
       <c r="AW21">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AX21">
         <v>15</v>
       </c>
       <c r="AY21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA21">
         <v>44</v>
       </c>
       <c r="BB21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC21">
         <v>13</v>
@@ -5790,52 +5790,52 @@
         <v>40</v>
       </c>
       <c r="BF21">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="BG21">
         <v>85</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BI21">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO21">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BQ21">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5847,13 +5847,13 @@
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="CB21" t="s">
         <v>142</v>
@@ -5888,10 +5888,10 @@
         <v>2.94</v>
       </c>
       <c r="J22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -5912,10 +5912,10 @@
         <v>1.84</v>
       </c>
       <c r="R22">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T22">
         <v>1.68</v>
@@ -5933,25 +5933,25 @@
         <v>16.5</v>
       </c>
       <c r="Y22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z22">
         <v>21</v>
       </c>
       <c r="AA22">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22">
         <v>13</v>
       </c>
       <c r="AE22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF22">
         <v>18.5</v>
@@ -5963,22 +5963,22 @@
         <v>15.5</v>
       </c>
       <c r="AI22">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ22">
         <v>38</v>
       </c>
       <c r="AK22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM22">
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO22">
         <v>23</v>
@@ -6017,16 +6017,16 @@
         <v>14</v>
       </c>
       <c r="BA22">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BB22">
         <v>23</v>
       </c>
       <c r="BC22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD22">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE22">
         <v>34</v>
@@ -6041,7 +6041,7 @@
         <v>3.7</v>
       </c>
       <c r="BI22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ22">
         <v>9</v>
@@ -6056,13 +6056,13 @@
         <v>65</v>
       </c>
       <c r="BN22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO22">
         <v>5.2</v>
       </c>
       <c r="BP22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ22">
         <v>13.5</v>
@@ -6089,13 +6089,13 @@
         <v>30</v>
       </c>
       <c r="BY22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ22">
         <v>22</v>
       </c>
       <c r="CA22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CB22" t="s">
         <v>142</v>
@@ -6118,19 +6118,19 @@
         <v>140</v>
       </c>
       <c r="F23">
+        <v>1.14</v>
+      </c>
+      <c r="G23">
         <v>1.15</v>
       </c>
-      <c r="G23">
-        <v>1.16</v>
-      </c>
       <c r="H23">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I23">
         <v>32</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="K23">
         <v>11</v>
@@ -6157,13 +6157,13 @@
         <v>2.32</v>
       </c>
       <c r="S23">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="T23">
         <v>2.12</v>
       </c>
       <c r="U23">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6178,7 +6178,7 @@
         <v>1000</v>
       </c>
       <c r="Z23">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AA23">
         <v>1000</v>
@@ -6190,19 +6190,19 @@
         <v>26</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AE23">
         <v>450</v>
       </c>
       <c r="AF23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG23">
         <v>16.5</v>
       </c>
       <c r="AH23">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6211,7 +6211,7 @@
         <v>9.4</v>
       </c>
       <c r="AK23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL23">
         <v>44</v>
@@ -6220,19 +6220,19 @@
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AO23">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AP23">
         <v>28</v>
       </c>
       <c r="AQ23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AR23">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AS23">
         <v>60</v>
@@ -6241,25 +6241,25 @@
         <v>16</v>
       </c>
       <c r="AU23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AW23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX23">
         <v>10</v>
       </c>
       <c r="AY23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ23">
         <v>25</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="BB23">
         <v>8.6</v>
@@ -6274,10 +6274,10 @@
         <v>44</v>
       </c>
       <c r="BF23">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BG23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH23">
         <v>8</v>
@@ -6360,22 +6360,22 @@
         <v>141</v>
       </c>
       <c r="F24">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G24">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I24">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J24">
         <v>3.85</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>1.83</v>
       </c>
       <c r="Q24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="146">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>UEFA Champions League</t>
   </si>
   <si>
+    <t>Georgian Umaglesi Liga</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -346,6 +349,9 @@
     <t>Fenerbahce</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Falkenbergs</t>
   </si>
   <si>
@@ -415,6 +421,9 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
     <t>Osters</t>
   </si>
   <si>
@@ -442,7 +451,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 08:32:26</t>
+    <t>2026-09-08 10:44:44</t>
   </si>
 </sst>
 </file>
@@ -774,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,22 +1033,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2">
         <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
         <v>3.15</v>
@@ -1069,7 +1078,7 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
         <v>1.51</v>
@@ -1078,7 +1087,7 @@
         <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U2">
         <v>2.46</v>
@@ -1087,7 +1096,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>21</v>
@@ -1111,7 +1120,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF2">
         <v>17</v>
@@ -1138,7 +1147,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>27</v>
@@ -1165,10 +1174,10 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1177,7 +1186,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1186,13 +1195,13 @@
         <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
         <v>21</v>
@@ -1204,7 +1213,7 @@
         <v>3.55</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
         <v>7.8</v>
@@ -1216,10 +1225,10 @@
         <v>21</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP2">
         <v>19</v>
@@ -1231,16 +1240,16 @@
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW2">
         <v>17</v>
@@ -1249,16 +1258,16 @@
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BZ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,40 +1275,40 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
         <v>3.1</v>
@@ -1308,16 +1317,16 @@
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
         <v>2.04</v>
@@ -1326,16 +1335,16 @@
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
         <v>44</v>
@@ -1344,10 +1353,10 @@
         <v>160</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
         <v>24</v>
@@ -1356,7 +1365,7 @@
         <v>100</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
@@ -1368,19 +1377,19 @@
         <v>110</v>
       </c>
       <c r="AJ3">
+        <v>26</v>
+      </c>
+      <c r="AK3">
         <v>28</v>
       </c>
-      <c r="AK3">
-        <v>29</v>
-      </c>
       <c r="AL3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO3">
         <v>140</v>
@@ -1392,10 +1401,10 @@
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1407,40 +1416,40 @@
         <v>17</v>
       </c>
       <c r="AW3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI3">
         <v>2.42</v>
@@ -1449,58 +1458,58 @@
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
+        <v>4.9</v>
+      </c>
+      <c r="BN3">
         <v>5.1</v>
       </c>
-      <c r="BN3">
-        <v>5.2</v>
-      </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
         <v>18</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="BV3">
         <v>60</v>
       </c>
       <c r="BW3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,37 +1517,37 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
         <v>4</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>2.94</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
         <v>1.16</v>
@@ -1565,13 +1574,13 @@
         <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>7.2</v>
@@ -1634,10 +1643,10 @@
         <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
         <v>5.8</v>
@@ -1649,7 +1658,7 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>11</v>
@@ -1658,19 +1667,19 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4">
         <v>11.5</v>
       </c>
       <c r="BB4">
+        <v>9.4</v>
+      </c>
+      <c r="BC4">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
       <c r="BD4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE4">
         <v>12</v>
@@ -1697,7 +1706,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BN4">
         <v>4.9</v>
@@ -1706,7 +1715,7 @@
         <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
         <v>10.5</v>
@@ -1715,25 +1724,25 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
@@ -1742,7 +1751,7 @@
         <v>2.1</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,70 +1759,70 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F5">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
         <v>1.6</v>
       </c>
       <c r="R5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U5">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X5">
         <v>26</v>
@@ -1822,7 +1831,7 @@
         <v>20</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1831,13 +1840,13 @@
         <v>15</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF5">
         <v>17</v>
@@ -1849,10 +1858,10 @@
         <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK5">
         <v>20</v>
@@ -1861,13 +1870,13 @@
         <v>30</v>
       </c>
       <c r="AM5">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AN5">
         <v>9.800000000000001</v>
       </c>
       <c r="AO5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP5">
         <v>20</v>
@@ -1876,7 +1885,7 @@
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
         <v>42</v>
@@ -1891,10 +1900,10 @@
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
@@ -1903,34 +1912,34 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BE5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
         <v>4</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
         <v>7.4</v>
@@ -1939,10 +1948,10 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BN5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO5">
         <v>4.9</v>
@@ -1960,31 +1969,31 @@
         <v>16.5</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5">
         <v>6.4</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BX5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY5">
         <v>21</v>
       </c>
       <c r="BZ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,16 +2001,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F6">
         <v>2.62</v>
@@ -2037,19 +2046,19 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
         <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2067,7 +2076,7 @@
         <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AB6">
         <v>12</v>
@@ -2079,10 +2088,10 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2094,22 +2103,22 @@
         <v>120</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN6">
         <v>24</v>
       </c>
       <c r="AO6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
@@ -2121,7 +2130,7 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2145,19 +2154,19 @@
         <v>14.5</v>
       </c>
       <c r="BA6">
+        <v>26</v>
+      </c>
+      <c r="BB6">
+        <v>28</v>
+      </c>
+      <c r="BC6">
+        <v>19</v>
+      </c>
+      <c r="BD6">
         <v>25</v>
       </c>
-      <c r="BB6">
-        <v>23</v>
-      </c>
-      <c r="BC6">
-        <v>18.5</v>
-      </c>
-      <c r="BD6">
-        <v>24</v>
-      </c>
       <c r="BE6">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF6">
         <v>20</v>
@@ -2169,64 +2178,64 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>2.18</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.67</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,16 +2243,16 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F7">
         <v>1.8</v>
@@ -2258,7 +2267,7 @@
         <v>4.8</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.3</v>
@@ -2315,7 +2324,7 @@
         <v>11</v>
       </c>
       <c r="AC7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
         <v>19</v>
@@ -2339,7 +2348,7 @@
         <v>21</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
         <v>32</v>
@@ -2360,7 +2369,7 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS7">
         <v>38</v>
@@ -2372,10 +2381,10 @@
         <v>8.6</v>
       </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2387,7 +2396,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2396,16 +2405,16 @@
         <v>15</v>
       </c>
       <c r="BD7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE7">
         <v>34</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2417,7 +2426,7 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2429,13 +2438,13 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2468,7 +2477,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,88 +2485,88 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F8">
         <v>2.2</v>
       </c>
       <c r="G8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
         <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>1.29</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T8">
         <v>1.32</v>
       </c>
       <c r="U8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X8">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z8">
         <v>40</v>
       </c>
       <c r="AA8">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AB8">
         <v>32</v>
       </c>
       <c r="AC8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD8">
         <v>17</v>
@@ -2566,7 +2575,7 @@
         <v>27</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>15</v>
@@ -2581,7 +2590,7 @@
         <v>40</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL8">
         <v>21</v>
@@ -2599,16 +2608,16 @@
         <v>28</v>
       </c>
       <c r="AQ8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR8">
+        <v>25</v>
+      </c>
+      <c r="AS8">
+        <v>34</v>
+      </c>
+      <c r="AT8">
         <v>22</v>
-      </c>
-      <c r="AS8">
-        <v>28</v>
-      </c>
-      <c r="AT8">
-        <v>21</v>
       </c>
       <c r="AU8">
         <v>12</v>
@@ -2617,22 +2626,22 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2641,7 +2650,7 @@
         <v>17.5</v>
       </c>
       <c r="BE8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BF8">
         <v>6</v>
@@ -2668,7 +2677,7 @@
         <v>30</v>
       </c>
       <c r="BN8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO8">
         <v>5.9</v>
@@ -2680,22 +2689,22 @@
         <v>10.5</v>
       </c>
       <c r="BR8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BW8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>24</v>
@@ -2710,7 +2719,7 @@
         <v>6.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2718,16 +2727,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2952,7 +2961,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2960,16 +2969,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F10">
         <v>1.83</v>
@@ -2978,16 +2987,16 @@
         <v>1.87</v>
       </c>
       <c r="H10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
         <v>4.4</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
         <v>1.24</v>
@@ -2999,7 +3008,7 @@
         <v>7.2</v>
       </c>
       <c r="O10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P10">
         <v>3.1</v>
@@ -3011,16 +3020,16 @@
         <v>1.85</v>
       </c>
       <c r="S10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T10">
         <v>1.48</v>
       </c>
       <c r="U10">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
         <v>2.12</v>
@@ -3059,7 +3068,7 @@
         <v>16</v>
       </c>
       <c r="AI10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
         <v>23</v>
@@ -3101,7 +3110,7 @@
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX10">
         <v>14.5</v>
@@ -3116,7 +3125,7 @@
         <v>22</v>
       </c>
       <c r="BB10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC10">
         <v>14.5</v>
@@ -3125,13 +3134,13 @@
         <v>19</v>
       </c>
       <c r="BE10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BF10">
         <v>6</v>
       </c>
       <c r="BG10">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH10">
         <v>5.2</v>
@@ -3194,7 +3203,7 @@
         <v>8.4</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3202,16 +3211,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F11">
         <v>2.38</v>
@@ -3226,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4.2</v>
@@ -3244,22 +3253,22 @@
         <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S11">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U11">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
         <v>1.5</v>
@@ -3298,7 +3307,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI11">
         <v>32</v>
@@ -3313,7 +3322,7 @@
         <v>28</v>
       </c>
       <c r="AM11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN11">
         <v>11.5</v>
@@ -3334,7 +3343,7 @@
         <v>26</v>
       </c>
       <c r="AT11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU11">
         <v>9</v>
@@ -3343,31 +3352,31 @@
         <v>12</v>
       </c>
       <c r="AW11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX11">
         <v>17</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
         <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BB11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC11">
         <v>19</v>
       </c>
       <c r="BD11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF11">
         <v>10</v>
@@ -3427,7 +3436,7 @@
         <v>25</v>
       </c>
       <c r="BY11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BZ11">
         <v>15</v>
@@ -3436,7 +3445,7 @@
         <v>11</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3444,28 +3453,28 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G12">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
         <v>5.4</v>
@@ -3498,16 +3507,16 @@
         <v>2.02</v>
       </c>
       <c r="T12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X12">
         <v>40</v>
@@ -3525,10 +3534,10 @@
         <v>15.5</v>
       </c>
       <c r="AC12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE12">
         <v>1000</v>
@@ -3543,10 +3552,10 @@
         <v>19</v>
       </c>
       <c r="AI12">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AJ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12">
         <v>14</v>
@@ -3558,16 +3567,16 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO12">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="AP12">
         <v>24</v>
       </c>
       <c r="AQ12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR12">
         <v>32</v>
@@ -3585,7 +3594,7 @@
         <v>18</v>
       </c>
       <c r="AW12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -3597,10 +3606,10 @@
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC12">
         <v>12</v>
@@ -3609,7 +3618,7 @@
         <v>20</v>
       </c>
       <c r="BE12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF12">
         <v>4.1</v>
@@ -3624,10 +3633,10 @@
         <v>4.8</v>
       </c>
       <c r="BJ12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3636,7 +3645,7 @@
         <v>50</v>
       </c>
       <c r="BN12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO12">
         <v>4.2</v>
@@ -3660,16 +3669,16 @@
         <v>9.4</v>
       </c>
       <c r="BV12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BZ12">
         <v>9.199999999999999</v>
@@ -3678,7 +3687,7 @@
         <v>6.8</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3686,31 +3695,31 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G13">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H13">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K13">
         <v>5.8</v>
@@ -3722,7 +3731,7 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O13">
         <v>1.13</v>
@@ -3734,100 +3743,100 @@
         <v>1.4</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="T13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="X13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z13">
         <v>1000</v>
       </c>
       <c r="AA13">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
         <v>15.5</v>
       </c>
       <c r="AC13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD13">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE13">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI13">
-        <v>690</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
         <v>15</v>
       </c>
       <c r="AK13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL13">
+        <v>23</v>
+      </c>
+      <c r="AM13">
+        <v>65</v>
+      </c>
+      <c r="AN13">
+        <v>4.3</v>
+      </c>
+      <c r="AO13">
+        <v>55</v>
+      </c>
+      <c r="AP13">
+        <v>34</v>
+      </c>
+      <c r="AQ13">
+        <v>32</v>
+      </c>
+      <c r="AR13">
+        <v>60</v>
+      </c>
+      <c r="AS13">
+        <v>48</v>
+      </c>
+      <c r="AT13">
+        <v>14</v>
+      </c>
+      <c r="AU13">
+        <v>12.5</v>
+      </c>
+      <c r="AV13">
         <v>25</v>
       </c>
-      <c r="AM13">
-        <v>75</v>
-      </c>
-      <c r="AN13">
-        <v>4.1</v>
-      </c>
-      <c r="AO13">
-        <v>1000</v>
-      </c>
-      <c r="AP13">
-        <v>32</v>
-      </c>
-      <c r="AQ13">
-        <v>40</v>
-      </c>
-      <c r="AR13">
-        <v>36</v>
-      </c>
-      <c r="AS13">
-        <v>50</v>
-      </c>
-      <c r="AT13">
-        <v>13.5</v>
-      </c>
-      <c r="AU13">
-        <v>13</v>
-      </c>
-      <c r="AV13">
-        <v>26</v>
-      </c>
       <c r="AW13">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AX13">
         <v>11.5</v>
@@ -3836,91 +3845,91 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BF13">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG13">
         <v>42</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI13">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO13">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ13">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS13">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3928,16 +3937,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14">
         <v>1.46</v>
@@ -3946,13 +3955,13 @@
         <v>1.48</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I14">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K14">
         <v>5.7</v>
@@ -3970,22 +3979,22 @@
         <v>1.15</v>
       </c>
       <c r="P14">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S14">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T14">
         <v>1.69</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3997,7 +4006,7 @@
         <v>36</v>
       </c>
       <c r="Y14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z14">
         <v>85</v>
@@ -4006,16 +4015,16 @@
         <v>220</v>
       </c>
       <c r="AB14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD14">
         <v>30</v>
       </c>
       <c r="AE14">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF14">
         <v>12</v>
@@ -4033,10 +4042,10 @@
         <v>14.5</v>
       </c>
       <c r="AK14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM14">
         <v>95</v>
@@ -4045,22 +4054,22 @@
         <v>4.7</v>
       </c>
       <c r="AO14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AR14">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AS14">
         <v>46</v>
       </c>
       <c r="AT14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU14">
         <v>12</v>
@@ -4072,19 +4081,19 @@
         <v>34</v>
       </c>
       <c r="AX14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>18</v>
       </c>
       <c r="BA14">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BB14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC14">
         <v>12</v>
@@ -4120,7 +4129,7 @@
         <v>55</v>
       </c>
       <c r="BN14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO14">
         <v>4</v>
@@ -4141,7 +4150,7 @@
         <v>13.5</v>
       </c>
       <c r="BU14">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BV14">
         <v>60</v>
@@ -4162,7 +4171,7 @@
         <v>7.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4170,28 +4179,28 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F15">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H15">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I15">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J15">
         <v>3.6</v>
@@ -4206,7 +4215,7 @@
         <v>1.06</v>
       </c>
       <c r="N15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
         <v>1.26</v>
@@ -4218,16 +4227,16 @@
         <v>1.79</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T15">
         <v>1.66</v>
       </c>
       <c r="U15">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -4245,13 +4254,13 @@
         <v>16</v>
       </c>
       <c r="AA15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB15">
         <v>16</v>
       </c>
       <c r="AC15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD15">
         <v>11</v>
@@ -4269,13 +4278,13 @@
         <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ15">
-        <v>640</v>
+        <v>85</v>
       </c>
       <c r="AK15">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL15">
         <v>44</v>
@@ -4287,7 +4296,7 @@
         <v>32</v>
       </c>
       <c r="AO15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP15">
         <v>15.5</v>
@@ -4323,25 +4332,25 @@
         <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB15">
         <v>30</v>
       </c>
       <c r="BC15">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BD15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE15">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF15">
         <v>21</v>
       </c>
       <c r="BG15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH15">
         <v>3.65</v>
@@ -4404,7 +4413,7 @@
         <v>15.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4412,40 +4421,40 @@
         <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16">
+        <v>2.2</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
+      </c>
+      <c r="H16">
+        <v>1.4</v>
+      </c>
+      <c r="I16">
         <v>110</v>
       </c>
-      <c r="E16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F16">
-        <v>1.86</v>
-      </c>
-      <c r="G16">
-        <v>2.06</v>
-      </c>
-      <c r="H16">
-        <v>3.8</v>
-      </c>
-      <c r="I16">
-        <v>4.3</v>
-      </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4454,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4466,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4478,112 +4487,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4646,42 +4655,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="G17">
-        <v>3.65</v>
+        <v>2.06</v>
       </c>
       <c r="H17">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="I17">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4696,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q17">
         <v>1.58</v>
@@ -4888,42 +4897,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G18">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="H18">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="I18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4938,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5130,42 +5139,42 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F19">
-        <v>1.71</v>
+        <v>3.8</v>
       </c>
       <c r="G19">
-        <v>1.83</v>
+        <v>4.8</v>
       </c>
       <c r="H19">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="I19">
-        <v>5.6</v>
+        <v>2.14</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5180,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5372,72 +5381,72 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
         <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F20">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="G20">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I20">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5446,175 +5455,175 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL20">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BB20">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD20">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BE20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BF20">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH20">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI20">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BJ20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK20">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP20">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR20">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BS20">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BT20">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU20">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV20">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BX20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY20">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BZ20">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA20">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5622,190 +5631,190 @@
         <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="G21">
-        <v>1.14</v>
+        <v>1.91</v>
       </c>
       <c r="H21">
+        <v>4.2</v>
+      </c>
+      <c r="I21">
+        <v>4.3</v>
+      </c>
+      <c r="J21">
+        <v>4.1</v>
+      </c>
+      <c r="K21">
+        <v>4.2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1.04</v>
+      </c>
+      <c r="N21">
+        <v>5.5</v>
+      </c>
+      <c r="O21">
+        <v>1.21</v>
+      </c>
+      <c r="P21">
+        <v>2.52</v>
+      </c>
+      <c r="Q21">
+        <v>1.62</v>
+      </c>
+      <c r="R21">
+        <v>1.61</v>
+      </c>
+      <c r="S21">
+        <v>2.5</v>
+      </c>
+      <c r="T21">
+        <v>1.6</v>
+      </c>
+      <c r="U21">
+        <v>2.6</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>25</v>
+      </c>
+      <c r="Y21">
         <v>23</v>
       </c>
-      <c r="I21">
+      <c r="Z21">
+        <v>36</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>17.5</v>
+      </c>
+      <c r="AE21">
+        <v>46</v>
+      </c>
+      <c r="AF21">
+        <v>14.5</v>
+      </c>
+      <c r="AG21">
+        <v>10.5</v>
+      </c>
+      <c r="AH21">
+        <v>16</v>
+      </c>
+      <c r="AI21">
+        <v>46</v>
+      </c>
+      <c r="AJ21">
+        <v>23</v>
+      </c>
+      <c r="AK21">
+        <v>18</v>
+      </c>
+      <c r="AL21">
+        <v>28</v>
+      </c>
+      <c r="AM21">
+        <v>65</v>
+      </c>
+      <c r="AN21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO21">
+        <v>34</v>
+      </c>
+      <c r="AP21">
+        <v>20</v>
+      </c>
+      <c r="AQ21">
+        <v>18</v>
+      </c>
+      <c r="AR21">
+        <v>22</v>
+      </c>
+      <c r="AS21">
+        <v>36</v>
+      </c>
+      <c r="AT21">
+        <v>11.5</v>
+      </c>
+      <c r="AU21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV21">
+        <v>15.5</v>
+      </c>
+      <c r="AW21">
+        <v>34</v>
+      </c>
+      <c r="AX21">
+        <v>12.5</v>
+      </c>
+      <c r="AY21">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
         <v>25</v>
       </c>
-      <c r="J21">
-        <v>13</v>
-      </c>
-      <c r="K21">
-        <v>14</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>17.5</v>
-      </c>
-      <c r="O21">
-        <v>1.05</v>
-      </c>
-      <c r="P21">
-        <v>6.6</v>
-      </c>
-      <c r="Q21">
-        <v>1.15</v>
-      </c>
-      <c r="R21">
-        <v>3.15</v>
-      </c>
-      <c r="S21">
-        <v>1.41</v>
-      </c>
-      <c r="T21">
-        <v>1.73</v>
-      </c>
-      <c r="U21">
-        <v>2.28</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>350</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>36</v>
-      </c>
-      <c r="AC21">
-        <v>48</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>310</v>
-      </c>
-      <c r="AF21">
-        <v>17.5</v>
-      </c>
-      <c r="AG21">
+      <c r="BB21">
         <v>19</v>
       </c>
-      <c r="AH21">
-        <v>140</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>11.5</v>
-      </c>
-      <c r="AK21">
+      <c r="BC21">
         <v>15</v>
       </c>
-      <c r="AL21">
-        <v>38</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1.91</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>40</v>
-      </c>
-      <c r="AQ21">
-        <v>40</v>
-      </c>
-      <c r="AR21">
-        <v>17</v>
-      </c>
-      <c r="AS21">
-        <v>60</v>
-      </c>
-      <c r="AT21">
-        <v>20</v>
-      </c>
-      <c r="AU21">
-        <v>23</v>
-      </c>
-      <c r="AV21">
-        <v>36</v>
-      </c>
-      <c r="AW21">
-        <v>16.5</v>
-      </c>
-      <c r="AX21">
-        <v>15</v>
-      </c>
-      <c r="AY21">
-        <v>16.5</v>
-      </c>
-      <c r="AZ21">
-        <v>26</v>
-      </c>
-      <c r="BA21">
-        <v>44</v>
-      </c>
-      <c r="BB21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC21">
-        <v>13</v>
-      </c>
       <c r="BD21">
+        <v>18</v>
+      </c>
+      <c r="BE21">
+        <v>30</v>
+      </c>
+      <c r="BF21">
+        <v>7.8</v>
+      </c>
+      <c r="BG21">
         <v>21</v>
       </c>
-      <c r="BE21">
-        <v>40</v>
-      </c>
-      <c r="BF21">
-        <v>1.84</v>
-      </c>
-      <c r="BG21">
-        <v>85</v>
-      </c>
       <c r="BH21">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BI21">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ21">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BK21">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -5814,49 +5823,49 @@
         <v>55</v>
       </c>
       <c r="BN21">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BO21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP21">
+        <v>13</v>
+      </c>
+      <c r="BQ21">
+        <v>11</v>
+      </c>
+      <c r="BR21">
+        <v>23</v>
+      </c>
+      <c r="BS21">
+        <v>16</v>
+      </c>
+      <c r="BT21">
+        <v>7.6</v>
+      </c>
+      <c r="BU21">
         <v>6.8</v>
       </c>
-      <c r="BQ21">
-        <v>5.3</v>
-      </c>
-      <c r="BR21">
-        <v>17.5</v>
-      </c>
-      <c r="BS21">
+      <c r="BV21">
+        <v>32</v>
+      </c>
+      <c r="BW21">
+        <v>21</v>
+      </c>
+      <c r="BX21">
+        <v>36</v>
+      </c>
+      <c r="BY21">
+        <v>24</v>
+      </c>
+      <c r="BZ21">
+        <v>16.5</v>
+      </c>
+      <c r="CA21">
         <v>11.5</v>
       </c>
-      <c r="BT21">
-        <v>26</v>
-      </c>
-      <c r="BU21">
-        <v>17</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.01</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>48</v>
-      </c>
-      <c r="BZ21">
-        <v>4.4</v>
-      </c>
-      <c r="CA21">
-        <v>3.2</v>
-      </c>
       <c r="CB21" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5864,64 +5873,64 @@
         <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F22">
-        <v>2.62</v>
+        <v>1.12</v>
       </c>
       <c r="G22">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="H22">
-        <v>2.92</v>
+        <v>23</v>
       </c>
       <c r="I22">
-        <v>2.94</v>
+        <v>25</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="O22">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="P22">
-        <v>2.12</v>
+        <v>6.8</v>
       </c>
       <c r="Q22">
-        <v>1.84</v>
+        <v>1.15</v>
       </c>
       <c r="R22">
-        <v>1.44</v>
+        <v>3.15</v>
       </c>
       <c r="S22">
-        <v>3.1</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
         <v>1.68</v>
       </c>
       <c r="U22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5930,175 +5939,175 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AA22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AC22">
-        <v>8.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="AD22">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="AF22">
         <v>18.5</v>
       </c>
       <c r="AG22">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AH22">
-        <v>15.5</v>
+        <v>150</v>
       </c>
       <c r="AI22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="AK22">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM22">
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>20</v>
+        <v>1.92</v>
       </c>
       <c r="AO22">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AQ22">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AR22">
         <v>18</v>
       </c>
       <c r="AS22">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AT22">
+        <v>20</v>
+      </c>
+      <c r="AU22">
+        <v>34</v>
+      </c>
+      <c r="AV22">
+        <v>36</v>
+      </c>
+      <c r="AW22">
+        <v>18</v>
+      </c>
+      <c r="AX22">
+        <v>15</v>
+      </c>
+      <c r="AY22">
+        <v>16</v>
+      </c>
+      <c r="AZ22">
+        <v>26</v>
+      </c>
+      <c r="BA22">
+        <v>44</v>
+      </c>
+      <c r="BB22">
+        <v>10.5</v>
+      </c>
+      <c r="BC22">
+        <v>12.5</v>
+      </c>
+      <c r="BD22">
+        <v>20</v>
+      </c>
+      <c r="BE22">
+        <v>40</v>
+      </c>
+      <c r="BF22">
+        <v>1.83</v>
+      </c>
+      <c r="BG22">
+        <v>85</v>
+      </c>
+      <c r="BH22">
+        <v>11</v>
+      </c>
+      <c r="BI22">
+        <v>8.4</v>
+      </c>
+      <c r="BJ22">
+        <v>15</v>
+      </c>
+      <c r="BK22">
+        <v>10</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>55</v>
+      </c>
+      <c r="BN22">
+        <v>5.8</v>
+      </c>
+      <c r="BO22">
+        <v>4.7</v>
+      </c>
+      <c r="BP22">
+        <v>6.6</v>
+      </c>
+      <c r="BQ22">
+        <v>5.3</v>
+      </c>
+      <c r="BR22">
+        <v>17</v>
+      </c>
+      <c r="BS22">
         <v>11.5</v>
       </c>
-      <c r="AU22">
-        <v>7.4</v>
-      </c>
-      <c r="AV22">
-        <v>11.5</v>
-      </c>
-      <c r="AW22">
-        <v>19</v>
-      </c>
-      <c r="AX22">
-        <v>16</v>
-      </c>
-      <c r="AY22">
-        <v>11</v>
-      </c>
-      <c r="AZ22">
-        <v>14</v>
-      </c>
-      <c r="BA22">
-        <v>24</v>
-      </c>
-      <c r="BB22">
-        <v>23</v>
-      </c>
-      <c r="BC22">
-        <v>18</v>
-      </c>
-      <c r="BD22">
-        <v>23</v>
-      </c>
-      <c r="BE22">
-        <v>34</v>
-      </c>
-      <c r="BF22">
-        <v>17.5</v>
-      </c>
-      <c r="BG22">
-        <v>20</v>
-      </c>
-      <c r="BH22">
-        <v>3.7</v>
-      </c>
-      <c r="BI22">
-        <v>3.4</v>
-      </c>
-      <c r="BJ22">
-        <v>9</v>
-      </c>
-      <c r="BK22">
-        <v>8</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>65</v>
-      </c>
-      <c r="BN22">
-        <v>5.7</v>
-      </c>
-      <c r="BO22">
-        <v>5.2</v>
-      </c>
-      <c r="BP22">
-        <v>19</v>
-      </c>
-      <c r="BQ22">
-        <v>13.5</v>
-      </c>
-      <c r="BR22">
-        <v>29</v>
-      </c>
-      <c r="BS22">
-        <v>20</v>
-      </c>
       <c r="BT22">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BU22">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="BV22">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BZ22">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="CA22">
-        <v>15.5</v>
+        <v>3.3</v>
       </c>
       <c r="CB22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6106,483 +6115,725 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F23">
-        <v>1.14</v>
+        <v>2.64</v>
       </c>
       <c r="G23">
-        <v>1.15</v>
+        <v>2.68</v>
       </c>
       <c r="H23">
+        <v>2.86</v>
+      </c>
+      <c r="I23">
+        <v>2.9</v>
+      </c>
+      <c r="J23">
+        <v>3.6</v>
+      </c>
+      <c r="K23">
+        <v>3.65</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1.06</v>
+      </c>
+      <c r="N23">
+        <v>4.3</v>
+      </c>
+      <c r="O23">
+        <v>1.29</v>
+      </c>
+      <c r="P23">
+        <v>2.12</v>
+      </c>
+      <c r="Q23">
+        <v>1.84</v>
+      </c>
+      <c r="R23">
+        <v>1.44</v>
+      </c>
+      <c r="S23">
+        <v>3.1</v>
+      </c>
+      <c r="T23">
+        <v>1.69</v>
+      </c>
+      <c r="U23">
+        <v>2.36</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>16.5</v>
+      </c>
+      <c r="Y23">
+        <v>14</v>
+      </c>
+      <c r="Z23">
+        <v>21</v>
+      </c>
+      <c r="AA23">
+        <v>44</v>
+      </c>
+      <c r="AB23">
+        <v>12.5</v>
+      </c>
+      <c r="AC23">
+        <v>8</v>
+      </c>
+      <c r="AD23">
+        <v>13</v>
+      </c>
+      <c r="AE23">
+        <v>30</v>
+      </c>
+      <c r="AF23">
+        <v>18</v>
+      </c>
+      <c r="AG23">
+        <v>12.5</v>
+      </c>
+      <c r="AH23">
+        <v>15.5</v>
+      </c>
+      <c r="AI23">
+        <v>44</v>
+      </c>
+      <c r="AJ23">
+        <v>38</v>
+      </c>
+      <c r="AK23">
         <v>28</v>
       </c>
-      <c r="I23">
-        <v>32</v>
-      </c>
-      <c r="J23">
-        <v>10.5</v>
-      </c>
-      <c r="K23">
+      <c r="AL23">
+        <v>38</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>20</v>
+      </c>
+      <c r="AO23">
+        <v>23</v>
+      </c>
+      <c r="AP23">
+        <v>15</v>
+      </c>
+      <c r="AQ23">
+        <v>12</v>
+      </c>
+      <c r="AR23">
+        <v>18</v>
+      </c>
+      <c r="AS23">
+        <v>25</v>
+      </c>
+      <c r="AT23">
+        <v>11.5</v>
+      </c>
+      <c r="AU23">
+        <v>7.4</v>
+      </c>
+      <c r="AV23">
+        <v>11.5</v>
+      </c>
+      <c r="AW23">
+        <v>19</v>
+      </c>
+      <c r="AX23">
+        <v>16</v>
+      </c>
+      <c r="AY23">
         <v>11</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>1.01</v>
-      </c>
-      <c r="N23">
-        <v>10.5</v>
-      </c>
-      <c r="O23">
-        <v>1.09</v>
-      </c>
-      <c r="P23">
-        <v>4.2</v>
-      </c>
-      <c r="Q23">
-        <v>1.28</v>
-      </c>
-      <c r="R23">
-        <v>2.32</v>
-      </c>
-      <c r="S23">
-        <v>1.68</v>
-      </c>
-      <c r="T23">
-        <v>2.12</v>
-      </c>
-      <c r="U23">
-        <v>1.85</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>60</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>370</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
+      <c r="AZ23">
+        <v>14</v>
+      </c>
+      <c r="BA23">
+        <v>24</v>
+      </c>
+      <c r="BB23">
+        <v>23</v>
+      </c>
+      <c r="BC23">
         <v>18.5</v>
       </c>
-      <c r="AC23">
-        <v>26</v>
-      </c>
-      <c r="AD23">
-        <v>120</v>
-      </c>
-      <c r="AE23">
-        <v>450</v>
-      </c>
-      <c r="AF23">
-        <v>11.5</v>
-      </c>
-      <c r="AG23">
-        <v>16.5</v>
-      </c>
-      <c r="AH23">
-        <v>55</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>9.4</v>
-      </c>
-      <c r="AK23">
+      <c r="BD23">
+        <v>23</v>
+      </c>
+      <c r="BE23">
+        <v>34</v>
+      </c>
+      <c r="BF23">
+        <v>17.5</v>
+      </c>
+      <c r="BG23">
+        <v>20</v>
+      </c>
+      <c r="BH23">
+        <v>3.7</v>
+      </c>
+      <c r="BI23">
+        <v>3.4</v>
+      </c>
+      <c r="BJ23">
+        <v>9</v>
+      </c>
+      <c r="BK23">
+        <v>8</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>65</v>
+      </c>
+      <c r="BN23">
+        <v>5.7</v>
+      </c>
+      <c r="BO23">
+        <v>5.2</v>
+      </c>
+      <c r="BP23">
+        <v>18.5</v>
+      </c>
+      <c r="BQ23">
+        <v>13.5</v>
+      </c>
+      <c r="BR23">
+        <v>29</v>
+      </c>
+      <c r="BS23">
+        <v>20</v>
+      </c>
+      <c r="BT23">
+        <v>6.2</v>
+      </c>
+      <c r="BU23">
+        <v>5.5</v>
+      </c>
+      <c r="BV23">
+        <v>21</v>
+      </c>
+      <c r="BW23">
         <v>15</v>
       </c>
-      <c r="AL23">
-        <v>44</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>2.34</v>
-      </c>
-      <c r="AO23">
-        <v>460</v>
-      </c>
-      <c r="AP23">
-        <v>28</v>
-      </c>
-      <c r="AQ23">
-        <v>40</v>
-      </c>
-      <c r="AR23">
-        <v>14</v>
-      </c>
-      <c r="AS23">
-        <v>60</v>
-      </c>
-      <c r="AT23">
-        <v>16</v>
-      </c>
-      <c r="AU23">
+      <c r="BX23">
+        <v>30</v>
+      </c>
+      <c r="BY23">
+        <v>21</v>
+      </c>
+      <c r="BZ23">
         <v>22</v>
       </c>
-      <c r="AV23">
-        <v>55</v>
-      </c>
-      <c r="AW23">
-        <v>65</v>
-      </c>
-      <c r="AX23">
-        <v>10</v>
-      </c>
-      <c r="AY23">
-        <v>14.5</v>
-      </c>
-      <c r="AZ23">
-        <v>25</v>
-      </c>
-      <c r="BA23">
-        <v>14</v>
-      </c>
-      <c r="BB23">
-        <v>8.6</v>
-      </c>
-      <c r="BC23">
-        <v>12.5</v>
-      </c>
-      <c r="BD23">
-        <v>25</v>
-      </c>
-      <c r="BE23">
-        <v>44</v>
-      </c>
-      <c r="BF23">
-        <v>2.2</v>
-      </c>
-      <c r="BG23">
-        <v>65</v>
-      </c>
-      <c r="BH23">
-        <v>8</v>
-      </c>
-      <c r="BI23">
-        <v>5.5</v>
-      </c>
-      <c r="BJ23">
-        <v>17</v>
-      </c>
-      <c r="BK23">
-        <v>11</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.01</v>
-      </c>
-      <c r="BN23">
-        <v>4.8</v>
-      </c>
-      <c r="BO23">
-        <v>3.45</v>
-      </c>
-      <c r="BP23">
-        <v>6.2</v>
-      </c>
-      <c r="BQ23">
-        <v>4.9</v>
-      </c>
-      <c r="BR23">
-        <v>22</v>
-      </c>
-      <c r="BS23">
-        <v>14.5</v>
-      </c>
-      <c r="BT23">
-        <v>27</v>
-      </c>
-      <c r="BU23">
-        <v>17.5</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.01</v>
-      </c>
-      <c r="BX23">
-        <v>120</v>
-      </c>
-      <c r="BY23">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23">
-        <v>5.8</v>
-      </c>
       <c r="CA23">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="CB23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F24">
-        <v>5.4</v>
+        <v>1.14</v>
       </c>
       <c r="G24">
-        <v>5.8</v>
+        <v>1.15</v>
       </c>
       <c r="H24">
+        <v>29</v>
+      </c>
+      <c r="I24">
+        <v>32</v>
+      </c>
+      <c r="J24">
+        <v>10.5</v>
+      </c>
+      <c r="K24">
+        <v>11</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>10.5</v>
+      </c>
+      <c r="O24">
+        <v>1.09</v>
+      </c>
+      <c r="P24">
+        <v>4.2</v>
+      </c>
+      <c r="Q24">
+        <v>1.28</v>
+      </c>
+      <c r="R24">
+        <v>2.34</v>
+      </c>
+      <c r="S24">
+        <v>1.69</v>
+      </c>
+      <c r="T24">
+        <v>2.1</v>
+      </c>
+      <c r="U24">
+        <v>1.86</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>60</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>330</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>18.5</v>
+      </c>
+      <c r="AC24">
+        <v>26</v>
+      </c>
+      <c r="AD24">
+        <v>110</v>
+      </c>
+      <c r="AE24">
+        <v>400</v>
+      </c>
+      <c r="AF24">
+        <v>11.5</v>
+      </c>
+      <c r="AG24">
+        <v>16.5</v>
+      </c>
+      <c r="AH24">
+        <v>44</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>9.4</v>
+      </c>
+      <c r="AK24">
+        <v>14.5</v>
+      </c>
+      <c r="AL24">
+        <v>44</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>2.3</v>
+      </c>
+      <c r="AO24">
+        <v>410</v>
+      </c>
+      <c r="AP24">
+        <v>28</v>
+      </c>
+      <c r="AQ24">
+        <v>40</v>
+      </c>
+      <c r="AR24">
+        <v>55</v>
+      </c>
+      <c r="AS24">
+        <v>17.5</v>
+      </c>
+      <c r="AT24">
+        <v>16</v>
+      </c>
+      <c r="AU24">
+        <v>22</v>
+      </c>
+      <c r="AV24">
+        <v>38</v>
+      </c>
+      <c r="AW24">
+        <v>55</v>
+      </c>
+      <c r="AX24">
+        <v>10</v>
+      </c>
+      <c r="AY24">
+        <v>14.5</v>
+      </c>
+      <c r="AZ24">
+        <v>36</v>
+      </c>
+      <c r="BA24">
+        <v>50</v>
+      </c>
+      <c r="BB24">
+        <v>8.6</v>
+      </c>
+      <c r="BC24">
+        <v>12.5</v>
+      </c>
+      <c r="BD24">
+        <v>25</v>
+      </c>
+      <c r="BE24">
+        <v>44</v>
+      </c>
+      <c r="BF24">
+        <v>2.22</v>
+      </c>
+      <c r="BG24">
+        <v>65</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>4.4</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25">
+        <v>5.3</v>
+      </c>
+      <c r="G25">
+        <v>5.7</v>
+      </c>
+      <c r="H25">
         <v>1.75</v>
       </c>
-      <c r="I24">
+      <c r="I25">
         <v>1.81</v>
       </c>
-      <c r="J24">
+      <c r="J25">
         <v>3.85</v>
       </c>
-      <c r="K24">
+      <c r="K25">
         <v>3.95</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>1.83</v>
-      </c>
-      <c r="Q24">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.94</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0</v>
-      </c>
-      <c r="AO24">
-        <v>0</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>0</v>
-      </c>
-      <c r="BC24">
-        <v>0</v>
-      </c>
-      <c r="BD24">
-        <v>0</v>
-      </c>
-      <c r="BE24">
-        <v>0</v>
-      </c>
-      <c r="BF24">
-        <v>0</v>
-      </c>
-      <c r="BG24">
-        <v>0</v>
-      </c>
-      <c r="BH24">
-        <v>0</v>
-      </c>
-      <c r="BI24">
-        <v>0</v>
-      </c>
-      <c r="BJ24">
-        <v>0</v>
-      </c>
-      <c r="BK24">
-        <v>0</v>
-      </c>
-      <c r="BL24">
-        <v>0</v>
-      </c>
-      <c r="BM24">
-        <v>0</v>
-      </c>
-      <c r="BN24">
-        <v>0</v>
-      </c>
-      <c r="BO24">
-        <v>0</v>
-      </c>
-      <c r="BP24">
-        <v>0</v>
-      </c>
-      <c r="BQ24">
-        <v>0</v>
-      </c>
-      <c r="BR24">
-        <v>0</v>
-      </c>
-      <c r="BS24">
-        <v>0</v>
-      </c>
-      <c r="BT24">
-        <v>0</v>
-      </c>
-      <c r="BU24">
-        <v>0</v>
-      </c>
-      <c r="BV24">
-        <v>0</v>
-      </c>
-      <c r="BW24">
-        <v>0</v>
-      </c>
-      <c r="BX24">
-        <v>0</v>
-      </c>
-      <c r="BY24">
-        <v>0</v>
-      </c>
-      <c r="BZ24">
-        <v>0</v>
-      </c>
-      <c r="CA24">
-        <v>0</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>142</v>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="159">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>UAE Arabian Gulf League</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
     <t>UEFA Champions League</t>
   </si>
   <si>
@@ -295,6 +301,15 @@
     <t>02:30:00</t>
   </si>
   <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
     <t>16:45:00</t>
   </si>
   <si>
@@ -331,16 +346,28 @@
     <t>Boyaca Chico</t>
   </si>
   <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>San Diego FC</t>
   </si>
   <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>Los Angeles FC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
+    <t>Al Jazira</t>
+  </si>
+  <si>
+    <t>Al Shamal</t>
+  </si>
+  <si>
+    <t>Al Sailiya</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>PSV</t>
@@ -364,18 +391,18 @@
     <t>Ostersunds FK</t>
   </si>
   <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>Slavia Prague</t>
+  </si>
+  <si>
+    <t>Man Utd</t>
+  </si>
+  <si>
     <t>Como</t>
   </si>
   <si>
-    <t>Bayern Munich</t>
-  </si>
-  <si>
-    <t>Slavia Prague</t>
-  </si>
-  <si>
-    <t>Man Utd</t>
-  </si>
-  <si>
     <t>Club Football Estrela</t>
   </si>
   <si>
@@ -403,16 +430,28 @@
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>San Jose Earthquakes</t>
   </si>
   <si>
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>New York Red Bulls</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
+    <t>Al Nasr (UAE)</t>
+  </si>
+  <si>
+    <t>Al-Wakra</t>
+  </si>
+  <si>
+    <t>Al-Sadd</t>
+  </si>
+  <si>
+    <t>Al Wasl</t>
   </si>
   <si>
     <t>Shakhtar</t>
@@ -436,22 +475,22 @@
     <t>IK Brage</t>
   </si>
   <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>FC Sabah</t>
+  </si>
+  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>FC Sabah</t>
-  </si>
-  <si>
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 10:44:44</t>
+    <t>2026-09-08 12:57:50</t>
   </si>
 </sst>
 </file>
@@ -783,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1033,25 +1072,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
         <v>3.2</v>
@@ -1072,7 +1111,7 @@
         <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
         <v>2.28</v>
@@ -1084,10 +1123,10 @@
         <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U2">
         <v>2.46</v>
@@ -1096,7 +1135,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>21</v>
@@ -1108,7 +1147,7 @@
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB2">
         <v>13</v>
@@ -1126,7 +1165,7 @@
         <v>17</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>16</v>
@@ -1159,10 +1198,10 @@
         <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
@@ -1171,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
         <v>21</v>
@@ -1186,13 +1225,13 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB2">
         <v>20</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
         <v>23</v>
@@ -1204,70 +1243,70 @@
         <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1275,16 +1314,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>1.87</v>
@@ -1296,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
         <v>3.45</v>
@@ -1305,22 +1344,22 @@
         <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
         <v>1.26</v>
@@ -1335,7 +1374,7 @@
         <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>2.06</v>
@@ -1347,22 +1386,22 @@
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA3">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
         <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
@@ -1371,10 +1410,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
         <v>26</v>
@@ -1383,40 +1422,40 @@
         <v>28</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN3">
         <v>21</v>
       </c>
       <c r="AO3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1425,28 +1464,28 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF3">
         <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH3">
         <v>3.45</v>
@@ -1476,7 +1515,7 @@
         <v>18</v>
       </c>
       <c r="BQ3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR3">
         <v>42</v>
@@ -1488,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="BU3">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
         <v>60</v>
@@ -1509,7 +1548,7 @@
         <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1517,22 +1556,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -1547,19 +1586,19 @@
         <v>3.05</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M4">
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O4">
         <v>1.69</v>
       </c>
       <c r="P4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
@@ -1580,7 +1619,7 @@
         <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>7.2</v>
@@ -1631,7 +1670,7 @@
         <v>330</v>
       </c>
       <c r="AN4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO4">
         <v>170</v>
@@ -1643,10 +1682,10 @@
         <v>8.6</v>
       </c>
       <c r="AR4">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>5.8</v>
@@ -1658,7 +1697,7 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>11</v>
@@ -1673,85 +1712,85 @@
         <v>11.5</v>
       </c>
       <c r="BB4">
+        <v>28</v>
+      </c>
+      <c r="BC4">
         <v>9.4</v>
       </c>
-      <c r="BC4">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BD4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
         <v>27</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH4">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>1.64</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>1.64</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>1.64</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>14.5</v>
+        <v>1.64</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>2.26</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>14</v>
+        <v>1.64</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="CB4" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1759,16 +1798,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F5">
         <v>2.14</v>
@@ -1777,16 +1816,16 @@
         <v>2.18</v>
       </c>
       <c r="H5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.29</v>
@@ -1801,10 +1840,10 @@
         <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
         <v>1.67</v>
@@ -1816,13 +1855,13 @@
         <v>1.55</v>
       </c>
       <c r="U5">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X5">
         <v>26</v>
@@ -1831,10 +1870,10 @@
         <v>20</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1858,22 +1897,22 @@
         <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
         <v>30</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM5">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO5">
         <v>23</v>
@@ -1900,7 +1939,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1921,16 +1960,16 @@
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
@@ -1945,13 +1984,13 @@
         <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM5">
         <v>50</v>
       </c>
       <c r="BN5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO5">
         <v>4.9</v>
@@ -1966,16 +2005,16 @@
         <v>25</v>
       </c>
       <c r="BS5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BU5">
         <v>6.4</v>
       </c>
       <c r="BV5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW5">
         <v>17</v>
@@ -1993,7 +2032,7 @@
         <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2001,16 +2040,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F6">
         <v>2.62</v>
@@ -2019,7 +2058,7 @@
         <v>2.74</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
         <v>2.94</v>
@@ -2031,13 +2070,13 @@
         <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -2046,7 +2085,7 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
         <v>1.39</v>
@@ -2055,10 +2094,10 @@
         <v>3.4</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2076,7 +2115,7 @@
         <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB6">
         <v>12</v>
@@ -2103,10 +2142,10 @@
         <v>120</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AK6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AL6">
         <v>60</v>
@@ -2118,19 +2157,19 @@
         <v>24</v>
       </c>
       <c r="AO6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2142,7 +2181,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2151,37 +2190,37 @@
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
+        <v>29</v>
+      </c>
+      <c r="BB6">
         <v>26</v>
-      </c>
-      <c r="BB6">
-        <v>28</v>
       </c>
       <c r="BC6">
         <v>19</v>
       </c>
       <c r="BD6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>6.6</v>
@@ -2190,52 +2229,52 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
         <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>2.54</v>
+        <v>3.9</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW6">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY6">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA6">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="CB6" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2243,22 +2282,22 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F7">
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H7">
         <v>4.5</v>
@@ -2273,19 +2312,19 @@
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
         <v>1.24</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
         <v>1.73</v>
@@ -2294,7 +2333,7 @@
         <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T7">
         <v>1.71</v>
@@ -2330,7 +2369,7 @@
         <v>19</v>
       </c>
       <c r="AE7">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AF7">
         <v>12.5</v>
@@ -2342,7 +2381,7 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2360,10 +2399,10 @@
         <v>9.4</v>
       </c>
       <c r="AO7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7">
         <v>17</v>
@@ -2372,10 +2411,10 @@
         <v>23</v>
       </c>
       <c r="AS7">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7">
         <v>8.6</v>
@@ -2384,7 +2423,7 @@
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2396,7 +2435,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2405,10 +2444,10 @@
         <v>15</v>
       </c>
       <c r="BD7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE7">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BF7">
         <v>8.4</v>
@@ -2477,7 +2516,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2485,16 +2524,16 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F8">
         <v>2.2</v>
@@ -2503,7 +2542,7 @@
         <v>2.26</v>
       </c>
       <c r="H8">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I8">
         <v>3.05</v>
@@ -2527,7 +2566,7 @@
         <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
         <v>1.29</v>
@@ -2536,7 +2575,7 @@
         <v>2.34</v>
       </c>
       <c r="S8">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T8">
         <v>1.32</v>
@@ -2545,7 +2584,7 @@
         <v>3.95</v>
       </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
         <v>1.79</v>
@@ -2554,13 +2593,13 @@
         <v>360</v>
       </c>
       <c r="Y8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z8">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AA8">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AB8">
         <v>32</v>
@@ -2575,10 +2614,10 @@
         <v>27</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
@@ -2587,10 +2626,10 @@
         <v>25</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL8">
         <v>21</v>
@@ -2599,25 +2638,25 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO8">
         <v>10</v>
       </c>
       <c r="AP8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AQ8">
         <v>24</v>
       </c>
       <c r="AR8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS8">
         <v>34</v>
       </c>
       <c r="AT8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AU8">
         <v>12</v>
@@ -2626,10 +2665,10 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2641,7 +2680,7 @@
         <v>18</v>
       </c>
       <c r="BB8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2650,7 +2689,7 @@
         <v>17.5</v>
       </c>
       <c r="BE8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF8">
         <v>6</v>
@@ -2659,67 +2698,67 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
+        <v>4.9</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>5.7</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>5.1</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>9</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>10</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
         <v>5.8</v>
       </c>
-      <c r="BJ8">
-        <v>9.6</v>
-      </c>
-      <c r="BK8">
-        <v>6.8</v>
-      </c>
-      <c r="BL8">
-        <v>55</v>
-      </c>
-      <c r="BM8">
-        <v>30</v>
-      </c>
-      <c r="BN8">
-        <v>8</v>
-      </c>
-      <c r="BO8">
-        <v>5.9</v>
-      </c>
-      <c r="BP8">
-        <v>16.5</v>
-      </c>
-      <c r="BQ8">
-        <v>10.5</v>
-      </c>
-      <c r="BR8">
-        <v>20</v>
-      </c>
-      <c r="BS8">
-        <v>12</v>
-      </c>
-      <c r="BT8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU8">
-        <v>6.8</v>
-      </c>
       <c r="BV8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BX8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2727,16 +2766,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2961,7 +3000,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2969,241 +3008,241 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R10">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S10">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T10">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="U10">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="X10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y10">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Z10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AG10">
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="AJ10">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AK10">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL10">
         <v>24</v>
       </c>
       <c r="AM10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
+        <v>4.3</v>
+      </c>
+      <c r="AO10">
+        <v>350</v>
+      </c>
+      <c r="AP10">
+        <v>29</v>
+      </c>
+      <c r="AQ10">
+        <v>27</v>
+      </c>
+      <c r="AR10">
+        <v>44</v>
+      </c>
+      <c r="AS10">
+        <v>46</v>
+      </c>
+      <c r="AT10">
+        <v>13.5</v>
+      </c>
+      <c r="AU10">
+        <v>12</v>
+      </c>
+      <c r="AV10">
+        <v>19.5</v>
+      </c>
+      <c r="AW10">
+        <v>48</v>
+      </c>
+      <c r="AX10">
+        <v>11.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>16.5</v>
+      </c>
+      <c r="BA10">
+        <v>36</v>
+      </c>
+      <c r="BB10">
+        <v>13.5</v>
+      </c>
+      <c r="BC10">
+        <v>12</v>
+      </c>
+      <c r="BD10">
+        <v>20</v>
+      </c>
+      <c r="BE10">
+        <v>42</v>
+      </c>
+      <c r="BF10">
+        <v>4</v>
+      </c>
+      <c r="BG10">
+        <v>28</v>
+      </c>
+      <c r="BH10">
+        <v>5.4</v>
+      </c>
+      <c r="BI10">
+        <v>4.9</v>
+      </c>
+      <c r="BJ10">
+        <v>9.4</v>
+      </c>
+      <c r="BK10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>50</v>
+      </c>
+      <c r="BN10">
+        <v>4.6</v>
+      </c>
+      <c r="BO10">
+        <v>4.2</v>
+      </c>
+      <c r="BP10">
+        <v>8.4</v>
+      </c>
+      <c r="BQ10">
+        <v>7.2</v>
+      </c>
+      <c r="BR10">
+        <v>17.5</v>
+      </c>
+      <c r="BS10">
+        <v>14.5</v>
+      </c>
+      <c r="BT10">
+        <v>11</v>
+      </c>
+      <c r="BU10">
+        <v>9.6</v>
+      </c>
+      <c r="BV10">
+        <v>46</v>
+      </c>
+      <c r="BW10">
+        <v>32</v>
+      </c>
+      <c r="BX10">
+        <v>40</v>
+      </c>
+      <c r="BY10">
+        <v>29</v>
+      </c>
+      <c r="BZ10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CA10">
         <v>6.8</v>
       </c>
-      <c r="AO10">
-        <v>25</v>
-      </c>
-      <c r="AP10">
-        <v>22</v>
-      </c>
-      <c r="AQ10">
-        <v>18</v>
-      </c>
-      <c r="AR10">
-        <v>23</v>
-      </c>
-      <c r="AS10">
-        <v>34</v>
-      </c>
-      <c r="AT10">
-        <v>14.5</v>
-      </c>
-      <c r="AU10">
-        <v>10</v>
-      </c>
-      <c r="AV10">
-        <v>15</v>
-      </c>
-      <c r="AW10">
-        <v>23</v>
-      </c>
-      <c r="AX10">
-        <v>14.5</v>
-      </c>
-      <c r="AY10">
-        <v>10</v>
-      </c>
-      <c r="AZ10">
-        <v>13.5</v>
-      </c>
-      <c r="BA10">
-        <v>22</v>
-      </c>
-      <c r="BB10">
-        <v>19</v>
-      </c>
-      <c r="BC10">
-        <v>14.5</v>
-      </c>
-      <c r="BD10">
-        <v>19</v>
-      </c>
-      <c r="BE10">
-        <v>26</v>
-      </c>
-      <c r="BF10">
-        <v>6</v>
-      </c>
-      <c r="BG10">
-        <v>17</v>
-      </c>
-      <c r="BH10">
-        <v>5.2</v>
-      </c>
-      <c r="BI10">
-        <v>4.6</v>
-      </c>
-      <c r="BJ10">
-        <v>8.6</v>
-      </c>
-      <c r="BK10">
-        <v>7.4</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>42</v>
-      </c>
-      <c r="BN10">
-        <v>5.4</v>
-      </c>
-      <c r="BO10">
-        <v>4.7</v>
-      </c>
-      <c r="BP10">
-        <v>11.5</v>
-      </c>
-      <c r="BQ10">
-        <v>10</v>
-      </c>
-      <c r="BR10">
-        <v>19</v>
-      </c>
-      <c r="BS10">
-        <v>15.5</v>
-      </c>
-      <c r="BT10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU10">
-        <v>7.2</v>
-      </c>
-      <c r="BV10">
-        <v>28</v>
-      </c>
-      <c r="BW10">
-        <v>19</v>
-      </c>
-      <c r="BX10">
-        <v>29</v>
-      </c>
-      <c r="BY10">
-        <v>20</v>
-      </c>
-      <c r="BZ10">
-        <v>12</v>
-      </c>
-      <c r="CA10">
-        <v>8.4</v>
-      </c>
       <c r="CB10" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3211,190 +3250,190 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F11">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="G11">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="H11">
-        <v>2.88</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="O11">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="R11">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="S11">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="T11">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="U11">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="Z11">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AD11">
+        <v>29</v>
+      </c>
+      <c r="AE11">
+        <v>85</v>
+      </c>
+      <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>20</v>
+      </c>
+      <c r="AI11">
+        <v>65</v>
+      </c>
+      <c r="AJ11">
+        <v>14.5</v>
+      </c>
+      <c r="AK11">
         <v>14</v>
       </c>
-      <c r="AE11">
-        <v>27</v>
-      </c>
-      <c r="AF11">
-        <v>20</v>
-      </c>
-      <c r="AG11">
-        <v>12.5</v>
-      </c>
-      <c r="AH11">
-        <v>14.5</v>
-      </c>
-      <c r="AI11">
-        <v>32</v>
-      </c>
-      <c r="AJ11">
-        <v>36</v>
-      </c>
-      <c r="AK11">
-        <v>22</v>
-      </c>
       <c r="AL11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AM11">
         <v>65</v>
       </c>
       <c r="AN11">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO11">
-        <v>16.5</v>
+        <v>760</v>
       </c>
       <c r="AP11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AQ11">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AR11">
+        <v>65</v>
+      </c>
+      <c r="AS11">
+        <v>48</v>
+      </c>
+      <c r="AT11">
+        <v>14</v>
+      </c>
+      <c r="AU11">
+        <v>13</v>
+      </c>
+      <c r="AV11">
+        <v>26</v>
+      </c>
+      <c r="AW11">
+        <v>34</v>
+      </c>
+      <c r="AX11">
+        <v>11</v>
+      </c>
+      <c r="AY11">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11">
+        <v>17.5</v>
+      </c>
+      <c r="BA11">
+        <v>55</v>
+      </c>
+      <c r="BB11">
+        <v>13</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
         <v>21</v>
       </c>
-      <c r="AS11">
-        <v>26</v>
-      </c>
-      <c r="AT11">
-        <v>15</v>
-      </c>
-      <c r="AU11">
-        <v>9</v>
-      </c>
-      <c r="AV11">
-        <v>12</v>
-      </c>
-      <c r="AW11">
-        <v>18.5</v>
-      </c>
-      <c r="AX11">
-        <v>17</v>
-      </c>
-      <c r="AY11">
-        <v>11</v>
-      </c>
-      <c r="AZ11">
-        <v>12.5</v>
-      </c>
-      <c r="BA11">
-        <v>19.5</v>
-      </c>
-      <c r="BB11">
-        <v>21</v>
-      </c>
-      <c r="BC11">
-        <v>19</v>
-      </c>
-      <c r="BD11">
-        <v>20</v>
-      </c>
       <c r="BE11">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BG11">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="BH11">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI11">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BJ11">
+        <v>9.6</v>
+      </c>
+      <c r="BK11">
         <v>8.4</v>
-      </c>
-      <c r="BK11">
-        <v>7.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3403,49 +3442,49 @@
         <v>21</v>
       </c>
       <c r="BN11">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO11">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ11">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BS11">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BT11">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BV11">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="BX11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="BZ11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3453,241 +3492,241 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F12">
+        <v>1.82</v>
+      </c>
+      <c r="G12">
+        <v>1.87</v>
+      </c>
+      <c r="H12">
+        <v>4.1</v>
+      </c>
+      <c r="I12">
+        <v>4.3</v>
+      </c>
+      <c r="J12">
+        <v>4.4</v>
+      </c>
+      <c r="K12">
+        <v>4.7</v>
+      </c>
+      <c r="L12">
+        <v>1.24</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>7.2</v>
+      </c>
+      <c r="O12">
+        <v>1.15</v>
+      </c>
+      <c r="P12">
+        <v>3.1</v>
+      </c>
+      <c r="Q12">
         <v>1.45</v>
       </c>
-      <c r="G12">
+      <c r="R12">
+        <v>1.85</v>
+      </c>
+      <c r="S12">
+        <v>2.12</v>
+      </c>
+      <c r="T12">
         <v>1.48</v>
       </c>
-      <c r="H12">
-        <v>6.8</v>
-      </c>
-      <c r="I12">
-        <v>7.6</v>
-      </c>
-      <c r="J12">
-        <v>5.4</v>
-      </c>
-      <c r="K12">
-        <v>5.8</v>
-      </c>
-      <c r="L12">
-        <v>1.23</v>
-      </c>
-      <c r="M12">
-        <v>1.02</v>
-      </c>
-      <c r="N12">
-        <v>7.6</v>
-      </c>
-      <c r="O12">
-        <v>1.13</v>
-      </c>
-      <c r="P12">
-        <v>3.3</v>
-      </c>
-      <c r="Q12">
-        <v>1.41</v>
-      </c>
-      <c r="R12">
-        <v>1.92</v>
-      </c>
-      <c r="S12">
-        <v>2.02</v>
-      </c>
-      <c r="T12">
-        <v>1.6</v>
-      </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="X12">
         <v>40</v>
       </c>
       <c r="Y12">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC12">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF12">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AG12">
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI12">
-        <v>420</v>
+        <v>42</v>
       </c>
       <c r="AJ12">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AK12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL12">
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN12">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AO12">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="AP12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ12">
+        <v>20</v>
+      </c>
+      <c r="AR12">
+        <v>28</v>
+      </c>
+      <c r="AS12">
+        <v>34</v>
+      </c>
+      <c r="AT12">
+        <v>14.5</v>
+      </c>
+      <c r="AU12">
+        <v>10</v>
+      </c>
+      <c r="AV12">
+        <v>15</v>
+      </c>
+      <c r="AW12">
+        <v>28</v>
+      </c>
+      <c r="AX12">
+        <v>14.5</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>13.5</v>
+      </c>
+      <c r="BA12">
         <v>27</v>
       </c>
-      <c r="AR12">
-        <v>32</v>
-      </c>
-      <c r="AS12">
-        <v>46</v>
-      </c>
-      <c r="AT12">
-        <v>13.5</v>
-      </c>
-      <c r="AU12">
-        <v>12</v>
-      </c>
-      <c r="AV12">
-        <v>18</v>
-      </c>
-      <c r="AW12">
+      <c r="BB12">
+        <v>16</v>
+      </c>
+      <c r="BC12">
+        <v>14.5</v>
+      </c>
+      <c r="BD12">
+        <v>19</v>
+      </c>
+      <c r="BE12">
         <v>34</v>
       </c>
-      <c r="AX12">
-        <v>11.5</v>
-      </c>
-      <c r="AY12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ12">
-        <v>16.5</v>
-      </c>
-      <c r="BA12">
-        <v>29</v>
-      </c>
-      <c r="BB12">
-        <v>13.5</v>
-      </c>
-      <c r="BC12">
-        <v>12</v>
-      </c>
-      <c r="BD12">
-        <v>20</v>
-      </c>
-      <c r="BE12">
-        <v>32</v>
-      </c>
       <c r="BF12">
+        <v>6</v>
+      </c>
+      <c r="BG12">
+        <v>17</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
         <v>4.1</v>
       </c>
-      <c r="BG12">
-        <v>28</v>
-      </c>
-      <c r="BH12">
-        <v>5.4</v>
-      </c>
-      <c r="BI12">
-        <v>4.8</v>
-      </c>
       <c r="BJ12">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
         <v>4.2</v>
       </c>
       <c r="BP12">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BT12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BV12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3695,241 +3734,241 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F13">
-        <v>1.46</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>1.48</v>
+        <v>2.44</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="I13">
-        <v>7.4</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="K13">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="Q13">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="R13">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="U13">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="X13">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Y13">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
         <v>14</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
+        <v>27</v>
+      </c>
+      <c r="AF13">
+        <v>20</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>14.5</v>
+      </c>
+      <c r="AI13">
+        <v>32</v>
+      </c>
+      <c r="AJ13">
+        <v>36</v>
+      </c>
+      <c r="AK13">
+        <v>22</v>
+      </c>
+      <c r="AL13">
         <v>28</v>
-      </c>
-      <c r="AE13">
-        <v>1000</v>
-      </c>
-      <c r="AF13">
-        <v>13</v>
-      </c>
-      <c r="AG13">
-        <v>10.5</v>
-      </c>
-      <c r="AH13">
-        <v>19</v>
-      </c>
-      <c r="AI13">
-        <v>65</v>
-      </c>
-      <c r="AJ13">
-        <v>15</v>
-      </c>
-      <c r="AK13">
-        <v>14</v>
-      </c>
-      <c r="AL13">
-        <v>23</v>
       </c>
       <c r="AM13">
         <v>65</v>
       </c>
       <c r="AN13">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="AP13">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AQ13">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AS13">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AT13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU13">
+        <v>9</v>
+      </c>
+      <c r="AV13">
+        <v>12</v>
+      </c>
+      <c r="AW13">
+        <v>22</v>
+      </c>
+      <c r="AX13">
+        <v>17</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
         <v>12.5</v>
       </c>
-      <c r="AV13">
-        <v>25</v>
-      </c>
-      <c r="AW13">
-        <v>65</v>
-      </c>
-      <c r="AX13">
-        <v>11.5</v>
-      </c>
-      <c r="AY13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13">
-        <v>17</v>
-      </c>
       <c r="BA13">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="BB13">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BC13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BD13">
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BF13">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BG13">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="BH13">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>6.2</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>4.7</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK13">
-        <v>8.4</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>21</v>
-      </c>
-      <c r="BN13">
-        <v>4.6</v>
-      </c>
-      <c r="BO13">
-        <v>4.2</v>
-      </c>
-      <c r="BP13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BQ13">
-        <v>7.2</v>
-      </c>
       <c r="BR13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>5.2</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>11.5</v>
       </c>
-      <c r="BU13">
-        <v>10</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>40</v>
-      </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3937,483 +3976,483 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G14">
+        <v>1.57</v>
+      </c>
+      <c r="H14">
+        <v>5.9</v>
+      </c>
+      <c r="I14">
+        <v>7.2</v>
+      </c>
+      <c r="J14">
+        <v>4.8</v>
+      </c>
+      <c r="K14">
+        <v>5.6</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>5.7</v>
+      </c>
+      <c r="O14">
+        <v>1.16</v>
+      </c>
+      <c r="P14">
+        <v>2.62</v>
+      </c>
+      <c r="Q14">
         <v>1.48</v>
       </c>
-      <c r="H14">
-        <v>7.2</v>
-      </c>
-      <c r="I14">
-        <v>7.6</v>
-      </c>
-      <c r="J14">
-        <v>5.4</v>
-      </c>
-      <c r="K14">
-        <v>5.7</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>1.03</v>
-      </c>
-      <c r="N14">
-        <v>6.8</v>
-      </c>
-      <c r="O14">
-        <v>1.15</v>
-      </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-      <c r="Q14">
-        <v>1.46</v>
-      </c>
       <c r="R14">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="S14">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
         <v>36</v>
       </c>
       <c r="Y14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA14">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AD14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ14">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AK14">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AL14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AM14">
         <v>95</v>
       </c>
       <c r="AN14">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AO14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP14">
         <v>21</v>
       </c>
       <c r="AQ14">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="AR14">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="AS14">
-        <v>46</v>
+        <v>4.6</v>
       </c>
       <c r="AT14">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV14">
         <v>18</v>
       </c>
       <c r="AW14">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="AX14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY14">
+        <v>9</v>
+      </c>
+      <c r="AZ14">
+        <v>14</v>
+      </c>
+      <c r="BA14">
+        <v>4.5</v>
+      </c>
+      <c r="BB14">
         <v>10.5</v>
       </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
-        <v>18</v>
-      </c>
-      <c r="BA14">
-        <v>32</v>
-      </c>
-      <c r="BB14">
-        <v>12.5</v>
-      </c>
       <c r="BC14">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BD14">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BE14">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BF14">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG14">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BH14">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F15">
+        <v>2.14</v>
+      </c>
+      <c r="G15">
+        <v>2.54</v>
+      </c>
+      <c r="H15">
+        <v>2.76</v>
+      </c>
+      <c r="I15">
         <v>3.45</v>
       </c>
-      <c r="G15">
-        <v>3.5</v>
-      </c>
-      <c r="H15">
-        <v>2.28</v>
-      </c>
-      <c r="I15">
-        <v>2.3</v>
-      </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="R15">
+        <v>1.6</v>
+      </c>
+      <c r="S15">
+        <v>2.22</v>
+      </c>
+      <c r="T15">
         <v>1.47</v>
       </c>
-      <c r="S15">
-        <v>2.92</v>
-      </c>
-      <c r="T15">
-        <v>1.66</v>
-      </c>
       <c r="U15">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X15">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AO15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4421,40 +4460,40 @@
         <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F16">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="H16">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="I16">
-        <v>110</v>
+        <v>1.3</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4463,10 +4502,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4475,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4487,112 +4526,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4655,42 +4694,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F17">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="G17">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="H17">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I17">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4705,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q17">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4897,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4905,64 +4944,64 @@
         <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F18">
-        <v>3.3</v>
+        <v>1.46</v>
       </c>
       <c r="G18">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="H18">
-        <v>2.12</v>
+        <v>7.2</v>
       </c>
       <c r="I18">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P18">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="Q18">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4971,175 +5010,175 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH18">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BI18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BJ18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK18">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BM18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5147,64 +5186,64 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F19">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="G19">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="I19">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="J19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K19">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5213,482 +5252,482 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F20">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="G20">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="H20">
+        <v>1.4</v>
+      </c>
+      <c r="I20">
         <v>4.8</v>
       </c>
-      <c r="I20">
-        <v>6.2</v>
-      </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.02</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F21">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="G21">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="I21">
         <v>4.3</v>
       </c>
       <c r="J21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="Q21">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="R21">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5697,240 +5736,240 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO21">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BG21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH21">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI21">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BJ21">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK21">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM21">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP21">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BS21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BT21">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU21">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV21">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BX21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY21">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BZ21">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA21">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F22">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
-        <v>1.13</v>
+        <v>3.65</v>
       </c>
       <c r="H22">
-        <v>23</v>
+        <v>2.12</v>
       </c>
       <c r="I22">
-        <v>25</v>
+        <v>2.3</v>
       </c>
       <c r="J22">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="K22">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="R22">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -5939,240 +5978,240 @@
         <v>0</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AQ22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AR22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AU22">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AV22">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AW22">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AX22">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY22">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AZ22">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BA22">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BB22">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF22">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BG22">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BH22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BI22">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BJ22">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BK22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM22">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN22">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BO22">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP22">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BQ22">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BR22">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BS22">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT22">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BU22">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY22">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BZ22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="CA22">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F23">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="G23">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="H23">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="I23">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="J23">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K23">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R23">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6181,240 +6220,240 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BH23">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BI23">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BJ23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM23">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN23">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO23">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP23">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ23">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BR23">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BS23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BT23">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU23">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW23">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BY23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BZ23">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA23">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F24">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="G24">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="H24">
-        <v>29</v>
+        <v>4.8</v>
       </c>
       <c r="I24">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="J24">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="K24">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -6423,417 +6462,1385 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AQ24">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AR24">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AT24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AW24">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY24">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BA24">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB24">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE24">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF24">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="BG24">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ24">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25">
+        <v>1.12</v>
+      </c>
+      <c r="G25">
+        <v>1.13</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>25</v>
+      </c>
+      <c r="J25">
+        <v>14</v>
+      </c>
+      <c r="K25">
+        <v>14.5</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>17.5</v>
+      </c>
+      <c r="O25">
+        <v>1.05</v>
+      </c>
+      <c r="P25">
+        <v>6.8</v>
+      </c>
+      <c r="Q25">
+        <v>1.15</v>
+      </c>
+      <c r="R25">
+        <v>3.25</v>
+      </c>
+      <c r="S25">
+        <v>1.4</v>
+      </c>
+      <c r="T25">
+        <v>1.67</v>
+      </c>
+      <c r="U25">
+        <v>2.42</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>360</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>36</v>
+      </c>
+      <c r="AC25">
+        <v>50</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>300</v>
+      </c>
+      <c r="AF25">
+        <v>18.5</v>
+      </c>
+      <c r="AG25">
+        <v>18.5</v>
+      </c>
+      <c r="AH25">
+        <v>160</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>11.5</v>
+      </c>
+      <c r="AK25">
+        <v>14.5</v>
+      </c>
+      <c r="AL25">
+        <v>32</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1.89</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>40</v>
+      </c>
+      <c r="AQ25">
+        <v>40</v>
+      </c>
+      <c r="AR25">
+        <v>19.5</v>
+      </c>
+      <c r="AS25">
+        <v>19.5</v>
+      </c>
+      <c r="AT25">
+        <v>26</v>
+      </c>
+      <c r="AU25">
+        <v>34</v>
+      </c>
+      <c r="AV25">
+        <v>36</v>
+      </c>
+      <c r="AW25">
+        <v>19.5</v>
+      </c>
+      <c r="AX25">
+        <v>16.5</v>
+      </c>
+      <c r="AY25">
+        <v>16</v>
+      </c>
+      <c r="AZ25">
+        <v>26</v>
+      </c>
+      <c r="BA25">
+        <v>44</v>
+      </c>
+      <c r="BB25">
+        <v>10.5</v>
+      </c>
+      <c r="BC25">
+        <v>12.5</v>
+      </c>
+      <c r="BD25">
+        <v>21</v>
+      </c>
+      <c r="BE25">
+        <v>40</v>
+      </c>
+      <c r="BF25">
+        <v>1.82</v>
+      </c>
+      <c r="BG25">
+        <v>85</v>
+      </c>
+      <c r="BH25">
+        <v>11</v>
+      </c>
+      <c r="BI25">
+        <v>8</v>
+      </c>
+      <c r="BJ25">
+        <v>14.5</v>
+      </c>
+      <c r="BK25">
+        <v>10</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>55</v>
+      </c>
+      <c r="BN25">
+        <v>5.8</v>
+      </c>
+      <c r="BO25">
+        <v>4.7</v>
+      </c>
+      <c r="BP25">
+        <v>6.6</v>
+      </c>
+      <c r="BQ25">
+        <v>5.3</v>
+      </c>
+      <c r="BR25">
+        <v>17</v>
+      </c>
+      <c r="BS25">
+        <v>11.5</v>
+      </c>
+      <c r="BT25">
+        <v>26</v>
+      </c>
+      <c r="BU25">
+        <v>17</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>48</v>
+      </c>
+      <c r="BZ25">
+        <v>4.4</v>
+      </c>
+      <c r="CA25">
+        <v>3.3</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26">
+        <v>2.66</v>
+      </c>
+      <c r="G26">
+        <v>2.7</v>
+      </c>
+      <c r="H26">
+        <v>2.86</v>
+      </c>
+      <c r="I26">
+        <v>2.88</v>
+      </c>
+      <c r="J26">
+        <v>3.6</v>
+      </c>
+      <c r="K26">
+        <v>3.65</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.06</v>
+      </c>
+      <c r="N26">
+        <v>4.3</v>
+      </c>
+      <c r="O26">
+        <v>1.28</v>
+      </c>
+      <c r="P26">
+        <v>2.14</v>
+      </c>
+      <c r="Q26">
+        <v>1.83</v>
+      </c>
+      <c r="R26">
+        <v>1.45</v>
+      </c>
+      <c r="S26">
+        <v>3.05</v>
+      </c>
+      <c r="T26">
+        <v>1.68</v>
+      </c>
+      <c r="U26">
+        <v>2.4</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>16.5</v>
+      </c>
+      <c r="Y26">
+        <v>14</v>
+      </c>
+      <c r="Z26">
+        <v>21</v>
+      </c>
+      <c r="AA26">
+        <v>44</v>
+      </c>
+      <c r="AB26">
+        <v>12.5</v>
+      </c>
+      <c r="AC26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>13</v>
+      </c>
+      <c r="AE26">
+        <v>30</v>
+      </c>
+      <c r="AF26">
+        <v>18</v>
+      </c>
+      <c r="AG26">
+        <v>12.5</v>
+      </c>
+      <c r="AH26">
+        <v>15.5</v>
+      </c>
+      <c r="AI26">
+        <v>44</v>
+      </c>
+      <c r="AJ26">
+        <v>38</v>
+      </c>
+      <c r="AK26">
+        <v>28</v>
+      </c>
+      <c r="AL26">
+        <v>38</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>20</v>
+      </c>
+      <c r="AO26">
+        <v>23</v>
+      </c>
+      <c r="AP26">
+        <v>15</v>
+      </c>
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
+        <v>18</v>
+      </c>
+      <c r="AS26">
+        <v>24</v>
+      </c>
+      <c r="AT26">
+        <v>11.5</v>
+      </c>
+      <c r="AU26">
+        <v>7.6</v>
+      </c>
+      <c r="AV26">
+        <v>11.5</v>
+      </c>
+      <c r="AW26">
+        <v>18.5</v>
+      </c>
+      <c r="AX26">
+        <v>16</v>
+      </c>
+      <c r="AY26">
+        <v>11</v>
+      </c>
+      <c r="AZ26">
+        <v>14</v>
+      </c>
+      <c r="BA26">
+        <v>23</v>
+      </c>
+      <c r="BB26">
+        <v>22</v>
+      </c>
+      <c r="BC26">
+        <v>18</v>
+      </c>
+      <c r="BD26">
+        <v>23</v>
+      </c>
+      <c r="BE26">
+        <v>32</v>
+      </c>
+      <c r="BF26">
+        <v>17.5</v>
+      </c>
+      <c r="BG26">
+        <v>20</v>
+      </c>
+      <c r="BH26">
+        <v>3.7</v>
+      </c>
+      <c r="BI26">
+        <v>3.4</v>
+      </c>
+      <c r="BJ26">
+        <v>9</v>
+      </c>
+      <c r="BK26">
+        <v>8</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>65</v>
+      </c>
+      <c r="BN26">
+        <v>5.7</v>
+      </c>
+      <c r="BO26">
+        <v>5.2</v>
+      </c>
+      <c r="BP26">
+        <v>19</v>
+      </c>
+      <c r="BQ26">
+        <v>13.5</v>
+      </c>
+      <c r="BR26">
+        <v>29</v>
+      </c>
+      <c r="BS26">
+        <v>20</v>
+      </c>
+      <c r="BT26">
+        <v>6.2</v>
+      </c>
+      <c r="BU26">
+        <v>5.5</v>
+      </c>
+      <c r="BV26">
+        <v>21</v>
+      </c>
+      <c r="BW26">
+        <v>15</v>
+      </c>
+      <c r="BX26">
+        <v>30</v>
+      </c>
+      <c r="BY26">
+        <v>21</v>
+      </c>
+      <c r="BZ26">
+        <v>22</v>
+      </c>
+      <c r="CA26">
+        <v>15.5</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27">
+        <v>1.14</v>
+      </c>
+      <c r="G27">
+        <v>1.16</v>
+      </c>
+      <c r="H27">
+        <v>28</v>
+      </c>
+      <c r="I27">
+        <v>29</v>
+      </c>
+      <c r="J27">
+        <v>10.5</v>
+      </c>
+      <c r="K27">
+        <v>11</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>10.5</v>
+      </c>
+      <c r="O27">
+        <v>1.09</v>
+      </c>
+      <c r="P27">
+        <v>4.2</v>
+      </c>
+      <c r="Q27">
+        <v>1.28</v>
+      </c>
+      <c r="R27">
+        <v>2.34</v>
+      </c>
+      <c r="S27">
+        <v>1.7</v>
+      </c>
+      <c r="T27">
+        <v>2.1</v>
+      </c>
+      <c r="U27">
+        <v>1.86</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>60</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>360</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>18.5</v>
+      </c>
+      <c r="AC27">
+        <v>26</v>
+      </c>
+      <c r="AD27">
         <v>120</v>
       </c>
-      <c r="E25" t="s">
-        <v>144</v>
-      </c>
-      <c r="F25">
+      <c r="AE27">
+        <v>440</v>
+      </c>
+      <c r="AF27">
+        <v>11.5</v>
+      </c>
+      <c r="AG27">
+        <v>16.5</v>
+      </c>
+      <c r="AH27">
+        <v>50</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>9.4</v>
+      </c>
+      <c r="AK27">
+        <v>14.5</v>
+      </c>
+      <c r="AL27">
+        <v>44</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>2.3</v>
+      </c>
+      <c r="AO27">
+        <v>440</v>
+      </c>
+      <c r="AP27">
+        <v>28</v>
+      </c>
+      <c r="AQ27">
+        <v>40</v>
+      </c>
+      <c r="AR27">
+        <v>55</v>
+      </c>
+      <c r="AS27">
+        <v>17</v>
+      </c>
+      <c r="AT27">
+        <v>16</v>
+      </c>
+      <c r="AU27">
+        <v>22</v>
+      </c>
+      <c r="AV27">
+        <v>38</v>
+      </c>
+      <c r="AW27">
+        <v>55</v>
+      </c>
+      <c r="AX27">
+        <v>10</v>
+      </c>
+      <c r="AY27">
+        <v>14</v>
+      </c>
+      <c r="AZ27">
+        <v>25</v>
+      </c>
+      <c r="BA27">
+        <v>50</v>
+      </c>
+      <c r="BB27">
+        <v>8.6</v>
+      </c>
+      <c r="BC27">
+        <v>12.5</v>
+      </c>
+      <c r="BD27">
+        <v>25</v>
+      </c>
+      <c r="BE27">
+        <v>44</v>
+      </c>
+      <c r="BF27">
+        <v>2.22</v>
+      </c>
+      <c r="BG27">
+        <v>65</v>
+      </c>
+      <c r="BH27">
+        <v>7.8</v>
+      </c>
+      <c r="BI27">
+        <v>5.4</v>
+      </c>
+      <c r="BJ27">
+        <v>16.5</v>
+      </c>
+      <c r="BK27">
+        <v>11</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>4.8</v>
+      </c>
+      <c r="BO27">
+        <v>3.45</v>
+      </c>
+      <c r="BP27">
+        <v>6.4</v>
+      </c>
+      <c r="BQ27">
+        <v>4.4</v>
+      </c>
+      <c r="BR27">
+        <v>22</v>
+      </c>
+      <c r="BS27">
+        <v>14</v>
+      </c>
+      <c r="BT27">
+        <v>26</v>
+      </c>
+      <c r="BU27">
+        <v>16.5</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>110</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>5.9</v>
+      </c>
+      <c r="CA27">
+        <v>4.1</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28">
+        <v>1.9</v>
+      </c>
+      <c r="G28">
+        <v>1.91</v>
+      </c>
+      <c r="H28">
+        <v>4.2</v>
+      </c>
+      <c r="I28">
+        <v>4.3</v>
+      </c>
+      <c r="J28">
+        <v>4.1</v>
+      </c>
+      <c r="K28">
+        <v>4.2</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>1.04</v>
+      </c>
+      <c r="N28">
+        <v>5.5</v>
+      </c>
+      <c r="O28">
+        <v>1.21</v>
+      </c>
+      <c r="P28">
+        <v>2.54</v>
+      </c>
+      <c r="Q28">
+        <v>1.62</v>
+      </c>
+      <c r="R28">
+        <v>1.61</v>
+      </c>
+      <c r="S28">
+        <v>2.48</v>
+      </c>
+      <c r="T28">
+        <v>1.6</v>
+      </c>
+      <c r="U28">
+        <v>2.6</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>25</v>
+      </c>
+      <c r="Y28">
+        <v>23</v>
+      </c>
+      <c r="Z28">
+        <v>36</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>13</v>
+      </c>
+      <c r="AC28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD28">
+        <v>17.5</v>
+      </c>
+      <c r="AE28">
+        <v>46</v>
+      </c>
+      <c r="AF28">
+        <v>14.5</v>
+      </c>
+      <c r="AG28">
+        <v>10.5</v>
+      </c>
+      <c r="AH28">
+        <v>16</v>
+      </c>
+      <c r="AI28">
+        <v>46</v>
+      </c>
+      <c r="AJ28">
+        <v>23</v>
+      </c>
+      <c r="AK28">
+        <v>18</v>
+      </c>
+      <c r="AL28">
+        <v>28</v>
+      </c>
+      <c r="AM28">
+        <v>65</v>
+      </c>
+      <c r="AN28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO28">
+        <v>34</v>
+      </c>
+      <c r="AP28">
+        <v>20</v>
+      </c>
+      <c r="AQ28">
+        <v>18</v>
+      </c>
+      <c r="AR28">
+        <v>22</v>
+      </c>
+      <c r="AS28">
+        <v>36</v>
+      </c>
+      <c r="AT28">
+        <v>11.5</v>
+      </c>
+      <c r="AU28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV28">
+        <v>15.5</v>
+      </c>
+      <c r="AW28">
+        <v>34</v>
+      </c>
+      <c r="AX28">
+        <v>12.5</v>
+      </c>
+      <c r="AY28">
+        <v>9.6</v>
+      </c>
+      <c r="AZ28">
+        <v>13.5</v>
+      </c>
+      <c r="BA28">
+        <v>25</v>
+      </c>
+      <c r="BB28">
+        <v>19</v>
+      </c>
+      <c r="BC28">
+        <v>15</v>
+      </c>
+      <c r="BD28">
+        <v>18</v>
+      </c>
+      <c r="BE28">
+        <v>30</v>
+      </c>
+      <c r="BF28">
+        <v>7.8</v>
+      </c>
+      <c r="BG28">
+        <v>21</v>
+      </c>
+      <c r="BH28">
+        <v>4.2</v>
+      </c>
+      <c r="BI28">
+        <v>3.8</v>
+      </c>
+      <c r="BJ28">
+        <v>9</v>
+      </c>
+      <c r="BK28">
+        <v>7.8</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>55</v>
+      </c>
+      <c r="BN28">
+        <v>5</v>
+      </c>
+      <c r="BO28">
+        <v>4.6</v>
+      </c>
+      <c r="BP28">
+        <v>13</v>
+      </c>
+      <c r="BQ28">
+        <v>11</v>
+      </c>
+      <c r="BR28">
+        <v>23</v>
+      </c>
+      <c r="BS28">
+        <v>15.5</v>
+      </c>
+      <c r="BT28">
+        <v>7.6</v>
+      </c>
+      <c r="BU28">
+        <v>6.8</v>
+      </c>
+      <c r="BV28">
+        <v>30</v>
+      </c>
+      <c r="BW28">
+        <v>20</v>
+      </c>
+      <c r="BX28">
+        <v>36</v>
+      </c>
+      <c r="BY28">
+        <v>23</v>
+      </c>
+      <c r="BZ28">
+        <v>16.5</v>
+      </c>
+      <c r="CA28">
+        <v>11</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29">
         <v>5.3</v>
       </c>
-      <c r="G25">
-        <v>5.7</v>
-      </c>
-      <c r="H25">
-        <v>1.75</v>
-      </c>
-      <c r="I25">
+      <c r="G29">
+        <v>6.2</v>
+      </c>
+      <c r="H29">
+        <v>1.73</v>
+      </c>
+      <c r="I29">
         <v>1.81</v>
       </c>
-      <c r="J25">
+      <c r="J29">
         <v>3.85</v>
       </c>
-      <c r="K25">
+      <c r="K29">
         <v>3.95</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>1.94</v>
       </c>
-      <c r="Q25">
-        <v>2</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-      <c r="BF25">
-        <v>0</v>
-      </c>
-      <c r="BG25">
-        <v>0</v>
-      </c>
-      <c r="BH25">
-        <v>0</v>
-      </c>
-      <c r="BI25">
-        <v>0</v>
-      </c>
-      <c r="BJ25">
-        <v>0</v>
-      </c>
-      <c r="BK25">
-        <v>0</v>
-      </c>
-      <c r="BL25">
-        <v>0</v>
-      </c>
-      <c r="BM25">
-        <v>0</v>
-      </c>
-      <c r="BN25">
-        <v>0</v>
-      </c>
-      <c r="BO25">
-        <v>0</v>
-      </c>
-      <c r="BP25">
-        <v>0</v>
-      </c>
-      <c r="BQ25">
-        <v>0</v>
-      </c>
-      <c r="BR25">
-        <v>0</v>
-      </c>
-      <c r="BS25">
-        <v>0</v>
-      </c>
-      <c r="BT25">
-        <v>0</v>
-      </c>
-      <c r="BU25">
-        <v>0</v>
-      </c>
-      <c r="BV25">
-        <v>0</v>
-      </c>
-      <c r="BW25">
-        <v>0</v>
-      </c>
-      <c r="BX25">
-        <v>0</v>
-      </c>
-      <c r="BY25">
-        <v>0</v>
-      </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CA25">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>145</v>
+      <c r="Q29">
+        <v>2.02</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
+      </c>
+      <c r="BQ29">
+        <v>0</v>
+      </c>
+      <c r="BR29">
+        <v>0</v>
+      </c>
+      <c r="BS29">
+        <v>0</v>
+      </c>
+      <c r="BT29">
+        <v>0</v>
+      </c>
+      <c r="BU29">
+        <v>0</v>
+      </c>
+      <c r="BV29">
+        <v>0</v>
+      </c>
+      <c r="BW29">
+        <v>0</v>
+      </c>
+      <c r="BX29">
+        <v>0</v>
+      </c>
+      <c r="BY29">
+        <v>0</v>
+      </c>
+      <c r="BZ29">
+        <v>0</v>
+      </c>
+      <c r="CA29">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
   <si>
     <t>League</t>
   </si>
@@ -274,15 +274,24 @@
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
     <t>UEFA Champions League</t>
   </si>
   <si>
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
@@ -307,6 +316,9 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>16:15:00</t>
   </si>
   <si>
@@ -316,6 +328,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -364,12 +379,15 @@
     <t>Al Shamal</t>
   </si>
   <si>
+    <t>SK Super Nova</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
     <t>Al Sailiya</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
     <t>PSV</t>
   </si>
   <si>
@@ -379,6 +397,9 @@
     <t>Gagra</t>
   </si>
   <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Falkenbergs</t>
   </si>
   <si>
@@ -391,6 +412,9 @@
     <t>Ostersunds FK</t>
   </si>
   <si>
+    <t>Enkopings SK</t>
+  </si>
+  <si>
     <t>Bayern Munich</t>
   </si>
   <si>
@@ -448,12 +472,15 @@
     <t>Al-Wakra</t>
   </si>
   <si>
+    <t>FK Tukums 2000</t>
+  </si>
+  <si>
+    <t>Al Wasl</t>
+  </si>
+  <si>
     <t>Al-Sadd</t>
   </si>
   <si>
-    <t>Al Wasl</t>
-  </si>
-  <si>
     <t>Shakhtar</t>
   </si>
   <si>
@@ -463,6 +490,9 @@
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
+    <t>Crvena Zvezda</t>
+  </si>
+  <si>
     <t>Osters</t>
   </si>
   <si>
@@ -475,6 +505,9 @@
     <t>IK Brage</t>
   </si>
   <si>
+    <t>Assyriska FF</t>
+  </si>
+  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
@@ -490,7 +523,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 12:57:50</t>
+    <t>2026-09-08 15:11:13</t>
   </si>
 </sst>
 </file>
@@ -822,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1072,25 +1105,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I2">
         <v>3.2</v>
@@ -1099,7 +1132,7 @@
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -1129,31 +1162,31 @@
         <v>1.63</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V2">
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z2">
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB2">
         <v>13</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -1189,7 +1222,7 @@
         <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP2">
         <v>17</v>
@@ -1213,28 +1246,28 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC2">
         <v>19</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE2">
         <v>44</v>
@@ -1264,7 +1297,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
         <v>4.4</v>
@@ -1306,7 +1339,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1314,16 +1347,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>1.87</v>
@@ -1350,16 +1383,16 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.26</v>
@@ -1548,7 +1581,7 @@
         <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1556,16 +1589,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F4">
         <v>2.32</v>
@@ -1790,7 +1823,7 @@
         <v>1.64</v>
       </c>
       <c r="CB4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1798,16 +1831,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>2.14</v>
@@ -1873,7 +1906,7 @@
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1909,7 +1942,7 @@
         <v>28</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="AN5">
         <v>10</v>
@@ -1924,10 +1957,10 @@
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT5">
         <v>13</v>
@@ -1939,7 +1972,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1951,16 +1984,16 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE5">
         <v>34</v>
@@ -1969,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH5">
         <v>4.5</v>
@@ -1978,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
         <v>7.4</v>
@@ -2032,7 +2065,7 @@
         <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2040,16 +2073,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>2.62</v>
@@ -2142,16 +2175,16 @@
         <v>120</v>
       </c>
       <c r="AJ6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK6">
         <v>36</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
         <v>24</v>
@@ -2169,7 +2202,7 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2181,7 +2214,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX6">
         <v>15</v>
@@ -2190,22 +2223,22 @@
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BC6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BF6">
         <v>20</v>
@@ -2274,7 +2307,7 @@
         <v>2.06</v>
       </c>
       <c r="CB6" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2282,22 +2315,22 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F7">
         <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H7">
         <v>4.5</v>
@@ -2381,7 +2414,7 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2414,7 +2447,7 @@
         <v>60</v>
       </c>
       <c r="AT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7">
         <v>8.6</v>
@@ -2516,7 +2549,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2524,28 +2557,28 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
         <v>2.26</v>
       </c>
       <c r="H8">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J8">
         <v>4.4</v>
@@ -2560,10 +2593,10 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P8">
         <v>4.2</v>
@@ -2575,34 +2608,34 @@
         <v>2.34</v>
       </c>
       <c r="S8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T8">
         <v>1.32</v>
       </c>
       <c r="U8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="V8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
         <v>1.79</v>
       </c>
       <c r="X8">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="Y8">
         <v>38</v>
       </c>
       <c r="Z8">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AA8">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC8">
         <v>14.5</v>
@@ -2614,22 +2647,22 @@
         <v>27</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
         <v>38</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL8">
         <v>21</v>
@@ -2638,7 +2671,7 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO8">
         <v>10</v>
@@ -2647,16 +2680,16 @@
         <v>32</v>
       </c>
       <c r="AQ8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS8">
         <v>34</v>
       </c>
       <c r="AT8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AU8">
         <v>12</v>
@@ -2665,10 +2698,10 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX8">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2677,10 +2710,10 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2689,13 +2722,13 @@
         <v>17.5</v>
       </c>
       <c r="BE8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2758,7 +2791,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2766,16 +2799,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -3000,7 +3033,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3008,16 +3041,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F10">
         <v>1.45</v>
@@ -3146,7 +3179,7 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AW10">
         <v>48</v>
@@ -3242,7 +3275,7 @@
         <v>6.8</v>
       </c>
       <c r="CB10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3250,16 +3283,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F11">
         <v>1.45</v>
@@ -3286,28 +3319,28 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O11">
         <v>1.13</v>
       </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R11">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3316,7 +3349,7 @@
         <v>3.1</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Y11">
         <v>46</v>
@@ -3328,106 +3361,106 @@
         <v>1000</v>
       </c>
       <c r="AB11">
+        <v>17</v>
+      </c>
+      <c r="AC11">
         <v>14.5</v>
       </c>
-      <c r="AC11">
-        <v>14</v>
-      </c>
       <c r="AD11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>410</v>
       </c>
       <c r="AJ11">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL11">
         <v>23</v>
       </c>
       <c r="AM11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AO11">
-        <v>760</v>
+        <v>400</v>
       </c>
       <c r="AP11">
         <v>32</v>
       </c>
       <c r="AQ11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR11">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AS11">
         <v>48</v>
       </c>
       <c r="AT11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW11">
         <v>34</v>
       </c>
       <c r="AX11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC11">
         <v>12</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF11">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BG11">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BH11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ11">
         <v>9.6</v>
@@ -3457,7 +3490,7 @@
         <v>17</v>
       </c>
       <c r="BS11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT11">
         <v>11.5</v>
@@ -3478,13 +3511,13 @@
         <v>34</v>
       </c>
       <c r="BZ11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA11">
         <v>7.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3492,16 +3525,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F12">
         <v>1.82</v>
@@ -3558,7 +3591,7 @@
         <v>2.14</v>
       </c>
       <c r="X12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y12">
         <v>29</v>
@@ -3606,7 +3639,7 @@
         <v>170</v>
       </c>
       <c r="AN12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO12">
         <v>25</v>
@@ -3615,10 +3648,10 @@
         <v>23</v>
       </c>
       <c r="AQ12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AS12">
         <v>34</v>
@@ -3633,7 +3666,7 @@
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3645,7 +3678,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB12">
         <v>16</v>
@@ -3657,7 +3690,7 @@
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF12">
         <v>6</v>
@@ -3726,7 +3759,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3734,25 +3767,25 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F13">
         <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I13">
         <v>3.05</v>
@@ -3770,7 +3803,7 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O13">
         <v>1.18</v>
@@ -3797,7 +3830,7 @@
         <v>1.49</v>
       </c>
       <c r="W13">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X13">
         <v>27</v>
@@ -3854,7 +3887,7 @@
         <v>16.5</v>
       </c>
       <c r="AP13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ13">
         <v>16.5</v>
@@ -3863,7 +3896,7 @@
         <v>21</v>
       </c>
       <c r="AS13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT13">
         <v>14.5</v>
@@ -3875,7 +3908,7 @@
         <v>12</v>
       </c>
       <c r="AW13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX13">
         <v>17</v>
@@ -3890,7 +3923,7 @@
         <v>24</v>
       </c>
       <c r="BB13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC13">
         <v>19</v>
@@ -3899,7 +3932,7 @@
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -3968,7 +4001,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3976,16 +4009,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F14">
         <v>1.47</v>
@@ -4210,7 +4243,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4218,16 +4251,16 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F15">
         <v>2.14</v>
@@ -4266,7 +4299,7 @@
         <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S15">
         <v>2.22</v>
@@ -4278,7 +4311,7 @@
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.65</v>
@@ -4452,249 +4485,249 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="G16">
-        <v>16.5</v>
+        <v>190</v>
       </c>
       <c r="H16">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="I16">
-        <v>1.3</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="K16">
-        <v>9.6</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4702,16 +4735,16 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F17">
         <v>1.68</v>
@@ -4732,16 +4765,16 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P17">
         <v>2.52</v>
@@ -4750,677 +4783,677 @@
         <v>1.52</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F18">
-        <v>1.46</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>1.48</v>
+        <v>14</v>
       </c>
       <c r="H18">
-        <v>7.2</v>
+        <v>1.26</v>
       </c>
       <c r="I18">
-        <v>7.6</v>
+        <v>1.31</v>
       </c>
       <c r="J18">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="K18">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="P18">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="Q18">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="R18">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S18">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F19">
-        <v>3.5</v>
+        <v>1.46</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="H19">
-        <v>2.26</v>
+        <v>7.4</v>
       </c>
       <c r="I19">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N19">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P19">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="R19">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="S19">
-        <v>2.92</v>
+        <v>2.16</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X19">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="Y19">
+        <v>36</v>
+      </c>
+      <c r="Z19">
+        <v>75</v>
+      </c>
+      <c r="AA19">
+        <v>210</v>
+      </c>
+      <c r="AB19">
+        <v>13.5</v>
+      </c>
+      <c r="AC19">
+        <v>13.5</v>
+      </c>
+      <c r="AD19">
+        <v>27</v>
+      </c>
+      <c r="AE19">
+        <v>110</v>
+      </c>
+      <c r="AF19">
         <v>12</v>
       </c>
-      <c r="Z19">
-        <v>15.5</v>
-      </c>
-      <c r="AA19">
-        <v>29</v>
-      </c>
-      <c r="AB19">
-        <v>16</v>
-      </c>
-      <c r="AC19">
-        <v>8</v>
-      </c>
-      <c r="AD19">
-        <v>11</v>
-      </c>
-      <c r="AE19">
+      <c r="AG19">
+        <v>10.5</v>
+      </c>
+      <c r="AH19">
+        <v>21</v>
+      </c>
+      <c r="AI19">
+        <v>70</v>
+      </c>
+      <c r="AJ19">
+        <v>14</v>
+      </c>
+      <c r="AK19">
+        <v>14</v>
+      </c>
+      <c r="AL19">
+        <v>25</v>
+      </c>
+      <c r="AM19">
+        <v>80</v>
+      </c>
+      <c r="AN19">
+        <v>4.7</v>
+      </c>
+      <c r="AO19">
+        <v>65</v>
+      </c>
+      <c r="AP19">
+        <v>27</v>
+      </c>
+      <c r="AQ19">
+        <v>32</v>
+      </c>
+      <c r="AR19">
+        <v>60</v>
+      </c>
+      <c r="AS19">
+        <v>46</v>
+      </c>
+      <c r="AT19">
+        <v>12</v>
+      </c>
+      <c r="AU19">
+        <v>12</v>
+      </c>
+      <c r="AV19">
+        <v>24</v>
+      </c>
+      <c r="AW19">
+        <v>34</v>
+      </c>
+      <c r="AX19">
+        <v>10.5</v>
+      </c>
+      <c r="AY19">
+        <v>9.6</v>
+      </c>
+      <c r="AZ19">
+        <v>18</v>
+      </c>
+      <c r="BA19">
+        <v>55</v>
+      </c>
+      <c r="BB19">
+        <v>13</v>
+      </c>
+      <c r="BC19">
+        <v>12</v>
+      </c>
+      <c r="BD19">
         <v>22</v>
       </c>
-      <c r="AF19">
-        <v>27</v>
-      </c>
-      <c r="AG19">
-        <v>14.5</v>
-      </c>
-      <c r="AH19">
-        <v>15.5</v>
-      </c>
-      <c r="AI19">
+      <c r="BE19">
         <v>34</v>
       </c>
-      <c r="AJ19">
-        <v>590</v>
-      </c>
-      <c r="AK19">
-        <v>38</v>
-      </c>
-      <c r="AL19">
-        <v>44</v>
-      </c>
-      <c r="AM19">
-        <v>85</v>
-      </c>
-      <c r="AN19">
+      <c r="BF19">
+        <v>4.4</v>
+      </c>
+      <c r="BG19">
+        <v>50</v>
+      </c>
+      <c r="BH19">
+        <v>5.9</v>
+      </c>
+      <c r="BI19">
+        <v>4.5</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>8.6</v>
+      </c>
+      <c r="BL19">
+        <v>110</v>
+      </c>
+      <c r="BM19">
+        <v>22</v>
+      </c>
+      <c r="BN19">
+        <v>5.3</v>
+      </c>
+      <c r="BO19">
+        <v>4</v>
+      </c>
+      <c r="BP19">
+        <v>10.5</v>
+      </c>
+      <c r="BQ19">
+        <v>7.6</v>
+      </c>
+      <c r="BR19">
+        <v>22</v>
+      </c>
+      <c r="BS19">
+        <v>13</v>
+      </c>
+      <c r="BT19">
+        <v>13.5</v>
+      </c>
+      <c r="BU19">
+        <v>9.4</v>
+      </c>
+      <c r="BV19">
+        <v>60</v>
+      </c>
+      <c r="BW19">
+        <v>34</v>
+      </c>
+      <c r="BX19">
+        <v>55</v>
+      </c>
+      <c r="BY19">
         <v>32</v>
       </c>
-      <c r="AO19">
-        <v>13</v>
-      </c>
-      <c r="AP19">
-        <v>15.5</v>
-      </c>
-      <c r="AQ19">
-        <v>11</v>
-      </c>
-      <c r="AR19">
-        <v>14</v>
-      </c>
-      <c r="AS19">
-        <v>25</v>
-      </c>
-      <c r="AT19">
-        <v>14.5</v>
-      </c>
-      <c r="AU19">
+      <c r="BZ19">
+        <v>12.5</v>
+      </c>
+      <c r="CA19">
         <v>7.4</v>
       </c>
-      <c r="AV19">
-        <v>10</v>
-      </c>
-      <c r="AW19">
-        <v>20</v>
-      </c>
-      <c r="AX19">
-        <v>24</v>
-      </c>
-      <c r="AY19">
-        <v>13</v>
-      </c>
-      <c r="AZ19">
-        <v>13.5</v>
-      </c>
-      <c r="BA19">
-        <v>30</v>
-      </c>
-      <c r="BB19">
-        <v>50</v>
-      </c>
-      <c r="BC19">
-        <v>30</v>
-      </c>
-      <c r="BD19">
-        <v>36</v>
-      </c>
-      <c r="BE19">
-        <v>50</v>
-      </c>
-      <c r="BF19">
-        <v>27</v>
-      </c>
-      <c r="BG19">
-        <v>12</v>
-      </c>
-      <c r="BH19">
-        <v>3.65</v>
-      </c>
-      <c r="BI19">
-        <v>3.35</v>
-      </c>
-      <c r="BJ19">
-        <v>11</v>
-      </c>
-      <c r="BK19">
-        <v>7.8</v>
-      </c>
-      <c r="BL19">
-        <v>120</v>
-      </c>
-      <c r="BM19">
-        <v>65</v>
-      </c>
-      <c r="BN19">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO19">
-        <v>6</v>
-      </c>
-      <c r="BP19">
-        <v>32</v>
-      </c>
-      <c r="BQ19">
-        <v>18.5</v>
-      </c>
-      <c r="BR19">
-        <v>42</v>
-      </c>
-      <c r="BS19">
-        <v>24</v>
-      </c>
-      <c r="BT19">
-        <v>6.2</v>
-      </c>
-      <c r="BU19">
-        <v>4.7</v>
-      </c>
-      <c r="BV19">
-        <v>19</v>
-      </c>
-      <c r="BW19">
-        <v>11.5</v>
-      </c>
-      <c r="BX19">
-        <v>34</v>
-      </c>
-      <c r="BY19">
-        <v>19.5</v>
-      </c>
-      <c r="BZ19">
-        <v>26</v>
-      </c>
-      <c r="CA19">
-        <v>15.5</v>
-      </c>
       <c r="CB19" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5428,241 +5461,241 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20">
+        <v>3.5</v>
+      </c>
+      <c r="G20">
+        <v>3.6</v>
+      </c>
+      <c r="H20">
+        <v>2.26</v>
+      </c>
+      <c r="I20">
+        <v>2.28</v>
+      </c>
+      <c r="J20">
+        <v>3.6</v>
+      </c>
+      <c r="K20">
+        <v>3.65</v>
+      </c>
+      <c r="L20">
+        <v>1.33</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
+        <v>4.6</v>
+      </c>
+      <c r="O20">
+        <v>1.26</v>
+      </c>
+      <c r="P20">
+        <v>2.26</v>
+      </c>
+      <c r="Q20">
+        <v>1.78</v>
+      </c>
+      <c r="R20">
+        <v>1.47</v>
+      </c>
+      <c r="S20">
+        <v>2.92</v>
+      </c>
+      <c r="T20">
+        <v>1.65</v>
+      </c>
+      <c r="U20">
+        <v>2.42</v>
+      </c>
+      <c r="V20">
+        <v>1.78</v>
+      </c>
+      <c r="W20">
+        <v>1.38</v>
+      </c>
+      <c r="X20">
+        <v>17</v>
+      </c>
+      <c r="Y20">
+        <v>12</v>
+      </c>
+      <c r="Z20">
+        <v>15.5</v>
+      </c>
+      <c r="AA20">
+        <v>28</v>
+      </c>
+      <c r="AB20">
+        <v>16</v>
+      </c>
+      <c r="AC20">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>11</v>
+      </c>
+      <c r="AE20">
+        <v>22</v>
+      </c>
+      <c r="AF20">
+        <v>26</v>
+      </c>
+      <c r="AG20">
+        <v>14</v>
+      </c>
+      <c r="AH20">
+        <v>15.5</v>
+      </c>
+      <c r="AI20">
+        <v>32</v>
+      </c>
+      <c r="AJ20">
+        <v>630</v>
+      </c>
+      <c r="AK20">
+        <v>36</v>
+      </c>
+      <c r="AL20">
+        <v>42</v>
+      </c>
+      <c r="AM20">
+        <v>85</v>
+      </c>
+      <c r="AN20">
+        <v>30</v>
+      </c>
+      <c r="AO20">
+        <v>13</v>
+      </c>
+      <c r="AP20">
+        <v>16</v>
+      </c>
+      <c r="AQ20">
+        <v>11.5</v>
+      </c>
+      <c r="AR20">
+        <v>14</v>
+      </c>
+      <c r="AS20">
+        <v>26</v>
+      </c>
+      <c r="AT20">
+        <v>15.5</v>
+      </c>
+      <c r="AU20">
+        <v>7.6</v>
+      </c>
+      <c r="AV20">
+        <v>10</v>
+      </c>
+      <c r="AW20">
+        <v>20</v>
+      </c>
+      <c r="AX20">
+        <v>24</v>
+      </c>
+      <c r="AY20">
+        <v>13</v>
+      </c>
+      <c r="AZ20">
+        <v>14.5</v>
+      </c>
+      <c r="BA20">
+        <v>29</v>
+      </c>
+      <c r="BB20">
+        <v>50</v>
+      </c>
+      <c r="BC20">
+        <v>32</v>
+      </c>
+      <c r="BD20">
+        <v>38</v>
+      </c>
+      <c r="BE20">
+        <v>60</v>
+      </c>
+      <c r="BF20">
+        <v>27</v>
+      </c>
+      <c r="BG20">
+        <v>12.5</v>
+      </c>
+      <c r="BH20">
+        <v>3.65</v>
+      </c>
+      <c r="BI20">
+        <v>3.35</v>
+      </c>
+      <c r="BJ20">
+        <v>11.5</v>
+      </c>
+      <c r="BK20">
+        <v>7.8</v>
+      </c>
+      <c r="BL20">
         <v>120</v>
       </c>
-      <c r="E20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F20">
-        <v>2.2</v>
-      </c>
-      <c r="G20">
-        <v>1000</v>
-      </c>
-      <c r="H20">
-        <v>1.4</v>
-      </c>
-      <c r="I20">
-        <v>4.8</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-      <c r="K20">
-        <v>950</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.01</v>
-      </c>
-      <c r="N20">
-        <v>1.24</v>
-      </c>
-      <c r="O20">
-        <v>1.01</v>
-      </c>
-      <c r="P20">
-        <v>1.24</v>
-      </c>
-      <c r="Q20">
-        <v>1.02</v>
-      </c>
-      <c r="R20">
-        <v>1.18</v>
-      </c>
-      <c r="S20">
-        <v>1.02</v>
-      </c>
-      <c r="T20">
-        <v>1.01</v>
-      </c>
-      <c r="U20">
-        <v>1.01</v>
-      </c>
-      <c r="V20">
-        <v>1.26</v>
-      </c>
-      <c r="W20">
-        <v>1.01</v>
-      </c>
-      <c r="X20">
-        <v>1000</v>
-      </c>
-      <c r="Y20">
-        <v>1000</v>
-      </c>
-      <c r="Z20">
-        <v>1000</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>1000</v>
-      </c>
-      <c r="AC20">
-        <v>1000</v>
-      </c>
-      <c r="AD20">
-        <v>1000</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
-      <c r="AG20">
-        <v>1000</v>
-      </c>
-      <c r="AH20">
-        <v>1000</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>1000</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>1.03</v>
-      </c>
-      <c r="AQ20">
-        <v>1.03</v>
-      </c>
-      <c r="AR20">
-        <v>1.03</v>
-      </c>
-      <c r="AS20">
-        <v>1.03</v>
-      </c>
-      <c r="AT20">
-        <v>1.03</v>
-      </c>
-      <c r="AU20">
-        <v>1.03</v>
-      </c>
-      <c r="AV20">
-        <v>1.03</v>
-      </c>
-      <c r="AW20">
-        <v>1.03</v>
-      </c>
-      <c r="AX20">
-        <v>1.03</v>
-      </c>
-      <c r="AY20">
-        <v>1.03</v>
-      </c>
-      <c r="AZ20">
-        <v>1.03</v>
-      </c>
-      <c r="BA20">
-        <v>1.03</v>
-      </c>
-      <c r="BB20">
-        <v>1.03</v>
-      </c>
-      <c r="BC20">
-        <v>1.03</v>
-      </c>
-      <c r="BD20">
-        <v>1.03</v>
-      </c>
-      <c r="BE20">
-        <v>1.03</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>1.01</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5670,1038 +5703,1038 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F21">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="H21">
+        <v>1.45</v>
+      </c>
+      <c r="I21">
+        <v>4.5</v>
+      </c>
+      <c r="J21">
+        <v>3.1</v>
+      </c>
+      <c r="K21">
         <v>3.85</v>
       </c>
-      <c r="I21">
-        <v>4.3</v>
-      </c>
-      <c r="J21">
-        <v>4</v>
-      </c>
-      <c r="K21">
-        <v>4.4</v>
-      </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="G22">
-        <v>3.65</v>
+        <v>210</v>
       </c>
       <c r="H22">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="I22">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="J22">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P22">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q22">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23">
+        <v>1.86</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>3.85</v>
+      </c>
+      <c r="I23">
+        <v>4.3</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4.4</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>2.42</v>
+      </c>
+      <c r="O23">
+        <v>1.16</v>
+      </c>
+      <c r="P23">
+        <v>2.42</v>
+      </c>
+      <c r="Q23">
+        <v>1.58</v>
+      </c>
+      <c r="R23">
+        <v>1.54</v>
+      </c>
+      <c r="S23">
+        <v>1.01</v>
+      </c>
+      <c r="T23">
+        <v>1.01</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.3</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>40</v>
+      </c>
+      <c r="AA23">
         <v>90</v>
       </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" t="s">
-        <v>151</v>
-      </c>
-      <c r="F23">
-        <v>3.8</v>
-      </c>
-      <c r="G23">
-        <v>4.8</v>
-      </c>
-      <c r="H23">
-        <v>1.93</v>
-      </c>
-      <c r="I23">
-        <v>2.14</v>
-      </c>
-      <c r="J23">
-        <v>3.7</v>
-      </c>
-      <c r="K23">
-        <v>4.2</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>1.98</v>
-      </c>
-      <c r="Q23">
-        <v>1.8</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24">
+        <v>3.35</v>
+      </c>
+      <c r="G24">
+        <v>3.6</v>
+      </c>
+      <c r="H24">
+        <v>2.14</v>
+      </c>
+      <c r="I24">
+        <v>2.24</v>
+      </c>
+      <c r="J24">
+        <v>3.75</v>
+      </c>
+      <c r="K24">
+        <v>4.1</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24">
+        <v>1.23</v>
+      </c>
+      <c r="P24">
+        <v>2.28</v>
+      </c>
+      <c r="Q24">
+        <v>1.63</v>
+      </c>
+      <c r="R24">
+        <v>1.43</v>
+      </c>
+      <c r="S24">
+        <v>2.68</v>
+      </c>
+      <c r="T24">
+        <v>1.6</v>
+      </c>
+      <c r="U24">
+        <v>2.22</v>
+      </c>
+      <c r="V24">
+        <v>1.8</v>
+      </c>
+      <c r="W24">
+        <v>1.38</v>
+      </c>
+      <c r="X24">
+        <v>22</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>19.5</v>
+      </c>
+      <c r="AA24">
+        <v>34</v>
+      </c>
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>9.6</v>
+      </c>
+      <c r="AD24">
+        <v>21</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>34</v>
+      </c>
+      <c r="AG24">
+        <v>18.5</v>
+      </c>
+      <c r="AH24">
+        <v>20</v>
+      </c>
+      <c r="AI24">
+        <v>38</v>
+      </c>
+      <c r="AJ24">
+        <v>80</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
         <v>90</v>
       </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24">
-        <v>1.71</v>
-      </c>
-      <c r="G24">
-        <v>1.83</v>
-      </c>
-      <c r="H24">
-        <v>4.8</v>
-      </c>
-      <c r="I24">
-        <v>5.4</v>
-      </c>
-      <c r="J24">
-        <v>3.95</v>
-      </c>
-      <c r="K24">
-        <v>4.4</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>2.02</v>
-      </c>
-      <c r="Q24">
-        <v>1.67</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
       <c r="AN24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F25">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="G25">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="H25">
-        <v>23</v>
+        <v>1.93</v>
       </c>
       <c r="I25">
-        <v>25</v>
+        <v>2.14</v>
       </c>
       <c r="J25">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="K25">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>17.5</v>
+        <v>3.3</v>
       </c>
       <c r="O25">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>6.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q25">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="R25">
-        <v>3.25</v>
+        <v>1.34</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>2.96</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6710,148 +6743,148 @@
         <v>1000</v>
       </c>
       <c r="Z25">
-        <v>360</v>
+        <v>17</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AC25">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AD25">
         <v>1000</v>
       </c>
       <c r="AE25">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AG25">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AH25">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ25">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP25">
-        <v>40</v>
+        <v>1.54</v>
       </c>
       <c r="AQ25">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="AR25">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS25">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AT25">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AU25">
-        <v>34</v>
+        <v>1.35</v>
       </c>
       <c r="AV25">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="AW25">
-        <v>19.5</v>
+        <v>1.54</v>
       </c>
       <c r="AX25">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AY25">
-        <v>16</v>
+        <v>1.44</v>
       </c>
       <c r="AZ25">
-        <v>26</v>
+        <v>1.54</v>
       </c>
       <c r="BA25">
-        <v>44</v>
+        <v>1.49</v>
       </c>
       <c r="BB25">
-        <v>10.5</v>
+        <v>1.54</v>
       </c>
       <c r="BC25">
-        <v>12.5</v>
+        <v>1.54</v>
       </c>
       <c r="BD25">
-        <v>21</v>
+        <v>1.54</v>
       </c>
       <c r="BE25">
-        <v>40</v>
+        <v>1.54</v>
       </c>
       <c r="BF25">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="BG25">
-        <v>85</v>
+        <v>1.41</v>
       </c>
       <c r="BH25">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="BI25">
-        <v>8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ25">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN25">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP25">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR25">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT25">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BV25">
         <v>1000</v>
@@ -6863,565 +6896,565 @@
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F26">
-        <v>2.66</v>
+        <v>1.72</v>
       </c>
       <c r="G26">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="H26">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="I26">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="J26">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K26">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O26">
+        <v>1.25</v>
+      </c>
+      <c r="P26">
+        <v>2.08</v>
+      </c>
+      <c r="Q26">
+        <v>1.79</v>
+      </c>
+      <c r="R26">
+        <v>1.35</v>
+      </c>
+      <c r="S26">
+        <v>3</v>
+      </c>
+      <c r="T26">
+        <v>1.8</v>
+      </c>
+      <c r="U26">
+        <v>1.91</v>
+      </c>
+      <c r="V26">
+        <v>1.23</v>
+      </c>
+      <c r="W26">
+        <v>2.2</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>16.5</v>
+      </c>
+      <c r="AC26">
+        <v>15.5</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>25</v>
+      </c>
+      <c r="AG26">
+        <v>23</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>18.5</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.35</v>
+      </c>
+      <c r="AQ26">
+        <v>1.35</v>
+      </c>
+      <c r="AR26">
+        <v>1.35</v>
+      </c>
+      <c r="AS26">
+        <v>1.35</v>
+      </c>
+      <c r="AT26">
+        <v>1.25</v>
+      </c>
+      <c r="AU26">
+        <v>6.2</v>
+      </c>
+      <c r="AV26">
+        <v>1.35</v>
+      </c>
+      <c r="AW26">
+        <v>1.35</v>
+      </c>
+      <c r="AX26">
         <v>1.28</v>
       </c>
-      <c r="P26">
-        <v>2.14</v>
-      </c>
-      <c r="Q26">
-        <v>1.83</v>
-      </c>
-      <c r="R26">
-        <v>1.45</v>
-      </c>
-      <c r="S26">
-        <v>3.05</v>
-      </c>
-      <c r="T26">
-        <v>1.68</v>
-      </c>
-      <c r="U26">
-        <v>2.4</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>16.5</v>
-      </c>
-      <c r="Y26">
-        <v>14</v>
-      </c>
-      <c r="Z26">
-        <v>21</v>
-      </c>
-      <c r="AA26">
-        <v>44</v>
-      </c>
-      <c r="AB26">
-        <v>12.5</v>
-      </c>
-      <c r="AC26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26">
-        <v>13</v>
-      </c>
-      <c r="AE26">
-        <v>30</v>
-      </c>
-      <c r="AF26">
-        <v>18</v>
-      </c>
-      <c r="AG26">
-        <v>12.5</v>
-      </c>
-      <c r="AH26">
-        <v>15.5</v>
-      </c>
-      <c r="AI26">
-        <v>44</v>
-      </c>
-      <c r="AJ26">
-        <v>38</v>
-      </c>
-      <c r="AK26">
-        <v>28</v>
-      </c>
-      <c r="AL26">
-        <v>38</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>20</v>
-      </c>
-      <c r="AO26">
-        <v>23</v>
-      </c>
-      <c r="AP26">
-        <v>15</v>
-      </c>
-      <c r="AQ26">
-        <v>12</v>
-      </c>
-      <c r="AR26">
-        <v>18</v>
-      </c>
-      <c r="AS26">
-        <v>24</v>
-      </c>
-      <c r="AT26">
-        <v>11.5</v>
-      </c>
-      <c r="AU26">
-        <v>7.6</v>
-      </c>
-      <c r="AV26">
-        <v>11.5</v>
-      </c>
-      <c r="AW26">
-        <v>18.5</v>
-      </c>
-      <c r="AX26">
-        <v>16</v>
-      </c>
       <c r="AY26">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BA26">
-        <v>23</v>
+        <v>1.35</v>
       </c>
       <c r="BB26">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC26">
-        <v>18</v>
+        <v>1.35</v>
       </c>
       <c r="BD26">
-        <v>23</v>
+        <v>1.35</v>
       </c>
       <c r="BE26">
-        <v>32</v>
+        <v>1.35</v>
       </c>
       <c r="BF26">
-        <v>17.5</v>
+        <v>1.26</v>
       </c>
       <c r="BG26">
-        <v>20</v>
+        <v>1.35</v>
       </c>
       <c r="BH26">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F27">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="G27">
-        <v>1.16</v>
+        <v>1000</v>
       </c>
       <c r="H27">
-        <v>28</v>
+        <v>1.6</v>
       </c>
       <c r="I27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="J27">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="K27">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.01</v>
+      </c>
+      <c r="N27">
+        <v>1.25</v>
+      </c>
+      <c r="O27">
+        <v>1.01</v>
+      </c>
+      <c r="P27">
+        <v>1.25</v>
+      </c>
+      <c r="Q27">
+        <v>1.01</v>
+      </c>
+      <c r="R27">
+        <v>1.24</v>
+      </c>
+      <c r="S27">
+        <v>1.01</v>
+      </c>
+      <c r="T27">
+        <v>1.01</v>
+      </c>
+      <c r="U27">
+        <v>1.01</v>
+      </c>
+      <c r="V27">
+        <v>1.01</v>
+      </c>
+      <c r="W27">
+        <v>1.01</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27">
+        <v>1.01</v>
+      </c>
+      <c r="AR27">
+        <v>1.01</v>
+      </c>
+      <c r="AS27">
+        <v>1.01</v>
+      </c>
+      <c r="AT27">
+        <v>1.01</v>
+      </c>
+      <c r="AU27">
+        <v>1.01</v>
+      </c>
+      <c r="AV27">
+        <v>1.01</v>
+      </c>
+      <c r="AW27">
+        <v>1.01</v>
+      </c>
+      <c r="AX27">
+        <v>1.01</v>
+      </c>
+      <c r="AY27">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27">
+        <v>1.01</v>
+      </c>
+      <c r="BA27">
+        <v>1.01</v>
+      </c>
+      <c r="BB27">
+        <v>1.01</v>
+      </c>
+      <c r="BC27">
+        <v>1.01</v>
+      </c>
+      <c r="BD27">
+        <v>1.01</v>
+      </c>
+      <c r="BE27">
+        <v>1.01</v>
+      </c>
+      <c r="BF27">
+        <v>1.01</v>
+      </c>
+      <c r="BG27">
+        <v>1.01</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>1.01</v>
-      </c>
-      <c r="N27">
-        <v>10.5</v>
-      </c>
-      <c r="O27">
-        <v>1.09</v>
-      </c>
-      <c r="P27">
-        <v>4.2</v>
-      </c>
-      <c r="Q27">
-        <v>1.28</v>
-      </c>
-      <c r="R27">
-        <v>2.34</v>
-      </c>
-      <c r="S27">
-        <v>1.7</v>
-      </c>
-      <c r="T27">
-        <v>2.1</v>
-      </c>
-      <c r="U27">
-        <v>1.86</v>
-      </c>
-      <c r="V27">
+      <c r="CA27">
         <v>0</v>
       </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>60</v>
-      </c>
-      <c r="Y27">
-        <v>1000</v>
-      </c>
-      <c r="Z27">
-        <v>360</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>18.5</v>
-      </c>
-      <c r="AC27">
-        <v>26</v>
-      </c>
-      <c r="AD27">
-        <v>120</v>
-      </c>
-      <c r="AE27">
-        <v>440</v>
-      </c>
-      <c r="AF27">
-        <v>11.5</v>
-      </c>
-      <c r="AG27">
-        <v>16.5</v>
-      </c>
-      <c r="AH27">
-        <v>50</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>9.4</v>
-      </c>
-      <c r="AK27">
-        <v>14.5</v>
-      </c>
-      <c r="AL27">
-        <v>44</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>2.3</v>
-      </c>
-      <c r="AO27">
-        <v>440</v>
-      </c>
-      <c r="AP27">
-        <v>28</v>
-      </c>
-      <c r="AQ27">
-        <v>40</v>
-      </c>
-      <c r="AR27">
-        <v>55</v>
-      </c>
-      <c r="AS27">
-        <v>17</v>
-      </c>
-      <c r="AT27">
-        <v>16</v>
-      </c>
-      <c r="AU27">
-        <v>22</v>
-      </c>
-      <c r="AV27">
-        <v>38</v>
-      </c>
-      <c r="AW27">
-        <v>55</v>
-      </c>
-      <c r="AX27">
-        <v>10</v>
-      </c>
-      <c r="AY27">
-        <v>14</v>
-      </c>
-      <c r="AZ27">
-        <v>25</v>
-      </c>
-      <c r="BA27">
-        <v>50</v>
-      </c>
-      <c r="BB27">
-        <v>8.6</v>
-      </c>
-      <c r="BC27">
-        <v>12.5</v>
-      </c>
-      <c r="BD27">
-        <v>25</v>
-      </c>
-      <c r="BE27">
-        <v>44</v>
-      </c>
-      <c r="BF27">
-        <v>2.22</v>
-      </c>
-      <c r="BG27">
-        <v>65</v>
-      </c>
-      <c r="BH27">
-        <v>7.8</v>
-      </c>
-      <c r="BI27">
-        <v>5.4</v>
-      </c>
-      <c r="BJ27">
-        <v>16.5</v>
-      </c>
-      <c r="BK27">
-        <v>11</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>1.01</v>
-      </c>
-      <c r="BN27">
-        <v>4.8</v>
-      </c>
-      <c r="BO27">
-        <v>3.45</v>
-      </c>
-      <c r="BP27">
-        <v>6.4</v>
-      </c>
-      <c r="BQ27">
-        <v>4.4</v>
-      </c>
-      <c r="BR27">
-        <v>22</v>
-      </c>
-      <c r="BS27">
-        <v>14</v>
-      </c>
-      <c r="BT27">
-        <v>26</v>
-      </c>
-      <c r="BU27">
-        <v>16.5</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>1.01</v>
-      </c>
-      <c r="BX27">
-        <v>110</v>
-      </c>
-      <c r="BY27">
-        <v>1.01</v>
-      </c>
-      <c r="BZ27">
-        <v>5.9</v>
-      </c>
-      <c r="CA27">
-        <v>4.1</v>
-      </c>
       <c r="CB27" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F28">
-        <v>1.9</v>
+        <v>1.12</v>
       </c>
       <c r="G28">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="H28">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="I28">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="J28">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="K28">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="O28">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="P28">
-        <v>2.54</v>
+        <v>6.8</v>
       </c>
       <c r="Q28">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="R28">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="S28">
-        <v>2.48</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -7430,124 +7463,124 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
+        <v>370</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
         <v>36</v>
       </c>
-      <c r="AA28">
-        <v>1000</v>
-      </c>
-      <c r="AB28">
-        <v>13</v>
-      </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AD28">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="AF28">
+        <v>18.5</v>
+      </c>
+      <c r="AG28">
+        <v>20</v>
+      </c>
+      <c r="AH28">
+        <v>150</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>11.5</v>
+      </c>
+      <c r="AK28">
         <v>14.5</v>
       </c>
-      <c r="AG28">
-        <v>10.5</v>
-      </c>
-      <c r="AH28">
+      <c r="AL28">
+        <v>32</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1.89</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>40</v>
+      </c>
+      <c r="AQ28">
+        <v>40</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
+        <v>21</v>
+      </c>
+      <c r="AT28">
+        <v>26</v>
+      </c>
+      <c r="AU28">
+        <v>34</v>
+      </c>
+      <c r="AV28">
+        <v>36</v>
+      </c>
+      <c r="AW28">
+        <v>20</v>
+      </c>
+      <c r="AX28">
+        <v>16.5</v>
+      </c>
+      <c r="AY28">
         <v>16</v>
       </c>
-      <c r="AI28">
-        <v>46</v>
-      </c>
-      <c r="AJ28">
-        <v>23</v>
-      </c>
-      <c r="AK28">
-        <v>18</v>
-      </c>
-      <c r="AL28">
-        <v>28</v>
-      </c>
-      <c r="AM28">
-        <v>65</v>
-      </c>
-      <c r="AN28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO28">
-        <v>34</v>
-      </c>
-      <c r="AP28">
-        <v>20</v>
-      </c>
-      <c r="AQ28">
-        <v>18</v>
-      </c>
-      <c r="AR28">
-        <v>22</v>
-      </c>
-      <c r="AS28">
-        <v>36</v>
-      </c>
-      <c r="AT28">
-        <v>11.5</v>
-      </c>
-      <c r="AU28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV28">
-        <v>15.5</v>
-      </c>
-      <c r="AW28">
-        <v>34</v>
-      </c>
-      <c r="AX28">
+      <c r="AZ28">
+        <v>26</v>
+      </c>
+      <c r="BA28">
+        <v>44</v>
+      </c>
+      <c r="BB28">
+        <v>10</v>
+      </c>
+      <c r="BC28">
         <v>12.5</v>
       </c>
-      <c r="AY28">
-        <v>9.6</v>
-      </c>
-      <c r="AZ28">
-        <v>13.5</v>
-      </c>
-      <c r="BA28">
-        <v>25</v>
-      </c>
-      <c r="BB28">
-        <v>19</v>
-      </c>
-      <c r="BC28">
-        <v>15</v>
-      </c>
       <c r="BD28">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BE28">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF28">
-        <v>7.8</v>
+        <v>1.82</v>
       </c>
       <c r="BG28">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="BH28">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BI28">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="BJ28">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BK28">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7556,114 +7589,114 @@
         <v>55</v>
       </c>
       <c r="BN28">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BO28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP28">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BQ28">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="BR28">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BS28">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT28">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BU28">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BV28">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BZ28">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="CA28">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="CB28" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F29">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="G29">
-        <v>6.2</v>
+        <v>2.68</v>
       </c>
       <c r="H29">
-        <v>1.73</v>
+        <v>2.86</v>
       </c>
       <c r="I29">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="J29">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K29">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P29">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q29">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7672,175 +7705,901 @@
         <v>0</v>
       </c>
       <c r="X29">
+        <v>16.5</v>
+      </c>
+      <c r="Y29">
+        <v>14</v>
+      </c>
+      <c r="Z29">
+        <v>21</v>
+      </c>
+      <c r="AA29">
+        <v>44</v>
+      </c>
+      <c r="AB29">
+        <v>12.5</v>
+      </c>
+      <c r="AC29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD29">
+        <v>13</v>
+      </c>
+      <c r="AE29">
+        <v>30</v>
+      </c>
+      <c r="AF29">
+        <v>18</v>
+      </c>
+      <c r="AG29">
+        <v>12.5</v>
+      </c>
+      <c r="AH29">
+        <v>15.5</v>
+      </c>
+      <c r="AI29">
+        <v>44</v>
+      </c>
+      <c r="AJ29">
+        <v>38</v>
+      </c>
+      <c r="AK29">
+        <v>28</v>
+      </c>
+      <c r="AL29">
+        <v>38</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>20</v>
+      </c>
+      <c r="AO29">
+        <v>23</v>
+      </c>
+      <c r="AP29">
+        <v>15</v>
+      </c>
+      <c r="AQ29">
+        <v>12</v>
+      </c>
+      <c r="AR29">
+        <v>18</v>
+      </c>
+      <c r="AS29">
+        <v>24</v>
+      </c>
+      <c r="AT29">
+        <v>11.5</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>11.5</v>
+      </c>
+      <c r="AW29">
+        <v>18.5</v>
+      </c>
+      <c r="AX29">
+        <v>16</v>
+      </c>
+      <c r="AY29">
+        <v>11</v>
+      </c>
+      <c r="AZ29">
+        <v>14</v>
+      </c>
+      <c r="BA29">
+        <v>23</v>
+      </c>
+      <c r="BB29">
+        <v>22</v>
+      </c>
+      <c r="BC29">
+        <v>18</v>
+      </c>
+      <c r="BD29">
+        <v>23</v>
+      </c>
+      <c r="BE29">
+        <v>32</v>
+      </c>
+      <c r="BF29">
+        <v>17.5</v>
+      </c>
+      <c r="BG29">
+        <v>20</v>
+      </c>
+      <c r="BH29">
+        <v>3.7</v>
+      </c>
+      <c r="BI29">
+        <v>3.4</v>
+      </c>
+      <c r="BJ29">
+        <v>9</v>
+      </c>
+      <c r="BK29">
+        <v>8</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>65</v>
+      </c>
+      <c r="BN29">
+        <v>5.7</v>
+      </c>
+      <c r="BO29">
+        <v>5.2</v>
+      </c>
+      <c r="BP29">
+        <v>19</v>
+      </c>
+      <c r="BQ29">
+        <v>13.5</v>
+      </c>
+      <c r="BR29">
+        <v>29</v>
+      </c>
+      <c r="BS29">
+        <v>20</v>
+      </c>
+      <c r="BT29">
+        <v>6.2</v>
+      </c>
+      <c r="BU29">
+        <v>5.5</v>
+      </c>
+      <c r="BV29">
+        <v>21</v>
+      </c>
+      <c r="BW29">
+        <v>15</v>
+      </c>
+      <c r="BX29">
+        <v>30</v>
+      </c>
+      <c r="BY29">
+        <v>21</v>
+      </c>
+      <c r="BZ29">
+        <v>22</v>
+      </c>
+      <c r="CA29">
+        <v>15.5</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30">
+        <v>1.15</v>
+      </c>
+      <c r="G30">
+        <v>1.16</v>
+      </c>
+      <c r="H30">
+        <v>28</v>
+      </c>
+      <c r="I30">
+        <v>29</v>
+      </c>
+      <c r="J30">
+        <v>10.5</v>
+      </c>
+      <c r="K30">
+        <v>11</v>
+      </c>
+      <c r="L30">
         <v>0</v>
       </c>
-      <c r="Y29">
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>10.5</v>
+      </c>
+      <c r="O30">
+        <v>1.09</v>
+      </c>
+      <c r="P30">
+        <v>4.2</v>
+      </c>
+      <c r="Q30">
+        <v>1.28</v>
+      </c>
+      <c r="R30">
+        <v>2.34</v>
+      </c>
+      <c r="S30">
+        <v>1.7</v>
+      </c>
+      <c r="T30">
+        <v>2.08</v>
+      </c>
+      <c r="U30">
+        <v>1.86</v>
+      </c>
+      <c r="V30">
         <v>0</v>
       </c>
-      <c r="Z29">
+      <c r="W30">
         <v>0</v>
       </c>
-      <c r="AA29">
+      <c r="X30">
+        <v>60</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>360</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>18.5</v>
+      </c>
+      <c r="AC30">
+        <v>26</v>
+      </c>
+      <c r="AD30">
+        <v>120</v>
+      </c>
+      <c r="AE30">
+        <v>440</v>
+      </c>
+      <c r="AF30">
+        <v>11.5</v>
+      </c>
+      <c r="AG30">
+        <v>16.5</v>
+      </c>
+      <c r="AH30">
+        <v>42</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>9.4</v>
+      </c>
+      <c r="AK30">
+        <v>14.5</v>
+      </c>
+      <c r="AL30">
+        <v>44</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>2.3</v>
+      </c>
+      <c r="AO30">
+        <v>440</v>
+      </c>
+      <c r="AP30">
+        <v>28</v>
+      </c>
+      <c r="AQ30">
+        <v>40</v>
+      </c>
+      <c r="AR30">
+        <v>55</v>
+      </c>
+      <c r="AS30">
+        <v>17</v>
+      </c>
+      <c r="AT30">
+        <v>16</v>
+      </c>
+      <c r="AU30">
+        <v>22</v>
+      </c>
+      <c r="AV30">
+        <v>38</v>
+      </c>
+      <c r="AW30">
+        <v>55</v>
+      </c>
+      <c r="AX30">
+        <v>10</v>
+      </c>
+      <c r="AY30">
+        <v>14</v>
+      </c>
+      <c r="AZ30">
+        <v>36</v>
+      </c>
+      <c r="BA30">
+        <v>50</v>
+      </c>
+      <c r="BB30">
+        <v>8.6</v>
+      </c>
+      <c r="BC30">
+        <v>12.5</v>
+      </c>
+      <c r="BD30">
+        <v>25</v>
+      </c>
+      <c r="BE30">
+        <v>44</v>
+      </c>
+      <c r="BF30">
+        <v>2.22</v>
+      </c>
+      <c r="BG30">
+        <v>70</v>
+      </c>
+      <c r="BH30">
+        <v>7.8</v>
+      </c>
+      <c r="BI30">
+        <v>5.4</v>
+      </c>
+      <c r="BJ30">
+        <v>16.5</v>
+      </c>
+      <c r="BK30">
+        <v>11</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.01</v>
+      </c>
+      <c r="BN30">
+        <v>4.8</v>
+      </c>
+      <c r="BO30">
+        <v>3.45</v>
+      </c>
+      <c r="BP30">
+        <v>6.4</v>
+      </c>
+      <c r="BQ30">
+        <v>4.4</v>
+      </c>
+      <c r="BR30">
+        <v>22</v>
+      </c>
+      <c r="BS30">
+        <v>14</v>
+      </c>
+      <c r="BT30">
+        <v>26</v>
+      </c>
+      <c r="BU30">
+        <v>17</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.01</v>
+      </c>
+      <c r="BX30">
+        <v>120</v>
+      </c>
+      <c r="BY30">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30">
+        <v>5.9</v>
+      </c>
+      <c r="CA30">
+        <v>4.1</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31">
+        <v>1.9</v>
+      </c>
+      <c r="G31">
+        <v>1.91</v>
+      </c>
+      <c r="H31">
+        <v>4.2</v>
+      </c>
+      <c r="I31">
+        <v>4.3</v>
+      </c>
+      <c r="J31">
+        <v>4.1</v>
+      </c>
+      <c r="K31">
+        <v>4.2</v>
+      </c>
+      <c r="L31">
         <v>0</v>
       </c>
-      <c r="AB29">
+      <c r="M31">
+        <v>1.04</v>
+      </c>
+      <c r="N31">
+        <v>5.5</v>
+      </c>
+      <c r="O31">
+        <v>1.21</v>
+      </c>
+      <c r="P31">
+        <v>2.54</v>
+      </c>
+      <c r="Q31">
+        <v>1.62</v>
+      </c>
+      <c r="R31">
+        <v>1.61</v>
+      </c>
+      <c r="S31">
+        <v>2.48</v>
+      </c>
+      <c r="T31">
+        <v>1.6</v>
+      </c>
+      <c r="U31">
+        <v>2.6</v>
+      </c>
+      <c r="V31">
         <v>0</v>
       </c>
-      <c r="AC29">
+      <c r="W31">
         <v>0</v>
       </c>
-      <c r="AD29">
+      <c r="X31">
+        <v>25</v>
+      </c>
+      <c r="Y31">
+        <v>23</v>
+      </c>
+      <c r="Z31">
+        <v>36</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>13</v>
+      </c>
+      <c r="AC31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD31">
+        <v>17.5</v>
+      </c>
+      <c r="AE31">
+        <v>46</v>
+      </c>
+      <c r="AF31">
+        <v>14.5</v>
+      </c>
+      <c r="AG31">
+        <v>10.5</v>
+      </c>
+      <c r="AH31">
+        <v>16</v>
+      </c>
+      <c r="AI31">
+        <v>46</v>
+      </c>
+      <c r="AJ31">
+        <v>23</v>
+      </c>
+      <c r="AK31">
+        <v>18</v>
+      </c>
+      <c r="AL31">
+        <v>28</v>
+      </c>
+      <c r="AM31">
+        <v>65</v>
+      </c>
+      <c r="AN31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO31">
+        <v>34</v>
+      </c>
+      <c r="AP31">
+        <v>20</v>
+      </c>
+      <c r="AQ31">
+        <v>18</v>
+      </c>
+      <c r="AR31">
+        <v>22</v>
+      </c>
+      <c r="AS31">
+        <v>36</v>
+      </c>
+      <c r="AT31">
+        <v>11.5</v>
+      </c>
+      <c r="AU31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV31">
+        <v>15.5</v>
+      </c>
+      <c r="AW31">
+        <v>34</v>
+      </c>
+      <c r="AX31">
+        <v>12.5</v>
+      </c>
+      <c r="AY31">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31">
+        <v>13.5</v>
+      </c>
+      <c r="BA31">
+        <v>25</v>
+      </c>
+      <c r="BB31">
+        <v>19</v>
+      </c>
+      <c r="BC31">
+        <v>15</v>
+      </c>
+      <c r="BD31">
+        <v>18</v>
+      </c>
+      <c r="BE31">
+        <v>30</v>
+      </c>
+      <c r="BF31">
+        <v>7.8</v>
+      </c>
+      <c r="BG31">
+        <v>21</v>
+      </c>
+      <c r="BH31">
+        <v>4.2</v>
+      </c>
+      <c r="BI31">
+        <v>3.8</v>
+      </c>
+      <c r="BJ31">
+        <v>9</v>
+      </c>
+      <c r="BK31">
+        <v>7.8</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>55</v>
+      </c>
+      <c r="BN31">
+        <v>5</v>
+      </c>
+      <c r="BO31">
+        <v>4.6</v>
+      </c>
+      <c r="BP31">
+        <v>13</v>
+      </c>
+      <c r="BQ31">
+        <v>11</v>
+      </c>
+      <c r="BR31">
+        <v>23</v>
+      </c>
+      <c r="BS31">
+        <v>15.5</v>
+      </c>
+      <c r="BT31">
+        <v>7.8</v>
+      </c>
+      <c r="BU31">
+        <v>6.8</v>
+      </c>
+      <c r="BV31">
+        <v>30</v>
+      </c>
+      <c r="BW31">
+        <v>21</v>
+      </c>
+      <c r="BX31">
+        <v>36</v>
+      </c>
+      <c r="BY31">
+        <v>24</v>
+      </c>
+      <c r="BZ31">
+        <v>16.5</v>
+      </c>
+      <c r="CA31">
+        <v>11</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32">
+        <v>5.4</v>
+      </c>
+      <c r="G32">
+        <v>5.9</v>
+      </c>
+      <c r="H32">
+        <v>1.73</v>
+      </c>
+      <c r="I32">
+        <v>1.81</v>
+      </c>
+      <c r="J32">
+        <v>3.85</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32">
         <v>0</v>
       </c>
-      <c r="AE29">
+      <c r="M32">
         <v>0</v>
       </c>
-      <c r="AF29">
+      <c r="N32">
         <v>0</v>
       </c>
-      <c r="AG29">
+      <c r="O32">
         <v>0</v>
       </c>
-      <c r="AH29">
+      <c r="P32">
+        <v>1.94</v>
+      </c>
+      <c r="Q32">
+        <v>2.02</v>
+      </c>
+      <c r="R32">
         <v>0</v>
       </c>
-      <c r="AI29">
+      <c r="S32">
         <v>0</v>
       </c>
-      <c r="AJ29">
+      <c r="T32">
         <v>0</v>
       </c>
-      <c r="AK29">
+      <c r="U32">
         <v>0</v>
       </c>
-      <c r="AL29">
+      <c r="V32">
         <v>0</v>
       </c>
-      <c r="AM29">
+      <c r="W32">
         <v>0</v>
       </c>
-      <c r="AN29">
+      <c r="X32">
         <v>0</v>
       </c>
-      <c r="AO29">
+      <c r="Y32">
         <v>0</v>
       </c>
-      <c r="AP29">
+      <c r="Z32">
         <v>0</v>
       </c>
-      <c r="AQ29">
+      <c r="AA32">
         <v>0</v>
       </c>
-      <c r="AR29">
+      <c r="AB32">
         <v>0</v>
       </c>
-      <c r="AS29">
+      <c r="AC32">
         <v>0</v>
       </c>
-      <c r="AT29">
+      <c r="AD32">
         <v>0</v>
       </c>
-      <c r="AU29">
+      <c r="AE32">
         <v>0</v>
       </c>
-      <c r="AV29">
+      <c r="AF32">
         <v>0</v>
       </c>
-      <c r="AW29">
+      <c r="AG32">
         <v>0</v>
       </c>
-      <c r="AX29">
+      <c r="AH32">
         <v>0</v>
       </c>
-      <c r="AY29">
+      <c r="AI32">
         <v>0</v>
       </c>
-      <c r="AZ29">
+      <c r="AJ32">
         <v>0</v>
       </c>
-      <c r="BA29">
+      <c r="AK32">
         <v>0</v>
       </c>
-      <c r="BB29">
+      <c r="AL32">
         <v>0</v>
       </c>
-      <c r="BC29">
+      <c r="AM32">
         <v>0</v>
       </c>
-      <c r="BD29">
+      <c r="AN32">
         <v>0</v>
       </c>
-      <c r="BE29">
+      <c r="AO32">
         <v>0</v>
       </c>
-      <c r="BF29">
+      <c r="AP32">
         <v>0</v>
       </c>
-      <c r="BG29">
+      <c r="AQ32">
         <v>0</v>
       </c>
-      <c r="BH29">
+      <c r="AR32">
         <v>0</v>
       </c>
-      <c r="BI29">
+      <c r="AS32">
         <v>0</v>
       </c>
-      <c r="BJ29">
+      <c r="AT32">
         <v>0</v>
       </c>
-      <c r="BK29">
+      <c r="AU32">
         <v>0</v>
       </c>
-      <c r="BL29">
+      <c r="AV32">
         <v>0</v>
       </c>
-      <c r="BM29">
+      <c r="AW32">
         <v>0</v>
       </c>
-      <c r="BN29">
+      <c r="AX32">
         <v>0</v>
       </c>
-      <c r="BO29">
+      <c r="AY32">
         <v>0</v>
       </c>
-      <c r="BP29">
+      <c r="AZ32">
         <v>0</v>
       </c>
-      <c r="BQ29">
+      <c r="BA32">
         <v>0</v>
       </c>
-      <c r="BR29">
+      <c r="BB32">
         <v>0</v>
       </c>
-      <c r="BS29">
+      <c r="BC32">
         <v>0</v>
       </c>
-      <c r="BT29">
+      <c r="BD32">
         <v>0</v>
       </c>
-      <c r="BU29">
+      <c r="BE32">
         <v>0</v>
       </c>
-      <c r="BV29">
+      <c r="BF32">
         <v>0</v>
       </c>
-      <c r="BW29">
+      <c r="BG32">
         <v>0</v>
       </c>
-      <c r="BX29">
+      <c r="BH32">
         <v>0</v>
       </c>
-      <c r="BY29">
+      <c r="BI32">
         <v>0</v>
       </c>
-      <c r="BZ29">
+      <c r="BJ32">
         <v>0</v>
       </c>
-      <c r="CA29">
+      <c r="BK32">
         <v>0</v>
       </c>
-      <c r="CB29" t="s">
-        <v>158</v>
+      <c r="BL32">
+        <v>0</v>
+      </c>
+      <c r="BM32">
+        <v>0</v>
+      </c>
+      <c r="BN32">
+        <v>0</v>
+      </c>
+      <c r="BO32">
+        <v>0</v>
+      </c>
+      <c r="BP32">
+        <v>0</v>
+      </c>
+      <c r="BQ32">
+        <v>0</v>
+      </c>
+      <c r="BR32">
+        <v>0</v>
+      </c>
+      <c r="BS32">
+        <v>0</v>
+      </c>
+      <c r="BT32">
+        <v>0</v>
+      </c>
+      <c r="BU32">
+        <v>0</v>
+      </c>
+      <c r="BV32">
+        <v>0</v>
+      </c>
+      <c r="BW32">
+        <v>0</v>
+      </c>
+      <c r="BX32">
+        <v>0</v>
+      </c>
+      <c r="BY32">
+        <v>0</v>
+      </c>
+      <c r="BZ32">
+        <v>0</v>
+      </c>
+      <c r="CA32">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="181">
   <si>
     <t>League</t>
   </si>
@@ -280,18 +280,27 @@
     <t>UEFA Champions League</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
     <t>Serbian Super League</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>Greek Super League</t>
+  </si>
+  <si>
+    <t>English Sky Bet League 1</t>
+  </si>
+  <si>
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
@@ -331,6 +340,12 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -394,6 +409,9 @@
     <t>Fenerbahce</t>
   </si>
   <si>
+    <t>Ostersunds FK</t>
+  </si>
+  <si>
     <t>Gagra</t>
   </si>
   <si>
@@ -409,24 +427,30 @@
     <t>Sundsvall</t>
   </si>
   <si>
-    <t>Ostersunds FK</t>
-  </si>
-  <si>
     <t>Enkopings SK</t>
   </si>
   <si>
+    <t>ES Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Panathinaikos</t>
+  </si>
+  <si>
+    <t>Man Utd</t>
+  </si>
+  <si>
+    <t>Slavia Prague</t>
+  </si>
+  <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>Stevenage</t>
+  </si>
+  <si>
     <t>Bayern Munich</t>
   </si>
   <si>
-    <t>Slavia Prague</t>
-  </si>
-  <si>
-    <t>Man Utd</t>
-  </si>
-  <si>
-    <t>Como</t>
-  </si>
-  <si>
     <t>Club Football Estrela</t>
   </si>
   <si>
@@ -487,6 +511,9 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>IK Brage</t>
+  </si>
+  <si>
     <t>Torpedo Kutaisi</t>
   </si>
   <si>
@@ -502,28 +529,34 @@
     <t>Orebro</t>
   </si>
   <si>
-    <t>IK Brage</t>
-  </si>
-  <si>
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>US Biskra</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>FC Sabah</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Luton</t>
+  </si>
+  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
-    <t>Lens</t>
-  </si>
-  <si>
-    <t>FC Sabah</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 15:11:13</t>
+    <t>2026-09-08 17:24:10</t>
   </si>
 </sst>
 </file>
@@ -855,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1105,16 +1138,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F2">
         <v>2.34</v>
@@ -1144,25 +1177,25 @@
         <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T2">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="U2">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
         <v>1.45</v>
@@ -1174,13 +1207,13 @@
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB2">
         <v>13</v>
@@ -1195,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1204,22 +1237,22 @@
         <v>16</v>
       </c>
       <c r="AI2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
         <v>32</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL2">
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>25</v>
@@ -1237,7 +1270,7 @@
         <v>32</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>8</v>
@@ -1246,7 +1279,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
@@ -1255,22 +1288,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1279,67 +1312,67 @@
         <v>20</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI2">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
+        <v>7.8</v>
+      </c>
+      <c r="BL2">
+        <v>110</v>
+      </c>
+      <c r="BM2">
+        <v>60</v>
+      </c>
+      <c r="BN2">
+        <v>5.5</v>
+      </c>
+      <c r="BO2">
+        <v>4.9</v>
+      </c>
+      <c r="BP2">
+        <v>19.5</v>
+      </c>
+      <c r="BQ2">
+        <v>13.5</v>
+      </c>
+      <c r="BR2">
+        <v>32</v>
+      </c>
+      <c r="BS2">
+        <v>18.5</v>
+      </c>
+      <c r="BT2">
         <v>6.6</v>
       </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>4.4</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.01</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1347,16 +1380,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F3">
         <v>1.87</v>
@@ -1374,7 +1407,7 @@
         <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.48</v>
@@ -1383,19 +1416,19 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q3">
         <v>2.26</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
         <v>4.4</v>
@@ -1440,7 +1473,7 @@
         <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>28</v>
@@ -1497,16 +1530,16 @@
         <v>9</v>
       </c>
       <c r="AZ3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA3">
         <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD3">
         <v>4.9</v>
@@ -1518,13 +1551,13 @@
         <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>3.45</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3">
         <v>13</v>
@@ -1536,7 +1569,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1548,7 +1581,7 @@
         <v>18</v>
       </c>
       <c r="BQ3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR3">
         <v>42</v>
@@ -1581,7 +1614,7 @@
         <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1589,19 +1622,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
         <v>2.4</v>
@@ -1610,13 +1643,13 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <v>1.64</v>
@@ -1631,22 +1664,22 @@
         <v>1.69</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R4">
         <v>1.15</v>
       </c>
       <c r="S4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V4">
         <v>1.31</v>
@@ -1661,7 +1694,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA4">
         <v>130</v>
@@ -1673,16 +1706,16 @@
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE4">
         <v>100</v>
       </c>
       <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
         <v>13</v>
-      </c>
-      <c r="AG4">
-        <v>15</v>
       </c>
       <c r="AH4">
         <v>29</v>
@@ -1700,13 +1733,13 @@
         <v>100</v>
       </c>
       <c r="AM4">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN4">
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>6.4</v>
@@ -1718,7 +1751,7 @@
         <v>22</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT4">
         <v>5.8</v>
@@ -1730,7 +1763,7 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX4">
         <v>11</v>
@@ -1742,88 +1775,88 @@
         <v>22</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BB4">
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BD4">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>1.21</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="CB4" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1831,16 +1864,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F5">
         <v>2.14</v>
@@ -1876,7 +1909,7 @@
         <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
         <v>1.67</v>
@@ -1906,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1951,16 +1984,16 @@
         <v>23</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT5">
         <v>13</v>
@@ -1972,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -1984,16 +2017,16 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB5">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE5">
         <v>34</v>
@@ -2008,7 +2041,7 @@
         <v>4.5</v>
       </c>
       <c r="BI5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5">
         <v>9.4</v>
@@ -2065,7 +2098,7 @@
         <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2073,16 +2106,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>2.62</v>
@@ -2130,7 +2163,7 @@
         <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2139,7 +2172,7 @@
         <v>1.57</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y6">
         <v>12.5</v>
@@ -2151,7 +2184,7 @@
         <v>60</v>
       </c>
       <c r="AB6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -2160,7 +2193,7 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AF6">
         <v>18</v>
@@ -2175,13 +2208,13 @@
         <v>120</v>
       </c>
       <c r="AJ6">
+        <v>65</v>
+      </c>
+      <c r="AK6">
+        <v>46</v>
+      </c>
+      <c r="AL6">
         <v>55</v>
-      </c>
-      <c r="AK6">
-        <v>36</v>
-      </c>
-      <c r="AL6">
-        <v>70</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2190,19 +2223,19 @@
         <v>24</v>
       </c>
       <c r="AO6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR6">
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2214,10 +2247,10 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY6">
         <v>11</v>
@@ -2226,19 +2259,19 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB6">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BC6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>20</v>
@@ -2250,7 +2283,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2262,52 +2295,52 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP6">
         <v>29</v>
       </c>
       <c r="BQ6">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BR6">
         <v>46</v>
       </c>
       <c r="BS6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
         <v>30</v>
       </c>
       <c r="BW6">
-        <v>2.02</v>
+        <v>4.3</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="BZ6">
         <v>38</v>
       </c>
       <c r="CA6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2315,16 +2348,16 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F7">
         <v>1.8</v>
@@ -2369,7 +2402,7 @@
         <v>2.86</v>
       </c>
       <c r="T7">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
         <v>2.3</v>
@@ -2414,7 +2447,7 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2441,10 +2474,10 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -2480,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF7">
         <v>8.4</v>
@@ -2492,13 +2525,13 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2507,16 +2540,16 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2528,7 +2561,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2549,7 +2582,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2557,34 +2590,34 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H8">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
         <v>1.18</v>
@@ -2593,7 +2626,7 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O8">
         <v>1.09</v>
@@ -2620,19 +2653,19 @@
         <v>1.47</v>
       </c>
       <c r="W8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X8">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="Y8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA8">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AB8">
         <v>30</v>
@@ -2671,13 +2704,13 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO8">
         <v>10</v>
       </c>
       <c r="AP8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AQ8">
         <v>23</v>
@@ -2686,7 +2719,7 @@
         <v>26</v>
       </c>
       <c r="AS8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT8">
         <v>22</v>
@@ -2701,7 +2734,7 @@
         <v>19.5</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2725,7 +2758,7 @@
         <v>23</v>
       </c>
       <c r="BF8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG8">
         <v>9</v>
@@ -2734,43 +2767,43 @@
         <v>1000</v>
       </c>
       <c r="BI8">
+        <v>5.1</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
         <v>4.9</v>
       </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>5</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>7.4</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>8.4</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
         <v>5.7</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>5.1</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>9</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>10</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>5.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2782,7 +2815,7 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
@@ -2791,7 +2824,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2799,16 +2832,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -3033,7 +3066,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3041,16 +3074,16 @@
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F10">
         <v>1.45</v>
@@ -3062,13 +3095,13 @@
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>5.4</v>
       </c>
       <c r="K10">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
         <v>1.23</v>
@@ -3077,7 +3110,7 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O10">
         <v>1.13</v>
@@ -3098,7 +3131,7 @@
         <v>1.6</v>
       </c>
       <c r="U10">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V10">
         <v>1.15</v>
@@ -3113,7 +3146,7 @@
         <v>40</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3122,7 +3155,7 @@
         <v>15.5</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD10">
         <v>28</v>
@@ -3131,7 +3164,7 @@
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG10">
         <v>11</v>
@@ -3170,7 +3203,7 @@
         <v>44</v>
       </c>
       <c r="AS10">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AT10">
         <v>13.5</v>
@@ -3179,10 +3212,10 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
@@ -3215,67 +3248,67 @@
         <v>28</v>
       </c>
       <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>4.2</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>6.6</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
         <v>5.4</v>
       </c>
-      <c r="BI10">
-        <v>4.9</v>
-      </c>
-      <c r="BJ10">
-        <v>9.4</v>
-      </c>
-      <c r="BK10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>50</v>
-      </c>
-      <c r="BN10">
-        <v>4.6</v>
-      </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR10">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BV10">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3283,22 +3316,22 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
         <v>7.2</v>
@@ -3319,7 +3352,7 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>1.13</v>
@@ -3331,7 +3364,7 @@
         <v>1.39</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S11">
         <v>1.96</v>
@@ -3340,16 +3373,16 @@
         <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y11">
         <v>46</v>
@@ -3361,7 +3394,7 @@
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
         <v>14.5</v>
@@ -3370,7 +3403,7 @@
         <v>30</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3382,10 +3415,10 @@
         <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>410</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK11">
         <v>13.5</v>
@@ -3400,13 +3433,13 @@
         <v>4.1</v>
       </c>
       <c r="AO11">
-        <v>400</v>
+        <v>540</v>
       </c>
       <c r="AP11">
         <v>32</v>
       </c>
       <c r="AQ11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR11">
         <v>34</v>
@@ -3433,7 +3466,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA11">
         <v>50</v>
@@ -3517,7 +3550,7 @@
         <v>7.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3525,16 +3558,16 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F12">
         <v>1.82</v>
@@ -3558,13 +3591,13 @@
         <v>1.24</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>7.2</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
         <v>3.1</v>
@@ -3579,7 +3612,7 @@
         <v>2.12</v>
       </c>
       <c r="T12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U12">
         <v>2.9</v>
@@ -3591,16 +3624,16 @@
         <v>2.14</v>
       </c>
       <c r="X12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z12">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB12">
         <v>17.5</v>
@@ -3621,7 +3654,7 @@
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
         <v>42</v>
@@ -3636,7 +3669,7 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN12">
         <v>6.6</v>
@@ -3645,16 +3678,16 @@
         <v>25</v>
       </c>
       <c r="AP12">
+        <v>22</v>
+      </c>
+      <c r="AQ12">
         <v>23</v>
       </c>
-      <c r="AQ12">
-        <v>19.5</v>
-      </c>
       <c r="AR12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS12">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AT12">
         <v>14.5</v>
@@ -3666,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3678,10 +3711,10 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC12">
         <v>14.5</v>
@@ -3690,7 +3723,7 @@
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BF12">
         <v>6</v>
@@ -3759,7 +3792,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3767,16 +3800,16 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>2.36</v>
@@ -3788,7 +3821,7 @@
         <v>2.88</v>
       </c>
       <c r="I13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>3.95</v>
@@ -3797,7 +3830,7 @@
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M13">
         <v>1.03</v>
@@ -3809,16 +3842,16 @@
         <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q13">
         <v>1.54</v>
       </c>
       <c r="R13">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S13">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T13">
         <v>1.51</v>
@@ -3827,10 +3860,10 @@
         <v>2.84</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X13">
         <v>27</v>
@@ -3866,10 +3899,10 @@
         <v>14.5</v>
       </c>
       <c r="AI13">
+        <v>30</v>
+      </c>
+      <c r="AJ13">
         <v>32</v>
-      </c>
-      <c r="AJ13">
-        <v>36</v>
       </c>
       <c r="AK13">
         <v>22</v>
@@ -3896,7 +3929,7 @@
         <v>21</v>
       </c>
       <c r="AS13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT13">
         <v>14.5</v>
@@ -3908,7 +3941,7 @@
         <v>12</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX13">
         <v>17</v>
@@ -3920,7 +3953,7 @@
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BB13">
         <v>22</v>
@@ -3932,7 +3965,7 @@
         <v>21</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -3944,7 +3977,7 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -3959,7 +3992,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO13">
         <v>4.7</v>
@@ -3968,7 +4001,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
@@ -3986,7 +4019,7 @@
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>1000</v>
@@ -4001,7 +4034,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4009,16 +4042,16 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F14">
         <v>1.47</v>
@@ -4066,7 +4099,7 @@
         <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -4243,7 +4276,7 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4251,19 +4284,19 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F15">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G15">
         <v>2.54</v>
@@ -4272,7 +4305,7 @@
         <v>2.76</v>
       </c>
       <c r="I15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
         <v>3.55</v>
@@ -4284,10 +4317,10 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>1.17</v>
@@ -4299,16 +4332,16 @@
         <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T15">
         <v>1.47</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V15">
         <v>1.4</v>
@@ -4365,7 +4398,7 @@
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4485,7 +4518,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4493,16 +4526,16 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F16">
         <v>1.6</v>
@@ -4517,7 +4550,7 @@
         <v>1000</v>
       </c>
       <c r="J16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4529,7 +4562,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="O16">
         <v>1.28</v>
@@ -4553,10 +4586,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4727,7 +4760,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4735,16 +4768,16 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F17">
         <v>1.68</v>
@@ -4771,7 +4804,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O17">
         <v>1.16</v>
@@ -4786,7 +4819,7 @@
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4969,7 +5002,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4977,16 +5010,16 @@
         <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F18">
         <v>11</v>
@@ -5022,7 +5055,7 @@
         <v>3.35</v>
       </c>
       <c r="Q18">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="R18">
         <v>1.81</v>
@@ -5211,7 +5244,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5219,16 +5252,16 @@
         <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F19">
         <v>1.46</v>
@@ -5237,7 +5270,7 @@
         <v>1.48</v>
       </c>
       <c r="H19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>7.6</v>
@@ -5252,28 +5285,28 @@
         <v>1.25</v>
       </c>
       <c r="M19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P19">
         <v>3</v>
       </c>
       <c r="Q19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R19">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T19">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U19">
         <v>2.38</v>
@@ -5288,10 +5321,10 @@
         <v>34</v>
       </c>
       <c r="Y19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA19">
         <v>210</v>
@@ -5300,16 +5333,16 @@
         <v>13.5</v>
       </c>
       <c r="AC19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD19">
         <v>27</v>
       </c>
       <c r="AE19">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5390,7 +5423,7 @@
         <v>4.4</v>
       </c>
       <c r="BG19">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BH19">
         <v>5.9</v>
@@ -5408,7 +5441,7 @@
         <v>110</v>
       </c>
       <c r="BM19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN19">
         <v>5.3</v>
@@ -5426,7 +5459,7 @@
         <v>22</v>
       </c>
       <c r="BS19">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BT19">
         <v>13.5</v>
@@ -5450,10 +5483,10 @@
         <v>12.5</v>
       </c>
       <c r="CA19">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5461,22 +5494,22 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F20">
         <v>3.5</v>
       </c>
       <c r="G20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H20">
         <v>2.26</v>
@@ -5491,10 +5524,10 @@
         <v>3.65</v>
       </c>
       <c r="L20">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
         <v>4.6</v>
@@ -5509,22 +5542,22 @@
         <v>1.78</v>
       </c>
       <c r="R20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S20">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V20">
         <v>1.78</v>
       </c>
       <c r="W20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X20">
         <v>17</v>
@@ -5569,7 +5602,7 @@
         <v>36</v>
       </c>
       <c r="AL20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM20">
         <v>85</v>
@@ -5581,7 +5614,7 @@
         <v>13</v>
       </c>
       <c r="AP20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ20">
         <v>11.5</v>
@@ -5614,10 +5647,10 @@
         <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC20">
         <v>32</v>
@@ -5635,13 +5668,13 @@
         <v>12.5</v>
       </c>
       <c r="BH20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI20">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK20">
         <v>7.8</v>
@@ -5650,10 +5683,10 @@
         <v>120</v>
       </c>
       <c r="BM20">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BN20">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BO20">
         <v>6</v>
@@ -5671,19 +5704,19 @@
         <v>24</v>
       </c>
       <c r="BT20">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU20">
         <v>4.7</v>
       </c>
       <c r="BV20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW20">
         <v>12</v>
       </c>
       <c r="BX20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY20">
         <v>20</v>
@@ -5695,7 +5728,7 @@
         <v>15.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5703,178 +5736,178 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F21">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H21">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="K21">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
+        <v>3.9</v>
+      </c>
+      <c r="O21">
+        <v>1.26</v>
+      </c>
+      <c r="P21">
+        <v>1.98</v>
+      </c>
+      <c r="Q21">
+        <v>1.8</v>
+      </c>
+      <c r="R21">
+        <v>1.36</v>
+      </c>
+      <c r="S21">
+        <v>2.84</v>
+      </c>
+      <c r="T21">
+        <v>1.78</v>
+      </c>
+      <c r="U21">
+        <v>1.94</v>
+      </c>
+      <c r="V21">
+        <v>1.19</v>
+      </c>
+      <c r="W21">
+        <v>2.18</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>970</v>
+      </c>
+      <c r="AC21">
+        <v>970</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>25</v>
+      </c>
+      <c r="AG21">
+        <v>23</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>970</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.35</v>
+      </c>
+      <c r="AQ21">
+        <v>1.35</v>
+      </c>
+      <c r="AR21">
+        <v>1.35</v>
+      </c>
+      <c r="AS21">
+        <v>1.35</v>
+      </c>
+      <c r="AT21">
         <v>1.25</v>
       </c>
-      <c r="O21">
-        <v>1.01</v>
-      </c>
-      <c r="P21">
-        <v>1.25</v>
-      </c>
-      <c r="Q21">
-        <v>1.3</v>
-      </c>
-      <c r="R21">
-        <v>1.18</v>
-      </c>
-      <c r="S21">
-        <v>1.3</v>
-      </c>
-      <c r="T21">
-        <v>1.01</v>
-      </c>
-      <c r="U21">
-        <v>1.01</v>
-      </c>
-      <c r="V21">
+      <c r="AU21">
+        <v>6.2</v>
+      </c>
+      <c r="AV21">
+        <v>10.5</v>
+      </c>
+      <c r="AW21">
+        <v>1.35</v>
+      </c>
+      <c r="AX21">
         <v>1.28</v>
       </c>
-      <c r="W21">
-        <v>1.01</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>1000</v>
-      </c>
-      <c r="AC21">
-        <v>1000</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>1000</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>1000</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21">
-        <v>1.03</v>
-      </c>
-      <c r="AR21">
-        <v>1.03</v>
-      </c>
-      <c r="AS21">
-        <v>1.03</v>
-      </c>
-      <c r="AT21">
-        <v>1.03</v>
-      </c>
-      <c r="AU21">
-        <v>1.03</v>
-      </c>
-      <c r="AV21">
-        <v>1.03</v>
-      </c>
-      <c r="AW21">
-        <v>1.03</v>
-      </c>
-      <c r="AX21">
-        <v>1.03</v>
-      </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5937,7 +5970,7 @@
         <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5945,34 +5978,34 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F22">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="G22">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="H22">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="I22">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="J22">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5981,22 +6014,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>3.15</v>
+        <v>1.26</v>
       </c>
       <c r="O22">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R22">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6005,10 +6038,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6179,7 +6212,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6187,34 +6220,34 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F23">
-        <v>1.86</v>
+        <v>8.6</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>3.85</v>
+        <v>1.24</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6223,22 +6256,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O23">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P23">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q23">
+        <v>1.35</v>
+      </c>
+      <c r="R23">
         <v>1.58</v>
       </c>
-      <c r="R23">
-        <v>1.54</v>
-      </c>
       <c r="S23">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6247,10 +6280,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6259,10 +6292,10 @@
         <v>1000</v>
       </c>
       <c r="Z23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
         <v>1000</v>
@@ -6277,13 +6310,13 @@
         <v>1000</v>
       </c>
       <c r="AF23">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
         <v>1000</v>
       </c>
       <c r="AH23">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6292,73 +6325,73 @@
         <v>1000</v>
       </c>
       <c r="AK23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6421,186 +6454,186 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24">
+        <v>1.86</v>
+      </c>
+      <c r="G24">
+        <v>2.02</v>
+      </c>
+      <c r="H24">
+        <v>3.85</v>
+      </c>
+      <c r="I24">
+        <v>4.3</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>4.4</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>2.44</v>
+      </c>
+      <c r="O24">
+        <v>1.16</v>
+      </c>
+      <c r="P24">
+        <v>2.44</v>
+      </c>
+      <c r="Q24">
+        <v>1.52</v>
+      </c>
+      <c r="R24">
+        <v>1.54</v>
+      </c>
+      <c r="S24">
+        <v>2.26</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
+        <v>1.3</v>
+      </c>
+      <c r="W24">
+        <v>1.98</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>40</v>
+      </c>
+      <c r="AA24">
         <v>90</v>
       </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F24">
-        <v>3.35</v>
-      </c>
-      <c r="G24">
-        <v>3.6</v>
-      </c>
-      <c r="H24">
-        <v>2.14</v>
-      </c>
-      <c r="I24">
-        <v>2.24</v>
-      </c>
-      <c r="J24">
-        <v>3.75</v>
-      </c>
-      <c r="K24">
-        <v>4.1</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-      <c r="O24">
-        <v>1.23</v>
-      </c>
-      <c r="P24">
-        <v>2.28</v>
-      </c>
-      <c r="Q24">
-        <v>1.63</v>
-      </c>
-      <c r="R24">
+      <c r="AB24">
+        <v>1000</v>
+      </c>
+      <c r="AC24">
+        <v>1000</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>18</v>
+      </c>
+      <c r="AG24">
+        <v>1000</v>
+      </c>
+      <c r="AH24">
+        <v>19.5</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>22</v>
+      </c>
+      <c r="AL24">
+        <v>34</v>
+      </c>
+      <c r="AM24">
+        <v>80</v>
+      </c>
+      <c r="AN24">
+        <v>11</v>
+      </c>
+      <c r="AO24">
+        <v>40</v>
+      </c>
+      <c r="AP24">
+        <v>1.52</v>
+      </c>
+      <c r="AQ24">
+        <v>1.52</v>
+      </c>
+      <c r="AR24">
+        <v>1.47</v>
+      </c>
+      <c r="AS24">
+        <v>1.5</v>
+      </c>
+      <c r="AT24">
+        <v>1.52</v>
+      </c>
+      <c r="AU24">
+        <v>7.4</v>
+      </c>
+      <c r="AV24">
+        <v>1.52</v>
+      </c>
+      <c r="AW24">
+        <v>1.52</v>
+      </c>
+      <c r="AX24">
+        <v>10.5</v>
+      </c>
+      <c r="AY24">
+        <v>8</v>
+      </c>
+      <c r="AZ24">
+        <v>1.41</v>
+      </c>
+      <c r="BA24">
+        <v>1.52</v>
+      </c>
+      <c r="BB24">
+        <v>16</v>
+      </c>
+      <c r="BC24">
         <v>1.43</v>
       </c>
-      <c r="S24">
-        <v>2.68</v>
-      </c>
-      <c r="T24">
-        <v>1.6</v>
-      </c>
-      <c r="U24">
-        <v>2.22</v>
-      </c>
-      <c r="V24">
-        <v>1.8</v>
-      </c>
-      <c r="W24">
-        <v>1.38</v>
-      </c>
-      <c r="X24">
-        <v>22</v>
-      </c>
-      <c r="Y24">
-        <v>1000</v>
-      </c>
-      <c r="Z24">
-        <v>19.5</v>
-      </c>
-      <c r="AA24">
-        <v>34</v>
-      </c>
-      <c r="AB24">
-        <v>1000</v>
-      </c>
-      <c r="AC24">
-        <v>9.6</v>
-      </c>
-      <c r="AD24">
-        <v>21</v>
-      </c>
-      <c r="AE24">
-        <v>1000</v>
-      </c>
-      <c r="AF24">
-        <v>34</v>
-      </c>
-      <c r="AG24">
-        <v>18.5</v>
-      </c>
-      <c r="AH24">
-        <v>20</v>
-      </c>
-      <c r="AI24">
-        <v>38</v>
-      </c>
-      <c r="AJ24">
-        <v>80</v>
-      </c>
-      <c r="AK24">
-        <v>1000</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>90</v>
-      </c>
-      <c r="AN24">
-        <v>36</v>
-      </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>16</v>
-      </c>
-      <c r="AQ24">
-        <v>10</v>
-      </c>
-      <c r="AR24">
-        <v>1.8</v>
-      </c>
-      <c r="AS24">
-        <v>19</v>
-      </c>
-      <c r="AT24">
-        <v>1.99</v>
-      </c>
-      <c r="AU24">
-        <v>7.6</v>
-      </c>
-      <c r="AV24">
-        <v>1.81</v>
-      </c>
-      <c r="AW24">
-        <v>17.5</v>
-      </c>
-      <c r="AX24">
-        <v>18</v>
-      </c>
-      <c r="AY24">
-        <v>1.79</v>
-      </c>
-      <c r="AZ24">
-        <v>1.8</v>
-      </c>
-      <c r="BA24">
-        <v>1.89</v>
-      </c>
-      <c r="BB24">
-        <v>1.94</v>
-      </c>
-      <c r="BC24">
-        <v>1.99</v>
-      </c>
       <c r="BD24">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="BE24">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="BF24">
-        <v>19</v>
+        <v>1.34</v>
       </c>
       <c r="BG24">
-        <v>11</v>
+        <v>1.47</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6663,192 +6696,192 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F25">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="G25">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="H25">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="I25">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="J25">
         <v>3.7</v>
       </c>
       <c r="K25">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N25">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P25">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="R25">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S25">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V25">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="W25">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y25">
         <v>1000</v>
       </c>
       <c r="Z25">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
+        <v>9.6</v>
+      </c>
+      <c r="AD25">
+        <v>21</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>34</v>
+      </c>
+      <c r="AG25">
+        <v>970</v>
+      </c>
+      <c r="AH25">
+        <v>970</v>
+      </c>
+      <c r="AI25">
+        <v>38</v>
+      </c>
+      <c r="AJ25">
+        <v>80</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>90</v>
+      </c>
+      <c r="AN25">
+        <v>36</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25">
+        <v>10</v>
+      </c>
+      <c r="AR25">
+        <v>1.8</v>
+      </c>
+      <c r="AS25">
+        <v>19</v>
+      </c>
+      <c r="AT25">
+        <v>1.99</v>
+      </c>
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
+        <v>1.81</v>
+      </c>
+      <c r="AW25">
+        <v>17.5</v>
+      </c>
+      <c r="AX25">
+        <v>18</v>
+      </c>
+      <c r="AY25">
+        <v>1.79</v>
+      </c>
+      <c r="AZ25">
+        <v>1.8</v>
+      </c>
+      <c r="BA25">
+        <v>1.89</v>
+      </c>
+      <c r="BB25">
+        <v>1.94</v>
+      </c>
+      <c r="BC25">
+        <v>1.99</v>
+      </c>
+      <c r="BD25">
+        <v>1.99</v>
+      </c>
+      <c r="BE25">
+        <v>1.94</v>
+      </c>
+      <c r="BF25">
+        <v>19</v>
+      </c>
+      <c r="BG25">
         <v>11</v>
       </c>
-      <c r="AD25">
-        <v>1000</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>40</v>
-      </c>
-      <c r="AG25">
-        <v>22</v>
-      </c>
-      <c r="AH25">
-        <v>1000</v>
-      </c>
-      <c r="AI25">
-        <v>44</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>17</v>
-      </c>
-      <c r="AP25">
-        <v>1.54</v>
-      </c>
-      <c r="AQ25">
-        <v>7</v>
-      </c>
-      <c r="AR25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS25">
-        <v>16</v>
-      </c>
-      <c r="AT25">
-        <v>11</v>
-      </c>
-      <c r="AU25">
-        <v>1.35</v>
-      </c>
-      <c r="AV25">
-        <v>7.4</v>
-      </c>
-      <c r="AW25">
-        <v>1.54</v>
-      </c>
-      <c r="AX25">
-        <v>21</v>
-      </c>
-      <c r="AY25">
-        <v>1.44</v>
-      </c>
-      <c r="AZ25">
-        <v>1.54</v>
-      </c>
-      <c r="BA25">
-        <v>1.49</v>
-      </c>
-      <c r="BB25">
-        <v>1.54</v>
-      </c>
-      <c r="BC25">
-        <v>1.54</v>
-      </c>
-      <c r="BD25">
-        <v>1.54</v>
-      </c>
-      <c r="BE25">
-        <v>1.54</v>
-      </c>
-      <c r="BF25">
-        <v>1.54</v>
-      </c>
-      <c r="BG25">
-        <v>1.41</v>
-      </c>
       <c r="BH25">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
@@ -6905,192 +6938,192 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F26">
-        <v>1.72</v>
+        <v>3.85</v>
       </c>
       <c r="G26">
-        <v>1.82</v>
+        <v>4.5</v>
       </c>
       <c r="H26">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="I26">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J26">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O26">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q26">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
         <v>1.35</v>
       </c>
       <c r="S26">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T26">
+        <v>1.68</v>
+      </c>
+      <c r="U26">
+        <v>2.08</v>
+      </c>
+      <c r="V26">
+        <v>1.9</v>
+      </c>
+      <c r="W26">
+        <v>1.28</v>
+      </c>
+      <c r="X26">
+        <v>20</v>
+      </c>
+      <c r="Y26">
+        <v>11</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>970</v>
+      </c>
+      <c r="AC26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>40</v>
+      </c>
+      <c r="AG26">
+        <v>970</v>
+      </c>
+      <c r="AH26">
+        <v>22</v>
+      </c>
+      <c r="AI26">
+        <v>44</v>
+      </c>
+      <c r="AJ26">
+        <v>100</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.71</v>
+      </c>
+      <c r="AQ26">
+        <v>7.2</v>
+      </c>
+      <c r="AR26">
+        <v>10.5</v>
+      </c>
+      <c r="AS26">
+        <v>16</v>
+      </c>
+      <c r="AT26">
+        <v>1.69</v>
+      </c>
+      <c r="AU26">
+        <v>7.2</v>
+      </c>
+      <c r="AV26">
+        <v>9</v>
+      </c>
+      <c r="AW26">
+        <v>16.5</v>
+      </c>
+      <c r="AX26">
+        <v>21</v>
+      </c>
+      <c r="AY26">
+        <v>1.7</v>
+      </c>
+      <c r="AZ26">
+        <v>1.73</v>
+      </c>
+      <c r="BA26">
         <v>1.8</v>
       </c>
-      <c r="U26">
-        <v>1.91</v>
-      </c>
-      <c r="V26">
-        <v>1.23</v>
-      </c>
-      <c r="W26">
-        <v>2.2</v>
-      </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>16.5</v>
-      </c>
-      <c r="AC26">
-        <v>15.5</v>
-      </c>
-      <c r="AD26">
-        <v>1000</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>25</v>
-      </c>
-      <c r="AG26">
-        <v>23</v>
-      </c>
-      <c r="AH26">
-        <v>1000</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>1000</v>
-      </c>
-      <c r="AK26">
-        <v>1000</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>18.5</v>
-      </c>
-      <c r="AO26">
-        <v>1000</v>
-      </c>
-      <c r="AP26">
-        <v>1.35</v>
-      </c>
-      <c r="AQ26">
-        <v>1.35</v>
-      </c>
-      <c r="AR26">
-        <v>1.35</v>
-      </c>
-      <c r="AS26">
-        <v>1.35</v>
-      </c>
-      <c r="AT26">
-        <v>1.25</v>
-      </c>
-      <c r="AU26">
-        <v>6.2</v>
-      </c>
-      <c r="AV26">
-        <v>1.35</v>
-      </c>
-      <c r="AW26">
-        <v>1.35</v>
-      </c>
-      <c r="AX26">
-        <v>1.28</v>
-      </c>
-      <c r="AY26">
-        <v>6.6</v>
-      </c>
-      <c r="AZ26">
-        <v>10.5</v>
-      </c>
-      <c r="BA26">
-        <v>1.35</v>
-      </c>
       <c r="BB26">
-        <v>8.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="BC26">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="BD26">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="BE26">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="BF26">
-        <v>1.26</v>
+        <v>1.88</v>
       </c>
       <c r="BG26">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
@@ -7147,7 +7180,7 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7155,16 +7188,16 @@
         <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F27">
         <v>1.85</v>
@@ -7179,7 +7212,7 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7194,19 +7227,19 @@
         <v>1.25</v>
       </c>
       <c r="O27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P27">
         <v>1.25</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R27">
         <v>1.24</v>
       </c>
       <c r="S27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T27">
         <v>1.01</v>
@@ -7275,52 +7308,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7389,78 +7422,78 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F28">
+        <v>1.04</v>
+      </c>
+      <c r="G28">
+        <v>1000</v>
+      </c>
+      <c r="H28">
+        <v>1.04</v>
+      </c>
+      <c r="I28">
+        <v>1000</v>
+      </c>
+      <c r="J28">
+        <v>1.02</v>
+      </c>
+      <c r="K28">
+        <v>950</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>1.25</v>
+      </c>
+      <c r="O28">
+        <v>1.33</v>
+      </c>
+      <c r="P28">
+        <v>1.24</v>
+      </c>
+      <c r="Q28">
+        <v>1.33</v>
+      </c>
+      <c r="R28">
         <v>1.12</v>
       </c>
-      <c r="G28">
-        <v>1.13</v>
-      </c>
-      <c r="H28">
-        <v>24</v>
-      </c>
-      <c r="I28">
-        <v>25</v>
-      </c>
-      <c r="J28">
-        <v>14.5</v>
-      </c>
-      <c r="K28">
-        <v>15.5</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>1.01</v>
-      </c>
-      <c r="N28">
-        <v>17.5</v>
-      </c>
-      <c r="O28">
-        <v>1.05</v>
-      </c>
-      <c r="P28">
-        <v>6.8</v>
-      </c>
-      <c r="Q28">
-        <v>1.15</v>
-      </c>
-      <c r="R28">
-        <v>3.25</v>
-      </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7469,148 +7502,148 @@
         <v>1000</v>
       </c>
       <c r="Z28">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
         <v>1000</v>
       </c>
       <c r="AE28">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
         <v>1000</v>
       </c>
       <c r="AN28">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AR28">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AU28">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AV28">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AW28">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BA28">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7622,258 +7655,258 @@
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F29">
-        <v>2.64</v>
+        <v>1.3</v>
       </c>
       <c r="G29">
-        <v>2.68</v>
+        <v>1.31</v>
       </c>
       <c r="H29">
-        <v>2.86</v>
+        <v>12.5</v>
       </c>
       <c r="I29">
-        <v>2.9</v>
+        <v>15</v>
       </c>
       <c r="J29">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="K29">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T29">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X29">
+        <v>19.5</v>
+      </c>
+      <c r="Y29">
+        <v>36</v>
+      </c>
+      <c r="Z29">
+        <v>160</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>7.6</v>
+      </c>
+      <c r="AC29">
+        <v>14.5</v>
+      </c>
+      <c r="AD29">
+        <v>55</v>
+      </c>
+      <c r="AE29">
+        <v>330</v>
+      </c>
+      <c r="AF29">
+        <v>7.4</v>
+      </c>
+      <c r="AG29">
+        <v>11.5</v>
+      </c>
+      <c r="AH29">
+        <v>40</v>
+      </c>
+      <c r="AI29">
+        <v>250</v>
+      </c>
+      <c r="AJ29">
+        <v>9.6</v>
+      </c>
+      <c r="AK29">
+        <v>17</v>
+      </c>
+      <c r="AL29">
+        <v>55</v>
+      </c>
+      <c r="AM29">
+        <v>310</v>
+      </c>
+      <c r="AN29">
+        <v>5.9</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
         <v>16.5</v>
       </c>
-      <c r="Y29">
+      <c r="AQ29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR29">
+        <v>10.5</v>
+      </c>
+      <c r="AS29">
+        <v>11</v>
+      </c>
+      <c r="AT29">
+        <v>6.8</v>
+      </c>
+      <c r="AU29">
+        <v>12</v>
+      </c>
+      <c r="AV29">
+        <v>9.4</v>
+      </c>
+      <c r="AW29">
+        <v>10.5</v>
+      </c>
+      <c r="AX29">
+        <v>6.4</v>
+      </c>
+      <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
+        <v>9</v>
+      </c>
+      <c r="BA29">
+        <v>10.5</v>
+      </c>
+      <c r="BB29">
+        <v>8.4</v>
+      </c>
+      <c r="BC29">
         <v>14</v>
       </c>
-      <c r="Z29">
-        <v>21</v>
-      </c>
-      <c r="AA29">
-        <v>44</v>
-      </c>
-      <c r="AB29">
-        <v>12.5</v>
-      </c>
-      <c r="AC29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD29">
-        <v>13</v>
-      </c>
-      <c r="AE29">
-        <v>30</v>
-      </c>
-      <c r="AF29">
-        <v>18</v>
-      </c>
-      <c r="AG29">
-        <v>12.5</v>
-      </c>
-      <c r="AH29">
-        <v>15.5</v>
-      </c>
-      <c r="AI29">
-        <v>44</v>
-      </c>
-      <c r="AJ29">
-        <v>38</v>
-      </c>
-      <c r="AK29">
-        <v>28</v>
-      </c>
-      <c r="AL29">
-        <v>38</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>20</v>
-      </c>
-      <c r="AO29">
-        <v>23</v>
-      </c>
-      <c r="AP29">
-        <v>15</v>
-      </c>
-      <c r="AQ29">
-        <v>12</v>
-      </c>
-      <c r="AR29">
-        <v>18</v>
-      </c>
-      <c r="AS29">
-        <v>24</v>
-      </c>
-      <c r="AT29">
-        <v>11.5</v>
-      </c>
-      <c r="AU29">
-        <v>7.6</v>
-      </c>
-      <c r="AV29">
-        <v>11.5</v>
-      </c>
-      <c r="AW29">
-        <v>18.5</v>
-      </c>
-      <c r="AX29">
-        <v>16</v>
-      </c>
-      <c r="AY29">
+      <c r="BD29">
+        <v>9.4</v>
+      </c>
+      <c r="BE29">
+        <v>10.5</v>
+      </c>
+      <c r="BF29">
+        <v>5.2</v>
+      </c>
+      <c r="BG29">
         <v>11</v>
       </c>
-      <c r="AZ29">
-        <v>14</v>
-      </c>
-      <c r="BA29">
-        <v>23</v>
-      </c>
-      <c r="BB29">
-        <v>22</v>
-      </c>
-      <c r="BC29">
-        <v>18</v>
-      </c>
-      <c r="BD29">
-        <v>23</v>
-      </c>
-      <c r="BE29">
-        <v>32</v>
-      </c>
-      <c r="BF29">
-        <v>17.5</v>
-      </c>
-      <c r="BG29">
-        <v>20</v>
-      </c>
       <c r="BH29">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="BJ29">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>8</v>
+        <v>1.29</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>65</v>
+        <v>1.29</v>
       </c>
       <c r="BN29">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP29">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>13.5</v>
+        <v>1.29</v>
       </c>
       <c r="BR29">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>20</v>
+        <v>1.29</v>
       </c>
       <c r="BT29">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>5.5</v>
+        <v>1.29</v>
       </c>
       <c r="BV29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>15</v>
+        <v>1.29</v>
       </c>
       <c r="BX29">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>21</v>
+        <v>1.29</v>
       </c>
       <c r="BZ29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>15.5</v>
+        <v>1.29</v>
       </c>
       <c r="CB29" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7881,22 +7914,22 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F30">
+        <v>1.14</v>
+      </c>
+      <c r="G30">
         <v>1.15</v>
-      </c>
-      <c r="G30">
-        <v>1.16</v>
       </c>
       <c r="H30">
         <v>28</v>
@@ -7908,10 +7941,10 @@
         <v>10.5</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M30">
         <v>1.01</v>
@@ -7923,28 +7956,28 @@
         <v>1.09</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q30">
         <v>1.28</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S30">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T30">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U30">
         <v>1.86</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="X30">
         <v>60</v>
@@ -7962,7 +7995,7 @@
         <v>18.5</v>
       </c>
       <c r="AC30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD30">
         <v>120</v>
@@ -7977,7 +8010,7 @@
         <v>16.5</v>
       </c>
       <c r="AH30">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI30">
         <v>1000</v>
@@ -8010,7 +8043,7 @@
         <v>55</v>
       </c>
       <c r="AS30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT30">
         <v>16</v>
@@ -8031,7 +8064,7 @@
         <v>14</v>
       </c>
       <c r="AZ30">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BA30">
         <v>50</v>
@@ -8052,7 +8085,7 @@
         <v>2.22</v>
       </c>
       <c r="BG30">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH30">
         <v>7.8</v>
@@ -8070,7 +8103,7 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN30">
         <v>4.8</v>
@@ -8100,13 +8133,13 @@
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX30">
         <v>120</v>
       </c>
       <c r="BY30">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ30">
         <v>5.9</v>
@@ -8115,7 +8148,7 @@
         <v>4.1</v>
       </c>
       <c r="CB30" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8123,483 +8156,1209 @@
         <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F31">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="G31">
-        <v>1.91</v>
+        <v>2.68</v>
       </c>
       <c r="H31">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="I31">
+        <v>2.9</v>
+      </c>
+      <c r="J31">
+        <v>3.6</v>
+      </c>
+      <c r="K31">
+        <v>3.65</v>
+      </c>
+      <c r="L31">
+        <v>1.36</v>
+      </c>
+      <c r="M31">
+        <v>1.06</v>
+      </c>
+      <c r="N31">
         <v>4.3</v>
       </c>
-      <c r="J31">
-        <v>4.1</v>
-      </c>
-      <c r="K31">
-        <v>4.2</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>1.04</v>
-      </c>
-      <c r="N31">
-        <v>5.5</v>
-      </c>
       <c r="O31">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="P31">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="R31">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="S31">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="T31">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X31">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="Y31">
+        <v>13.5</v>
+      </c>
+      <c r="Z31">
+        <v>21</v>
+      </c>
+      <c r="AA31">
+        <v>44</v>
+      </c>
+      <c r="AB31">
+        <v>12.5</v>
+      </c>
+      <c r="AC31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD31">
+        <v>13</v>
+      </c>
+      <c r="AE31">
+        <v>29</v>
+      </c>
+      <c r="AF31">
+        <v>18</v>
+      </c>
+      <c r="AG31">
+        <v>12</v>
+      </c>
+      <c r="AH31">
+        <v>15.5</v>
+      </c>
+      <c r="AI31">
+        <v>38</v>
+      </c>
+      <c r="AJ31">
+        <v>38</v>
+      </c>
+      <c r="AK31">
+        <v>27</v>
+      </c>
+      <c r="AL31">
+        <v>38</v>
+      </c>
+      <c r="AM31">
+        <v>75</v>
+      </c>
+      <c r="AN31">
+        <v>19.5</v>
+      </c>
+      <c r="AO31">
         <v>23</v>
       </c>
-      <c r="Z31">
-        <v>36</v>
-      </c>
-      <c r="AA31">
-        <v>1000</v>
-      </c>
-      <c r="AB31">
-        <v>13</v>
-      </c>
-      <c r="AC31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD31">
+      <c r="AP31">
+        <v>15</v>
+      </c>
+      <c r="AQ31">
+        <v>12.5</v>
+      </c>
+      <c r="AR31">
+        <v>18</v>
+      </c>
+      <c r="AS31">
+        <v>40</v>
+      </c>
+      <c r="AT31">
+        <v>12</v>
+      </c>
+      <c r="AU31">
+        <v>7.6</v>
+      </c>
+      <c r="AV31">
+        <v>11.5</v>
+      </c>
+      <c r="AW31">
+        <v>26</v>
+      </c>
+      <c r="AX31">
+        <v>16.5</v>
+      </c>
+      <c r="AY31">
+        <v>11</v>
+      </c>
+      <c r="AZ31">
+        <v>14.5</v>
+      </c>
+      <c r="BA31">
+        <v>34</v>
+      </c>
+      <c r="BB31">
+        <v>34</v>
+      </c>
+      <c r="BC31">
+        <v>24</v>
+      </c>
+      <c r="BD31">
+        <v>32</v>
+      </c>
+      <c r="BE31">
+        <v>32</v>
+      </c>
+      <c r="BF31">
         <v>17.5</v>
       </c>
-      <c r="AE31">
-        <v>46</v>
-      </c>
-      <c r="AF31">
-        <v>14.5</v>
-      </c>
-      <c r="AG31">
-        <v>10.5</v>
-      </c>
-      <c r="AH31">
-        <v>16</v>
-      </c>
-      <c r="AI31">
-        <v>46</v>
-      </c>
-      <c r="AJ31">
-        <v>23</v>
-      </c>
-      <c r="AK31">
-        <v>18</v>
-      </c>
-      <c r="AL31">
-        <v>28</v>
-      </c>
-      <c r="AM31">
-        <v>65</v>
-      </c>
-      <c r="AN31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO31">
-        <v>34</v>
-      </c>
-      <c r="AP31">
-        <v>20</v>
-      </c>
-      <c r="AQ31">
-        <v>18</v>
-      </c>
-      <c r="AR31">
-        <v>22</v>
-      </c>
-      <c r="AS31">
-        <v>36</v>
-      </c>
-      <c r="AT31">
-        <v>11.5</v>
-      </c>
-      <c r="AU31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV31">
-        <v>15.5</v>
-      </c>
-      <c r="AW31">
-        <v>34</v>
-      </c>
-      <c r="AX31">
-        <v>12.5</v>
-      </c>
-      <c r="AY31">
-        <v>9.6</v>
-      </c>
-      <c r="AZ31">
-        <v>13.5</v>
-      </c>
-      <c r="BA31">
-        <v>25</v>
-      </c>
-      <c r="BB31">
-        <v>19</v>
-      </c>
-      <c r="BC31">
-        <v>15</v>
-      </c>
-      <c r="BD31">
-        <v>18</v>
-      </c>
-      <c r="BE31">
-        <v>30</v>
-      </c>
-      <c r="BF31">
-        <v>7.8</v>
-      </c>
       <c r="BG31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH31">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BI31">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BJ31">
         <v>9</v>
       </c>
       <c r="BK31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="BN31">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BO31">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BP31">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BQ31">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BR31">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BS31">
+        <v>20</v>
+      </c>
+      <c r="BT31">
+        <v>6.2</v>
+      </c>
+      <c r="BU31">
+        <v>5.5</v>
+      </c>
+      <c r="BV31">
+        <v>21</v>
+      </c>
+      <c r="BW31">
+        <v>15</v>
+      </c>
+      <c r="BX31">
+        <v>30</v>
+      </c>
+      <c r="BY31">
+        <v>21</v>
+      </c>
+      <c r="BZ31">
+        <v>22</v>
+      </c>
+      <c r="CA31">
         <v>15.5</v>
       </c>
-      <c r="BT31">
-        <v>7.8</v>
-      </c>
-      <c r="BU31">
-        <v>6.8</v>
-      </c>
-      <c r="BV31">
-        <v>30</v>
-      </c>
-      <c r="BW31">
-        <v>21</v>
-      </c>
-      <c r="BX31">
-        <v>36</v>
-      </c>
-      <c r="BY31">
-        <v>24</v>
-      </c>
-      <c r="BZ31">
-        <v>16.5</v>
-      </c>
-      <c r="CA31">
-        <v>11</v>
-      </c>
       <c r="CB31" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F32">
-        <v>5.4</v>
+        <v>1.92</v>
       </c>
       <c r="G32">
+        <v>1.94</v>
+      </c>
+      <c r="H32">
+        <v>4.1</v>
+      </c>
+      <c r="I32">
+        <v>4.2</v>
+      </c>
+      <c r="J32">
+        <v>4.1</v>
+      </c>
+      <c r="K32">
+        <v>4.2</v>
+      </c>
+      <c r="L32">
+        <v>1.29</v>
+      </c>
+      <c r="M32">
+        <v>1.04</v>
+      </c>
+      <c r="N32">
+        <v>5.5</v>
+      </c>
+      <c r="O32">
+        <v>1.21</v>
+      </c>
+      <c r="P32">
+        <v>2.52</v>
+      </c>
+      <c r="Q32">
+        <v>1.62</v>
+      </c>
+      <c r="R32">
+        <v>1.61</v>
+      </c>
+      <c r="S32">
+        <v>2.5</v>
+      </c>
+      <c r="T32">
+        <v>1.6</v>
+      </c>
+      <c r="U32">
+        <v>2.6</v>
+      </c>
+      <c r="V32">
+        <v>1.31</v>
+      </c>
+      <c r="W32">
+        <v>2.06</v>
+      </c>
+      <c r="X32">
+        <v>24</v>
+      </c>
+      <c r="Y32">
+        <v>22</v>
+      </c>
+      <c r="Z32">
+        <v>34</v>
+      </c>
+      <c r="AA32">
+        <v>85</v>
+      </c>
+      <c r="AB32">
+        <v>13</v>
+      </c>
+      <c r="AC32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD32">
+        <v>17</v>
+      </c>
+      <c r="AE32">
+        <v>42</v>
+      </c>
+      <c r="AF32">
+        <v>14.5</v>
+      </c>
+      <c r="AG32">
+        <v>10.5</v>
+      </c>
+      <c r="AH32">
+        <v>16</v>
+      </c>
+      <c r="AI32">
+        <v>44</v>
+      </c>
+      <c r="AJ32">
+        <v>22</v>
+      </c>
+      <c r="AK32">
+        <v>17.5</v>
+      </c>
+      <c r="AL32">
+        <v>27</v>
+      </c>
+      <c r="AM32">
+        <v>65</v>
+      </c>
+      <c r="AN32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO32">
+        <v>34</v>
+      </c>
+      <c r="AP32">
+        <v>20</v>
+      </c>
+      <c r="AQ32">
+        <v>19.5</v>
+      </c>
+      <c r="AR32">
+        <v>30</v>
+      </c>
+      <c r="AS32">
+        <v>36</v>
+      </c>
+      <c r="AT32">
+        <v>12</v>
+      </c>
+      <c r="AU32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV32">
+        <v>15</v>
+      </c>
+      <c r="AW32">
+        <v>38</v>
+      </c>
+      <c r="AX32">
+        <v>12.5</v>
+      </c>
+      <c r="AY32">
+        <v>9.6</v>
+      </c>
+      <c r="AZ32">
+        <v>14</v>
+      </c>
+      <c r="BA32">
+        <v>38</v>
+      </c>
+      <c r="BB32">
+        <v>19.5</v>
+      </c>
+      <c r="BC32">
+        <v>15.5</v>
+      </c>
+      <c r="BD32">
+        <v>23</v>
+      </c>
+      <c r="BE32">
+        <v>50</v>
+      </c>
+      <c r="BF32">
+        <v>8</v>
+      </c>
+      <c r="BG32">
+        <v>27</v>
+      </c>
+      <c r="BH32">
+        <v>4.2</v>
+      </c>
+      <c r="BI32">
+        <v>3.8</v>
+      </c>
+      <c r="BJ32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK32">
+        <v>7.8</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>21</v>
+      </c>
+      <c r="BN32">
+        <v>5</v>
+      </c>
+      <c r="BO32">
+        <v>4.6</v>
+      </c>
+      <c r="BP32">
+        <v>13</v>
+      </c>
+      <c r="BQ32">
+        <v>11</v>
+      </c>
+      <c r="BR32">
+        <v>23</v>
+      </c>
+      <c r="BS32">
+        <v>15.5</v>
+      </c>
+      <c r="BT32">
+        <v>7.8</v>
+      </c>
+      <c r="BU32">
+        <v>7</v>
+      </c>
+      <c r="BV32">
+        <v>30</v>
+      </c>
+      <c r="BW32">
+        <v>21</v>
+      </c>
+      <c r="BX32">
+        <v>36</v>
+      </c>
+      <c r="BY32">
+        <v>24</v>
+      </c>
+      <c r="BZ32">
+        <v>16</v>
+      </c>
+      <c r="CA32">
+        <v>11</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33">
+        <v>3.25</v>
+      </c>
+      <c r="G33">
+        <v>3.45</v>
+      </c>
+      <c r="H33">
+        <v>2.32</v>
+      </c>
+      <c r="I33">
+        <v>2.42</v>
+      </c>
+      <c r="J33">
+        <v>3.45</v>
+      </c>
+      <c r="K33">
+        <v>3.65</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.07</v>
+      </c>
+      <c r="N33">
+        <v>3.55</v>
+      </c>
+      <c r="O33">
+        <v>1.35</v>
+      </c>
+      <c r="P33">
+        <v>1.84</v>
+      </c>
+      <c r="Q33">
+        <v>2.02</v>
+      </c>
+      <c r="R33">
+        <v>1.34</v>
+      </c>
+      <c r="S33">
+        <v>3.55</v>
+      </c>
+      <c r="T33">
+        <v>1.82</v>
+      </c>
+      <c r="U33">
+        <v>2.08</v>
+      </c>
+      <c r="V33">
+        <v>1.71</v>
+      </c>
+      <c r="W33">
+        <v>1.4</v>
+      </c>
+      <c r="X33">
+        <v>16</v>
+      </c>
+      <c r="Y33">
+        <v>10.5</v>
+      </c>
+      <c r="Z33">
+        <v>18.5</v>
+      </c>
+      <c r="AA33">
+        <v>40</v>
+      </c>
+      <c r="AB33">
+        <v>15</v>
+      </c>
+      <c r="AC33">
+        <v>8</v>
+      </c>
+      <c r="AD33">
+        <v>14</v>
+      </c>
+      <c r="AE33">
+        <v>32</v>
+      </c>
+      <c r="AF33">
+        <v>28</v>
+      </c>
+      <c r="AG33">
+        <v>17.5</v>
+      </c>
+      <c r="AH33">
+        <v>22</v>
+      </c>
+      <c r="AI33">
+        <v>50</v>
+      </c>
+      <c r="AJ33">
+        <v>75</v>
+      </c>
+      <c r="AK33">
+        <v>50</v>
+      </c>
+      <c r="AL33">
+        <v>65</v>
+      </c>
+      <c r="AM33">
+        <v>120</v>
+      </c>
+      <c r="AN33">
+        <v>48</v>
+      </c>
+      <c r="AO33">
+        <v>26</v>
+      </c>
+      <c r="AP33">
+        <v>11.5</v>
+      </c>
+      <c r="AQ33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR33">
+        <v>13</v>
+      </c>
+      <c r="AS33">
+        <v>5.8</v>
+      </c>
+      <c r="AT33">
+        <v>10.5</v>
+      </c>
+      <c r="AU33">
+        <v>7</v>
+      </c>
+      <c r="AV33">
+        <v>10</v>
+      </c>
+      <c r="AW33">
+        <v>19</v>
+      </c>
+      <c r="AX33">
+        <v>19.5</v>
+      </c>
+      <c r="AY33">
+        <v>12.5</v>
+      </c>
+      <c r="AZ33">
+        <v>15.5</v>
+      </c>
+      <c r="BA33">
         <v>5.9</v>
       </c>
-      <c r="H32">
-        <v>1.73</v>
-      </c>
-      <c r="I32">
-        <v>1.81</v>
-      </c>
-      <c r="J32">
-        <v>3.85</v>
-      </c>
-      <c r="K32">
-        <v>4</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.94</v>
-      </c>
-      <c r="Q32">
+      <c r="BB33">
+        <v>6</v>
+      </c>
+      <c r="BC33">
+        <v>5.9</v>
+      </c>
+      <c r="BD33">
+        <v>6</v>
+      </c>
+      <c r="BE33">
+        <v>6.2</v>
+      </c>
+      <c r="BF33">
+        <v>5.9</v>
+      </c>
+      <c r="BG33">
+        <v>18.5</v>
+      </c>
+      <c r="BH33">
+        <v>4.1</v>
+      </c>
+      <c r="BI33">
+        <v>2.82</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.33</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.33</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.33</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.33</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.33</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.33</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.33</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.33</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.33</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34">
+        <v>1.12</v>
+      </c>
+      <c r="G34">
+        <v>1.13</v>
+      </c>
+      <c r="H34">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>26</v>
+      </c>
+      <c r="J34">
+        <v>14</v>
+      </c>
+      <c r="K34">
+        <v>14.5</v>
+      </c>
+      <c r="L34">
+        <v>1.1</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>17.5</v>
+      </c>
+      <c r="O34">
+        <v>1.05</v>
+      </c>
+      <c r="P34">
+        <v>6.8</v>
+      </c>
+      <c r="Q34">
+        <v>1.15</v>
+      </c>
+      <c r="R34">
+        <v>3.2</v>
+      </c>
+      <c r="S34">
+        <v>1.41</v>
+      </c>
+      <c r="T34">
+        <v>1.69</v>
+      </c>
+      <c r="U34">
+        <v>2.42</v>
+      </c>
+      <c r="V34">
+        <v>1.04</v>
+      </c>
+      <c r="W34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>370</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>36</v>
+      </c>
+      <c r="AC34">
+        <v>55</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>310</v>
+      </c>
+      <c r="AF34">
+        <v>19</v>
+      </c>
+      <c r="AG34">
+        <v>18.5</v>
+      </c>
+      <c r="AH34">
+        <v>160</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>11.5</v>
+      </c>
+      <c r="AK34">
+        <v>14.5</v>
+      </c>
+      <c r="AL34">
+        <v>32</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1.9</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>40</v>
+      </c>
+      <c r="AQ34">
+        <v>40</v>
+      </c>
+      <c r="AR34">
+        <v>13.5</v>
+      </c>
+      <c r="AS34">
+        <v>14</v>
+      </c>
+      <c r="AT34">
+        <v>21</v>
+      </c>
+      <c r="AU34">
+        <v>24</v>
+      </c>
+      <c r="AV34">
+        <v>36</v>
+      </c>
+      <c r="AW34">
+        <v>13.5</v>
+      </c>
+      <c r="AX34">
+        <v>16.5</v>
+      </c>
+      <c r="AY34">
+        <v>16.5</v>
+      </c>
+      <c r="AZ34">
+        <v>26</v>
+      </c>
+      <c r="BA34">
+        <v>44</v>
+      </c>
+      <c r="BB34">
+        <v>10</v>
+      </c>
+      <c r="BC34">
+        <v>12.5</v>
+      </c>
+      <c r="BD34">
+        <v>20</v>
+      </c>
+      <c r="BE34">
+        <v>40</v>
+      </c>
+      <c r="BF34">
+        <v>1.83</v>
+      </c>
+      <c r="BG34">
+        <v>85</v>
+      </c>
+      <c r="BH34">
+        <v>11</v>
+      </c>
+      <c r="BI34">
+        <v>8</v>
+      </c>
+      <c r="BJ34">
+        <v>14.5</v>
+      </c>
+      <c r="BK34">
+        <v>10</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>21</v>
+      </c>
+      <c r="BN34">
+        <v>5.8</v>
+      </c>
+      <c r="BO34">
+        <v>4.7</v>
+      </c>
+      <c r="BP34">
+        <v>6.6</v>
+      </c>
+      <c r="BQ34">
+        <v>5.3</v>
+      </c>
+      <c r="BR34">
+        <v>17</v>
+      </c>
+      <c r="BS34">
+        <v>13.5</v>
+      </c>
+      <c r="BT34">
+        <v>26</v>
+      </c>
+      <c r="BU34">
+        <v>17</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>21</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>48</v>
+      </c>
+      <c r="BZ34">
+        <v>4.4</v>
+      </c>
+      <c r="CA34">
+        <v>3.35</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35">
+        <v>5.5</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35">
+        <v>1.75</v>
+      </c>
+      <c r="I35">
+        <v>1.78</v>
+      </c>
+      <c r="J35">
+        <v>3.9</v>
+      </c>
+      <c r="K35">
+        <v>4.1</v>
+      </c>
+      <c r="L35">
+        <v>1.43</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>3.35</v>
+      </c>
+      <c r="O35">
+        <v>1.33</v>
+      </c>
+      <c r="P35">
+        <v>1.86</v>
+      </c>
+      <c r="Q35">
         <v>2.02</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
-      <c r="AY32">
-        <v>0</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>0</v>
-      </c>
-      <c r="BC32">
-        <v>0</v>
-      </c>
-      <c r="BD32">
-        <v>0</v>
-      </c>
-      <c r="BE32">
-        <v>0</v>
-      </c>
-      <c r="BF32">
-        <v>0</v>
-      </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
-      <c r="BH32">
-        <v>0</v>
-      </c>
-      <c r="BI32">
-        <v>0</v>
-      </c>
-      <c r="BJ32">
-        <v>0</v>
-      </c>
-      <c r="BK32">
-        <v>0</v>
-      </c>
-      <c r="BL32">
-        <v>0</v>
-      </c>
-      <c r="BM32">
-        <v>0</v>
-      </c>
-      <c r="BN32">
-        <v>0</v>
-      </c>
-      <c r="BO32">
-        <v>0</v>
-      </c>
-      <c r="BP32">
-        <v>0</v>
-      </c>
-      <c r="BQ32">
-        <v>0</v>
-      </c>
-      <c r="BR32">
-        <v>0</v>
-      </c>
-      <c r="BS32">
-        <v>0</v>
-      </c>
-      <c r="BT32">
-        <v>0</v>
-      </c>
-      <c r="BU32">
-        <v>0</v>
-      </c>
-      <c r="BV32">
-        <v>0</v>
-      </c>
-      <c r="BW32">
-        <v>0</v>
-      </c>
-      <c r="BX32">
-        <v>0</v>
-      </c>
-      <c r="BY32">
-        <v>0</v>
-      </c>
-      <c r="BZ32">
-        <v>0</v>
-      </c>
-      <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>169</v>
+      <c r="R35">
+        <v>1.33</v>
+      </c>
+      <c r="S35">
+        <v>3.65</v>
+      </c>
+      <c r="T35">
+        <v>1.83</v>
+      </c>
+      <c r="U35">
+        <v>1.86</v>
+      </c>
+      <c r="V35">
+        <v>2.28</v>
+      </c>
+      <c r="W35">
+        <v>1.21</v>
+      </c>
+      <c r="X35">
+        <v>13.5</v>
+      </c>
+      <c r="Y35">
+        <v>8.4</v>
+      </c>
+      <c r="Z35">
+        <v>10.5</v>
+      </c>
+      <c r="AA35">
+        <v>18</v>
+      </c>
+      <c r="AB35">
+        <v>20</v>
+      </c>
+      <c r="AC35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD35">
+        <v>10.5</v>
+      </c>
+      <c r="AE35">
+        <v>21</v>
+      </c>
+      <c r="AF35">
+        <v>48</v>
+      </c>
+      <c r="AG35">
+        <v>24</v>
+      </c>
+      <c r="AH35">
+        <v>24</v>
+      </c>
+      <c r="AI35">
+        <v>46</v>
+      </c>
+      <c r="AJ35">
+        <v>170</v>
+      </c>
+      <c r="AK35">
+        <v>95</v>
+      </c>
+      <c r="AL35">
+        <v>100</v>
+      </c>
+      <c r="AM35">
+        <v>160</v>
+      </c>
+      <c r="AN35">
+        <v>110</v>
+      </c>
+      <c r="AO35">
+        <v>13</v>
+      </c>
+      <c r="AP35">
+        <v>11.5</v>
+      </c>
+      <c r="AQ35">
+        <v>7.2</v>
+      </c>
+      <c r="AR35">
+        <v>8.6</v>
+      </c>
+      <c r="AS35">
+        <v>15.5</v>
+      </c>
+      <c r="AT35">
+        <v>15</v>
+      </c>
+      <c r="AU35">
+        <v>7.8</v>
+      </c>
+      <c r="AV35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW35">
+        <v>16.5</v>
+      </c>
+      <c r="AX35">
+        <v>34</v>
+      </c>
+      <c r="AY35">
+        <v>17.5</v>
+      </c>
+      <c r="AZ35">
+        <v>18.5</v>
+      </c>
+      <c r="BA35">
+        <v>29</v>
+      </c>
+      <c r="BB35">
+        <v>9.6</v>
+      </c>
+      <c r="BC35">
+        <v>50</v>
+      </c>
+      <c r="BD35">
+        <v>10</v>
+      </c>
+      <c r="BE35">
+        <v>10.5</v>
+      </c>
+      <c r="BF35">
+        <v>10</v>
+      </c>
+      <c r="BG35">
+        <v>10.5</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.26</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.95</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.22</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>5.6</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.22</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.22</v>
+      </c>
+      <c r="BT35">
+        <v>5.8</v>
+      </c>
+      <c r="BU35">
+        <v>3.2</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.95</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.22</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.22</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -556,7 +556,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 17:24:10</t>
+    <t>2026-09-08 19:36:57</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1150,7 @@
         <v>146</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
         <v>2.42</v>
@@ -1183,10 +1183,10 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
         <v>2.88</v>
@@ -1204,7 +1204,7 @@
         <v>1.7</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y2">
         <v>15.5</v>
@@ -1213,7 +1213,7 @@
         <v>24</v>
       </c>
       <c r="AA2">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AB2">
         <v>13</v>
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ2">
         <v>32</v>
@@ -1249,7 +1249,7 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2">
         <v>15</v>
@@ -1267,10 +1267,10 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
@@ -1288,25 +1288,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
+        <v>28</v>
+      </c>
+      <c r="BB2">
+        <v>22</v>
+      </c>
+      <c r="BC2">
+        <v>20</v>
+      </c>
+      <c r="BD2">
         <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>24</v>
-      </c>
-      <c r="BC2">
-        <v>19.5</v>
-      </c>
-      <c r="BD2">
-        <v>27</v>
       </c>
       <c r="BE2">
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG2">
         <v>20</v>
@@ -1416,7 +1416,7 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.43</v>
@@ -1425,10 +1425,10 @@
         <v>1.72</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
         <v>4.4</v>
@@ -1512,7 +1512,7 @@
         <v>5.2</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
         <v>7.2</v>
@@ -1527,7 +1527,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
         <v>4.4</v>
@@ -1560,7 +1560,7 @@
         <v>2.76</v>
       </c>
       <c r="BJ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
         <v>3.65</v>
@@ -1569,7 +1569,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1578,16 +1578,16 @@
         <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ3">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT3">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>60</v>
       </c>
       <c r="BW3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX3">
         <v>80</v>
@@ -1611,7 +1611,7 @@
         <v>40</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
         <v>180</v>
@@ -1646,7 +1646,7 @@
         <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K4">
         <v>3</v>
@@ -1664,22 +1664,22 @@
         <v>1.69</v>
       </c>
       <c r="P4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R4">
         <v>1.15</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
         <v>1.31</v>
@@ -1688,16 +1688,16 @@
         <v>1.71</v>
       </c>
       <c r="X4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB4">
         <v>6.4</v>
@@ -1712,7 +1712,7 @@
         <v>100</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG4">
         <v>13</v>
@@ -1721,10 +1721,10 @@
         <v>29</v>
       </c>
       <c r="AI4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK4">
         <v>40</v>
@@ -1733,13 +1733,13 @@
         <v>100</v>
       </c>
       <c r="AM4">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>6.4</v>
@@ -1751,7 +1751,7 @@
         <v>22</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>5.8</v>
@@ -1763,37 +1763,37 @@
         <v>17</v>
       </c>
       <c r="AW4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX4">
         <v>11</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB4">
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BF4">
         <v>30</v>
       </c>
       <c r="BG4">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1939,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1984,16 +1984,16 @@
         <v>23</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
         <v>17</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT5">
         <v>13</v>
@@ -2005,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -2017,16 +2017,16 @@
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE5">
         <v>34</v>
@@ -2044,10 +2044,10 @@
         <v>4.1</v>
       </c>
       <c r="BJ5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL5">
         <v>80</v>
@@ -2118,7 +2118,7 @@
         <v>150</v>
       </c>
       <c r="F6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G6">
         <v>2.74</v>
@@ -2142,7 +2142,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -2163,7 +2163,7 @@
         <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2205,16 +2205,16 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
+        <v>48</v>
+      </c>
+      <c r="AK6">
+        <v>34</v>
+      </c>
+      <c r="AL6">
         <v>65</v>
-      </c>
-      <c r="AK6">
-        <v>46</v>
-      </c>
-      <c r="AL6">
-        <v>55</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2235,7 +2235,7 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2247,7 +2247,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6">
         <v>16</v>
@@ -2262,13 +2262,13 @@
         <v>29</v>
       </c>
       <c r="BB6">
+        <v>30</v>
+      </c>
+      <c r="BC6">
+        <v>23</v>
+      </c>
+      <c r="BD6">
         <v>26</v>
-      </c>
-      <c r="BC6">
-        <v>20</v>
-      </c>
-      <c r="BD6">
-        <v>28</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2277,16 +2277,16 @@
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.22</v>
+        <v>1.57</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>6.6</v>
@@ -2295,49 +2295,49 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.8</v>
+        <v>1.86</v>
       </c>
       <c r="BP6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.2</v>
+        <v>2.58</v>
       </c>
       <c r="BR6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="BT6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>4.7</v>
+        <v>1.91</v>
       </c>
       <c r="BV6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="BX6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="BZ6">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="CB6" t="s">
         <v>180</v>
@@ -2447,7 +2447,7 @@
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2474,10 +2474,10 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -2608,7 +2608,7 @@
         <v>2.2</v>
       </c>
       <c r="H8">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
         <v>3.15</v>
@@ -2629,52 +2629,52 @@
         <v>11</v>
       </c>
       <c r="O8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="T8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="U8">
         <v>3.9</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
         <v>1.83</v>
       </c>
       <c r="X8">
-        <v>380</v>
+        <v>95</v>
       </c>
       <c r="Y8">
         <v>40</v>
       </c>
       <c r="Z8">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AA8">
-        <v>340</v>
+        <v>580</v>
       </c>
       <c r="AB8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC8">
         <v>14.5</v>
       </c>
       <c r="AD8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE8">
         <v>27</v>
@@ -2683,16 +2683,16 @@
         <v>28</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK8">
         <v>19.5</v>
@@ -2707,10 +2707,10 @@
         <v>6.4</v>
       </c>
       <c r="AO8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ8">
         <v>23</v>
@@ -2719,22 +2719,22 @@
         <v>26</v>
       </c>
       <c r="AS8">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV8">
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2746,28 +2746,28 @@
         <v>20</v>
       </c>
       <c r="BB8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD8">
         <v>17.5</v>
       </c>
       <c r="BE8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BF8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>5.1</v>
+        <v>1.46</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2779,49 +2779,49 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>1.45</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>7.4</v>
+        <v>1.75</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>1.75</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>1.5</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>11</v>
+        <v>1.75</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.6</v>
+        <v>1.75</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="CB8" t="s">
         <v>180</v>
@@ -3101,7 +3101,7 @@
         <v>5.4</v>
       </c>
       <c r="K10">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L10">
         <v>1.23</v>
@@ -3122,13 +3122,13 @@
         <v>1.41</v>
       </c>
       <c r="R10">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S10">
         <v>2</v>
       </c>
       <c r="T10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U10">
         <v>2.52</v>
@@ -3146,7 +3146,7 @@
         <v>40</v>
       </c>
       <c r="Z10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3191,10 +3191,10 @@
         <v>4.3</v>
       </c>
       <c r="AO10">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="AP10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ10">
         <v>27</v>
@@ -3203,7 +3203,7 @@
         <v>44</v>
       </c>
       <c r="AS10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT10">
         <v>13.5</v>
@@ -3212,7 +3212,7 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW10">
         <v>46</v>
@@ -3239,7 +3239,7 @@
         <v>20</v>
       </c>
       <c r="BE10">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF10">
         <v>4</v>
@@ -3248,64 +3248,64 @@
         <v>28</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI10">
+        <v>4.9</v>
+      </c>
+      <c r="BJ10">
+        <v>9.4</v>
+      </c>
+      <c r="BK10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL10">
+        <v>75</v>
+      </c>
+      <c r="BM10">
+        <v>50</v>
+      </c>
+      <c r="BN10">
+        <v>4.7</v>
+      </c>
+      <c r="BO10">
         <v>4.2</v>
       </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>6.6</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>5.4</v>
-      </c>
-      <c r="BO10">
-        <v>3.8</v>
-      </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BQ10">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS10">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB10" t="s">
         <v>180</v>
@@ -3328,22 +3328,22 @@
         <v>155</v>
       </c>
       <c r="F11">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G11">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>1.22</v>
@@ -3379,7 +3379,7 @@
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X11">
         <v>40</v>
@@ -3388,7 +3388,7 @@
         <v>46</v>
       </c>
       <c r="Z11">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
@@ -3400,10 +3400,10 @@
         <v>14.5</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE11">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3430,16 +3430,16 @@
         <v>75</v>
       </c>
       <c r="AN11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>540</v>
+        <v>60</v>
       </c>
       <c r="AP11">
         <v>32</v>
       </c>
       <c r="AQ11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AR11">
         <v>34</v>
@@ -3454,16 +3454,16 @@
         <v>12.5</v>
       </c>
       <c r="AV11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
         <v>16.5</v>
@@ -3481,13 +3481,13 @@
         <v>20</v>
       </c>
       <c r="BE11">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BF11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH11">
         <v>5.5</v>
@@ -3502,10 +3502,10 @@
         <v>8.4</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BN11">
         <v>4.6</v>
@@ -3535,19 +3535,19 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BZ11">
         <v>8.800000000000001</v>
       </c>
       <c r="CA11">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB11" t="s">
         <v>180</v>
@@ -3627,13 +3627,13 @@
         <v>40</v>
       </c>
       <c r="Y12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z12">
         <v>46</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
         <v>17.5</v>
@@ -3681,16 +3681,16 @@
         <v>22</v>
       </c>
       <c r="AQ12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AS12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU12">
         <v>10</v>
@@ -3699,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3711,7 +3711,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB12">
         <v>19</v>
@@ -3723,13 +3723,13 @@
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF12">
         <v>6</v>
       </c>
       <c r="BG12">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3824,7 +3824,7 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>4.2</v>
@@ -3839,7 +3839,7 @@
         <v>6.2</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P13">
         <v>2.74</v>
@@ -3866,7 +3866,7 @@
         <v>1.69</v>
       </c>
       <c r="X13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y13">
         <v>19</v>
@@ -3908,19 +3908,19 @@
         <v>22</v>
       </c>
       <c r="AL13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN13">
         <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AQ13">
         <v>16.5</v>
@@ -3941,7 +3941,7 @@
         <v>12</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AX13">
         <v>17</v>
@@ -3953,19 +3953,19 @@
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC13">
         <v>19</v>
       </c>
       <c r="BD13">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE13">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>1.57</v>
       </c>
       <c r="H14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>7.2</v>
@@ -4087,7 +4087,7 @@
         <v>2.62</v>
       </c>
       <c r="Q14">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R14">
         <v>1.65</v>
@@ -4099,7 +4099,7 @@
         <v>1.65</v>
       </c>
       <c r="U14">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -4299,7 +4299,7 @@
         <v>2.12</v>
       </c>
       <c r="G15">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H15">
         <v>2.76</v>
@@ -4347,7 +4347,7 @@
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4562,7 +4562,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O16">
         <v>1.28</v>
@@ -4813,13 +4813,13 @@
         <v>2.52</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -5264,13 +5264,13 @@
         <v>163</v>
       </c>
       <c r="F19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G19">
         <v>1.48</v>
       </c>
       <c r="H19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I19">
         <v>7.6</v>
@@ -5291,7 +5291,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P19">
         <v>3</v>
@@ -5306,16 +5306,16 @@
         <v>2.18</v>
       </c>
       <c r="T19">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
         <v>1.15</v>
       </c>
       <c r="W19">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X19">
         <v>34</v>
@@ -5339,10 +5339,10 @@
         <v>27</v>
       </c>
       <c r="AE19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5372,7 +5372,7 @@
         <v>65</v>
       </c>
       <c r="AP19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ19">
         <v>32</v>
@@ -5384,10 +5384,10 @@
         <v>46</v>
       </c>
       <c r="AT19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV19">
         <v>24</v>
@@ -5444,7 +5444,7 @@
         <v>21</v>
       </c>
       <c r="BN19">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO19">
         <v>4</v>
@@ -5506,7 +5506,7 @@
         <v>164</v>
       </c>
       <c r="F20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G20">
         <v>3.55</v>
@@ -5515,7 +5515,7 @@
         <v>2.26</v>
       </c>
       <c r="I20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J20">
         <v>3.6</v>
@@ -5545,13 +5545,13 @@
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T20">
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
         <v>1.78</v>
@@ -5569,7 +5569,7 @@
         <v>15.5</v>
       </c>
       <c r="AA20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB20">
         <v>16</v>
@@ -5596,13 +5596,13 @@
         <v>32</v>
       </c>
       <c r="AJ20">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="AK20">
         <v>36</v>
       </c>
       <c r="AL20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM20">
         <v>85</v>
@@ -5614,7 +5614,7 @@
         <v>13</v>
       </c>
       <c r="AP20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ20">
         <v>11.5</v>
@@ -5626,7 +5626,7 @@
         <v>26</v>
       </c>
       <c r="AT20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU20">
         <v>7.6</v>
@@ -5668,7 +5668,7 @@
         <v>12.5</v>
       </c>
       <c r="BH20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI20">
         <v>3.45</v>
@@ -5692,7 +5692,7 @@
         <v>6</v>
       </c>
       <c r="BP20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ20">
         <v>18.5</v>
@@ -5701,7 +5701,7 @@
         <v>42</v>
       </c>
       <c r="BS20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BT20">
         <v>5.2</v>
@@ -5722,7 +5722,7 @@
         <v>20</v>
       </c>
       <c r="BZ20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA20">
         <v>15.5</v>
@@ -5772,7 +5772,7 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
         <v>1.26</v>
@@ -5796,7 +5796,7 @@
         <v>1.94</v>
       </c>
       <c r="V21">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
         <v>2.18</v>
@@ -6014,13 +6014,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O22">
         <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q22">
         <v>1.3</v>
@@ -6029,7 +6029,7 @@
         <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6247,7 +6247,7 @@
         <v>5.3</v>
       </c>
       <c r="K23">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6256,7 +6256,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
         <v>1.14</v>
@@ -6268,7 +6268,7 @@
         <v>1.35</v>
       </c>
       <c r="R23">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S23">
         <v>2.08</v>
@@ -6477,7 +6477,7 @@
         <v>1.86</v>
       </c>
       <c r="G24">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H24">
         <v>3.85</v>
@@ -6498,22 +6498,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
         <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6525,7 +6525,7 @@
         <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6785,7 +6785,7 @@
         <v>1000</v>
       </c>
       <c r="AC25">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD25">
         <v>21</v>
@@ -6842,7 +6842,7 @@
         <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AW25">
         <v>17.5</v>
@@ -6854,13 +6854,13 @@
         <v>1.79</v>
       </c>
       <c r="AZ25">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BA25">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BB25">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BC25">
         <v>1.99</v>
@@ -6869,7 +6869,7 @@
         <v>1.99</v>
       </c>
       <c r="BE25">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BF25">
         <v>19</v>
@@ -6991,7 +6991,7 @@
         <v>2</v>
       </c>
       <c r="Q26">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R26">
         <v>1.35</v>
@@ -7015,7 +7015,7 @@
         <v>20</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
         <v>1000</v>
@@ -7027,10 +7027,10 @@
         <v>970</v>
       </c>
       <c r="AC26">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE26">
         <v>1000</v>
@@ -7066,7 +7066,7 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ26">
         <v>7.2</v>
@@ -7078,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="AT26">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AU26">
         <v>7.2</v>
@@ -7093,28 +7093,28 @@
         <v>21</v>
       </c>
       <c r="AY26">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AZ26">
+        <v>1.63</v>
+      </c>
+      <c r="BA26">
+        <v>1.69</v>
+      </c>
+      <c r="BB26">
         <v>1.73</v>
       </c>
-      <c r="BA26">
-        <v>1.8</v>
-      </c>
-      <c r="BB26">
-        <v>1.84</v>
-      </c>
       <c r="BC26">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BD26">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BE26">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BF26">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BG26">
         <v>11</v>
@@ -7442,22 +7442,22 @@
         <v>172</v>
       </c>
       <c r="F28">
+        <v>1.36</v>
+      </c>
+      <c r="G28">
+        <v>1000</v>
+      </c>
+      <c r="H28">
+        <v>1.36</v>
+      </c>
+      <c r="I28">
+        <v>1000</v>
+      </c>
+      <c r="J28">
         <v>1.04</v>
       </c>
-      <c r="G28">
-        <v>1000</v>
-      </c>
-      <c r="H28">
-        <v>1.04</v>
-      </c>
-      <c r="I28">
-        <v>1000</v>
-      </c>
-      <c r="J28">
-        <v>1.02</v>
-      </c>
       <c r="K28">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7466,22 +7466,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
+        <v>1.26</v>
+      </c>
+      <c r="O28">
+        <v>1.32</v>
+      </c>
+      <c r="P28">
         <v>1.25</v>
       </c>
-      <c r="O28">
-        <v>1.33</v>
-      </c>
-      <c r="P28">
-        <v>1.24</v>
-      </c>
       <c r="Q28">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R28">
         <v>1.12</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7490,10 +7490,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7696,7 +7696,7 @@
         <v>15</v>
       </c>
       <c r="J29">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K29">
         <v>6.4</v>
@@ -7944,13 +7944,13 @@
         <v>11.5</v>
       </c>
       <c r="L30">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="M30">
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O30">
         <v>1.09</v>
@@ -7971,7 +7971,7 @@
         <v>2.1</v>
       </c>
       <c r="U30">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V30">
         <v>1.03</v>
@@ -7983,7 +7983,7 @@
         <v>60</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="Z30">
         <v>360</v>
@@ -7995,7 +7995,7 @@
         <v>18.5</v>
       </c>
       <c r="AC30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD30">
         <v>120</v>
@@ -8010,7 +8010,7 @@
         <v>16.5</v>
       </c>
       <c r="AH30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AI30">
         <v>1000</v>
@@ -8022,7 +8022,7 @@
         <v>14.5</v>
       </c>
       <c r="AL30">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM30">
         <v>1000</v>
@@ -8034,7 +8034,7 @@
         <v>440</v>
       </c>
       <c r="AP30">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AQ30">
         <v>40</v>
@@ -8043,13 +8043,13 @@
         <v>55</v>
       </c>
       <c r="AS30">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AT30">
         <v>16</v>
       </c>
       <c r="AU30">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV30">
         <v>38</v>
@@ -8064,7 +8064,7 @@
         <v>14</v>
       </c>
       <c r="AZ30">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BA30">
         <v>50</v>
@@ -8076,7 +8076,7 @@
         <v>12.5</v>
       </c>
       <c r="BD30">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE30">
         <v>44</v>
@@ -8085,10 +8085,10 @@
         <v>2.22</v>
       </c>
       <c r="BG30">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH30">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BI30">
         <v>5.4</v>
@@ -8097,7 +8097,7 @@
         <v>16.5</v>
       </c>
       <c r="BK30">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8109,25 +8109,25 @@
         <v>4.8</v>
       </c>
       <c r="BO30">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP30">
         <v>6.4</v>
       </c>
       <c r="BQ30">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BR30">
         <v>22</v>
       </c>
       <c r="BS30">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BT30">
         <v>26</v>
       </c>
       <c r="BU30">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8145,7 +8145,7 @@
         <v>5.9</v>
       </c>
       <c r="CA30">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB30" t="s">
         <v>180</v>
@@ -8177,7 +8177,7 @@
         <v>2.86</v>
       </c>
       <c r="I31">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8186,16 +8186,16 @@
         <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M31">
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O31">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P31">
         <v>2.14</v>
@@ -8207,16 +8207,16 @@
         <v>1.45</v>
       </c>
       <c r="S31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U31">
         <v>2.38</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
         <v>1.59</v>
@@ -8363,7 +8363,7 @@
         <v>29</v>
       </c>
       <c r="BS31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT31">
         <v>6.2</v>
@@ -8387,7 +8387,7 @@
         <v>22</v>
       </c>
       <c r="CA31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CB31" t="s">
         <v>180</v>
@@ -8410,46 +8410,46 @@
         <v>176</v>
       </c>
       <c r="F32">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G32">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K32">
         <v>4.2</v>
       </c>
       <c r="L32">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M32">
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O32">
         <v>1.21</v>
       </c>
       <c r="P32">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q32">
+        <v>1.61</v>
+      </c>
+      <c r="R32">
         <v>1.62</v>
       </c>
-      <c r="R32">
-        <v>1.61</v>
-      </c>
       <c r="S32">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T32">
         <v>1.6</v>
@@ -8458,7 +8458,7 @@
         <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>2.06</v>
@@ -8470,7 +8470,7 @@
         <v>22</v>
       </c>
       <c r="Z32">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA32">
         <v>85</v>
@@ -8497,7 +8497,7 @@
         <v>16</v>
       </c>
       <c r="AI32">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ32">
         <v>22</v>
@@ -8533,7 +8533,7 @@
         <v>12</v>
       </c>
       <c r="AU32">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV32">
         <v>15</v>
@@ -8542,7 +8542,7 @@
         <v>38</v>
       </c>
       <c r="AX32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY32">
         <v>9.6</v>
@@ -8575,7 +8575,7 @@
         <v>4.2</v>
       </c>
       <c r="BI32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ32">
         <v>8.800000000000001</v>
@@ -8611,7 +8611,7 @@
         <v>7.8</v>
       </c>
       <c r="BU32">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV32">
         <v>30</v>
@@ -8658,13 +8658,13 @@
         <v>3.45</v>
       </c>
       <c r="H33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I33">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K33">
         <v>3.65</v>
@@ -8676,22 +8676,22 @@
         <v>1.07</v>
       </c>
       <c r="N33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P33">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S33">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T33">
         <v>1.82</v>
@@ -8718,7 +8718,7 @@
         <v>40</v>
       </c>
       <c r="AB33">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC33">
         <v>8</v>
@@ -8754,7 +8754,7 @@
         <v>120</v>
       </c>
       <c r="AN33">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO33">
         <v>26</v>
@@ -8763,13 +8763,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ33">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR33">
         <v>13</v>
       </c>
       <c r="AS33">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT33">
         <v>10.5</v>
@@ -8790,25 +8790,25 @@
         <v>12.5</v>
       </c>
       <c r="AZ33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA33">
+        <v>5.8</v>
+      </c>
+      <c r="BB33">
         <v>5.9</v>
       </c>
-      <c r="BB33">
-        <v>6</v>
-      </c>
       <c r="BC33">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD33">
         <v>6</v>
       </c>
       <c r="BE33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF33">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG33">
         <v>18.5</v>
@@ -8900,28 +8900,28 @@
         <v>1.13</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34">
         <v>14</v>
       </c>
       <c r="K34">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="M34">
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="O34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P34">
         <v>6.8</v>
@@ -8930,16 +8930,16 @@
         <v>1.15</v>
       </c>
       <c r="R34">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S34">
         <v>1.41</v>
       </c>
       <c r="T34">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
         <v>1.04</v>
@@ -8954,7 +8954,7 @@
         <v>1000</v>
       </c>
       <c r="Z34">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AA34">
         <v>1000</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="AC34">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AD34">
         <v>1000</v>
@@ -8972,10 +8972,10 @@
         <v>310</v>
       </c>
       <c r="AF34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG34">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH34">
         <v>160</v>
@@ -8987,7 +8987,7 @@
         <v>11.5</v>
       </c>
       <c r="AK34">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL34">
         <v>32</v>
@@ -8996,7 +8996,7 @@
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AO34">
         <v>1000</v>
@@ -9005,25 +9005,25 @@
         <v>40</v>
       </c>
       <c r="AQ34">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR34">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AS34">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AT34">
         <v>21</v>
       </c>
       <c r="AU34">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AV34">
         <v>36</v>
       </c>
       <c r="AW34">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX34">
         <v>16.5</v>
@@ -9044,13 +9044,13 @@
         <v>12.5</v>
       </c>
       <c r="BD34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE34">
         <v>40</v>
       </c>
       <c r="BF34">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BG34">
         <v>85</v>
@@ -9059,13 +9059,13 @@
         <v>11</v>
       </c>
       <c r="BI34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BJ34">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BK34">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9077,22 +9077,22 @@
         <v>5.8</v>
       </c>
       <c r="BO34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BQ34">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS34">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BU34">
         <v>17</v>
@@ -9110,10 +9110,10 @@
         <v>48</v>
       </c>
       <c r="BZ34">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="CA34">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="CB34" t="s">
         <v>180</v>
@@ -9142,31 +9142,31 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I35">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J35">
         <v>3.9</v>
       </c>
       <c r="K35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L35">
         <v>1.43</v>
       </c>
       <c r="M35">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O35">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P35">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q35">
         <v>2.02</v>
@@ -9178,31 +9178,31 @@
         <v>3.65</v>
       </c>
       <c r="T35">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="U35">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="V35">
         <v>2.28</v>
       </c>
       <c r="W35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
         <v>13.5</v>
       </c>
       <c r="Y35">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA35">
+        <v>18.5</v>
+      </c>
+      <c r="AB35">
         <v>18</v>
-      </c>
-      <c r="AB35">
-        <v>20</v>
       </c>
       <c r="AC35">
         <v>8.800000000000001</v>
@@ -9211,37 +9211,37 @@
         <v>10.5</v>
       </c>
       <c r="AE35">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF35">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH35">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI35">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ35">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK35">
+        <v>90</v>
+      </c>
+      <c r="AL35">
         <v>95</v>
       </c>
-      <c r="AL35">
-        <v>100</v>
-      </c>
       <c r="AM35">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN35">
         <v>110</v>
       </c>
       <c r="AO35">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP35">
         <v>11.5</v>
@@ -9250,13 +9250,13 @@
         <v>7.2</v>
       </c>
       <c r="AR35">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU35">
         <v>7.8</v>
@@ -9265,37 +9265,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW35">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX35">
+        <v>38</v>
+      </c>
+      <c r="AY35">
+        <v>20</v>
+      </c>
+      <c r="AZ35">
+        <v>19.5</v>
+      </c>
+      <c r="BA35">
         <v>34</v>
       </c>
-      <c r="AY35">
-        <v>17.5</v>
-      </c>
-      <c r="AZ35">
-        <v>18.5</v>
-      </c>
-      <c r="BA35">
-        <v>29</v>
-      </c>
       <c r="BB35">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC35">
         <v>50</v>
       </c>
       <c r="BD35">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BE35">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BF35">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="BG35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH35">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -556,7 +556,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 19:36:57</t>
+    <t>2026-09-08 21:50:44</t>
   </si>
 </sst>
 </file>
@@ -1150,13 +1150,13 @@
         <v>146</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
         <v>3.2</v>
@@ -1165,7 +1165,7 @@
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -1183,16 +1183,16 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
         <v>2.44</v>
@@ -1201,7 +1201,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
         <v>20</v>
@@ -1213,7 +1213,7 @@
         <v>24</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB2">
         <v>13</v>
@@ -1228,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="AF2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1261,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="AQ2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
@@ -1288,25 +1288,25 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC2">
         <v>20</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
         <v>20</v>
@@ -1354,16 +1354,16 @@
         <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BZ2">
         <v>24</v>
@@ -1416,7 +1416,7 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.43</v>
@@ -1455,7 +1455,7 @@
         <v>48</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
@@ -1464,13 +1464,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE3">
         <v>110</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1506,13 +1506,13 @@
         <v>13</v>
       </c>
       <c r="AR3">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>7.2</v>
@@ -1521,7 +1521,7 @@
         <v>18</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1530,46 +1530,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
         <v>17.5</v>
       </c>
       <c r="BC3">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF3">
         <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3">
         <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1578,10 +1578,10 @@
         <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BR3">
         <v>42</v>
@@ -1605,7 +1605,7 @@
         <v>80</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ3">
         <v>40</v>
@@ -1634,10 +1634,10 @@
         <v>148</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -1646,136 +1646,136 @@
         <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N4">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="O4">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S4">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="V4">
         <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AC4">
+        <v>7.6</v>
+      </c>
+      <c r="AD4">
+        <v>25</v>
+      </c>
+      <c r="AE4">
+        <v>130</v>
+      </c>
+      <c r="AF4">
+        <v>13.5</v>
+      </c>
+      <c r="AG4">
+        <v>18.5</v>
+      </c>
+      <c r="AH4">
+        <v>44</v>
+      </c>
+      <c r="AI4">
+        <v>180</v>
+      </c>
+      <c r="AJ4">
+        <v>44</v>
+      </c>
+      <c r="AK4">
+        <v>60</v>
+      </c>
+      <c r="AL4">
+        <v>130</v>
+      </c>
+      <c r="AM4">
+        <v>430</v>
+      </c>
+      <c r="AN4">
+        <v>100</v>
+      </c>
+      <c r="AO4">
+        <v>210</v>
+      </c>
+      <c r="AP4">
+        <v>5.4</v>
+      </c>
+      <c r="AQ4">
         <v>7.4</v>
       </c>
-      <c r="AD4">
+      <c r="AR4">
         <v>19</v>
       </c>
-      <c r="AE4">
-        <v>100</v>
-      </c>
-      <c r="AF4">
-        <v>13</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
-      </c>
-      <c r="AH4">
-        <v>29</v>
-      </c>
-      <c r="AI4">
-        <v>130</v>
-      </c>
-      <c r="AJ4">
-        <v>36</v>
-      </c>
-      <c r="AK4">
-        <v>40</v>
-      </c>
-      <c r="AL4">
-        <v>100</v>
-      </c>
-      <c r="AM4">
-        <v>310</v>
-      </c>
-      <c r="AN4">
-        <v>44</v>
-      </c>
-      <c r="AO4">
-        <v>150</v>
-      </c>
-      <c r="AP4">
-        <v>6.4</v>
-      </c>
-      <c r="AQ4">
-        <v>8.6</v>
-      </c>
-      <c r="AR4">
-        <v>22</v>
-      </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AX4">
         <v>11</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA4">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
         <v>28</v>
@@ -1784,16 +1784,16 @@
         <v>32</v>
       </c>
       <c r="BD4">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE4">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
         <v>30</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1876,25 +1876,25 @@
         <v>149</v>
       </c>
       <c r="F5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1924,13 +1924,13 @@
         <v>2.7</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y5">
         <v>20</v>
@@ -1939,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AB5">
         <v>15</v>
@@ -1948,64 +1948,64 @@
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK5">
+        <v>19</v>
+      </c>
+      <c r="AL5">
+        <v>27</v>
+      </c>
+      <c r="AM5">
+        <v>60</v>
+      </c>
+      <c r="AN5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO5">
+        <v>24</v>
+      </c>
+      <c r="AP5">
         <v>21</v>
       </c>
-      <c r="AL5">
-        <v>28</v>
-      </c>
-      <c r="AM5">
-        <v>300</v>
-      </c>
-      <c r="AN5">
-        <v>10</v>
-      </c>
-      <c r="AO5">
-        <v>23</v>
-      </c>
-      <c r="AP5">
-        <v>19.5</v>
-      </c>
       <c r="AQ5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX5">
         <v>14.5</v>
@@ -2014,31 +2014,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA5">
+        <v>32</v>
+      </c>
+      <c r="BB5">
+        <v>25</v>
+      </c>
+      <c r="BC5">
+        <v>17</v>
+      </c>
+      <c r="BD5">
         <v>23</v>
       </c>
-      <c r="BB5">
-        <v>21</v>
-      </c>
-      <c r="BC5">
-        <v>16.5</v>
-      </c>
-      <c r="BD5">
-        <v>21</v>
-      </c>
       <c r="BE5">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BH5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>4.1</v>
@@ -2124,16 +2124,16 @@
         <v>2.74</v>
       </c>
       <c r="H6">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.4</v>
@@ -2163,7 +2163,7 @@
         <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2205,16 +2205,16 @@
         <v>17</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AK6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2247,7 +2247,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX6">
         <v>16</v>
@@ -2262,22 +2262,22 @@
         <v>29</v>
       </c>
       <c r="BB6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF6">
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2316,7 +2316,7 @@
         <v>2.58</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
         <v>1.91</v>
@@ -2360,22 +2360,22 @@
         <v>151</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="G7">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H7">
+        <v>4.3</v>
+      </c>
+      <c r="I7">
         <v>4.5</v>
       </c>
-      <c r="I7">
-        <v>4.8</v>
-      </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2393,7 +2393,7 @@
         <v>2.28</v>
       </c>
       <c r="Q7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R7">
         <v>1.51</v>
@@ -2402,25 +2402,25 @@
         <v>2.86</v>
       </c>
       <c r="T7">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
         <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X7">
         <v>21</v>
       </c>
       <c r="Y7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA7">
         <v>1000</v>
@@ -2432,28 +2432,28 @@
         <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE7">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI7">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
         <v>21</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL7">
         <v>32</v>
@@ -2462,10 +2462,10 @@
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO7">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AP7">
         <v>17.5</v>
@@ -2477,10 +2477,10 @@
         <v>23</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU7">
         <v>8.6</v>
@@ -2492,7 +2492,7 @@
         <v>32</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2501,7 +2501,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2516,10 +2516,10 @@
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2561,7 +2561,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2602,97 +2602,97 @@
         <v>152</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J8">
         <v>4.5</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
         <v>1.18</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R8">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="T8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="U8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X8">
+        <v>70</v>
+      </c>
+      <c r="Y8">
+        <v>34</v>
+      </c>
+      <c r="Z8">
+        <v>38</v>
+      </c>
+      <c r="AA8">
         <v>95</v>
       </c>
-      <c r="Y8">
-        <v>40</v>
-      </c>
-      <c r="Z8">
-        <v>85</v>
-      </c>
-      <c r="AA8">
-        <v>580</v>
-      </c>
       <c r="AB8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC8">
         <v>14.5</v>
       </c>
       <c r="AD8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE8">
         <v>27</v>
       </c>
       <c r="AF8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>13.5</v>
       </c>
       <c r="AI8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK8">
         <v>19.5</v>
@@ -2704,7 +2704,7 @@
         <v>34</v>
       </c>
       <c r="AN8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO8">
         <v>10.5</v>
@@ -2713,19 +2713,19 @@
         <v>32</v>
       </c>
       <c r="AQ8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AU8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV8">
         <v>14.5</v>
@@ -2746,22 +2746,22 @@
         <v>20</v>
       </c>
       <c r="BB8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD8">
         <v>17.5</v>
       </c>
       <c r="BE8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BF8">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2847,13 +2847,13 @@
         <v>1.04</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>1.1</v>
       </c>
       <c r="I9">
-        <v>1.63</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2892,7 +2892,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -3086,16 +3086,16 @@
         <v>154</v>
       </c>
       <c r="F10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G10">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>5.4</v>
@@ -3110,19 +3110,19 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>1.13</v>
       </c>
       <c r="P10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q10">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S10">
         <v>2</v>
@@ -3137,7 +3137,7 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X10">
         <v>40</v>
@@ -3146,7 +3146,7 @@
         <v>40</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3161,7 +3161,7 @@
         <v>28</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF10">
         <v>12.5</v>
@@ -3170,13 +3170,13 @@
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="AJ10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK10">
         <v>14</v>
@@ -3188,13 +3188,13 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO10">
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ10">
         <v>27</v>
@@ -3203,16 +3203,16 @@
         <v>44</v>
       </c>
       <c r="AS10">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AT10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW10">
         <v>46</v>
@@ -3221,7 +3221,7 @@
         <v>11.5</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
         <v>16.5</v>
@@ -3239,13 +3239,13 @@
         <v>20</v>
       </c>
       <c r="BE10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH10">
         <v>5.4</v>
@@ -3254,7 +3254,7 @@
         <v>4.9</v>
       </c>
       <c r="BJ10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK10">
         <v>8.199999999999999</v>
@@ -3266,16 +3266,16 @@
         <v>50</v>
       </c>
       <c r="BN10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
         <v>4.2</v>
       </c>
       <c r="BP10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>17.5</v>
@@ -3284,28 +3284,28 @@
         <v>14.5</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BV10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY10">
         <v>29</v>
       </c>
       <c r="BZ10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CA10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>180</v>
@@ -3328,7 +3328,7 @@
         <v>155</v>
       </c>
       <c r="F11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G11">
         <v>1.45</v>
@@ -3340,10 +3340,10 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L11">
         <v>1.22</v>
@@ -3361,10 +3361,10 @@
         <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R11">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>1.96</v>
@@ -3373,13 +3373,13 @@
         <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
         <v>40</v>
@@ -3400,10 +3400,10 @@
         <v>14.5</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3457,7 +3457,7 @@
         <v>26</v>
       </c>
       <c r="AW11">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
@@ -3466,13 +3466,13 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
         <v>50</v>
       </c>
       <c r="BB11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC11">
         <v>12</v>
@@ -3481,13 +3481,13 @@
         <v>20</v>
       </c>
       <c r="BE11">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BF11">
         <v>3.8</v>
       </c>
       <c r="BG11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH11">
         <v>5.5</v>
@@ -3544,7 +3544,7 @@
         <v>29</v>
       </c>
       <c r="BZ11">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CA11">
         <v>6.6</v>
@@ -3573,7 +3573,7 @@
         <v>1.82</v>
       </c>
       <c r="G12">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H12">
         <v>4.1</v>
@@ -3594,25 +3594,25 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U12">
         <v>2.9</v>
@@ -3621,7 +3621,7 @@
         <v>1.3</v>
       </c>
       <c r="W12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X12">
         <v>40</v>
@@ -3642,22 +3642,22 @@
         <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE12">
         <v>46</v>
       </c>
       <c r="AF12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG12">
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ12">
         <v>23</v>
@@ -3666,10 +3666,10 @@
         <v>17</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN12">
         <v>6.6</v>
@@ -3681,7 +3681,7 @@
         <v>22</v>
       </c>
       <c r="AQ12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR12">
         <v>26</v>
@@ -3696,10 +3696,10 @@
         <v>10</v>
       </c>
       <c r="AV12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3711,7 +3711,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB12">
         <v>19</v>
@@ -3726,10 +3726,10 @@
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3848,7 +3848,7 @@
         <v>1.54</v>
       </c>
       <c r="R13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S13">
         <v>2.34</v>
@@ -3875,10 +3875,10 @@
         <v>25</v>
       </c>
       <c r="AA13">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -3917,10 +3917,10 @@
         <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
         <v>16.5</v>
@@ -3929,7 +3929,7 @@
         <v>21</v>
       </c>
       <c r="AS13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT13">
         <v>14.5</v>
@@ -3941,7 +3941,7 @@
         <v>12</v>
       </c>
       <c r="AW13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX13">
         <v>17</v>
@@ -3953,19 +3953,19 @@
         <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC13">
         <v>19</v>
       </c>
       <c r="BD13">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -4054,7 +4054,7 @@
         <v>158</v>
       </c>
       <c r="F14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G14">
         <v>1.57</v>
@@ -4198,10 +4198,10 @@
         <v>4.5</v>
       </c>
       <c r="BB14">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC14">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD14">
         <v>19</v>
@@ -4311,7 +4311,7 @@
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4547,10 +4547,10 @@
         <v>1.9</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4586,10 +4586,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4804,7 +4804,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O17">
         <v>1.16</v>
@@ -5279,7 +5279,7 @@
         <v>5.4</v>
       </c>
       <c r="K19">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L19">
         <v>1.25</v>
@@ -5339,7 +5339,7 @@
         <v>27</v>
       </c>
       <c r="AE19">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF19">
         <v>12</v>
@@ -5438,7 +5438,7 @@
         <v>8.6</v>
       </c>
       <c r="BL19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM19">
         <v>21</v>
@@ -5462,10 +5462,10 @@
         <v>15.5</v>
       </c>
       <c r="BT19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV19">
         <v>60</v>
@@ -5515,7 +5515,7 @@
         <v>2.26</v>
       </c>
       <c r="I20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J20">
         <v>3.6</v>
@@ -5530,28 +5530,28 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q20">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R20">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="T20">
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V20">
         <v>1.78</v>
@@ -5560,10 +5560,10 @@
         <v>1.39</v>
       </c>
       <c r="X20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z20">
         <v>15.5</v>
@@ -5590,13 +5590,13 @@
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI20">
         <v>32</v>
       </c>
       <c r="AJ20">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="AK20">
         <v>36</v>
@@ -5608,7 +5608,7 @@
         <v>85</v>
       </c>
       <c r="AN20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO20">
         <v>13</v>
@@ -5647,25 +5647,25 @@
         <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC20">
         <v>32</v>
       </c>
       <c r="BD20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE20">
         <v>60</v>
       </c>
       <c r="BF20">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BG20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH20">
         <v>3.75</v>
@@ -5692,7 +5692,7 @@
         <v>6</v>
       </c>
       <c r="BP20">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BQ20">
         <v>18.5</v>
@@ -5722,7 +5722,7 @@
         <v>20</v>
       </c>
       <c r="BZ20">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CA20">
         <v>15.5</v>
@@ -5757,7 +5757,7 @@
         <v>4.4</v>
       </c>
       <c r="I21">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>3.95</v>
@@ -6014,13 +6014,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O22">
         <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q22">
         <v>1.3</v>
@@ -6029,7 +6029,7 @@
         <v>1.18</v>
       </c>
       <c r="S22">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -6041,7 +6041,7 @@
         <v>1.3</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6498,22 +6498,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P24">
         <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S24">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6624,7 +6624,7 @@
         <v>1.43</v>
       </c>
       <c r="BD24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BE24">
         <v>1.5</v>
@@ -6749,7 +6749,7 @@
         <v>2.3</v>
       </c>
       <c r="Q25">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R25">
         <v>1.43</v>
@@ -6785,7 +6785,7 @@
         <v>1000</v>
       </c>
       <c r="AC25">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD25">
         <v>21</v>
@@ -6842,7 +6842,7 @@
         <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AW25">
         <v>17.5</v>
@@ -6854,13 +6854,13 @@
         <v>1.79</v>
       </c>
       <c r="AZ25">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BA25">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BB25">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BC25">
         <v>1.99</v>
@@ -6869,7 +6869,7 @@
         <v>1.99</v>
       </c>
       <c r="BE25">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BF25">
         <v>19</v>
@@ -6961,7 +6961,7 @@
         <v>3.85</v>
       </c>
       <c r="G26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H26">
         <v>1.93</v>
@@ -6982,19 +6982,19 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O26">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q26">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S26">
         <v>2.96</v>
@@ -7009,7 +7009,7 @@
         <v>1.9</v>
       </c>
       <c r="W26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X26">
         <v>20</v>
@@ -7030,7 +7030,7 @@
         <v>970</v>
       </c>
       <c r="AD26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
         <v>1000</v>
@@ -7066,25 +7066,25 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AQ26">
         <v>7.2</v>
       </c>
       <c r="AR26">
-        <v>10.5</v>
+        <v>1.52</v>
       </c>
       <c r="AS26">
         <v>16</v>
       </c>
       <c r="AT26">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AU26">
-        <v>7.2</v>
+        <v>1.36</v>
       </c>
       <c r="AV26">
-        <v>9</v>
+        <v>1.52</v>
       </c>
       <c r="AW26">
         <v>16.5</v>
@@ -7093,31 +7093,31 @@
         <v>21</v>
       </c>
       <c r="AY26">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="BA26">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="BB26">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="BC26">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="BD26">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="BE26">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="BF26">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="BG26">
-        <v>11</v>
+        <v>1.52</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7212,7 +7212,7 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7248,10 +7248,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7445,13 +7445,13 @@
         <v>1.36</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H28">
         <v>1.36</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J28">
         <v>1.04</v>
@@ -7475,13 +7475,13 @@
         <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R28">
         <v>1.12</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7696,7 +7696,7 @@
         <v>15</v>
       </c>
       <c r="J29">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K29">
         <v>6.4</v>
@@ -7735,7 +7735,7 @@
         <v>1.07</v>
       </c>
       <c r="W29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X29">
         <v>19.5</v>
@@ -8010,7 +8010,7 @@
         <v>16.5</v>
       </c>
       <c r="AH30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AI30">
         <v>1000</v>
@@ -8061,7 +8061,7 @@
         <v>10</v>
       </c>
       <c r="AY30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ30">
         <v>36</v>
@@ -8091,13 +8091,13 @@
         <v>6.8</v>
       </c>
       <c r="BI30">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BJ30">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK30">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8124,10 +8124,10 @@
         <v>16.5</v>
       </c>
       <c r="BT30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BU30">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BV30">
         <v>1000</v>
@@ -8136,7 +8136,7 @@
         <v>21</v>
       </c>
       <c r="BX30">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BY30">
         <v>21</v>
@@ -8171,13 +8171,13 @@
         <v>2.66</v>
       </c>
       <c r="G31">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H31">
         <v>2.86</v>
       </c>
       <c r="I31">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8351,7 +8351,7 @@
         <v>5.7</v>
       </c>
       <c r="BO31">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP31">
         <v>19</v>
@@ -8410,10 +8410,10 @@
         <v>176</v>
       </c>
       <c r="F32">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G32">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H32">
         <v>4.2</v>
@@ -8461,7 +8461,7 @@
         <v>1.3</v>
       </c>
       <c r="W32">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X32">
         <v>24</v>
@@ -8476,7 +8476,7 @@
         <v>85</v>
       </c>
       <c r="AB32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC32">
         <v>9.800000000000001</v>
@@ -8536,7 +8536,7 @@
         <v>9</v>
       </c>
       <c r="AV32">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW32">
         <v>38</v>
@@ -8551,7 +8551,7 @@
         <v>14</v>
       </c>
       <c r="BA32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB32">
         <v>19.5</v>
@@ -8572,7 +8572,7 @@
         <v>27</v>
       </c>
       <c r="BH32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI32">
         <v>3.9</v>
@@ -8581,7 +8581,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8655,10 +8655,10 @@
         <v>3.25</v>
       </c>
       <c r="G33">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H33">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I33">
         <v>2.4</v>
@@ -8679,13 +8679,13 @@
         <v>3.5</v>
       </c>
       <c r="O33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P33">
         <v>1.85</v>
       </c>
       <c r="Q33">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R33">
         <v>1.33</v>
@@ -8703,7 +8703,7 @@
         <v>1.71</v>
       </c>
       <c r="W33">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X33">
         <v>16</v>
@@ -8763,7 +8763,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ33">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR33">
         <v>13</v>
@@ -8903,7 +8903,7 @@
         <v>23</v>
       </c>
       <c r="I34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J34">
         <v>14</v>
@@ -8918,13 +8918,13 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="O34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>1.15</v>
@@ -8936,16 +8936,16 @@
         <v>1.41</v>
       </c>
       <c r="T34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V34">
         <v>1.04</v>
       </c>
       <c r="W34">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -8954,16 +8954,16 @@
         <v>1000</v>
       </c>
       <c r="Z34">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AA34">
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AC34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AD34">
         <v>1000</v>
@@ -8972,19 +8972,19 @@
         <v>310</v>
       </c>
       <c r="AF34">
+        <v>23</v>
+      </c>
+      <c r="AG34">
         <v>18.5</v>
       </c>
-      <c r="AG34">
-        <v>21</v>
-      </c>
       <c r="AH34">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AI34">
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK34">
         <v>14</v>
@@ -8996,25 +8996,25 @@
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AO34">
         <v>1000</v>
       </c>
       <c r="AP34">
+        <v>38</v>
+      </c>
+      <c r="AQ34">
         <v>40</v>
       </c>
-      <c r="AQ34">
-        <v>42</v>
-      </c>
       <c r="AR34">
+        <v>16.5</v>
+      </c>
+      <c r="AS34">
+        <v>17.5</v>
+      </c>
+      <c r="AT34">
         <v>20</v>
-      </c>
-      <c r="AS34">
-        <v>19.5</v>
-      </c>
-      <c r="AT34">
-        <v>21</v>
       </c>
       <c r="AU34">
         <v>34</v>
@@ -9023,7 +9023,7 @@
         <v>36</v>
       </c>
       <c r="AW34">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX34">
         <v>16.5</v>
@@ -9032,7 +9032,7 @@
         <v>16.5</v>
       </c>
       <c r="AZ34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA34">
         <v>44</v>
@@ -9044,19 +9044,19 @@
         <v>12.5</v>
       </c>
       <c r="BD34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE34">
         <v>40</v>
       </c>
       <c r="BF34">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BG34">
         <v>85</v>
       </c>
       <c r="BH34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BI34">
         <v>8.199999999999999</v>
@@ -9080,19 +9080,19 @@
         <v>4.6</v>
       </c>
       <c r="BP34">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ34">
         <v>5.2</v>
       </c>
       <c r="BR34">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BS34">
         <v>8.199999999999999</v>
       </c>
       <c r="BT34">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BU34">
         <v>17</v>
@@ -9136,22 +9136,22 @@
         <v>179</v>
       </c>
       <c r="F35">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H35">
         <v>1.74</v>
       </c>
       <c r="I35">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J35">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L35">
         <v>1.43</v>
@@ -9166,43 +9166,43 @@
         <v>1.35</v>
       </c>
       <c r="P35">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q35">
         <v>2.02</v>
       </c>
       <c r="R35">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S35">
         <v>3.65</v>
       </c>
       <c r="T35">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U35">
         <v>1.93</v>
       </c>
       <c r="V35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W35">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X35">
         <v>13.5</v>
       </c>
       <c r="Y35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA35">
         <v>18.5</v>
       </c>
       <c r="AB35">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC35">
         <v>8.800000000000001</v>
@@ -9211,13 +9211,13 @@
         <v>10.5</v>
       </c>
       <c r="AE35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG35">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH35">
         <v>22</v>
@@ -9226,13 +9226,13 @@
         <v>40</v>
       </c>
       <c r="AJ35">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK35">
+        <v>80</v>
+      </c>
+      <c r="AL35">
         <v>90</v>
-      </c>
-      <c r="AL35">
-        <v>95</v>
       </c>
       <c r="AM35">
         <v>140</v>
@@ -9247,7 +9247,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR35">
         <v>8.800000000000001</v>
@@ -9259,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="AU35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV35">
         <v>9.199999999999999</v>
@@ -9268,10 +9268,10 @@
         <v>17</v>
       </c>
       <c r="AX35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY35">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ35">
         <v>19.5</v>
@@ -9280,19 +9280,19 @@
         <v>34</v>
       </c>
       <c r="BB35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC35">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="BD35">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE35">
         <v>14</v>
       </c>
       <c r="BF35">
-        <v>70</v>
+        <v>16.5</v>
       </c>
       <c r="BG35">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -556,7 +556,7 @@
     <t>Braga</t>
   </si>
   <si>
-    <t>2026-09-08 21:50:44</t>
+    <t>2026-09-09 00:03:37</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1153,7 @@
         <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
         <v>3.1</v>
@@ -1237,7 +1237,7 @@
         <v>16</v>
       </c>
       <c r="AI2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
         <v>32</v>
@@ -1249,7 +1249,7 @@
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
         <v>15</v>
@@ -1261,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
         <v>8</v>
@@ -1288,10 +1288,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB2">
         <v>25</v>
@@ -1300,10 +1300,10 @@
         <v>20</v>
       </c>
       <c r="BD2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1354,16 +1354,16 @@
         <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ2">
         <v>24</v>
@@ -1398,7 +1398,7 @@
         <v>1.93</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
         <v>5.3</v>
@@ -1479,10 +1479,10 @@
         <v>28</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK3">
         <v>28</v>
@@ -1494,7 +1494,7 @@
         <v>200</v>
       </c>
       <c r="AN3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO3">
         <v>150</v>
@@ -1509,7 +1509,7 @@
         <v>32</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT3">
         <v>6.4</v>
@@ -1521,7 +1521,7 @@
         <v>18</v>
       </c>
       <c r="AW3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX3">
         <v>9.199999999999999</v>
@@ -1530,28 +1530,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC3">
         <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF3">
         <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH3">
         <v>3.3</v>
@@ -1569,7 +1569,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1581,16 +1581,16 @@
         <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU3">
         <v>5.1</v>
@@ -1605,7 +1605,7 @@
         <v>80</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
         <v>40</v>
@@ -1634,19 +1634,19 @@
         <v>148</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K4">
         <v>2.96</v>
@@ -1655,10 +1655,10 @@
         <v>1.66</v>
       </c>
       <c r="M4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
         <v>1.79</v>
@@ -1667,133 +1667,133 @@
         <v>1.38</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R4">
         <v>1.13</v>
       </c>
       <c r="S4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="U4">
         <v>1.52</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="X4">
         <v>6.4</v>
       </c>
       <c r="Y4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>36</v>
+      </c>
+      <c r="AI4">
+        <v>170</v>
+      </c>
+      <c r="AJ4">
+        <v>38</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>110</v>
+      </c>
+      <c r="AM4">
+        <v>390</v>
+      </c>
+      <c r="AN4">
+        <v>55</v>
+      </c>
+      <c r="AO4">
+        <v>200</v>
+      </c>
+      <c r="AP4">
+        <v>5.7</v>
+      </c>
+      <c r="AQ4">
+        <v>8.4</v>
+      </c>
+      <c r="AR4">
         <v>25</v>
       </c>
-      <c r="AE4">
-        <v>130</v>
-      </c>
-      <c r="AF4">
-        <v>13.5</v>
-      </c>
-      <c r="AG4">
-        <v>18.5</v>
-      </c>
-      <c r="AH4">
-        <v>44</v>
-      </c>
-      <c r="AI4">
-        <v>180</v>
-      </c>
-      <c r="AJ4">
-        <v>44</v>
-      </c>
-      <c r="AK4">
-        <v>60</v>
-      </c>
-      <c r="AL4">
-        <v>130</v>
-      </c>
-      <c r="AM4">
-        <v>430</v>
-      </c>
-      <c r="AN4">
-        <v>100</v>
-      </c>
-      <c r="AO4">
-        <v>210</v>
-      </c>
-      <c r="AP4">
-        <v>5.4</v>
-      </c>
-      <c r="AQ4">
-        <v>7.4</v>
-      </c>
-      <c r="AR4">
-        <v>19</v>
-      </c>
       <c r="AS4">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AX4">
         <v>11</v>
       </c>
       <c r="AY4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
         <v>30</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BB4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD4">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BF4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1885,46 +1885,46 @@
         <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="S5">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
         <v>1.86</v>
@@ -1936,16 +1936,16 @@
         <v>20</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA5">
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>15</v>
@@ -1960,16 +1960,16 @@
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>27</v>
@@ -1978,16 +1978,16 @@
         <v>60</v>
       </c>
       <c r="AN5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR5">
         <v>25</v>
@@ -1996,10 +1996,10 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
         <v>13.5</v>
@@ -2026,10 +2026,10 @@
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF5">
         <v>9.199999999999999</v>
@@ -2041,7 +2041,7 @@
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ5">
         <v>9.6</v>
@@ -2071,7 +2071,7 @@
         <v>25</v>
       </c>
       <c r="BS5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BT5">
         <v>7.4</v>
@@ -2124,13 +2124,13 @@
         <v>2.74</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
         <v>2.92</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
         <v>3.65</v>
@@ -2163,7 +2163,7 @@
         <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>1.52</v>
@@ -2193,7 +2193,7 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6">
         <v>18</v>
@@ -2208,13 +2208,13 @@
         <v>50</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AK6">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2226,7 +2226,7 @@
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
         <v>11</v>
@@ -2235,7 +2235,7 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2247,7 +2247,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AX6">
         <v>16</v>
@@ -2259,19 +2259,19 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC6">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BD6">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF6">
         <v>20</v>
@@ -2363,7 +2363,7 @@
         <v>1.86</v>
       </c>
       <c r="G7">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H7">
         <v>4.3</v>
@@ -2375,7 +2375,7 @@
         <v>4.1</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2393,7 +2393,7 @@
         <v>2.28</v>
       </c>
       <c r="Q7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
         <v>1.51</v>
@@ -2408,10 +2408,10 @@
         <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X7">
         <v>21</v>
@@ -2447,7 +2447,7 @@
         <v>18</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2474,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="AR7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS7">
         <v>55</v>
@@ -2492,10 +2492,10 @@
         <v>32</v>
       </c>
       <c r="AX7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
         <v>15.5</v>
@@ -2504,22 +2504,22 @@
         <v>32</v>
       </c>
       <c r="BB7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF7">
         <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2602,13 +2602,13 @@
         <v>152</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>3.1</v>
@@ -2641,7 +2641,7 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T8">
         <v>1.33</v>
@@ -2656,7 +2656,7 @@
         <v>1.81</v>
       </c>
       <c r="X8">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y8">
         <v>34</v>
@@ -2665,13 +2665,13 @@
         <v>38</v>
       </c>
       <c r="AA8">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="AB8">
         <v>28</v>
       </c>
       <c r="AC8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8">
         <v>17</v>
@@ -2713,16 +2713,16 @@
         <v>32</v>
       </c>
       <c r="AQ8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU8">
         <v>12.5</v>
@@ -2731,10 +2731,10 @@
         <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2746,7 +2746,7 @@
         <v>20</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC8">
         <v>16.5</v>
@@ -2758,70 +2758,70 @@
         <v>27</v>
       </c>
       <c r="BF8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG8">
         <v>9.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI8">
-        <v>1.46</v>
+        <v>5.8</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BM8">
-        <v>1.75</v>
+        <v>5.8</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
-        <v>1.45</v>
+        <v>5.8</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS8">
-        <v>1.75</v>
+        <v>5.1</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY8">
-        <v>1.75</v>
+        <v>5.4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA8">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="CB8" t="s">
         <v>180</v>
@@ -2844,16 +2844,16 @@
         <v>153</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
         <v>110</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>2.04</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -2868,22 +2868,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="O9">
         <v>1.3</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q9">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="R9">
         <v>1.13</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2892,10 +2892,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3092,7 +3092,7 @@
         <v>1.46</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>7.6</v>
@@ -3101,7 +3101,7 @@
         <v>5.4</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
         <v>1.23</v>
@@ -3119,7 +3119,7 @@
         <v>3.35</v>
       </c>
       <c r="Q10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R10">
         <v>1.95</v>
@@ -3137,13 +3137,13 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X10">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z10">
         <v>100</v>
@@ -3161,10 +3161,10 @@
         <v>28</v>
       </c>
       <c r="AE10">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AF10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG10">
         <v>11</v>
@@ -3173,7 +3173,7 @@
         <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>570</v>
+        <v>790</v>
       </c>
       <c r="AJ10">
         <v>15</v>
@@ -3185,16 +3185,16 @@
         <v>24</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO10">
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ10">
         <v>27</v>
@@ -3212,10 +3212,10 @@
         <v>12.5</v>
       </c>
       <c r="AV10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AW10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
@@ -3227,10 +3227,10 @@
         <v>16.5</v>
       </c>
       <c r="BA10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
         <v>12</v>
@@ -3242,7 +3242,7 @@
         <v>40</v>
       </c>
       <c r="BF10">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG10">
         <v>29</v>
@@ -3254,7 +3254,7 @@
         <v>4.9</v>
       </c>
       <c r="BJ10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK10">
         <v>8.199999999999999</v>
@@ -3287,13 +3287,13 @@
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW10">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BX10">
         <v>42</v>
@@ -3331,7 +3331,7 @@
         <v>1.44</v>
       </c>
       <c r="G11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
         <v>7.4</v>
@@ -3361,7 +3361,7 @@
         <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R11">
         <v>2</v>
@@ -3373,7 +3373,7 @@
         <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3385,7 +3385,7 @@
         <v>40</v>
       </c>
       <c r="Y11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z11">
         <v>1000</v>
@@ -3403,7 +3403,7 @@
         <v>30</v>
       </c>
       <c r="AE11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF11">
         <v>13.5</v>
@@ -3430,13 +3430,13 @@
         <v>75</v>
       </c>
       <c r="AN11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AO11">
         <v>60</v>
       </c>
       <c r="AP11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ11">
         <v>29</v>
@@ -3451,13 +3451,13 @@
         <v>14.5</v>
       </c>
       <c r="AU11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV11">
         <v>26</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX11">
         <v>11.5</v>
@@ -3472,7 +3472,7 @@
         <v>50</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC11">
         <v>12</v>
@@ -3481,10 +3481,10 @@
         <v>20</v>
       </c>
       <c r="BE11">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG11">
         <v>29</v>
@@ -3547,7 +3547,7 @@
         <v>8.6</v>
       </c>
       <c r="CA11">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="s">
         <v>180</v>
@@ -3573,7 +3573,7 @@
         <v>1.82</v>
       </c>
       <c r="G12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H12">
         <v>4.1</v>
@@ -3615,13 +3615,13 @@
         <v>1.48</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V12">
         <v>1.3</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X12">
         <v>40</v>
@@ -3648,7 +3648,7 @@
         <v>46</v>
       </c>
       <c r="AF12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG12">
         <v>11</v>
@@ -3684,10 +3684,10 @@
         <v>19.5</v>
       </c>
       <c r="AR12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT12">
         <v>15</v>
@@ -3699,7 +3699,7 @@
         <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -3723,7 +3723,7 @@
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF12">
         <v>5.9</v>
@@ -3812,16 +3812,16 @@
         <v>157</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H13">
         <v>2.88</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -3842,7 +3842,7 @@
         <v>1.17</v>
       </c>
       <c r="P13">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q13">
         <v>1.54</v>
@@ -3887,7 +3887,7 @@
         <v>14</v>
       </c>
       <c r="AE13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF13">
         <v>20</v>
@@ -3917,10 +3917,10 @@
         <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ13">
         <v>16.5</v>
@@ -3929,7 +3929,7 @@
         <v>21</v>
       </c>
       <c r="AS13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT13">
         <v>14.5</v>
@@ -3956,16 +3956,16 @@
         <v>23</v>
       </c>
       <c r="BB13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC13">
         <v>19</v>
       </c>
       <c r="BD13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF13">
         <v>10</v>
@@ -3974,64 +3974,64 @@
         <v>14</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI13">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK13">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BN13">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO13">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13">
         <v>8.6</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW13">
         <v>10</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="s">
         <v>180</v>
@@ -4069,7 +4069,7 @@
         <v>4.8</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4078,22 +4078,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="R14">
         <v>1.65</v>
       </c>
       <c r="S14">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="T14">
         <v>1.65</v>
@@ -4117,7 +4117,7 @@
         <v>75</v>
       </c>
       <c r="AA14">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB14">
         <v>15</v>
@@ -4129,10 +4129,10 @@
         <v>32</v>
       </c>
       <c r="AE14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG14">
         <v>13</v>
@@ -4141,10 +4141,10 @@
         <v>24</v>
       </c>
       <c r="AI14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK14">
         <v>17.5</v>
@@ -4156,7 +4156,7 @@
         <v>95</v>
       </c>
       <c r="AN14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO14">
         <v>80</v>
@@ -4165,25 +4165,25 @@
         <v>21</v>
       </c>
       <c r="AQ14">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS14">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT14">
         <v>10.5</v>
       </c>
       <c r="AU14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW14">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX14">
         <v>9.800000000000001</v>
@@ -4192,13 +4192,13 @@
         <v>9</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC14">
         <v>12</v>
@@ -4207,13 +4207,13 @@
         <v>19</v>
       </c>
       <c r="BE14">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4299,16 +4299,16 @@
         <v>2.12</v>
       </c>
       <c r="G15">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H15">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="I15">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
         <v>4.9</v>
@@ -4326,7 +4326,7 @@
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q15">
         <v>1.51</v>
@@ -4344,10 +4344,10 @@
         <v>2.48</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4398,7 +4398,7 @@
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4550,7 +4550,7 @@
         <v>110</v>
       </c>
       <c r="J16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4586,10 +4586,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4780,22 +4780,22 @@
         <v>161</v>
       </c>
       <c r="F17">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G17">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H17">
         <v>4.3</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
         <v>4.1</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4804,16 +4804,16 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
         <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="R17">
         <v>1.18</v>
@@ -4822,10 +4822,10 @@
         <v>1.54</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
         <v>1.01</v>
@@ -4882,7 +4882,7 @@
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO17">
         <v>1000</v>
@@ -4900,25 +4900,25 @@
         <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
         <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
         <v>1.03</v>
@@ -4927,7 +4927,7 @@
         <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
         <v>1.03</v>
@@ -5022,22 +5022,22 @@
         <v>162</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18">
         <v>1.26</v>
       </c>
       <c r="I18">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="J18">
         <v>6.8</v>
       </c>
       <c r="K18">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5070,7 +5070,7 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="W18">
         <v>1.08</v>
@@ -5270,10 +5270,10 @@
         <v>1.48</v>
       </c>
       <c r="H19">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
         <v>5.4</v>
@@ -5291,7 +5291,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P19">
         <v>3</v>
@@ -5321,7 +5321,7 @@
         <v>34</v>
       </c>
       <c r="Y19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z19">
         <v>70</v>
@@ -5363,10 +5363,10 @@
         <v>25</v>
       </c>
       <c r="AM19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN19">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AO19">
         <v>65</v>
@@ -5375,10 +5375,10 @@
         <v>28</v>
       </c>
       <c r="AQ19">
+        <v>30</v>
+      </c>
+      <c r="AR19">
         <v>32</v>
-      </c>
-      <c r="AR19">
-        <v>60</v>
       </c>
       <c r="AS19">
         <v>46</v>
@@ -5417,7 +5417,7 @@
         <v>22</v>
       </c>
       <c r="BE19">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF19">
         <v>4.4</v>
@@ -5462,10 +5462,10 @@
         <v>15.5</v>
       </c>
       <c r="BT19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BV19">
         <v>60</v>
@@ -5539,7 +5539,7 @@
         <v>2.28</v>
       </c>
       <c r="Q20">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R20">
         <v>1.49</v>
@@ -5560,7 +5560,7 @@
         <v>1.39</v>
       </c>
       <c r="X20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y20">
         <v>12.5</v>
@@ -5590,13 +5590,13 @@
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI20">
         <v>32</v>
       </c>
       <c r="AJ20">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="AK20">
         <v>36</v>
@@ -5605,7 +5605,7 @@
         <v>42</v>
       </c>
       <c r="AM20">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN20">
         <v>28</v>
@@ -5620,7 +5620,7 @@
         <v>11.5</v>
       </c>
       <c r="AR20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS20">
         <v>26</v>
@@ -5668,64 +5668,64 @@
         <v>12</v>
       </c>
       <c r="BH20">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL20">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BP20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BX20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>180</v>
@@ -5778,10 +5778,10 @@
         <v>1.26</v>
       </c>
       <c r="P21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R21">
         <v>1.36</v>
@@ -6014,13 +6014,13 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O22">
         <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q22">
         <v>1.3</v>
@@ -6038,10 +6038,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6232,13 +6232,13 @@
         <v>167</v>
       </c>
       <c r="F23">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I23">
         <v>1.4</v>
@@ -6247,7 +6247,7 @@
         <v>5.3</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6262,16 +6262,16 @@
         <v>1.14</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="R23">
         <v>1.59</v>
       </c>
       <c r="S23">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6283,7 +6283,7 @@
         <v>3.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6337,7 +6337,7 @@
         <v>1000</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP23">
         <v>1.03</v>
@@ -6498,28 +6498,28 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.44</v>
+        <v>5.2</v>
       </c>
       <c r="O24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P24">
         <v>2.44</v>
       </c>
       <c r="Q24">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S24">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -6719,13 +6719,13 @@
         <v>3.35</v>
       </c>
       <c r="G25">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="H25">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="I25">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J25">
         <v>3.7</v>
@@ -6737,13 +6737,13 @@
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25">
         <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P25">
         <v>2.3</v>
@@ -6758,19 +6758,19 @@
         <v>2.68</v>
       </c>
       <c r="T25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V25">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
         <v>1000</v>
@@ -6824,25 +6824,25 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>14.5</v>
+        <v>1.81</v>
       </c>
       <c r="AQ25">
         <v>10</v>
       </c>
       <c r="AR25">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AS25">
         <v>19</v>
       </c>
       <c r="AT25">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AU25">
         <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AW25">
         <v>17.5</v>
@@ -6851,25 +6851,25 @@
         <v>18</v>
       </c>
       <c r="AY25">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AZ25">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="BA25">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="BB25">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="BC25">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="BD25">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="BE25">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="BF25">
         <v>19</v>
@@ -6961,10 +6961,10 @@
         <v>3.85</v>
       </c>
       <c r="G26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H26">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I26">
         <v>2.1</v>
@@ -6982,28 +6982,28 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P26">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R26">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S26">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T26">
         <v>1.68</v>
       </c>
       <c r="U26">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V26">
         <v>1.9</v>
@@ -7012,10 +7012,10 @@
         <v>1.3</v>
       </c>
       <c r="X26">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z26">
         <v>1000</v>
@@ -7027,16 +7027,16 @@
         <v>970</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE26">
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG26">
         <v>970</v>
@@ -7045,7 +7045,7 @@
         <v>22</v>
       </c>
       <c r="AI26">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ26">
         <v>100</v>
@@ -7066,25 +7066,25 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AQ26">
         <v>7.2</v>
       </c>
       <c r="AR26">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="AS26">
         <v>16</v>
       </c>
       <c r="AT26">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AU26">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AV26">
-        <v>1.52</v>
+        <v>9</v>
       </c>
       <c r="AW26">
         <v>16.5</v>
@@ -7093,31 +7093,31 @@
         <v>21</v>
       </c>
       <c r="AY26">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AZ26">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="BA26">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="BB26">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="BC26">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BD26">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BE26">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BF26">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="BG26">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7212,7 +7212,7 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7248,10 +7248,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7442,19 +7442,19 @@
         <v>172</v>
       </c>
       <c r="F28">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="H28">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="I28">
         <v>110</v>
       </c>
       <c r="J28">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
         <v>4</v>
@@ -7475,13 +7475,13 @@
         <v>1.25</v>
       </c>
       <c r="Q28">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R28">
         <v>1.12</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7490,10 +7490,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
         <v>29</v>
       </c>
       <c r="J30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K30">
         <v>11.5</v>
@@ -7977,7 +7977,7 @@
         <v>1.03</v>
       </c>
       <c r="W30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X30">
         <v>60</v>
@@ -8010,7 +8010,7 @@
         <v>16.5</v>
       </c>
       <c r="AH30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI30">
         <v>1000</v>
@@ -8028,7 +8028,7 @@
         <v>1000</v>
       </c>
       <c r="AN30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AO30">
         <v>440</v>
@@ -8061,10 +8061,10 @@
         <v>10</v>
       </c>
       <c r="AY30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA30">
         <v>50</v>
@@ -8076,16 +8076,16 @@
         <v>12.5</v>
       </c>
       <c r="BD30">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BE30">
         <v>44</v>
       </c>
       <c r="BF30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BG30">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BH30">
         <v>6.8</v>
@@ -8168,16 +8168,16 @@
         <v>175</v>
       </c>
       <c r="F31">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G31">
         <v>2.7</v>
       </c>
       <c r="H31">
+        <v>2.84</v>
+      </c>
+      <c r="I31">
         <v>2.86</v>
-      </c>
-      <c r="I31">
-        <v>2.9</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8201,7 +8201,7 @@
         <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
         <v>1.45</v>
@@ -8219,7 +8219,7 @@
         <v>1.53</v>
       </c>
       <c r="W31">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X31">
         <v>16.5</v>
@@ -8228,7 +8228,7 @@
         <v>13.5</v>
       </c>
       <c r="Z31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA31">
         <v>44</v>
@@ -8240,13 +8240,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE31">
         <v>29</v>
       </c>
       <c r="AF31">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG31">
         <v>12</v>
@@ -8273,7 +8273,7 @@
         <v>19.5</v>
       </c>
       <c r="AO31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP31">
         <v>15</v>
@@ -8366,13 +8366,13 @@
         <v>21</v>
       </c>
       <c r="BT31">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU31">
         <v>5.5</v>
       </c>
       <c r="BV31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW31">
         <v>15</v>
@@ -8413,7 +8413,7 @@
         <v>1.9</v>
       </c>
       <c r="G32">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H32">
         <v>4.2</v>
@@ -8422,7 +8422,7 @@
         <v>4.3</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K32">
         <v>4.2</v>
@@ -8434,10 +8434,10 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P32">
         <v>2.58</v>
@@ -8452,7 +8452,7 @@
         <v>2.54</v>
       </c>
       <c r="T32">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U32">
         <v>2.6</v>
@@ -8479,7 +8479,7 @@
         <v>13.5</v>
       </c>
       <c r="AC32">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD32">
         <v>17</v>
@@ -8512,10 +8512,10 @@
         <v>65</v>
       </c>
       <c r="AN32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP32">
         <v>20</v>
@@ -8572,64 +8572,64 @@
         <v>27</v>
       </c>
       <c r="BH32">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BJ32">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BR32">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV32">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
         <v>180</v>
@@ -8655,16 +8655,16 @@
         <v>3.25</v>
       </c>
       <c r="G33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H33">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I33">
         <v>2.4</v>
       </c>
       <c r="J33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K33">
         <v>3.65</v>
@@ -8676,22 +8676,22 @@
         <v>1.07</v>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O33">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S33">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T33">
         <v>1.82</v>
@@ -8703,10 +8703,10 @@
         <v>1.71</v>
       </c>
       <c r="W33">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X33">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y33">
         <v>10.5</v>
@@ -8748,7 +8748,7 @@
         <v>50</v>
       </c>
       <c r="AL33">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM33">
         <v>120</v>
@@ -8769,7 +8769,7 @@
         <v>13</v>
       </c>
       <c r="AS33">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT33">
         <v>10.5</v>
@@ -8793,22 +8793,22 @@
         <v>16</v>
       </c>
       <c r="BA33">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB33">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD33">
+        <v>6.2</v>
+      </c>
+      <c r="BE33">
+        <v>6.6</v>
+      </c>
+      <c r="BF33">
         <v>6</v>
-      </c>
-      <c r="BE33">
-        <v>6</v>
-      </c>
-      <c r="BF33">
-        <v>5.7</v>
       </c>
       <c r="BG33">
         <v>18.5</v>
@@ -8936,10 +8936,10 @@
         <v>1.41</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
         <v>1.04</v>
@@ -8960,7 +8960,7 @@
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AC34">
         <v>100</v>
@@ -8969,22 +8969,22 @@
         <v>1000</v>
       </c>
       <c r="AE34">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AF34">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AG34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH34">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AI34">
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK34">
         <v>14</v>
@@ -8996,7 +8996,7 @@
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AO34">
         <v>1000</v>
@@ -9008,10 +9008,10 @@
         <v>40</v>
       </c>
       <c r="AR34">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS34">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT34">
         <v>20</v>
@@ -9023,7 +9023,7 @@
         <v>36</v>
       </c>
       <c r="AW34">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX34">
         <v>16.5</v>
@@ -9032,22 +9032,22 @@
         <v>16.5</v>
       </c>
       <c r="AZ34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA34">
         <v>44</v>
       </c>
       <c r="BB34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC34">
         <v>12.5</v>
       </c>
       <c r="BD34">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF34">
         <v>1.83</v>
@@ -9080,7 +9080,7 @@
         <v>4.6</v>
       </c>
       <c r="BP34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BQ34">
         <v>5.2</v>
@@ -9136,13 +9136,13 @@
         <v>179</v>
       </c>
       <c r="F35">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G35">
         <v>5.7</v>
       </c>
       <c r="H35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I35">
         <v>1.76</v>
@@ -9160,25 +9160,25 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35">
         <v>1.35</v>
       </c>
       <c r="P35">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q35">
         <v>2.02</v>
       </c>
       <c r="R35">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S35">
         <v>3.65</v>
       </c>
       <c r="T35">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U35">
         <v>1.93</v>
@@ -9190,7 +9190,7 @@
         <v>1.21</v>
       </c>
       <c r="X35">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -9280,13 +9280,13 @@
         <v>34</v>
       </c>
       <c r="BB35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BE35">
         <v>14</v>
@@ -9313,7 +9313,7 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="BN35">
         <v>1000</v>
@@ -9325,13 +9325,13 @@
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="BT35">
         <v>5.8</v>
@@ -9349,13 +9349,13 @@
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="CB35" t="s">
         <v>180</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -475,21 +475,21 @@
     <t>Panathinaikos</t>
   </si>
   <si>
+    <t>Man Utd</t>
+  </si>
+  <si>
+    <t>Slavia Prague</t>
+  </si>
+  <si>
     <t>Como</t>
   </si>
   <si>
-    <t>Man Utd</t>
+    <t>Stevenage</t>
   </si>
   <si>
     <t>Bayern Munich</t>
   </si>
   <si>
-    <t>Stevenage</t>
-  </si>
-  <si>
-    <t>Slavia Prague</t>
-  </si>
-  <si>
     <t>Club Football Estrela</t>
   </si>
   <si>
@@ -607,21 +607,21 @@
     <t>Kifisia</t>
   </si>
   <si>
+    <t>FC Sabah</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
-    <t>FC Sabah</t>
+    <t>Luton</t>
   </si>
   <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
-    <t>Luton</t>
-  </si>
-  <si>
-    <t>Lens</t>
-  </si>
-  <si>
     <t>Braga</t>
   </si>
   <si>
@@ -643,7 +643,7 @@
     <t>Goias</t>
   </si>
   <si>
-    <t>2026-09-09 13:48:23</t>
+    <t>2026-09-09 16:08:31</t>
   </si>
 </sst>
 </file>
@@ -1237,19 +1237,19 @@
         <v>165</v>
       </c>
       <c r="F2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H2">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
         <v>3.75</v>
@@ -1264,7 +1264,7 @@
         <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
         <v>2.28</v>
@@ -1273,7 +1273,7 @@
         <v>1.74</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
         <v>2.88</v>
@@ -1285,10 +1285,10 @@
         <v>2.56</v>
       </c>
       <c r="V2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X2">
         <v>18.5</v>
@@ -1297,31 +1297,31 @@
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2">
         <v>44</v>
       </c>
       <c r="AB2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2">
         <v>36</v>
@@ -1330,13 +1330,13 @@
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL2">
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2">
         <v>17.5</v>
@@ -1345,7 +1345,7 @@
         <v>21</v>
       </c>
       <c r="AP2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2">
         <v>12.5</v>
@@ -1354,7 +1354,7 @@
         <v>18.5</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1369,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="AX2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1381,7 +1381,7 @@
         <v>30</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC2">
         <v>22</v>
@@ -1393,10 +1393,10 @@
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH2">
         <v>3.9</v>
@@ -1405,7 +1405,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2">
         <v>7.8</v>
@@ -1420,7 +1420,7 @@
         <v>5.8</v>
       </c>
       <c r="BO2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP2">
         <v>19</v>
@@ -1435,19 +1435,19 @@
         <v>20</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2">
         <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY2">
         <v>22</v>
@@ -1479,10 +1479,10 @@
         <v>166</v>
       </c>
       <c r="F3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H3">
         <v>5.5</v>
@@ -1503,7 +1503,7 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
         <v>1.41</v>
@@ -1524,13 +1524,13 @@
         <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X3">
         <v>12</v>
@@ -1554,7 +1554,7 @@
         <v>27</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>9.800000000000001</v>
@@ -1581,7 +1581,7 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3">
         <v>140</v>
@@ -1599,10 +1599,10 @@
         <v>16</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>20</v>
@@ -1611,7 +1611,7 @@
         <v>55</v>
       </c>
       <c r="AX3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
         <v>9.4</v>
@@ -1623,7 +1623,7 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC3">
         <v>19</v>
@@ -1632,7 +1632,7 @@
         <v>40</v>
       </c>
       <c r="BE3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF3">
         <v>13</v>
@@ -1650,13 +1650,13 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BN3">
         <v>4.2</v>
@@ -1668,16 +1668,16 @@
         <v>13</v>
       </c>
       <c r="BQ3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR3">
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BU3">
         <v>5</v>
@@ -1686,19 +1686,19 @@
         <v>55</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>65</v>
       </c>
       <c r="BY3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
         <v>34</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
         <v>209</v>
@@ -1724,79 +1724,79 @@
         <v>2.48</v>
       </c>
       <c r="G4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="L4">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="M4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="N4">
+        <v>1.97</v>
+      </c>
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4">
-        <v>1.97</v>
-      </c>
       <c r="P4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="S4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="U4">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>26</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF4">
         <v>13</v>
@@ -1805,13 +1805,13 @@
         <v>15</v>
       </c>
       <c r="AH4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AJ4">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AK4">
         <v>55</v>
@@ -1820,16 +1820,16 @@
         <v>130</v>
       </c>
       <c r="AM4">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="AN4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AP4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
@@ -1838,10 +1838,10 @@
         <v>24</v>
       </c>
       <c r="AS4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1853,94 +1853,94 @@
         <v>85</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
         <v>14</v>
       </c>
       <c r="AZ4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA4">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="BB4">
         <v>38</v>
       </c>
       <c r="BC4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD4">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF4">
         <v>60</v>
       </c>
       <c r="BG4">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="BH4">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.97</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="BP4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
+        <v>8.4</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>14</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>2.56</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>13.5</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
         <v>12.5</v>
       </c>
-      <c r="BR4">
-        <v>75</v>
-      </c>
-      <c r="BS4">
-        <v>2.04</v>
-      </c>
-      <c r="BT4">
-        <v>7.2</v>
-      </c>
-      <c r="BU4">
-        <v>6.4</v>
-      </c>
-      <c r="BV4">
-        <v>55</v>
-      </c>
-      <c r="BW4">
-        <v>2.04</v>
-      </c>
-      <c r="BX4">
-        <v>100</v>
-      </c>
-      <c r="BY4">
-        <v>2.04</v>
-      </c>
       <c r="BZ4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.04</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>209</v>
@@ -1966,13 +1966,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2002,19 +2002,19 @@
         <v>1.67</v>
       </c>
       <c r="S5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
         <v>1.57</v>
       </c>
       <c r="U5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V5">
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -2029,10 +2029,10 @@
         <v>75</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>16.5</v>
@@ -2068,7 +2068,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP5">
         <v>21</v>
@@ -2095,7 +2095,7 @@
         <v>32</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -2119,7 +2119,7 @@
         <v>46</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG5">
         <v>23</v>
@@ -2149,7 +2149,7 @@
         <v>4.7</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
         <v>11</v>
@@ -2176,13 +2176,13 @@
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BZ5">
         <v>16</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB5" t="s">
         <v>209</v>
@@ -2205,16 +2205,16 @@
         <v>169</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>3.55</v>
@@ -2235,10 +2235,10 @@
         <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
         <v>1.41</v>
@@ -2247,13 +2247,13 @@
         <v>3.35</v>
       </c>
       <c r="T6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
         <v>2.3</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
         <v>1.62</v>
@@ -2268,7 +2268,7 @@
         <v>20</v>
       </c>
       <c r="AA6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB6">
         <v>12</v>
@@ -2283,7 +2283,7 @@
         <v>32</v>
       </c>
       <c r="AF6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2295,7 +2295,7 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK6">
         <v>28</v>
@@ -2322,10 +2322,10 @@
         <v>18</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
         <v>7.4</v>
@@ -2334,7 +2334,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX6">
         <v>15.5</v>
@@ -2346,7 +2346,7 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>32</v>
@@ -2355,37 +2355,37 @@
         <v>24</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE6">
         <v>65</v>
       </c>
       <c r="BF6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG6">
         <v>23</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
         <v>3.3</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO6">
         <v>5.1</v>
@@ -2394,7 +2394,7 @@
         <v>19</v>
       </c>
       <c r="BQ6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
         <v>30</v>
@@ -2409,16 +2409,16 @@
         <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>32</v>
       </c>
       <c r="BY6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>24</v>
@@ -2453,16 +2453,16 @@
         <v>2.04</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7">
+        <v>3.9</v>
+      </c>
+      <c r="K7">
         <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.1</v>
       </c>
       <c r="L7">
         <v>1.36</v>
@@ -2471,7 +2471,7 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
         <v>1.26</v>
@@ -2486,10 +2486,10 @@
         <v>1.48</v>
       </c>
       <c r="S7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
         <v>2.34</v>
@@ -2498,10 +2498,10 @@
         <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y7">
         <v>17.5</v>
@@ -2513,7 +2513,7 @@
         <v>75</v>
       </c>
       <c r="AB7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -2609,10 +2609,10 @@
         <v>32</v>
       </c>
       <c r="BH7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI7">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7">
         <v>9.199999999999999</v>
@@ -2624,16 +2624,16 @@
         <v>100</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
         <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
         <v>11.5</v>
@@ -2642,31 +2642,31 @@
         <v>26</v>
       </c>
       <c r="BS7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
         <v>6.6</v>
       </c>
       <c r="BV7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BX7">
         <v>38</v>
       </c>
       <c r="BY7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BZ7">
         <v>21</v>
       </c>
       <c r="CA7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CB7" t="s">
         <v>209</v>
@@ -2689,10 +2689,10 @@
         <v>171</v>
       </c>
       <c r="F8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H8">
         <v>2.82</v>
@@ -2701,10 +2701,10 @@
         <v>2.88</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.18</v>
@@ -2728,19 +2728,19 @@
         <v>2.36</v>
       </c>
       <c r="S8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="U8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="V8">
         <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X8">
         <v>60</v>
@@ -2758,16 +2758,16 @@
         <v>32</v>
       </c>
       <c r="AC8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE8">
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>14</v>
@@ -2776,10 +2776,10 @@
         <v>13</v>
       </c>
       <c r="AI8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK8">
         <v>21</v>
@@ -2791,10 +2791,10 @@
         <v>30</v>
       </c>
       <c r="AN8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP8">
         <v>48</v>
@@ -2833,82 +2833,82 @@
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BF8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG8">
         <v>8.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BI8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BJ8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK8">
         <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BN8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ8">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BR8">
+        <v>18</v>
+      </c>
+      <c r="BS8">
+        <v>6.4</v>
+      </c>
+      <c r="BT8">
+        <v>7.8</v>
+      </c>
+      <c r="BU8">
+        <v>6.6</v>
+      </c>
+      <c r="BV8">
         <v>17</v>
-      </c>
-      <c r="BS8">
-        <v>8</v>
-      </c>
-      <c r="BT8">
-        <v>7.4</v>
-      </c>
-      <c r="BU8">
-        <v>6.8</v>
-      </c>
-      <c r="BV8">
-        <v>17.5</v>
       </c>
       <c r="BW8">
         <v>12.5</v>
       </c>
       <c r="BX8">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BY8">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8">
         <v>8.6</v>
       </c>
       <c r="CA8">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB8" t="s">
         <v>209</v>
@@ -2931,19 +2931,19 @@
         <v>172</v>
       </c>
       <c r="F9">
+        <v>1.81</v>
+      </c>
+      <c r="G9">
         <v>1.82</v>
       </c>
-      <c r="G9">
-        <v>1.84</v>
-      </c>
       <c r="H9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I9">
         <v>4.4</v>
       </c>
       <c r="J9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
         <v>4.7</v>
@@ -2958,58 +2958,58 @@
         <v>7.6</v>
       </c>
       <c r="O9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
         <v>1.43</v>
       </c>
       <c r="R9">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U9">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
+        <v>34</v>
+      </c>
+      <c r="Y9">
+        <v>30</v>
+      </c>
+      <c r="Z9">
         <v>42</v>
       </c>
-      <c r="Y9">
-        <v>29</v>
-      </c>
-      <c r="Z9">
-        <v>46</v>
-      </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB9">
         <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG9">
         <v>11</v>
@@ -3024,13 +3024,13 @@
         <v>23</v>
       </c>
       <c r="AK9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN9">
         <v>6.4</v>
@@ -3039,25 +3039,25 @@
         <v>24</v>
       </c>
       <c r="AP9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
         <v>34</v>
@@ -3072,19 +3072,19 @@
         <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF9">
         <v>5.9</v>
@@ -3108,19 +3108,19 @@
         <v>65</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
       </c>
       <c r="BO9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP9">
         <v>11</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BR9">
         <v>18</v>
@@ -3132,25 +3132,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV9">
         <v>27</v>
       </c>
       <c r="BW9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY9">
         <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="s">
         <v>209</v>
@@ -3203,25 +3203,25 @@
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S10">
         <v>2.2</v>
       </c>
       <c r="T10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
         <v>1.64</v>
@@ -3239,7 +3239,7 @@
         <v>40</v>
       </c>
       <c r="AB10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC10">
         <v>10.5</v>
@@ -3332,7 +3332,7 @@
         <v>10</v>
       </c>
       <c r="BG10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH10">
         <v>4.9</v>
@@ -3350,7 +3350,7 @@
         <v>60</v>
       </c>
       <c r="BM10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BN10">
         <v>6.2</v>
@@ -3427,7 +3427,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K11">
         <v>5.9</v>
@@ -3454,13 +3454,13 @@
         <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V11">
         <v>1.14</v>
@@ -3478,7 +3478,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
         <v>15.5</v>
@@ -3493,7 +3493,7 @@
         <v>80</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
         <v>11</v>
@@ -3517,13 +3517,13 @@
         <v>65</v>
       </c>
       <c r="AN11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
         <v>60</v>
       </c>
       <c r="AP11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ11">
         <v>38</v>
@@ -3541,13 +3541,13 @@
         <v>13</v>
       </c>
       <c r="AV11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY11">
         <v>10</v>
@@ -3559,7 +3559,7 @@
         <v>55</v>
       </c>
       <c r="BB11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC11">
         <v>12.5</v>
@@ -3574,34 +3574,34 @@
         <v>3.95</v>
       </c>
       <c r="BG11">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BH11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI11">
         <v>5</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK11">
         <v>8.4</v>
       </c>
       <c r="BL11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM11">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="BN11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO11">
         <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ11">
         <v>7.2</v>
@@ -3610,31 +3610,31 @@
         <v>17</v>
       </c>
       <c r="BS11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT11">
         <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BV11">
         <v>46</v>
       </c>
       <c r="BW11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BX11">
         <v>40</v>
       </c>
       <c r="BY11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BZ11">
         <v>8.6</v>
       </c>
       <c r="CA11">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="s">
         <v>209</v>
@@ -3663,7 +3663,7 @@
         <v>1.38</v>
       </c>
       <c r="H12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>9.6</v>
@@ -3678,10 +3678,10 @@
         <v>1.21</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>1.11</v>
@@ -3738,7 +3738,7 @@
         <v>12.5</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
         <v>21</v>
@@ -3759,16 +3759,16 @@
         <v>70</v>
       </c>
       <c r="AN12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP12">
         <v>38</v>
       </c>
       <c r="AQ12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR12">
         <v>80</v>
@@ -3786,7 +3786,7 @@
         <v>30</v>
       </c>
       <c r="AW12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -3798,7 +3798,7 @@
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB12">
         <v>12</v>
@@ -3813,10 +3813,10 @@
         <v>55</v>
       </c>
       <c r="BF12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH12">
         <v>5.7</v>
@@ -3840,7 +3840,7 @@
         <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP12">
         <v>7.6</v>
@@ -3858,7 +3858,7 @@
         <v>13</v>
       </c>
       <c r="BU12">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BV12">
         <v>55</v>
@@ -3923,7 +3923,7 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O13">
         <v>1.31</v>
@@ -3947,7 +3947,7 @@
         <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
         <v>1.38</v>
@@ -4150,7 +4150,7 @@
         <v>1.24</v>
       </c>
       <c r="I14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J14">
         <v>4.6</v>
@@ -4159,34 +4159,34 @@
         <v>13</v>
       </c>
       <c r="L14">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>8.4</v>
       </c>
       <c r="O14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P14">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q14">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="R14">
         <v>1.69</v>
       </c>
       <c r="S14">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="T14">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="U14">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V14">
         <v>3</v>
@@ -4195,40 +4195,40 @@
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB14">
         <v>1000</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF14">
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
         <v>1000</v>
@@ -4246,61 +4246,61 @@
         <v>1000</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AZ14">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4386,7 +4386,7 @@
         <v>1.53</v>
       </c>
       <c r="G15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H15">
         <v>5.4</v>
@@ -4398,7 +4398,7 @@
         <v>4.7</v>
       </c>
       <c r="K15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15">
         <v>1.22</v>
@@ -4413,10 +4413,10 @@
         <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q15">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R15">
         <v>1.66</v>
@@ -4494,10 +4494,10 @@
         <v>21</v>
       </c>
       <c r="AQ15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS15">
         <v>7</v>
@@ -4524,7 +4524,7 @@
         <v>16</v>
       </c>
       <c r="BA15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB15">
         <v>13</v>
@@ -4542,7 +4542,7 @@
         <v>5.1</v>
       </c>
       <c r="BG15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH15">
         <v>4.9</v>
@@ -4554,13 +4554,13 @@
         <v>10</v>
       </c>
       <c r="BK15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN15">
         <v>4.7</v>
@@ -4572,34 +4572,34 @@
         <v>9.6</v>
       </c>
       <c r="BQ15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR15">
         <v>20</v>
       </c>
       <c r="BS15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT15">
         <v>10.5</v>
       </c>
       <c r="BU15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV15">
         <v>46</v>
       </c>
       <c r="BW15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15">
         <v>44</v>
       </c>
       <c r="BY15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA15">
         <v>5.6</v>
@@ -4631,16 +4631,16 @@
         <v>2.42</v>
       </c>
       <c r="H16">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I16">
         <v>3.15</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4649,28 +4649,28 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R16">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="S16">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V16">
         <v>1.46</v>
@@ -4718,7 +4718,7 @@
         <v>34</v>
       </c>
       <c r="AK16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL16">
         <v>34</v>
@@ -4736,10 +4736,10 @@
         <v>18</v>
       </c>
       <c r="AQ16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS16">
         <v>6.2</v>
@@ -4766,7 +4766,7 @@
         <v>13</v>
       </c>
       <c r="BA16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB16">
         <v>5.7</v>
@@ -4775,10 +4775,10 @@
         <v>5.3</v>
       </c>
       <c r="BD16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF16">
         <v>10.5</v>
@@ -4867,166 +4867,166 @@
         <v>180</v>
       </c>
       <c r="F17">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="G17">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="H17">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="I17">
-        <v>130</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17">
+        <v>4.1</v>
+      </c>
+      <c r="K17">
+        <v>6.4</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>3.85</v>
+      </c>
+      <c r="O17">
+        <v>1.19</v>
+      </c>
+      <c r="P17">
+        <v>2.56</v>
+      </c>
+      <c r="Q17">
+        <v>1.49</v>
+      </c>
+      <c r="R17">
+        <v>1.51</v>
+      </c>
+      <c r="S17">
+        <v>2.36</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.12</v>
+      </c>
+      <c r="W17">
+        <v>2.86</v>
+      </c>
+      <c r="X17">
+        <v>30</v>
+      </c>
+      <c r="Y17">
+        <v>36</v>
+      </c>
+      <c r="Z17">
+        <v>80</v>
+      </c>
+      <c r="AA17">
+        <v>290</v>
+      </c>
+      <c r="AB17">
+        <v>13</v>
+      </c>
+      <c r="AC17">
+        <v>14</v>
+      </c>
+      <c r="AD17">
+        <v>34</v>
+      </c>
+      <c r="AE17">
+        <v>110</v>
+      </c>
+      <c r="AF17">
+        <v>11.5</v>
+      </c>
+      <c r="AG17">
+        <v>12.5</v>
+      </c>
+      <c r="AH17">
+        <v>26</v>
+      </c>
+      <c r="AI17">
+        <v>95</v>
+      </c>
+      <c r="AJ17">
+        <v>15.5</v>
+      </c>
+      <c r="AK17">
+        <v>17</v>
+      </c>
+      <c r="AL17">
+        <v>36</v>
+      </c>
+      <c r="AM17">
+        <v>120</v>
+      </c>
+      <c r="AN17">
+        <v>6.2</v>
+      </c>
+      <c r="AO17">
+        <v>140</v>
+      </c>
+      <c r="AP17">
+        <v>4.4</v>
+      </c>
+      <c r="AQ17">
+        <v>4.5</v>
+      </c>
+      <c r="AR17">
+        <v>4.8</v>
+      </c>
+      <c r="AS17">
+        <v>5.1</v>
+      </c>
+      <c r="AT17">
+        <v>3.7</v>
+      </c>
+      <c r="AU17">
+        <v>3.75</v>
+      </c>
+      <c r="AV17">
+        <v>4.5</v>
+      </c>
+      <c r="AW17">
         <v>4.9</v>
       </c>
-      <c r="K17">
-        <v>950</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>1.02</v>
-      </c>
-      <c r="O17">
-        <v>1.13</v>
-      </c>
-      <c r="P17">
-        <v>2.52</v>
-      </c>
-      <c r="Q17">
-        <v>1.5</v>
-      </c>
-      <c r="R17">
-        <v>1.63</v>
-      </c>
-      <c r="S17">
-        <v>2.16</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
-      <c r="V17">
-        <v>1.01</v>
-      </c>
-      <c r="W17">
-        <v>3.35</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17">
-        <v>1.03</v>
-      </c>
-      <c r="AR17">
-        <v>1.03</v>
-      </c>
-      <c r="AS17">
-        <v>1.03</v>
-      </c>
-      <c r="AT17">
-        <v>1.03</v>
-      </c>
-      <c r="AU17">
-        <v>1.03</v>
-      </c>
-      <c r="AV17">
-        <v>1.03</v>
-      </c>
-      <c r="AW17">
-        <v>1.03</v>
-      </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5109,19 +5109,19 @@
         <v>181</v>
       </c>
       <c r="F18">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H18">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="I18">
         <v>1000</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5133,34 +5133,34 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O18">
         <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Q18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R18">
         <v>1.06</v>
       </c>
       <c r="S18">
+        <v>1.26</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
         <v>1.02</v>
       </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.01</v>
-      </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5366,19 +5366,19 @@
         <v>2.68</v>
       </c>
       <c r="K19">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
         <v>2.48</v>
       </c>
       <c r="O19">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="P19">
         <v>1.56</v>
@@ -5387,10 +5387,10 @@
         <v>1.97</v>
       </c>
       <c r="R19">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5593,16 +5593,16 @@
         <v>183</v>
       </c>
       <c r="F20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H20">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J20">
         <v>3.6</v>
@@ -5617,7 +5617,7 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
         <v>1.28</v>
@@ -5626,25 +5626,25 @@
         <v>2.08</v>
       </c>
       <c r="Q20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S20">
         <v>3</v>
       </c>
       <c r="T20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U20">
         <v>2.24</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X20">
         <v>21</v>
@@ -5674,13 +5674,13 @@
         <v>17.5</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH20">
         <v>21</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
         <v>34</v>
@@ -5692,67 +5692,67 @@
         <v>40</v>
       </c>
       <c r="AM20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN20">
         <v>17.5</v>
       </c>
       <c r="AO20">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP20">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ20">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR20">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS20">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT20">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="AU20">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV20">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AW20">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX20">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
         <v>12</v>
       </c>
       <c r="BA20">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB20">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC20">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="BD20">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE20">
+        <v>5.3</v>
+      </c>
+      <c r="BF20">
+        <v>12.5</v>
+      </c>
+      <c r="BG20">
         <v>4.8</v>
-      </c>
-      <c r="BF20">
-        <v>3.95</v>
-      </c>
-      <c r="BG20">
-        <v>4.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5835,16 +5835,16 @@
         <v>184</v>
       </c>
       <c r="F21">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G21">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H21">
         <v>4.4</v>
       </c>
       <c r="I21">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>4.3</v>
@@ -5859,28 +5859,28 @@
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P21">
+        <v>2.52</v>
+      </c>
+      <c r="Q21">
+        <v>1.53</v>
+      </c>
+      <c r="R21">
+        <v>1.61</v>
+      </c>
+      <c r="S21">
         <v>2.32</v>
       </c>
-      <c r="Q21">
-        <v>1.17</v>
-      </c>
-      <c r="R21">
-        <v>1.2</v>
-      </c>
-      <c r="S21">
-        <v>1.01</v>
-      </c>
       <c r="T21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V21">
         <v>1.01</v>
@@ -5904,43 +5904,43 @@
         <v>13.5</v>
       </c>
       <c r="AC21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD21">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF21">
         <v>14</v>
       </c>
       <c r="AG21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI21">
         <v>55</v>
       </c>
       <c r="AJ21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN21">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AO21">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP21">
         <v>20</v>
@@ -5949,34 +5949,34 @@
         <v>20</v>
       </c>
       <c r="AR21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT21">
         <v>11</v>
       </c>
       <c r="AU21">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV21">
         <v>16.5</v>
       </c>
       <c r="AW21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB21">
         <v>16</v>
@@ -5985,16 +5985,16 @@
         <v>14</v>
       </c>
       <c r="BD21">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="BE21">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF21">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6077,43 +6077,43 @@
         <v>185</v>
       </c>
       <c r="F22">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="G22">
         <v>17</v>
       </c>
       <c r="H22">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J22">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L22">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M22">
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>3.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O22">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P22">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R22">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="S22">
         <v>1.78</v>
@@ -6125,7 +6125,7 @@
         <v>2.04</v>
       </c>
       <c r="V22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="W22">
         <v>1.07</v>
@@ -6137,7 +6137,7 @@
         <v>16.5</v>
       </c>
       <c r="Z22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA22">
         <v>13.5</v>
@@ -6185,19 +6185,19 @@
         <v>3.1</v>
       </c>
       <c r="AP22">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR22">
         <v>9.800000000000001</v>
       </c>
       <c r="AS22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT22">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="AU22">
         <v>16</v>
@@ -6209,22 +6209,22 @@
         <v>11.5</v>
       </c>
       <c r="AX22">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY22">
         <v>24</v>
       </c>
       <c r="AZ22">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BA22">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB22">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC22">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD22">
         <v>7.4</v>
@@ -6233,7 +6233,7 @@
         <v>7.4</v>
       </c>
       <c r="BF22">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG22">
         <v>2.74</v>
@@ -6322,13 +6322,13 @@
         <v>3.55</v>
       </c>
       <c r="G23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H23">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I23">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J23">
         <v>3.65</v>
@@ -6364,16 +6364,16 @@
         <v>1.65</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y23">
         <v>12.5</v>
@@ -6412,7 +6412,7 @@
         <v>65</v>
       </c>
       <c r="AK23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL23">
         <v>42</v>
@@ -6424,7 +6424,7 @@
         <v>30</v>
       </c>
       <c r="AO23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP23">
         <v>16.5</v>
@@ -6436,7 +6436,7 @@
         <v>14</v>
       </c>
       <c r="AS23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT23">
         <v>15.5</v>
@@ -6457,7 +6457,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA23">
         <v>28</v>
@@ -6481,7 +6481,7 @@
         <v>12</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI23">
         <v>3.1</v>
@@ -6496,13 +6496,13 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BN23">
         <v>8</v>
       </c>
       <c r="BO23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP23">
         <v>38</v>
@@ -6517,10 +6517,10 @@
         <v>24</v>
       </c>
       <c r="BT23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV23">
         <v>22</v>
@@ -6538,7 +6538,7 @@
         <v>30</v>
       </c>
       <c r="CA23">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="CB23" t="s">
         <v>209</v>
@@ -6564,19 +6564,19 @@
         <v>1.46</v>
       </c>
       <c r="G24">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J24">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L24">
         <v>1.25</v>
@@ -6597,7 +6597,7 @@
         <v>1.46</v>
       </c>
       <c r="R24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S24">
         <v>2.16</v>
@@ -6612,7 +6612,7 @@
         <v>1.15</v>
       </c>
       <c r="W24">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X24">
         <v>34</v>
@@ -6630,7 +6630,7 @@
         <v>13.5</v>
       </c>
       <c r="AC24">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD24">
         <v>27</v>
@@ -6645,7 +6645,7 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI24">
         <v>70</v>
@@ -6669,25 +6669,25 @@
         <v>65</v>
       </c>
       <c r="AP24">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AQ24">
+        <v>30</v>
+      </c>
+      <c r="AR24">
         <v>32</v>
-      </c>
-      <c r="AR24">
-        <v>60</v>
       </c>
       <c r="AS24">
         <v>46</v>
       </c>
       <c r="AT24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU24">
         <v>12</v>
       </c>
       <c r="AV24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW24">
         <v>34</v>
@@ -6702,7 +6702,7 @@
         <v>18</v>
       </c>
       <c r="BA24">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB24">
         <v>13</v>
@@ -6720,7 +6720,7 @@
         <v>4.4</v>
       </c>
       <c r="BG24">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BH24">
         <v>5.9</v>
@@ -6741,7 +6741,7 @@
         <v>21</v>
       </c>
       <c r="BN24">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO24">
         <v>4</v>
@@ -6753,31 +6753,31 @@
         <v>7.6</v>
       </c>
       <c r="BR24">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BS24">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BT24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU24">
         <v>9.6</v>
       </c>
       <c r="BV24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BW24">
         <v>34</v>
       </c>
       <c r="BX24">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY24">
         <v>32</v>
       </c>
       <c r="BZ24">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CA24">
         <v>8.6</v>
@@ -6803,70 +6803,70 @@
         <v>188</v>
       </c>
       <c r="F25">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G25">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="H25">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="J25">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N25">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O25">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P25">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="Q25">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R25">
+        <v>1.3</v>
+      </c>
+      <c r="S25">
+        <v>2.34</v>
+      </c>
+      <c r="T25">
+        <v>1.6</v>
+      </c>
+      <c r="U25">
+        <v>2.22</v>
+      </c>
+      <c r="V25">
+        <v>1.83</v>
+      </c>
+      <c r="W25">
         <v>1.32</v>
-      </c>
-      <c r="S25">
-        <v>1.01</v>
-      </c>
-      <c r="T25">
-        <v>1.01</v>
-      </c>
-      <c r="U25">
-        <v>1.01</v>
-      </c>
-      <c r="V25">
-        <v>1.64</v>
-      </c>
-      <c r="W25">
-        <v>1.35</v>
       </c>
       <c r="X25">
         <v>20</v>
       </c>
       <c r="Y25">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA25">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AB25">
         <v>17</v>
@@ -6875,13 +6875,13 @@
         <v>10</v>
       </c>
       <c r="AD25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF25">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AG25">
         <v>16.5</v>
@@ -6890,13 +6890,13 @@
         <v>19</v>
       </c>
       <c r="AI25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ25">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AK25">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL25">
         <v>50</v>
@@ -6905,64 +6905,64 @@
         <v>90</v>
       </c>
       <c r="AN25">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AO25">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP25">
+        <v>4.3</v>
+      </c>
+      <c r="AQ25">
+        <v>3.85</v>
+      </c>
+      <c r="AR25">
         <v>4.1</v>
       </c>
-      <c r="AQ25">
-        <v>3.7</v>
-      </c>
-      <c r="AR25">
-        <v>4</v>
-      </c>
       <c r="AS25">
+        <v>4.7</v>
+      </c>
+      <c r="AT25">
+        <v>4.2</v>
+      </c>
+      <c r="AU25">
+        <v>3.55</v>
+      </c>
+      <c r="AV25">
+        <v>3.85</v>
+      </c>
+      <c r="AW25">
         <v>4.5</v>
       </c>
-      <c r="AT25">
-        <v>3.95</v>
-      </c>
-      <c r="AU25">
-        <v>3.4</v>
-      </c>
-      <c r="AV25">
-        <v>3.65</v>
-      </c>
-      <c r="AW25">
+      <c r="AX25">
+        <v>4.8</v>
+      </c>
+      <c r="AY25">
+        <v>4.1</v>
+      </c>
+      <c r="AZ25">
         <v>4.3</v>
       </c>
-      <c r="AX25">
-        <v>4.3</v>
-      </c>
-      <c r="AY25">
-        <v>3.9</v>
-      </c>
-      <c r="AZ25">
-        <v>4</v>
-      </c>
       <c r="BA25">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB25">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC25">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD25">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE25">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF25">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7045,178 +7045,178 @@
         <v>189</v>
       </c>
       <c r="F26">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H26">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="I26">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="K26">
+        <v>7.8</v>
+      </c>
+      <c r="L26">
+        <v>1.22</v>
+      </c>
+      <c r="M26">
+        <v>1.03</v>
+      </c>
+      <c r="N26">
         <v>5.9</v>
       </c>
-      <c r="K26">
-        <v>9</v>
-      </c>
-      <c r="L26">
-        <v>1.2</v>
-      </c>
-      <c r="M26">
-        <v>1.02</v>
-      </c>
-      <c r="N26">
-        <v>3.45</v>
-      </c>
       <c r="O26">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P26">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q26">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="R26">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S26">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="T26">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z26">
         <v>9.199999999999999</v>
       </c>
       <c r="AA26">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AB26">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AC26">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AD26">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE26">
         <v>14.5</v>
       </c>
       <c r="AF26">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AG26">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AH26">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AI26">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AK26">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="AL26">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AM26">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AN26">
-        <v>400</v>
+        <v>260</v>
       </c>
       <c r="AO26">
+        <v>4.3</v>
+      </c>
+      <c r="AP26">
+        <v>21</v>
+      </c>
+      <c r="AQ26">
+        <v>5</v>
+      </c>
+      <c r="AR26">
+        <v>7.2</v>
+      </c>
+      <c r="AS26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT26">
+        <v>25</v>
+      </c>
+      <c r="AU26">
+        <v>5.7</v>
+      </c>
+      <c r="AV26">
+        <v>5.1</v>
+      </c>
+      <c r="AW26">
+        <v>5.4</v>
+      </c>
+      <c r="AX26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY26">
+        <v>24</v>
+      </c>
+      <c r="AZ26">
+        <v>23</v>
+      </c>
+      <c r="BA26">
+        <v>7.2</v>
+      </c>
+      <c r="BB26">
+        <v>21</v>
+      </c>
+      <c r="BC26">
+        <v>19.5</v>
+      </c>
+      <c r="BD26">
+        <v>27</v>
+      </c>
+      <c r="BE26">
+        <v>30</v>
+      </c>
+      <c r="BF26">
+        <v>8.4</v>
+      </c>
+      <c r="BG26">
         <v>3.6</v>
       </c>
-      <c r="AP26">
-        <v>6.4</v>
-      </c>
-      <c r="AQ26">
-        <v>4.8</v>
-      </c>
-      <c r="AR26">
-        <v>4.2</v>
-      </c>
-      <c r="AS26">
-        <v>7.6</v>
-      </c>
-      <c r="AT26">
-        <v>15</v>
-      </c>
-      <c r="AU26">
-        <v>6.2</v>
-      </c>
-      <c r="AV26">
-        <v>4.9</v>
-      </c>
-      <c r="AW26">
-        <v>5.5</v>
-      </c>
-      <c r="AX26">
-        <v>34</v>
-      </c>
-      <c r="AY26">
-        <v>15</v>
-      </c>
-      <c r="AZ26">
-        <v>11</v>
-      </c>
-      <c r="BA26">
-        <v>11.5</v>
-      </c>
-      <c r="BB26">
-        <v>7.8</v>
-      </c>
-      <c r="BC26">
-        <v>7.6</v>
-      </c>
-      <c r="BD26">
-        <v>38</v>
-      </c>
-      <c r="BE26">
-        <v>38</v>
-      </c>
-      <c r="BF26">
-        <v>7.4</v>
-      </c>
-      <c r="BG26">
-        <v>2.92</v>
-      </c>
       <c r="BH26">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BI26">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK26">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
@@ -7225,46 +7225,46 @@
         <v>4.7</v>
       </c>
       <c r="BN26">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BO26">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ26">
         <v>4.6</v>
       </c>
       <c r="BR26">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="BS26">
         <v>4.6</v>
       </c>
       <c r="BT26">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU26">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="BV26">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BW26">
-        <v>2.98</v>
+        <v>5.3</v>
       </c>
       <c r="BX26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY26">
         <v>4</v>
       </c>
       <c r="BZ26">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="CA26">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="CB26" t="s">
         <v>209</v>
@@ -7287,16 +7287,16 @@
         <v>190</v>
       </c>
       <c r="F27">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H27">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I27">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J27">
         <v>4</v>
@@ -7311,7 +7311,7 @@
         <v>1.04</v>
       </c>
       <c r="N27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O27">
         <v>1.2</v>
@@ -7320,25 +7320,25 @@
         <v>2.52</v>
       </c>
       <c r="Q27">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R27">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S27">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T27">
         <v>1.59</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X27">
         <v>24</v>
@@ -7347,7 +7347,7 @@
         <v>20</v>
       </c>
       <c r="Z27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA27">
         <v>70</v>
@@ -7356,7 +7356,7 @@
         <v>13.5</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27">
         <v>16</v>
@@ -7365,13 +7365,13 @@
         <v>38</v>
       </c>
       <c r="AF27">
+        <v>15.5</v>
+      </c>
+      <c r="AG27">
+        <v>11</v>
+      </c>
+      <c r="AH27">
         <v>16</v>
-      </c>
-      <c r="AG27">
-        <v>11.5</v>
-      </c>
-      <c r="AH27">
-        <v>16.5</v>
       </c>
       <c r="AI27">
         <v>40</v>
@@ -7386,25 +7386,25 @@
         <v>28</v>
       </c>
       <c r="AM27">
-        <v>75</v>
+        <v>720</v>
       </c>
       <c r="AN27">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP27">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ27">
         <v>17</v>
       </c>
       <c r="AR27">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS27">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AT27">
         <v>12</v>
@@ -7416,73 +7416,73 @@
         <v>13.5</v>
       </c>
       <c r="AW27">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AX27">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27">
         <v>14</v>
       </c>
       <c r="BA27">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BB27">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC27">
         <v>16</v>
       </c>
       <c r="BD27">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BE27">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BF27">
         <v>8.800000000000001</v>
       </c>
       <c r="BG27">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH27">
         <v>4.3</v>
       </c>
       <c r="BI27">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ27">
         <v>9</v>
       </c>
       <c r="BK27">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN27">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP27">
         <v>14</v>
       </c>
       <c r="BQ27">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR27">
         <v>23</v>
       </c>
       <c r="BS27">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT27">
         <v>7.6</v>
@@ -7491,22 +7491,22 @@
         <v>5.7</v>
       </c>
       <c r="BV27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW27">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BX27">
         <v>32</v>
       </c>
       <c r="BY27">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ27">
         <v>16.5</v>
       </c>
       <c r="CA27">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB27" t="s">
         <v>209</v>
@@ -7553,7 +7553,7 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O28">
         <v>1.24</v>
@@ -7565,22 +7565,22 @@
         <v>1.71</v>
       </c>
       <c r="R28">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S28">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W28">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X28">
         <v>24</v>
@@ -7595,7 +7595,7 @@
         <v>34</v>
       </c>
       <c r="AB28">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AC28">
         <v>9.199999999999999</v>
@@ -7631,10 +7631,10 @@
         <v>85</v>
       </c>
       <c r="AN28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO28">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP28">
         <v>17</v>
@@ -7679,7 +7679,7 @@
         <v>5.7</v>
       </c>
       <c r="BD28">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE28">
         <v>6</v>
@@ -7688,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="BG28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7700,7 +7700,7 @@
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7712,7 +7712,7 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="BP28">
         <v>1000</v>
@@ -7730,7 +7730,7 @@
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7783,7 +7783,7 @@
         <v>2.08</v>
       </c>
       <c r="J29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K29">
         <v>4</v>
@@ -7798,34 +7798,34 @@
         <v>4</v>
       </c>
       <c r="O29">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P29">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S29">
         <v>3.05</v>
       </c>
       <c r="T29">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U29">
         <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X29">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y29">
         <v>10.5</v>
@@ -7846,7 +7846,7 @@
         <v>11</v>
       </c>
       <c r="AE29">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF29">
         <v>38</v>
@@ -7855,25 +7855,25 @@
         <v>970</v>
       </c>
       <c r="AH29">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI29">
         <v>42</v>
       </c>
       <c r="AJ29">
+        <v>95</v>
+      </c>
+      <c r="AK29">
+        <v>55</v>
+      </c>
+      <c r="AL29">
+        <v>55</v>
+      </c>
+      <c r="AM29">
         <v>100</v>
       </c>
-      <c r="AK29">
-        <v>60</v>
-      </c>
-      <c r="AL29">
-        <v>65</v>
-      </c>
-      <c r="AM29">
-        <v>110</v>
-      </c>
       <c r="AN29">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO29">
         <v>13</v>
@@ -7888,7 +7888,7 @@
         <v>11.5</v>
       </c>
       <c r="AS29">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AT29">
         <v>14</v>
@@ -7903,7 +7903,7 @@
         <v>17.5</v>
       </c>
       <c r="AX29">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY29">
         <v>14</v>
@@ -7912,22 +7912,22 @@
         <v>15.5</v>
       </c>
       <c r="BA29">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB29">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC29">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD29">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE29">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF29">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG29">
         <v>11</v>
@@ -8019,10 +8019,10 @@
         <v>1.83</v>
       </c>
       <c r="H30">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I30">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J30">
         <v>3.7</v>
@@ -8055,13 +8055,13 @@
         <v>3</v>
       </c>
       <c r="T30">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W30">
         <v>2.2</v>
@@ -8070,31 +8070,31 @@
         <v>1000</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA30">
         <v>1000</v>
       </c>
       <c r="AB30">
+        <v>10.5</v>
+      </c>
+      <c r="AC30">
+        <v>13</v>
+      </c>
+      <c r="AD30">
+        <v>28</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
         <v>970</v>
       </c>
-      <c r="AC30">
-        <v>970</v>
-      </c>
-      <c r="AD30">
-        <v>1000</v>
-      </c>
-      <c r="AE30">
-        <v>1000</v>
-      </c>
-      <c r="AF30">
-        <v>20</v>
-      </c>
       <c r="AG30">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH30">
         <v>1000</v>
@@ -8121,58 +8121,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AQ30">
-        <v>1.43</v>
+        <v>13.5</v>
       </c>
       <c r="AR30">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AS30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AT30">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="AU30">
-        <v>1.31</v>
+        <v>7.2</v>
       </c>
       <c r="AV30">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="AW30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AX30">
-        <v>1.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AZ30">
-        <v>1.43</v>
+        <v>14</v>
       </c>
       <c r="BA30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="BB30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="BC30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="BD30">
-        <v>1.43</v>
+        <v>21</v>
       </c>
       <c r="BE30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="BF30">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="BG30">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8255,7 +8255,7 @@
         <v>194</v>
       </c>
       <c r="F31">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G31">
         <v>110</v>
@@ -8267,7 +8267,7 @@
         <v>110</v>
       </c>
       <c r="J31">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8303,10 +8303,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8497,19 +8497,19 @@
         <v>195</v>
       </c>
       <c r="F32">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H32">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I32">
         <v>110</v>
       </c>
       <c r="J32">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K32">
         <v>4</v>
@@ -8518,25 +8518,25 @@
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N32">
         <v>1.26</v>
       </c>
       <c r="O32">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="P32">
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R32">
         <v>1.12</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8548,7 +8548,7 @@
         <v>1.1</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8739,7 +8739,7 @@
         <v>196</v>
       </c>
       <c r="F33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G33">
         <v>1.31</v>
@@ -8748,13 +8748,13 @@
         <v>13.5</v>
       </c>
       <c r="I33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J33">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K33">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L33">
         <v>1.35</v>
@@ -8769,7 +8769,7 @@
         <v>1.27</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q33">
         <v>1.79</v>
@@ -8781,7 +8781,7 @@
         <v>3</v>
       </c>
       <c r="T33">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U33">
         <v>1.67</v>
@@ -8790,7 +8790,7 @@
         <v>1.07</v>
       </c>
       <c r="W33">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X33">
         <v>19</v>
@@ -8814,7 +8814,7 @@
         <v>50</v>
       </c>
       <c r="AE33">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AF33">
         <v>7.2</v>
@@ -8823,7 +8823,7 @@
         <v>11.5</v>
       </c>
       <c r="AH33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI33">
         <v>220</v>
@@ -8853,10 +8853,10 @@
         <v>29</v>
       </c>
       <c r="AR33">
+        <v>15</v>
+      </c>
+      <c r="AS33">
         <v>16.5</v>
-      </c>
-      <c r="AS33">
-        <v>17</v>
       </c>
       <c r="AT33">
         <v>7</v>
@@ -8868,10 +8868,10 @@
         <v>42</v>
       </c>
       <c r="AW33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX33">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY33">
         <v>10</v>
@@ -8880,7 +8880,7 @@
         <v>32</v>
       </c>
       <c r="BA33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB33">
         <v>8.6</v>
@@ -8904,7 +8904,7 @@
         <v>3.85</v>
       </c>
       <c r="BI33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ33">
         <v>14.5</v>
@@ -8934,7 +8934,7 @@
         <v>28</v>
       </c>
       <c r="BS33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT33">
         <v>16.5</v>
@@ -8958,7 +8958,7 @@
         <v>13.5</v>
       </c>
       <c r="CA33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB33" t="s">
         <v>209</v>
@@ -8981,226 +8981,226 @@
         <v>197</v>
       </c>
       <c r="F34">
-        <v>1.9</v>
+        <v>1.13</v>
       </c>
       <c r="G34">
-        <v>1.91</v>
+        <v>1.14</v>
       </c>
       <c r="H34">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="I34">
-        <v>4.3</v>
+        <v>29</v>
       </c>
       <c r="J34">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="K34">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="L34">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="M34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N34">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="O34">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="P34">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q34">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="R34">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="T34">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="W34">
-        <v>2.08</v>
+        <v>8</v>
       </c>
       <c r="X34">
+        <v>60</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>340</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>18</v>
+      </c>
+      <c r="AC34">
+        <v>30</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>410</v>
+      </c>
+      <c r="AF34">
+        <v>11</v>
+      </c>
+      <c r="AG34">
+        <v>16</v>
+      </c>
+      <c r="AH34">
+        <v>50</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>9.4</v>
+      </c>
+      <c r="AK34">
+        <v>14</v>
+      </c>
+      <c r="AL34">
+        <v>38</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>2.26</v>
+      </c>
+      <c r="AO34">
+        <v>490</v>
+      </c>
+      <c r="AP34">
+        <v>42</v>
+      </c>
+      <c r="AQ34">
+        <v>38</v>
+      </c>
+      <c r="AR34">
+        <v>55</v>
+      </c>
+      <c r="AS34">
+        <v>21</v>
+      </c>
+      <c r="AT34">
+        <v>16</v>
+      </c>
+      <c r="AU34">
+        <v>25</v>
+      </c>
+      <c r="AV34">
+        <v>55</v>
+      </c>
+      <c r="AW34">
+        <v>55</v>
+      </c>
+      <c r="AX34">
+        <v>10</v>
+      </c>
+      <c r="AY34">
+        <v>14</v>
+      </c>
+      <c r="AZ34">
+        <v>42</v>
+      </c>
+      <c r="BA34">
+        <v>50</v>
+      </c>
+      <c r="BB34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC34">
+        <v>13</v>
+      </c>
+      <c r="BD34">
+        <v>32</v>
+      </c>
+      <c r="BE34">
+        <v>46</v>
+      </c>
+      <c r="BF34">
+        <v>2.2</v>
+      </c>
+      <c r="BG34">
+        <v>65</v>
+      </c>
+      <c r="BH34">
+        <v>7.6</v>
+      </c>
+      <c r="BI34">
+        <v>6</v>
+      </c>
+      <c r="BJ34">
+        <v>16.5</v>
+      </c>
+      <c r="BK34">
+        <v>12.5</v>
+      </c>
+      <c r="BL34">
+        <v>150</v>
+      </c>
+      <c r="BM34">
+        <v>29</v>
+      </c>
+      <c r="BN34">
+        <v>4.7</v>
+      </c>
+      <c r="BO34">
+        <v>3.8</v>
+      </c>
+      <c r="BP34">
+        <v>6.4</v>
+      </c>
+      <c r="BQ34">
+        <v>5</v>
+      </c>
+      <c r="BR34">
+        <v>22</v>
+      </c>
+      <c r="BS34">
+        <v>16.5</v>
+      </c>
+      <c r="BT34">
+        <v>26</v>
+      </c>
+      <c r="BU34">
+        <v>19</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>32</v>
+      </c>
+      <c r="BX34">
+        <v>110</v>
+      </c>
+      <c r="BY34">
         <v>24</v>
       </c>
-      <c r="Y34">
-        <v>22</v>
-      </c>
-      <c r="Z34">
-        <v>36</v>
-      </c>
-      <c r="AA34">
-        <v>100</v>
-      </c>
-      <c r="AB34">
-        <v>13.5</v>
-      </c>
-      <c r="AC34">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD34">
-        <v>17</v>
-      </c>
-      <c r="AE34">
-        <v>42</v>
-      </c>
-      <c r="AF34">
-        <v>14.5</v>
-      </c>
-      <c r="AG34">
-        <v>10.5</v>
-      </c>
-      <c r="AH34">
-        <v>16</v>
-      </c>
-      <c r="AI34">
-        <v>42</v>
-      </c>
-      <c r="AJ34">
-        <v>22</v>
-      </c>
-      <c r="AK34">
-        <v>17.5</v>
-      </c>
-      <c r="AL34">
-        <v>27</v>
-      </c>
-      <c r="AM34">
-        <v>65</v>
-      </c>
-      <c r="AN34">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO34">
-        <v>32</v>
-      </c>
-      <c r="AP34">
-        <v>21</v>
-      </c>
-      <c r="AQ34">
-        <v>19.5</v>
-      </c>
-      <c r="AR34">
-        <v>30</v>
-      </c>
-      <c r="AS34">
-        <v>36</v>
-      </c>
-      <c r="AT34">
-        <v>12</v>
-      </c>
-      <c r="AU34">
-        <v>9</v>
-      </c>
-      <c r="AV34">
-        <v>15.5</v>
-      </c>
-      <c r="AW34">
-        <v>38</v>
-      </c>
-      <c r="AX34">
-        <v>13</v>
-      </c>
-      <c r="AY34">
-        <v>9.6</v>
-      </c>
-      <c r="AZ34">
-        <v>14</v>
-      </c>
-      <c r="BA34">
-        <v>36</v>
-      </c>
-      <c r="BB34">
-        <v>20</v>
-      </c>
-      <c r="BC34">
-        <v>15.5</v>
-      </c>
-      <c r="BD34">
-        <v>23</v>
-      </c>
-      <c r="BE34">
-        <v>50</v>
-      </c>
-      <c r="BF34">
-        <v>7.8</v>
-      </c>
-      <c r="BG34">
-        <v>27</v>
-      </c>
-      <c r="BH34">
-        <v>1000</v>
-      </c>
-      <c r="BI34">
-        <v>3.45</v>
-      </c>
-      <c r="BJ34">
-        <v>1000</v>
-      </c>
-      <c r="BK34">
-        <v>8</v>
-      </c>
-      <c r="BL34">
-        <v>1000</v>
-      </c>
-      <c r="BM34">
-        <v>2.18</v>
-      </c>
-      <c r="BN34">
-        <v>6.2</v>
-      </c>
-      <c r="BO34">
-        <v>4</v>
-      </c>
-      <c r="BP34">
-        <v>1000</v>
-      </c>
-      <c r="BQ34">
-        <v>2.18</v>
-      </c>
-      <c r="BR34">
-        <v>1000</v>
-      </c>
-      <c r="BS34">
-        <v>2.18</v>
-      </c>
-      <c r="BT34">
-        <v>1000</v>
-      </c>
-      <c r="BU34">
-        <v>1.82</v>
-      </c>
-      <c r="BV34">
-        <v>1000</v>
-      </c>
-      <c r="BW34">
-        <v>12.5</v>
-      </c>
-      <c r="BX34">
-        <v>1000</v>
-      </c>
-      <c r="BY34">
-        <v>2.18</v>
-      </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="CA34">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB34" t="s">
         <v>209</v>
@@ -9223,226 +9223,226 @@
         <v>198</v>
       </c>
       <c r="F35">
-        <v>1.13</v>
+        <v>2.7</v>
       </c>
       <c r="G35">
-        <v>1.14</v>
+        <v>2.72</v>
       </c>
       <c r="H35">
-        <v>28</v>
+        <v>2.82</v>
       </c>
       <c r="I35">
+        <v>2.84</v>
+      </c>
+      <c r="J35">
+        <v>3.6</v>
+      </c>
+      <c r="K35">
+        <v>3.65</v>
+      </c>
+      <c r="L35">
+        <v>1.38</v>
+      </c>
+      <c r="M35">
+        <v>1.06</v>
+      </c>
+      <c r="N35">
+        <v>4.4</v>
+      </c>
+      <c r="O35">
+        <v>1.28</v>
+      </c>
+      <c r="P35">
+        <v>2.14</v>
+      </c>
+      <c r="Q35">
+        <v>1.83</v>
+      </c>
+      <c r="R35">
+        <v>1.45</v>
+      </c>
+      <c r="S35">
+        <v>3.1</v>
+      </c>
+      <c r="T35">
+        <v>1.69</v>
+      </c>
+      <c r="U35">
+        <v>2.42</v>
+      </c>
+      <c r="V35">
+        <v>1.54</v>
+      </c>
+      <c r="W35">
+        <v>1.58</v>
+      </c>
+      <c r="X35">
+        <v>17</v>
+      </c>
+      <c r="Y35">
+        <v>13.5</v>
+      </c>
+      <c r="Z35">
+        <v>20</v>
+      </c>
+      <c r="AA35">
+        <v>42</v>
+      </c>
+      <c r="AB35">
+        <v>12.5</v>
+      </c>
+      <c r="AC35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD35">
+        <v>12.5</v>
+      </c>
+      <c r="AE35">
         <v>29</v>
       </c>
-      <c r="J35">
+      <c r="AF35">
+        <v>18.5</v>
+      </c>
+      <c r="AG35">
+        <v>12.5</v>
+      </c>
+      <c r="AH35">
+        <v>15.5</v>
+      </c>
+      <c r="AI35">
+        <v>38</v>
+      </c>
+      <c r="AJ35">
+        <v>38</v>
+      </c>
+      <c r="AK35">
+        <v>27</v>
+      </c>
+      <c r="AL35">
+        <v>36</v>
+      </c>
+      <c r="AM35">
+        <v>75</v>
+      </c>
+      <c r="AN35">
+        <v>20</v>
+      </c>
+      <c r="AO35">
+        <v>22</v>
+      </c>
+      <c r="AP35">
+        <v>15.5</v>
+      </c>
+      <c r="AQ35">
+        <v>12.5</v>
+      </c>
+      <c r="AR35">
+        <v>18</v>
+      </c>
+      <c r="AS35">
+        <v>36</v>
+      </c>
+      <c r="AT35">
+        <v>12</v>
+      </c>
+      <c r="AU35">
+        <v>7.8</v>
+      </c>
+      <c r="AV35">
         <v>11.5</v>
       </c>
-      <c r="K35">
-        <v>12</v>
-      </c>
-      <c r="L35">
-        <v>1.18</v>
-      </c>
-      <c r="M35">
-        <v>1.01</v>
-      </c>
-      <c r="N35">
-        <v>11.5</v>
-      </c>
-      <c r="O35">
-        <v>1.09</v>
-      </c>
-      <c r="P35">
-        <v>4.4</v>
-      </c>
-      <c r="Q35">
-        <v>1.28</v>
-      </c>
-      <c r="R35">
-        <v>2.38</v>
-      </c>
-      <c r="S35">
-        <v>1.69</v>
-      </c>
-      <c r="T35">
-        <v>2.1</v>
-      </c>
-      <c r="U35">
-        <v>1.86</v>
-      </c>
-      <c r="V35">
-        <v>1.03</v>
-      </c>
-      <c r="W35">
-        <v>8</v>
-      </c>
-      <c r="X35">
-        <v>60</v>
-      </c>
-      <c r="Y35">
-        <v>1000</v>
-      </c>
-      <c r="Z35">
-        <v>340</v>
-      </c>
-      <c r="AA35">
-        <v>1000</v>
-      </c>
-      <c r="AB35">
-        <v>18.5</v>
-      </c>
-      <c r="AC35">
-        <v>29</v>
-      </c>
-      <c r="AD35">
-        <v>1000</v>
-      </c>
-      <c r="AE35">
-        <v>420</v>
-      </c>
-      <c r="AF35">
+      <c r="AW35">
+        <v>26</v>
+      </c>
+      <c r="AX35">
+        <v>17</v>
+      </c>
+      <c r="AY35">
         <v>11</v>
       </c>
-      <c r="AG35">
-        <v>16</v>
-      </c>
-      <c r="AH35">
-        <v>48</v>
-      </c>
-      <c r="AI35">
-        <v>1000</v>
-      </c>
-      <c r="AJ35">
-        <v>9.4</v>
-      </c>
-      <c r="AK35">
-        <v>14</v>
-      </c>
-      <c r="AL35">
-        <v>38</v>
-      </c>
-      <c r="AM35">
-        <v>1000</v>
-      </c>
-      <c r="AN35">
-        <v>2.32</v>
-      </c>
-      <c r="AO35">
-        <v>440</v>
-      </c>
-      <c r="AP35">
-        <v>40</v>
-      </c>
-      <c r="AQ35">
-        <v>40</v>
-      </c>
-      <c r="AR35">
-        <v>55</v>
-      </c>
-      <c r="AS35">
-        <v>21</v>
-      </c>
-      <c r="AT35">
-        <v>17</v>
-      </c>
-      <c r="AU35">
-        <v>24</v>
-      </c>
-      <c r="AV35">
-        <v>38</v>
-      </c>
-      <c r="AW35">
-        <v>55</v>
-      </c>
-      <c r="AX35">
-        <v>10</v>
-      </c>
-      <c r="AY35">
-        <v>14</v>
-      </c>
       <c r="AZ35">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BB35">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BC35">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BD35">
         <v>32</v>
       </c>
       <c r="BE35">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF35">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="BG35">
+        <v>20</v>
+      </c>
+      <c r="BH35">
+        <v>3.7</v>
+      </c>
+      <c r="BI35">
+        <v>3.4</v>
+      </c>
+      <c r="BJ35">
+        <v>9</v>
+      </c>
+      <c r="BK35">
+        <v>8</v>
+      </c>
+      <c r="BL35">
+        <v>95</v>
+      </c>
+      <c r="BM35">
         <v>65</v>
       </c>
-      <c r="BH35">
-        <v>7.6</v>
-      </c>
-      <c r="BI35">
+      <c r="BN35">
+        <v>5.7</v>
+      </c>
+      <c r="BO35">
+        <v>5.3</v>
+      </c>
+      <c r="BP35">
+        <v>19.5</v>
+      </c>
+      <c r="BQ35">
+        <v>14</v>
+      </c>
+      <c r="BR35">
+        <v>29</v>
+      </c>
+      <c r="BS35">
+        <v>22</v>
+      </c>
+      <c r="BT35">
         <v>5.9</v>
       </c>
-      <c r="BJ35">
+      <c r="BU35">
+        <v>5.4</v>
+      </c>
+      <c r="BV35">
+        <v>20</v>
+      </c>
+      <c r="BW35">
+        <v>14.5</v>
+      </c>
+      <c r="BX35">
+        <v>30</v>
+      </c>
+      <c r="BY35">
+        <v>22</v>
+      </c>
+      <c r="BZ35">
+        <v>22</v>
+      </c>
+      <c r="CA35">
         <v>16.5</v>
-      </c>
-      <c r="BK35">
-        <v>12.5</v>
-      </c>
-      <c r="BL35">
-        <v>150</v>
-      </c>
-      <c r="BM35">
-        <v>29</v>
-      </c>
-      <c r="BN35">
-        <v>4.8</v>
-      </c>
-      <c r="BO35">
-        <v>3.8</v>
-      </c>
-      <c r="BP35">
-        <v>6.4</v>
-      </c>
-      <c r="BQ35">
-        <v>5</v>
-      </c>
-      <c r="BR35">
-        <v>22</v>
-      </c>
-      <c r="BS35">
-        <v>16.5</v>
-      </c>
-      <c r="BT35">
-        <v>26</v>
-      </c>
-      <c r="BU35">
-        <v>19</v>
-      </c>
-      <c r="BV35">
-        <v>1000</v>
-      </c>
-      <c r="BW35">
-        <v>34</v>
-      </c>
-      <c r="BX35">
-        <v>110</v>
-      </c>
-      <c r="BY35">
-        <v>24</v>
-      </c>
-      <c r="BZ35">
-        <v>5.9</v>
-      </c>
-      <c r="CA35">
-        <v>4.7</v>
       </c>
       <c r="CB35" t="s">
         <v>209</v>
@@ -9465,226 +9465,226 @@
         <v>199</v>
       </c>
       <c r="F36">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="G36">
-        <v>1.13</v>
+        <v>1.91</v>
       </c>
       <c r="H36">
+        <v>4.2</v>
+      </c>
+      <c r="I36">
+        <v>4.3</v>
+      </c>
+      <c r="J36">
+        <v>4.1</v>
+      </c>
+      <c r="K36">
+        <v>4.3</v>
+      </c>
+      <c r="L36">
+        <v>1.31</v>
+      </c>
+      <c r="M36">
+        <v>1.04</v>
+      </c>
+      <c r="N36">
+        <v>5.7</v>
+      </c>
+      <c r="O36">
+        <v>1.2</v>
+      </c>
+      <c r="P36">
+        <v>2.6</v>
+      </c>
+      <c r="Q36">
+        <v>1.62</v>
+      </c>
+      <c r="R36">
+        <v>1.63</v>
+      </c>
+      <c r="S36">
+        <v>2.52</v>
+      </c>
+      <c r="T36">
+        <v>1.58</v>
+      </c>
+      <c r="U36">
+        <v>2.62</v>
+      </c>
+      <c r="V36">
+        <v>1.3</v>
+      </c>
+      <c r="W36">
+        <v>2.1</v>
+      </c>
+      <c r="X36">
+        <v>24</v>
+      </c>
+      <c r="Y36">
+        <v>22</v>
+      </c>
+      <c r="Z36">
+        <v>36</v>
+      </c>
+      <c r="AA36">
+        <v>100</v>
+      </c>
+      <c r="AB36">
+        <v>13.5</v>
+      </c>
+      <c r="AC36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD36">
+        <v>17</v>
+      </c>
+      <c r="AE36">
+        <v>42</v>
+      </c>
+      <c r="AF36">
+        <v>14.5</v>
+      </c>
+      <c r="AG36">
+        <v>10.5</v>
+      </c>
+      <c r="AH36">
+        <v>16</v>
+      </c>
+      <c r="AI36">
+        <v>42</v>
+      </c>
+      <c r="AJ36">
+        <v>22</v>
+      </c>
+      <c r="AK36">
+        <v>17.5</v>
+      </c>
+      <c r="AL36">
+        <v>27</v>
+      </c>
+      <c r="AM36">
+        <v>65</v>
+      </c>
+      <c r="AN36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO36">
+        <v>32</v>
+      </c>
+      <c r="AP36">
+        <v>21</v>
+      </c>
+      <c r="AQ36">
+        <v>19.5</v>
+      </c>
+      <c r="AR36">
+        <v>30</v>
+      </c>
+      <c r="AS36">
+        <v>36</v>
+      </c>
+      <c r="AT36">
+        <v>12</v>
+      </c>
+      <c r="AU36">
+        <v>9</v>
+      </c>
+      <c r="AV36">
+        <v>15.5</v>
+      </c>
+      <c r="AW36">
+        <v>38</v>
+      </c>
+      <c r="AX36">
+        <v>13</v>
+      </c>
+      <c r="AY36">
+        <v>9.6</v>
+      </c>
+      <c r="AZ36">
+        <v>14</v>
+      </c>
+      <c r="BA36">
+        <v>36</v>
+      </c>
+      <c r="BB36">
+        <v>20</v>
+      </c>
+      <c r="BC36">
+        <v>15.5</v>
+      </c>
+      <c r="BD36">
         <v>23</v>
       </c>
-      <c r="I36">
-        <v>25</v>
-      </c>
-      <c r="J36">
-        <v>14</v>
-      </c>
-      <c r="K36">
-        <v>14.5</v>
-      </c>
-      <c r="L36">
-        <v>1.12</v>
-      </c>
-      <c r="M36">
-        <v>1.01</v>
-      </c>
-      <c r="N36">
-        <v>18</v>
-      </c>
-      <c r="O36">
-        <v>1.05</v>
-      </c>
-      <c r="P36">
-        <v>6.8</v>
-      </c>
-      <c r="Q36">
-        <v>1.15</v>
-      </c>
-      <c r="R36">
-        <v>3.25</v>
-      </c>
-      <c r="S36">
-        <v>1.41</v>
-      </c>
-      <c r="T36">
-        <v>1.71</v>
-      </c>
-      <c r="U36">
-        <v>2.36</v>
-      </c>
-      <c r="V36">
-        <v>1.04</v>
-      </c>
-      <c r="W36">
-        <v>8.6</v>
-      </c>
-      <c r="X36">
-        <v>120</v>
-      </c>
-      <c r="Y36">
-        <v>1000</v>
-      </c>
-      <c r="Z36">
-        <v>340</v>
-      </c>
-      <c r="AA36">
-        <v>1000</v>
-      </c>
-      <c r="AB36">
-        <v>30</v>
-      </c>
-      <c r="AC36">
-        <v>75</v>
-      </c>
-      <c r="AD36">
-        <v>1000</v>
-      </c>
-      <c r="AE36">
-        <v>290</v>
-      </c>
-      <c r="AF36">
-        <v>18.5</v>
-      </c>
-      <c r="AG36">
-        <v>19.5</v>
-      </c>
-      <c r="AH36">
-        <v>55</v>
-      </c>
-      <c r="AI36">
-        <v>1000</v>
-      </c>
-      <c r="AJ36">
-        <v>12</v>
-      </c>
-      <c r="AK36">
-        <v>14.5</v>
-      </c>
-      <c r="AL36">
-        <v>36</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>1.89</v>
-      </c>
-      <c r="AO36">
-        <v>1000</v>
-      </c>
-      <c r="AP36">
-        <v>38</v>
-      </c>
-      <c r="AQ36">
+      <c r="BE36">
         <v>42</v>
       </c>
-      <c r="AR36">
-        <v>18.5</v>
-      </c>
-      <c r="AS36">
-        <v>18.5</v>
-      </c>
-      <c r="AT36">
-        <v>25</v>
-      </c>
-      <c r="AU36">
-        <v>29</v>
-      </c>
-      <c r="AV36">
-        <v>36</v>
-      </c>
-      <c r="AW36">
-        <v>18.5</v>
-      </c>
-      <c r="AX36">
-        <v>15</v>
-      </c>
-      <c r="AY36">
-        <v>16.5</v>
-      </c>
-      <c r="AZ36">
-        <v>25</v>
-      </c>
-      <c r="BA36">
-        <v>44</v>
-      </c>
-      <c r="BB36">
-        <v>10</v>
-      </c>
-      <c r="BC36">
+      <c r="BF36">
+        <v>8</v>
+      </c>
+      <c r="BG36">
+        <v>27</v>
+      </c>
+      <c r="BH36">
+        <v>1000</v>
+      </c>
+      <c r="BI36">
+        <v>3.45</v>
+      </c>
+      <c r="BJ36">
+        <v>1000</v>
+      </c>
+      <c r="BK36">
+        <v>8</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>2.34</v>
+      </c>
+      <c r="BN36">
+        <v>6.2</v>
+      </c>
+      <c r="BO36">
+        <v>4</v>
+      </c>
+      <c r="BP36">
+        <v>1000</v>
+      </c>
+      <c r="BQ36">
+        <v>2.18</v>
+      </c>
+      <c r="BR36">
+        <v>1000</v>
+      </c>
+      <c r="BS36">
+        <v>2.34</v>
+      </c>
+      <c r="BT36">
+        <v>1000</v>
+      </c>
+      <c r="BU36">
+        <v>1.93</v>
+      </c>
+      <c r="BV36">
+        <v>1000</v>
+      </c>
+      <c r="BW36">
         <v>12.5</v>
       </c>
-      <c r="BD36">
-        <v>20</v>
-      </c>
-      <c r="BE36">
-        <v>55</v>
-      </c>
-      <c r="BF36">
-        <v>1.83</v>
-      </c>
-      <c r="BG36">
-        <v>85</v>
-      </c>
-      <c r="BH36">
-        <v>10.5</v>
-      </c>
-      <c r="BI36">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BJ36">
-        <v>12.5</v>
-      </c>
-      <c r="BK36">
+      <c r="BX36">
+        <v>1000</v>
+      </c>
+      <c r="BY36">
+        <v>2.34</v>
+      </c>
+      <c r="BZ36">
+        <v>1000</v>
+      </c>
+      <c r="CA36">
         <v>8.4</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>21</v>
-      </c>
-      <c r="BN36">
-        <v>5</v>
-      </c>
-      <c r="BO36">
-        <v>4.6</v>
-      </c>
-      <c r="BP36">
-        <v>6.6</v>
-      </c>
-      <c r="BQ36">
-        <v>5.2</v>
-      </c>
-      <c r="BR36">
-        <v>16</v>
-      </c>
-      <c r="BS36">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT36">
-        <v>23</v>
-      </c>
-      <c r="BU36">
-        <v>17.5</v>
-      </c>
-      <c r="BV36">
-        <v>1000</v>
-      </c>
-      <c r="BW36">
-        <v>29</v>
-      </c>
-      <c r="BX36">
-        <v>75</v>
-      </c>
-      <c r="BY36">
-        <v>48</v>
-      </c>
-      <c r="BZ36">
-        <v>4.1</v>
-      </c>
-      <c r="CA36">
-        <v>3.75</v>
       </c>
       <c r="CB36" t="s">
         <v>209</v>
@@ -9713,13 +9713,13 @@
         <v>3.35</v>
       </c>
       <c r="H37">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I37">
         <v>2.44</v>
       </c>
       <c r="J37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K37">
         <v>3.65</v>
@@ -9731,13 +9731,13 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O37">
         <v>1.34</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -9749,13 +9749,13 @@
         <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
         <v>1.42</v>
@@ -9776,16 +9776,16 @@
         <v>13</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD37">
         <v>12</v>
       </c>
       <c r="AE37">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF37">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG37">
         <v>17.5</v>
@@ -9812,7 +9812,7 @@
         <v>40</v>
       </c>
       <c r="AO37">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP37">
         <v>12</v>
@@ -9824,10 +9824,10 @@
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9845,16 +9845,16 @@
         <v>12.5</v>
       </c>
       <c r="AZ37">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA37">
         <v>6.4</v>
       </c>
       <c r="BB37">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC37">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD37">
         <v>38</v>
@@ -9866,10 +9866,10 @@
         <v>6.2</v>
       </c>
       <c r="BG37">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH37">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BI37">
         <v>3.05</v>
@@ -9878,13 +9878,13 @@
         <v>11.5</v>
       </c>
       <c r="BK37">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BN37">
         <v>7.8</v>
@@ -9896,13 +9896,13 @@
         <v>34</v>
       </c>
       <c r="BQ37">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BR37">
         <v>48</v>
       </c>
       <c r="BS37">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BT37">
         <v>6.2</v>
@@ -9914,19 +9914,19 @@
         <v>22</v>
       </c>
       <c r="BW37">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BX37">
         <v>38</v>
       </c>
       <c r="BY37">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ37">
         <v>34</v>
       </c>
       <c r="CA37">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB37" t="s">
         <v>209</v>
@@ -9949,226 +9949,226 @@
         <v>201</v>
       </c>
       <c r="F38">
-        <v>2.7</v>
+        <v>1.12</v>
       </c>
       <c r="G38">
-        <v>2.74</v>
+        <v>1.13</v>
       </c>
       <c r="H38">
-        <v>2.82</v>
+        <v>24</v>
       </c>
       <c r="I38">
-        <v>2.84</v>
+        <v>25</v>
       </c>
       <c r="J38">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="K38">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="L38">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="M38">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N38">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="O38">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="P38">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="Q38">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="R38">
-        <v>1.45</v>
+        <v>3.25</v>
       </c>
       <c r="S38">
-        <v>3.1</v>
+        <v>1.41</v>
       </c>
       <c r="T38">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U38">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V38">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="W38">
-        <v>1.58</v>
+        <v>8.6</v>
       </c>
       <c r="X38">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="Y38">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z38">
+        <v>330</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>32</v>
+      </c>
+      <c r="AC38">
+        <v>42</v>
+      </c>
+      <c r="AD38">
+        <v>100</v>
+      </c>
+      <c r="AE38">
+        <v>280</v>
+      </c>
+      <c r="AF38">
+        <v>18</v>
+      </c>
+      <c r="AG38">
+        <v>18.5</v>
+      </c>
+      <c r="AH38">
+        <v>44</v>
+      </c>
+      <c r="AI38">
+        <v>160</v>
+      </c>
+      <c r="AJ38">
+        <v>12</v>
+      </c>
+      <c r="AK38">
+        <v>15</v>
+      </c>
+      <c r="AL38">
+        <v>32</v>
+      </c>
+      <c r="AM38">
+        <v>130</v>
+      </c>
+      <c r="AN38">
+        <v>1.89</v>
+      </c>
+      <c r="AO38">
+        <v>190</v>
+      </c>
+      <c r="AP38">
+        <v>50</v>
+      </c>
+      <c r="AQ38">
+        <v>42</v>
+      </c>
+      <c r="AR38">
+        <v>19.5</v>
+      </c>
+      <c r="AS38">
         <v>20</v>
       </c>
-      <c r="AA38">
-        <v>42</v>
-      </c>
-      <c r="AB38">
-        <v>12.5</v>
-      </c>
-      <c r="AC38">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD38">
-        <v>12.5</v>
-      </c>
-      <c r="AE38">
-        <v>29</v>
-      </c>
-      <c r="AF38">
-        <v>18.5</v>
-      </c>
-      <c r="AG38">
-        <v>12.5</v>
-      </c>
-      <c r="AH38">
-        <v>15</v>
-      </c>
-      <c r="AI38">
+      <c r="AT38">
+        <v>20</v>
+      </c>
+      <c r="AU38">
+        <v>36</v>
+      </c>
+      <c r="AV38">
         <v>38</v>
       </c>
-      <c r="AJ38">
-        <v>38</v>
-      </c>
-      <c r="AK38">
-        <v>28</v>
-      </c>
-      <c r="AL38">
+      <c r="AW38">
+        <v>19</v>
+      </c>
+      <c r="AX38">
+        <v>15.5</v>
+      </c>
+      <c r="AY38">
+        <v>16.5</v>
+      </c>
+      <c r="AZ38">
         <v>36</v>
       </c>
-      <c r="AM38">
-        <v>75</v>
-      </c>
-      <c r="AN38">
-        <v>20</v>
-      </c>
-      <c r="AO38">
-        <v>22</v>
-      </c>
-      <c r="AP38">
-        <v>15.5</v>
-      </c>
-      <c r="AQ38">
-        <v>12.5</v>
-      </c>
-      <c r="AR38">
-        <v>18</v>
-      </c>
-      <c r="AS38">
-        <v>38</v>
-      </c>
-      <c r="AT38">
-        <v>12</v>
-      </c>
-      <c r="AU38">
-        <v>7.8</v>
-      </c>
-      <c r="AV38">
-        <v>11.5</v>
-      </c>
-      <c r="AW38">
-        <v>26</v>
-      </c>
-      <c r="AX38">
-        <v>17</v>
-      </c>
-      <c r="AY38">
-        <v>11</v>
-      </c>
-      <c r="AZ38">
-        <v>14.5</v>
-      </c>
       <c r="BA38">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BB38">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BC38">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BD38">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BE38">
         <v>60</v>
       </c>
       <c r="BF38">
-        <v>18</v>
+        <v>1.81</v>
       </c>
       <c r="BG38">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="BH38">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BI38">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BJ38">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BK38">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BL38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM38">
+        <v>21</v>
+      </c>
+      <c r="BN38">
+        <v>5.2</v>
+      </c>
+      <c r="BO38">
+        <v>4.6</v>
+      </c>
+      <c r="BP38">
+        <v>6.6</v>
+      </c>
+      <c r="BQ38">
+        <v>5.2</v>
+      </c>
+      <c r="BR38">
+        <v>15</v>
+      </c>
+      <c r="BS38">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT38">
+        <v>28</v>
+      </c>
+      <c r="BU38">
+        <v>19.5</v>
+      </c>
+      <c r="BV38">
+        <v>120</v>
+      </c>
+      <c r="BW38">
+        <v>29</v>
+      </c>
+      <c r="BX38">
         <v>65</v>
       </c>
-      <c r="BN38">
-        <v>5.7</v>
-      </c>
-      <c r="BO38">
-        <v>5.3</v>
-      </c>
-      <c r="BP38">
-        <v>19.5</v>
-      </c>
-      <c r="BQ38">
-        <v>14</v>
-      </c>
-      <c r="BR38">
-        <v>29</v>
-      </c>
-      <c r="BS38">
-        <v>21</v>
-      </c>
-      <c r="BT38">
-        <v>5.9</v>
-      </c>
-      <c r="BU38">
-        <v>5.4</v>
-      </c>
-      <c r="BV38">
-        <v>20</v>
-      </c>
-      <c r="BW38">
-        <v>14.5</v>
-      </c>
-      <c r="BX38">
-        <v>30</v>
-      </c>
       <c r="BY38">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="BZ38">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="CA38">
-        <v>16</v>
+        <v>3.65</v>
       </c>
       <c r="CB38" t="s">
         <v>209</v>
@@ -10191,22 +10191,22 @@
         <v>202</v>
       </c>
       <c r="F39">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G39">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H39">
         <v>1.74</v>
       </c>
       <c r="I39">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J39">
         <v>4</v>
       </c>
       <c r="K39">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L39">
         <v>1.39</v>
@@ -10215,13 +10215,13 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O39">
         <v>1.33</v>
       </c>
       <c r="P39">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q39">
         <v>1.99</v>
@@ -10239,7 +10239,7 @@
         <v>1.99</v>
       </c>
       <c r="V39">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W39">
         <v>1.21</v>
@@ -10257,7 +10257,7 @@
         <v>18</v>
       </c>
       <c r="AB39">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC39">
         <v>9</v>
@@ -10269,7 +10269,7 @@
         <v>19</v>
       </c>
       <c r="AF39">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG39">
         <v>22</v>
@@ -10317,7 +10317,7 @@
         <v>8</v>
       </c>
       <c r="AV39">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW39">
         <v>16.5</v>
@@ -10335,16 +10335,16 @@
         <v>32</v>
       </c>
       <c r="BB39">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC39">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BD39">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF39">
         <v>70</v>
@@ -10457,16 +10457,16 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="O40">
         <v>1.36</v>
       </c>
       <c r="P40">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="R40">
         <v>1.28</v>
@@ -10675,19 +10675,19 @@
         <v>204</v>
       </c>
       <c r="F41">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="G41">
         <v>1000</v>
       </c>
       <c r="H41">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="I41">
         <v>1000</v>
       </c>
       <c r="J41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K41">
         <v>950</v>
@@ -10699,19 +10699,19 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="O41">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P41">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="Q41">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R41">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="S41">
         <v>1.01</v>
@@ -10723,7 +10723,7 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W41">
         <v>1.01</v>
@@ -10917,166 +10917,166 @@
         <v>205</v>
       </c>
       <c r="F42">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="G42">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="H42">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I42">
+        <v>4.3</v>
+      </c>
+      <c r="J42">
+        <v>2.8</v>
+      </c>
+      <c r="K42">
+        <v>3.6</v>
+      </c>
+      <c r="L42">
+        <v>1.53</v>
+      </c>
+      <c r="M42">
+        <v>1.14</v>
+      </c>
+      <c r="N42">
+        <v>2.36</v>
+      </c>
+      <c r="O42">
+        <v>1.59</v>
+      </c>
+      <c r="P42">
+        <v>1.42</v>
+      </c>
+      <c r="Q42">
+        <v>2.68</v>
+      </c>
+      <c r="R42">
+        <v>1.16</v>
+      </c>
+      <c r="S42">
         <v>6</v>
       </c>
-      <c r="J42">
-        <v>1.1</v>
-      </c>
-      <c r="K42">
-        <v>3.45</v>
-      </c>
-      <c r="L42">
-        <v>1.01</v>
-      </c>
-      <c r="M42">
-        <v>1.09</v>
-      </c>
-      <c r="N42">
-        <v>1.01</v>
-      </c>
-      <c r="O42">
-        <v>1.54</v>
-      </c>
-      <c r="P42">
-        <v>1.52</v>
-      </c>
-      <c r="Q42">
-        <v>2.56</v>
-      </c>
-      <c r="R42">
-        <v>1.13</v>
-      </c>
-      <c r="S42">
-        <v>3.15</v>
-      </c>
       <c r="T42">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U42">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V42">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W42">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="X42">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z42">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AA42">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB42">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC42">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD42">
+        <v>22</v>
+      </c>
+      <c r="AE42">
+        <v>85</v>
+      </c>
+      <c r="AF42">
+        <v>14.5</v>
+      </c>
+      <c r="AG42">
+        <v>15.5</v>
+      </c>
+      <c r="AH42">
         <v>27</v>
       </c>
-      <c r="AE42">
-        <v>120</v>
-      </c>
-      <c r="AF42">
+      <c r="AI42">
+        <v>140</v>
+      </c>
+      <c r="AJ42">
+        <v>46</v>
+      </c>
+      <c r="AK42">
+        <v>46</v>
+      </c>
+      <c r="AL42">
+        <v>90</v>
+      </c>
+      <c r="AM42">
+        <v>270</v>
+      </c>
+      <c r="AN42">
+        <v>55</v>
+      </c>
+      <c r="AO42">
+        <v>130</v>
+      </c>
+      <c r="AP42">
+        <v>5.8</v>
+      </c>
+      <c r="AQ42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR42">
+        <v>18.5</v>
+      </c>
+      <c r="AS42">
+        <v>4.8</v>
+      </c>
+      <c r="AT42">
+        <v>6</v>
+      </c>
+      <c r="AU42">
+        <v>6</v>
+      </c>
+      <c r="AV42">
         <v>13</v>
       </c>
-      <c r="AG42">
-        <v>14</v>
-      </c>
-      <c r="AH42">
-        <v>34</v>
-      </c>
-      <c r="AI42">
-        <v>150</v>
-      </c>
-      <c r="AJ42">
-        <v>32</v>
-      </c>
-      <c r="AK42">
-        <v>36</v>
-      </c>
-      <c r="AL42">
-        <v>80</v>
-      </c>
-      <c r="AM42">
-        <v>290</v>
-      </c>
-      <c r="AN42">
-        <v>34</v>
-      </c>
-      <c r="AO42">
-        <v>210</v>
-      </c>
-      <c r="AP42">
-        <v>3.05</v>
-      </c>
-      <c r="AQ42">
-        <v>3.45</v>
-      </c>
-      <c r="AR42">
-        <v>4</v>
-      </c>
-      <c r="AS42">
-        <v>4.4</v>
-      </c>
-      <c r="AT42">
-        <v>2.82</v>
-      </c>
-      <c r="AU42">
-        <v>3</v>
-      </c>
-      <c r="AV42">
-        <v>3.85</v>
-      </c>
       <c r="AW42">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX42">
-        <v>3.35</v>
+        <v>11.5</v>
       </c>
       <c r="AY42">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AZ42">
-        <v>3.95</v>
+        <v>19</v>
       </c>
       <c r="BA42">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB42">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BC42">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD42">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE42">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF42">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BG42">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11183,13 +11183,13 @@
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O43">
         <v>1.27</v>
       </c>
       <c r="P43">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q43">
         <v>1.01</v>
@@ -11198,7 +11198,7 @@
         <v>1.28</v>
       </c>
       <c r="S43">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T43">
         <v>1.86</v>
@@ -11518,7 +11518,7 @@
         <v>7.8</v>
       </c>
       <c r="AS44">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT44">
         <v>6.8</v>
@@ -11530,7 +11530,7 @@
         <v>17.5</v>
       </c>
       <c r="AW44">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX44">
         <v>9.6</v>
@@ -11542,7 +11542,7 @@
         <v>19</v>
       </c>
       <c r="BA44">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB44">
         <v>18.5</v>
@@ -11551,16 +11551,16 @@
         <v>19.5</v>
       </c>
       <c r="BD44">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE44">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF44">
         <v>14</v>
       </c>
       <c r="BG44">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11572,55 +11572,55 @@
         <v>1000</v>
       </c>
       <c r="BK44">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BN44">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO44">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BP44">
         <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BR44">
         <v>1000</v>
       </c>
       <c r="BS44">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BT44">
         <v>1000</v>
       </c>
       <c r="BU44">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BV44">
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BZ44">
         <v>1000</v>
       </c>
       <c r="CA44">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="CB44" t="s">
         <v>209</v>
@@ -11643,7 +11643,7 @@
         <v>208</v>
       </c>
       <c r="F45">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G45">
         <v>2.14</v>
@@ -11670,25 +11670,25 @@
         <v>2.68</v>
       </c>
       <c r="O45">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P45">
         <v>1.55</v>
       </c>
       <c r="Q45">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
         <v>1.2</v>
       </c>
       <c r="S45">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T45">
         <v>2.22</v>
       </c>
       <c r="U45">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V45">
         <v>1.25</v>
@@ -11700,7 +11700,7 @@
         <v>8.6</v>
       </c>
       <c r="Y45">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z45">
         <v>36</v>
@@ -11715,7 +11715,7 @@
         <v>7.4</v>
       </c>
       <c r="AD45">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE45">
         <v>110</v>
@@ -11736,10 +11736,10 @@
         <v>28</v>
       </c>
       <c r="AK45">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AL45">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM45">
         <v>230</v>
@@ -11751,7 +11751,7 @@
         <v>160</v>
       </c>
       <c r="AP45">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ45">
         <v>11</v>
@@ -11763,7 +11763,7 @@
         <v>9.4</v>
       </c>
       <c r="AT45">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU45">
         <v>6.4</v>
@@ -11790,7 +11790,7 @@
         <v>7.6</v>
       </c>
       <c r="BC45">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD45">
         <v>9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -643,7 +643,7 @@
     <t>Goias</t>
   </si>
   <si>
-    <t>2026-09-09 16:08:31</t>
+    <t>2026-09-09 18:26:45</t>
   </si>
 </sst>
 </file>
@@ -1237,22 +1237,22 @@
         <v>165</v>
       </c>
       <c r="F2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
         <v>2.76</v>
       </c>
       <c r="I2">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J2">
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1261,49 +1261,49 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O2">
         <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
         <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T2">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y2">
+        <v>14</v>
+      </c>
+      <c r="Z2">
+        <v>20</v>
+      </c>
+      <c r="AA2">
+        <v>40</v>
+      </c>
+      <c r="AB2">
         <v>14.5</v>
-      </c>
-      <c r="Z2">
-        <v>21</v>
-      </c>
-      <c r="AA2">
-        <v>44</v>
-      </c>
-      <c r="AB2">
-        <v>14</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
@@ -1312,10 +1312,10 @@
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1339,16 +1339,16 @@
         <v>65</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP2">
         <v>17.5</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
         <v>18.5</v>
@@ -1360,13 +1360,13 @@
         <v>13</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX2">
         <v>18</v>
@@ -1384,7 +1384,7 @@
         <v>34</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD2">
         <v>30</v>
@@ -1393,7 +1393,7 @@
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG2">
         <v>18</v>
@@ -1414,7 +1414,7 @@
         <v>110</v>
       </c>
       <c r="BM2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>5.8</v>
@@ -1432,7 +1432,7 @@
         <v>28</v>
       </c>
       <c r="BS2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>6</v>
@@ -1444,13 +1444,13 @@
         <v>20</v>
       </c>
       <c r="BW2">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>29</v>
       </c>
       <c r="BY2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>21</v>
@@ -1479,19 +1479,19 @@
         <v>166</v>
       </c>
       <c r="F3">
+        <v>1.76</v>
+      </c>
+      <c r="G3">
         <v>1.78</v>
       </c>
-      <c r="G3">
-        <v>1.8</v>
-      </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
         <v>3.85</v>
@@ -1506,7 +1506,7 @@
         <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
         <v>1.8</v>
@@ -1524,100 +1524,100 @@
         <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
         <v>12</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA3">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE3">
+        <v>130</v>
+      </c>
+      <c r="AF3">
+        <v>9.6</v>
+      </c>
+      <c r="AG3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH3">
+        <v>24</v>
+      </c>
+      <c r="AI3">
         <v>120</v>
       </c>
-      <c r="AF3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <v>100</v>
-      </c>
       <c r="AJ3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AX3">
         <v>8.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>55</v>
@@ -1632,16 +1632,16 @@
         <v>40</v>
       </c>
       <c r="BE3">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="BF3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BH3">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BI3">
         <v>2.86</v>
@@ -1656,49 +1656,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BN3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO3">
         <v>3.8</v>
       </c>
       <c r="BP3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>9</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
         <v>34</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>209</v>
@@ -1721,64 +1721,64 @@
         <v>167</v>
       </c>
       <c r="F4">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H4">
         <v>4.1</v>
       </c>
       <c r="I4">
+        <v>4.2</v>
+      </c>
+      <c r="J4">
+        <v>2.7</v>
+      </c>
+      <c r="K4">
+        <v>2.74</v>
+      </c>
+      <c r="L4">
+        <v>1.96</v>
+      </c>
+      <c r="M4">
+        <v>1.25</v>
+      </c>
+      <c r="N4">
+        <v>1.95</v>
+      </c>
+      <c r="O4">
+        <v>2.04</v>
+      </c>
+      <c r="P4">
+        <v>1.28</v>
+      </c>
+      <c r="Q4">
         <v>4.3</v>
       </c>
-      <c r="J4">
-        <v>2.78</v>
-      </c>
-      <c r="K4">
-        <v>2.82</v>
-      </c>
-      <c r="L4">
-        <v>1.92</v>
-      </c>
-      <c r="M4">
-        <v>1.24</v>
-      </c>
-      <c r="N4">
-        <v>1.97</v>
-      </c>
-      <c r="O4">
-        <v>2</v>
-      </c>
-      <c r="P4">
-        <v>1.3</v>
-      </c>
-      <c r="Q4">
-        <v>4.1</v>
-      </c>
       <c r="R4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="U4">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="V4">
         <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
         <v>26</v>
@@ -1802,79 +1802,79 @@
         <v>13</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AI4">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ4">
+        <v>48</v>
+      </c>
+      <c r="AK4">
         <v>60</v>
       </c>
-      <c r="AK4">
-        <v>55</v>
-      </c>
       <c r="AL4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM4">
-        <v>510</v>
+        <v>640</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
         <v>24</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AT4">
         <v>5.3</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW4">
         <v>85</v>
       </c>
       <c r="AX4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BA4">
         <v>150</v>
       </c>
       <c r="BB4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="BE4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BF4">
         <v>60</v>
@@ -1883,28 +1883,28 @@
         <v>130</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="BI4">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>2.14</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1916,31 +1916,31 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CB4" t="s">
         <v>209</v>
@@ -1969,7 +1969,7 @@
         <v>2.04</v>
       </c>
       <c r="H5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
         <v>3.85</v>
@@ -1978,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.3</v>
@@ -1987,28 +1987,28 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U5">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V5">
         <v>1.35</v>
@@ -2017,10 +2017,10 @@
         <v>1.96</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -2035,10 +2035,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF5">
         <v>15.5</v>
@@ -2047,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI5">
         <v>38</v>
@@ -2056,13 +2056,13 @@
         <v>25</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
         <v>26</v>
       </c>
       <c r="AM5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN5">
         <v>9.199999999999999</v>
@@ -2071,22 +2071,22 @@
         <v>26</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS5">
         <v>60</v>
       </c>
       <c r="AT5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV5">
         <v>14.5</v>
@@ -2110,7 +2110,7 @@
         <v>22</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD5">
         <v>23</v>
@@ -2125,7 +2125,7 @@
         <v>23</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>4</v>
@@ -2134,13 +2134,13 @@
         <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>80</v>
       </c>
       <c r="BM5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BN5">
         <v>5.2</v>
@@ -2158,7 +2158,7 @@
         <v>23</v>
       </c>
       <c r="BS5">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>7.4</v>
@@ -2170,19 +2170,19 @@
         <v>27</v>
       </c>
       <c r="BW5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>32</v>
       </c>
       <c r="BY5">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
         <v>16</v>
       </c>
       <c r="CA5">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>209</v>
@@ -2205,16 +2205,16 @@
         <v>169</v>
       </c>
       <c r="F6">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J6">
         <v>3.55</v>
@@ -2235,22 +2235,22 @@
         <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
         <v>1.5</v>
@@ -2265,7 +2265,7 @@
         <v>13</v>
       </c>
       <c r="Z6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA6">
         <v>46</v>
@@ -2274,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
         <v>13</v>
@@ -2292,13 +2292,13 @@
         <v>16.5</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ6">
         <v>38</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6">
         <v>38</v>
@@ -2331,10 +2331,10 @@
         <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX6">
         <v>15.5</v>
@@ -2358,10 +2358,10 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG6">
         <v>23</v>
@@ -2394,13 +2394,13 @@
         <v>19</v>
       </c>
       <c r="BQ6">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BR6">
         <v>30</v>
       </c>
       <c r="BS6">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BT6">
         <v>6</v>
@@ -2412,7 +2412,7 @@
         <v>22</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BX6">
         <v>32</v>
@@ -2424,7 +2424,7 @@
         <v>24</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="CB6" t="s">
         <v>209</v>
@@ -2447,22 +2447,22 @@
         <v>170</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
         <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L7">
         <v>1.36</v>
@@ -2477,37 +2477,37 @@
         <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R7">
         <v>1.48</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y7">
         <v>17.5</v>
       </c>
       <c r="Z7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA7">
         <v>75</v>
@@ -2519,22 +2519,22 @@
         <v>9</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE7">
         <v>44</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
         <v>24</v>
@@ -2546,10 +2546,10 @@
         <v>32</v>
       </c>
       <c r="AM7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO7">
         <v>38</v>
@@ -2564,7 +2564,7 @@
         <v>26</v>
       </c>
       <c r="AS7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -2579,7 +2579,7 @@
         <v>38</v>
       </c>
       <c r="AX7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
@@ -2591,16 +2591,16 @@
         <v>40</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD7">
         <v>28</v>
       </c>
       <c r="BE7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF7">
         <v>10.5</v>
@@ -2609,7 +2609,7 @@
         <v>32</v>
       </c>
       <c r="BH7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI7">
         <v>3.55</v>
@@ -2624,7 +2624,7 @@
         <v>100</v>
       </c>
       <c r="BM7">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2636,37 +2636,37 @@
         <v>14</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR7">
         <v>26</v>
       </c>
       <c r="BS7">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU7">
         <v>6.6</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BX7">
         <v>38</v>
       </c>
       <c r="BY7">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="BZ7">
         <v>21</v>
       </c>
       <c r="CA7">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="s">
         <v>209</v>
@@ -2689,16 +2689,16 @@
         <v>171</v>
       </c>
       <c r="F8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G8">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J8">
         <v>4.3</v>
@@ -2713,40 +2713,40 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
+        <v>1.28</v>
+      </c>
+      <c r="R8">
+        <v>2.42</v>
+      </c>
+      <c r="S8">
+        <v>1.69</v>
+      </c>
+      <c r="T8">
         <v>1.29</v>
       </c>
-      <c r="R8">
-        <v>2.36</v>
-      </c>
-      <c r="S8">
-        <v>1.71</v>
-      </c>
-      <c r="T8">
-        <v>1.31</v>
-      </c>
       <c r="U8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X8">
         <v>60</v>
       </c>
       <c r="Y8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z8">
         <v>36</v>
@@ -2764,10 +2764,10 @@
         <v>15.5</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG8">
         <v>14</v>
@@ -2791,16 +2791,16 @@
         <v>30</v>
       </c>
       <c r="AN8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO8">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AQ8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR8">
         <v>30</v>
@@ -2809,10 +2809,10 @@
         <v>48</v>
       </c>
       <c r="AT8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV8">
         <v>14</v>
@@ -2821,22 +2821,22 @@
         <v>22</v>
       </c>
       <c r="AX8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB8">
         <v>34</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD8">
         <v>19.5</v>
@@ -2848,13 +2848,13 @@
         <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH8">
         <v>8</v>
       </c>
       <c r="BI8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BJ8">
         <v>8.4</v>
@@ -2866,10 +2866,10 @@
         <v>42</v>
       </c>
       <c r="BM8">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BN8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
         <v>6.2</v>
@@ -2881,13 +2881,13 @@
         <v>6.2</v>
       </c>
       <c r="BR8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
         <v>6.6</v>
@@ -2908,7 +2908,7 @@
         <v>8.6</v>
       </c>
       <c r="CA8">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>209</v>
@@ -2931,10 +2931,10 @@
         <v>172</v>
       </c>
       <c r="F9">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
         <v>4.2</v>
@@ -2946,7 +2946,7 @@
         <v>4.5</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.24</v>
@@ -2955,28 +2955,28 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O9">
         <v>1.13</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S9">
         <v>2.06</v>
       </c>
       <c r="T9">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V9">
         <v>1.29</v>
@@ -2985,7 +2985,7 @@
         <v>2.2</v>
       </c>
       <c r="X9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y9">
         <v>30</v>
@@ -2994,7 +2994,7 @@
         <v>42</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AB9">
         <v>17.5</v>
@@ -3003,7 +3003,7 @@
         <v>12</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>40</v>
@@ -3018,13 +3018,13 @@
         <v>15</v>
       </c>
       <c r="AI9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
         <v>22</v>
@@ -3033,13 +3033,13 @@
         <v>46</v>
       </c>
       <c r="AN9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ9">
         <v>28</v>
@@ -3051,10 +3051,10 @@
         <v>70</v>
       </c>
       <c r="AT9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV9">
         <v>16.5</v>
@@ -3063,7 +3063,7 @@
         <v>34</v>
       </c>
       <c r="AX9">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY9">
         <v>10</v>
@@ -3075,28 +3075,28 @@
         <v>32</v>
       </c>
       <c r="BB9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF9">
         <v>5.9</v>
       </c>
       <c r="BG9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH9">
         <v>5.2</v>
       </c>
       <c r="BI9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ9">
         <v>8.4</v>
@@ -3105,16 +3105,16 @@
         <v>7.6</v>
       </c>
       <c r="BL9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
       </c>
       <c r="BO9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP9">
         <v>11</v>
@@ -3126,7 +3126,7 @@
         <v>18</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BT9">
         <v>8.199999999999999</v>
@@ -3135,22 +3135,22 @@
         <v>7.6</v>
       </c>
       <c r="BV9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BX9">
         <v>29</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>11</v>
       </c>
       <c r="CA9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="s">
         <v>209</v>
@@ -3176,7 +3176,7 @@
         <v>2.52</v>
       </c>
       <c r="G10">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H10">
         <v>2.7</v>
@@ -3197,40 +3197,40 @@
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q10">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S10">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T10">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V10">
         <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X10">
         <v>32</v>
       </c>
       <c r="Y10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z10">
         <v>25</v>
@@ -3239,22 +3239,22 @@
         <v>40</v>
       </c>
       <c r="AB10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE10">
         <v>24</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
         <v>14</v>
@@ -3263,7 +3263,7 @@
         <v>27</v>
       </c>
       <c r="AJ10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK10">
         <v>22</v>
@@ -3272,31 +3272,31 @@
         <v>26</v>
       </c>
       <c r="AM10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS10">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT10">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
         <v>12</v>
@@ -3305,7 +3305,7 @@
         <v>21</v>
       </c>
       <c r="AX10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY10">
         <v>11.5</v>
@@ -3314,16 +3314,16 @@
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE10">
         <v>36</v>
@@ -3335,7 +3335,7 @@
         <v>11.5</v>
       </c>
       <c r="BH10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI10">
         <v>4.4</v>
@@ -3368,28 +3368,28 @@
         <v>22</v>
       </c>
       <c r="BS10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BT10">
         <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV10">
         <v>17.5</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BX10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY10">
         <v>18.5</v>
       </c>
       <c r="BZ10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA10">
         <v>11</v>
@@ -3418,13 +3418,13 @@
         <v>1.44</v>
       </c>
       <c r="G11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H11">
         <v>7.4</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>5.6</v>
@@ -3439,37 +3439,37 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R11">
+        <v>1.98</v>
+      </c>
+      <c r="S11">
         <v>1.97</v>
       </c>
-      <c r="S11">
-        <v>1.99</v>
-      </c>
       <c r="T11">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.14</v>
       </c>
       <c r="W11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y11">
         <v>42</v>
@@ -3478,7 +3478,7 @@
         <v>75</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB11">
         <v>15.5</v>
@@ -3499,10 +3499,10 @@
         <v>11</v>
       </c>
       <c r="AH11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ11">
         <v>14.5</v>
@@ -3520,7 +3520,7 @@
         <v>4</v>
       </c>
       <c r="AO11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11">
         <v>36</v>
@@ -3532,16 +3532,16 @@
         <v>65</v>
       </c>
       <c r="AS11">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AT11">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU11">
         <v>13</v>
       </c>
       <c r="AV11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11">
         <v>70</v>
@@ -3571,10 +3571,10 @@
         <v>55</v>
       </c>
       <c r="BF11">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG11">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BH11">
         <v>5.5</v>
@@ -3666,13 +3666,13 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L12">
         <v>1.21</v>
@@ -3687,10 +3687,10 @@
         <v>1.11</v>
       </c>
       <c r="P12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R12">
         <v>2.08</v>
@@ -3702,7 +3702,7 @@
         <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
         <v>1.11</v>
@@ -3714,7 +3714,7 @@
         <v>46</v>
       </c>
       <c r="Y12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z12">
         <v>95</v>
@@ -3726,7 +3726,7 @@
         <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD12">
         <v>34</v>
@@ -3765,7 +3765,7 @@
         <v>95</v>
       </c>
       <c r="AP12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AQ12">
         <v>44</v>
@@ -3786,7 +3786,7 @@
         <v>30</v>
       </c>
       <c r="AW12">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -3810,7 +3810,7 @@
         <v>22</v>
       </c>
       <c r="BE12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF12">
         <v>3.4</v>
@@ -3852,7 +3852,7 @@
         <v>16.5</v>
       </c>
       <c r="BS12">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BT12">
         <v>13</v>
@@ -4016,7 +4016,7 @@
         <v>12</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT13">
         <v>10</v>
@@ -4040,22 +4040,22 @@
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG13">
         <v>15.5</v>
@@ -4141,166 +4141,166 @@
         <v>177</v>
       </c>
       <c r="F14">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>12.5</v>
+      </c>
+      <c r="H14">
+        <v>1.29</v>
+      </c>
+      <c r="I14">
+        <v>1.37</v>
+      </c>
+      <c r="J14">
+        <v>6.2</v>
+      </c>
+      <c r="K14">
+        <v>8.4</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
         <v>8.6</v>
-      </c>
-      <c r="G14">
-        <v>1000</v>
-      </c>
-      <c r="H14">
-        <v>1.24</v>
-      </c>
-      <c r="I14">
-        <v>1.49</v>
-      </c>
-      <c r="J14">
-        <v>4.6</v>
-      </c>
-      <c r="K14">
-        <v>13</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>8.4</v>
       </c>
       <c r="O14">
         <v>1.09</v>
       </c>
       <c r="P14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="R14">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="S14">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="T14">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="U14">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
+        <v>60</v>
+      </c>
+      <c r="Y14">
+        <v>19</v>
+      </c>
+      <c r="Z14">
+        <v>14.5</v>
+      </c>
+      <c r="AA14">
+        <v>14.5</v>
+      </c>
+      <c r="AB14">
+        <v>65</v>
+      </c>
+      <c r="AC14">
+        <v>18.5</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>14</v>
+      </c>
+      <c r="AF14">
+        <v>120</v>
+      </c>
+      <c r="AG14">
+        <v>44</v>
+      </c>
+      <c r="AH14">
+        <v>28</v>
+      </c>
+      <c r="AI14">
+        <v>30</v>
+      </c>
+      <c r="AJ14">
+        <v>320</v>
+      </c>
+      <c r="AK14">
+        <v>130</v>
+      </c>
+      <c r="AL14">
         <v>95</v>
       </c>
-      <c r="Y14">
-        <v>970</v>
-      </c>
-      <c r="Z14">
-        <v>970</v>
-      </c>
-      <c r="AA14">
-        <v>970</v>
-      </c>
-      <c r="AB14">
-        <v>1000</v>
-      </c>
-      <c r="AC14">
-        <v>970</v>
-      </c>
-      <c r="AD14">
-        <v>17</v>
-      </c>
-      <c r="AE14">
-        <v>19.5</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>90</v>
-      </c>
-      <c r="AH14">
-        <v>40</v>
-      </c>
-      <c r="AI14">
+      <c r="AM14">
+        <v>95</v>
+      </c>
+      <c r="AN14">
         <v>100</v>
       </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
       <c r="AO14">
-        <v>970</v>
+        <v>3.45</v>
       </c>
       <c r="AP14">
-        <v>1.48</v>
+        <v>22</v>
       </c>
       <c r="AQ14">
-        <v>1.53</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>1.43</v>
+        <v>10.5</v>
       </c>
       <c r="AS14">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT14">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU14">
-        <v>1.46</v>
+        <v>14.5</v>
       </c>
       <c r="AV14">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AX14">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY14">
-        <v>1.48</v>
+        <v>22</v>
       </c>
       <c r="AZ14">
-        <v>1.45</v>
+        <v>20</v>
       </c>
       <c r="BA14">
-        <v>1.48</v>
+        <v>16.5</v>
       </c>
       <c r="BB14">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC14">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE14">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF14">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG14">
-        <v>1.36</v>
+        <v>2.76</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4383,7 +4383,7 @@
         <v>178</v>
       </c>
       <c r="F15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G15">
         <v>1.64</v>
@@ -4416,13 +4416,13 @@
         <v>2.64</v>
       </c>
       <c r="Q15">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="R15">
         <v>1.66</v>
       </c>
       <c r="S15">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="T15">
         <v>1.64</v>
@@ -4625,16 +4625,16 @@
         <v>179</v>
       </c>
       <c r="F16">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G16">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>3.9</v>
@@ -4649,58 +4649,58 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q16">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S16">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="X16">
         <v>30</v>
       </c>
       <c r="Y16">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
         <v>17</v>
       </c>
       <c r="AE16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF16">
         <v>23</v>
@@ -4712,19 +4712,19 @@
         <v>18.5</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
         <v>34</v>
       </c>
       <c r="AK16">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL16">
         <v>34</v>
       </c>
       <c r="AM16">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN16">
         <v>12.5</v>
@@ -4736,13 +4736,13 @@
         <v>18</v>
       </c>
       <c r="AQ16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR16">
+        <v>5.2</v>
+      </c>
+      <c r="AS16">
         <v>5.7</v>
-      </c>
-      <c r="AS16">
-        <v>6.2</v>
       </c>
       <c r="AT16">
         <v>13</v>
@@ -4757,34 +4757,34 @@
         <v>21</v>
       </c>
       <c r="AX16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
+        <v>5.3</v>
+      </c>
+      <c r="BB16">
+        <v>5.3</v>
+      </c>
+      <c r="BC16">
+        <v>5.1</v>
+      </c>
+      <c r="BD16">
+        <v>21</v>
+      </c>
+      <c r="BE16">
         <v>5.8</v>
-      </c>
-      <c r="BB16">
-        <v>5.7</v>
-      </c>
-      <c r="BC16">
-        <v>5.3</v>
-      </c>
-      <c r="BD16">
-        <v>5.8</v>
-      </c>
-      <c r="BE16">
-        <v>6.4</v>
       </c>
       <c r="BF16">
         <v>10.5</v>
       </c>
       <c r="BG16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4867,166 +4867,166 @@
         <v>180</v>
       </c>
       <c r="F17">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="G17">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="H17">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="J17">
+        <v>4.3</v>
+      </c>
+      <c r="K17">
+        <v>7.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
         <v>4.1</v>
       </c>
-      <c r="K17">
-        <v>6.4</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>3.85</v>
-      </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q17">
+        <v>1.52</v>
+      </c>
+      <c r="R17">
         <v>1.49</v>
       </c>
-      <c r="R17">
-        <v>1.51</v>
-      </c>
       <c r="S17">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V17">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W17">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="X17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y17">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AA17">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="AB17">
         <v>13</v>
       </c>
       <c r="AC17">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AE17">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AF17">
         <v>11.5</v>
       </c>
       <c r="AG17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AJ17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM17">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN17">
         <v>6.2</v>
       </c>
       <c r="AO17">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP17">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ17">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR17">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AS17">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT17">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AU17">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AV17">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW17">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX17">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AY17">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AZ17">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BA17">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB17">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BC17">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BD17">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BE17">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF17">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="BG17">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5112,16 +5112,16 @@
         <v>1.45</v>
       </c>
       <c r="G18">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H18">
         <v>2.2</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -5133,22 +5133,22 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O18">
         <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="R18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -5160,7 +5160,7 @@
         <v>1.02</v>
       </c>
       <c r="W18">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5268,7 +5268,7 @@
         <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5390,7 +5390,7 @@
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5459,52 +5459,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5608,7 +5608,7 @@
         <v>3.6</v>
       </c>
       <c r="K20">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5853,7 +5853,7 @@
         <v>4.7</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M21">
         <v>1.01</v>
@@ -5874,13 +5874,13 @@
         <v>1.61</v>
       </c>
       <c r="S21">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
         <v>1.57</v>
       </c>
       <c r="U21">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
         <v>1.01</v>
@@ -5892,10 +5892,10 @@
         <v>32</v>
       </c>
       <c r="Y21">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA21">
         <v>110</v>
@@ -5931,10 +5931,10 @@
         <v>18</v>
       </c>
       <c r="AL21">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM21">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN21">
         <v>8</v>
@@ -5949,10 +5949,10 @@
         <v>20</v>
       </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT21">
         <v>11</v>
@@ -5964,7 +5964,7 @@
         <v>16.5</v>
       </c>
       <c r="AW21">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5976,7 +5976,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BB21">
         <v>16</v>
@@ -5985,16 +5985,16 @@
         <v>14</v>
       </c>
       <c r="BD21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE21">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF21">
         <v>6.6</v>
       </c>
       <c r="BG21">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6077,22 +6077,22 @@
         <v>185</v>
       </c>
       <c r="F22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="I22">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L22">
         <v>1.16</v>
@@ -6101,55 +6101,55 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O22">
         <v>1.1</v>
       </c>
       <c r="P22">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R22">
+        <v>2.14</v>
+      </c>
+      <c r="S22">
+        <v>1.74</v>
+      </c>
+      <c r="T22">
+        <v>1.84</v>
+      </c>
+      <c r="U22">
         <v>2.02</v>
       </c>
-      <c r="S22">
-        <v>1.78</v>
-      </c>
-      <c r="T22">
-        <v>1.78</v>
-      </c>
-      <c r="U22">
-        <v>2.04</v>
-      </c>
       <c r="V22">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>60</v>
       </c>
       <c r="Y22">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z22">
+        <v>12.5</v>
+      </c>
+      <c r="AA22">
         <v>13</v>
-      </c>
-      <c r="AA22">
-        <v>13.5</v>
       </c>
       <c r="AB22">
         <v>75</v>
       </c>
       <c r="AC22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AD22">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE22">
         <v>14</v>
@@ -6161,13 +6161,13 @@
         <v>60</v>
       </c>
       <c r="AH22">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI22">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ22">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="AK22">
         <v>200</v>
@@ -6179,64 +6179,64 @@
         <v>130</v>
       </c>
       <c r="AN22">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AO22">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AP22">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT22">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU22">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW22">
         <v>11.5</v>
       </c>
       <c r="AX22">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY22">
         <v>24</v>
       </c>
       <c r="AZ22">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA22">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB22">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC22">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD22">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE22">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF22">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG22">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6337,13 +6337,13 @@
         <v>3.7</v>
       </c>
       <c r="L23">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M23">
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O23">
         <v>1.25</v>
@@ -6352,19 +6352,19 @@
         <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R23">
         <v>1.49</v>
       </c>
       <c r="S23">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T23">
         <v>1.65</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
         <v>1.8</v>
@@ -6376,16 +6376,16 @@
         <v>18</v>
       </c>
       <c r="Y23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA23">
         <v>28</v>
       </c>
       <c r="AB23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -6394,7 +6394,7 @@
         <v>10.5</v>
       </c>
       <c r="AE23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23">
         <v>27</v>
@@ -6406,13 +6406,13 @@
         <v>15</v>
       </c>
       <c r="AI23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ23">
         <v>65</v>
       </c>
       <c r="AK23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL23">
         <v>42</v>
@@ -6427,16 +6427,16 @@
         <v>12.5</v>
       </c>
       <c r="AP23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT23">
         <v>15.5</v>
@@ -6451,10 +6451,10 @@
         <v>19.5</v>
       </c>
       <c r="AX23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ23">
         <v>14</v>
@@ -6475,7 +6475,7 @@
         <v>60</v>
       </c>
       <c r="BF23">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG23">
         <v>12</v>
@@ -6532,13 +6532,13 @@
         <v>38</v>
       </c>
       <c r="BY23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BZ23">
         <v>30</v>
       </c>
       <c r="CA23">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="s">
         <v>209</v>
@@ -6561,22 +6561,22 @@
         <v>187</v>
       </c>
       <c r="F24">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G24">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="H24">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I24">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J24">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K24">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L24">
         <v>1.25</v>
@@ -6597,46 +6597,46 @@
         <v>1.46</v>
       </c>
       <c r="R24">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S24">
         <v>2.16</v>
       </c>
       <c r="T24">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U24">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W24">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="X24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z24">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA24">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB24">
         <v>13.5</v>
       </c>
       <c r="AC24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE24">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF24">
         <v>12</v>
@@ -6645,28 +6645,28 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ24">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK24">
         <v>13.5</v>
       </c>
       <c r="AL24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO24">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP24">
         <v>29</v>
@@ -6675,7 +6675,7 @@
         <v>30</v>
       </c>
       <c r="AR24">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AS24">
         <v>46</v>
@@ -6684,28 +6684,28 @@
         <v>13</v>
       </c>
       <c r="AU24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW24">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AX24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BB24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC24">
         <v>12.5</v>
@@ -6720,7 +6720,7 @@
         <v>4.4</v>
       </c>
       <c r="BG24">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BH24">
         <v>5.9</v>
@@ -6738,13 +6738,13 @@
         <v>100</v>
       </c>
       <c r="BM24">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BN24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP24">
         <v>10.5</v>
@@ -6753,10 +6753,10 @@
         <v>7.6</v>
       </c>
       <c r="BR24">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BS24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT24">
         <v>13.5</v>
@@ -6765,22 +6765,22 @@
         <v>9.6</v>
       </c>
       <c r="BV24">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BW24">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BX24">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BY24">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="BZ24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA24">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="CB24" t="s">
         <v>209</v>
@@ -6812,10 +6812,10 @@
         <v>2</v>
       </c>
       <c r="I25">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J25">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K25">
         <v>4.1</v>
@@ -6827,13 +6827,13 @@
         <v>1.04</v>
       </c>
       <c r="N25">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
         <v>1.25</v>
       </c>
       <c r="P25">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="Q25">
         <v>1.69</v>
@@ -6842,16 +6842,16 @@
         <v>1.3</v>
       </c>
       <c r="S25">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T25">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U25">
         <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W25">
         <v>1.32</v>
@@ -7048,73 +7048,73 @@
         <v>11</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="H26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I26">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K26">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N26">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O26">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R26">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S26">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T26">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z26">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>10.5</v>
       </c>
       <c r="AB26">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AC26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD26">
         <v>12.5</v>
@@ -7126,16 +7126,16 @@
         <v>140</v>
       </c>
       <c r="AG26">
+        <v>60</v>
+      </c>
+      <c r="AH26">
+        <v>34</v>
+      </c>
+      <c r="AI26">
         <v>48</v>
       </c>
-      <c r="AH26">
-        <v>32</v>
-      </c>
-      <c r="AI26">
-        <v>46</v>
-      </c>
       <c r="AJ26">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="AK26">
         <v>220</v>
@@ -7147,100 +7147,100 @@
         <v>180</v>
       </c>
       <c r="AN26">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AO26">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AP26">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AQ26">
         <v>5</v>
       </c>
       <c r="AR26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS26">
+        <v>4.6</v>
+      </c>
+      <c r="AT26">
+        <v>12.5</v>
+      </c>
+      <c r="AU26">
+        <v>5.8</v>
+      </c>
+      <c r="AV26">
+        <v>5</v>
+      </c>
+      <c r="AW26">
+        <v>5.3</v>
+      </c>
+      <c r="AX26">
+        <v>28</v>
+      </c>
+      <c r="AY26">
+        <v>12.5</v>
+      </c>
+      <c r="AZ26">
+        <v>6.6</v>
+      </c>
+      <c r="BA26">
+        <v>10</v>
+      </c>
+      <c r="BB26">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT26">
-        <v>25</v>
-      </c>
-      <c r="AU26">
-        <v>5.7</v>
-      </c>
-      <c r="AV26">
-        <v>5.1</v>
-      </c>
-      <c r="AW26">
-        <v>5.4</v>
-      </c>
-      <c r="AX26">
+      <c r="BC26">
+        <v>19</v>
+      </c>
+      <c r="BD26">
+        <v>30</v>
+      </c>
+      <c r="BE26">
+        <v>8</v>
+      </c>
+      <c r="BF26">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY26">
-        <v>24</v>
-      </c>
-      <c r="AZ26">
-        <v>23</v>
-      </c>
-      <c r="BA26">
-        <v>7.2</v>
-      </c>
-      <c r="BB26">
-        <v>21</v>
-      </c>
-      <c r="BC26">
-        <v>19.5</v>
-      </c>
-      <c r="BD26">
-        <v>27</v>
-      </c>
-      <c r="BE26">
-        <v>30</v>
-      </c>
-      <c r="BF26">
-        <v>8.4</v>
-      </c>
       <c r="BG26">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BH26">
         <v>5.6</v>
       </c>
       <c r="BI26">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ26">
         <v>14.5</v>
       </c>
       <c r="BK26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN26">
         <v>17.5</v>
       </c>
       <c r="BO26">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP26">
         <v>110</v>
       </c>
       <c r="BQ26">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR26">
         <v>90</v>
       </c>
       <c r="BS26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT26">
         <v>4.6</v>
@@ -7249,7 +7249,7 @@
         <v>3.1</v>
       </c>
       <c r="BV26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW26">
         <v>5.3</v>
@@ -7258,13 +7258,13 @@
         <v>25</v>
       </c>
       <c r="BY26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="CB26" t="s">
         <v>209</v>
@@ -7290,13 +7290,13 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H27">
         <v>3.65</v>
       </c>
       <c r="I27">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J27">
         <v>4</v>
@@ -7317,13 +7317,13 @@
         <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q27">
         <v>1.61</v>
       </c>
       <c r="R27">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S27">
         <v>2.52</v>
@@ -7335,10 +7335,10 @@
         <v>2.62</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X27">
         <v>24</v>
@@ -7386,7 +7386,7 @@
         <v>28</v>
       </c>
       <c r="AM27">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="AN27">
         <v>9.800000000000001</v>
@@ -7395,13 +7395,13 @@
         <v>28</v>
       </c>
       <c r="AP27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ27">
         <v>17</v>
       </c>
       <c r="AR27">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS27">
         <v>32</v>
@@ -7443,10 +7443,10 @@
         <v>30</v>
       </c>
       <c r="BF27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG27">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BH27">
         <v>4.3</v>
@@ -7467,7 +7467,7 @@
         <v>10</v>
       </c>
       <c r="BN27">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO27">
         <v>4.7</v>
@@ -7485,10 +7485,10 @@
         <v>7.6</v>
       </c>
       <c r="BT27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU27">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV27">
         <v>27</v>
@@ -7574,7 +7574,7 @@
         <v>1.63</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
         <v>1.79</v>
@@ -7646,7 +7646,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT28">
         <v>14</v>
@@ -7774,19 +7774,19 @@
         <v>3.85</v>
       </c>
       <c r="G29">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H29">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I29">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J29">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29">
         <v>1.39</v>
@@ -7801,28 +7801,28 @@
         <v>1.29</v>
       </c>
       <c r="P29">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R29">
         <v>1.42</v>
       </c>
       <c r="S29">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T29">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U29">
         <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="W29">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X29">
         <v>17.5</v>
@@ -7849,19 +7849,19 @@
         <v>22</v>
       </c>
       <c r="AF29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG29">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH29">
         <v>18</v>
       </c>
       <c r="AI29">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ29">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK29">
         <v>55</v>
@@ -7876,22 +7876,22 @@
         <v>55</v>
       </c>
       <c r="AO29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP29">
         <v>14.5</v>
       </c>
       <c r="AQ29">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR29">
         <v>11.5</v>
       </c>
       <c r="AS29">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU29">
         <v>7.8</v>
@@ -7900,10 +7900,10 @@
         <v>9.4</v>
       </c>
       <c r="AW29">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX29">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY29">
         <v>14</v>
@@ -7912,25 +7912,25 @@
         <v>15.5</v>
       </c>
       <c r="BA29">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC29">
+        <v>7.8</v>
+      </c>
+      <c r="BD29">
+        <v>7.8</v>
+      </c>
+      <c r="BE29">
         <v>8.4</v>
       </c>
-      <c r="BC29">
-        <v>8</v>
-      </c>
-      <c r="BD29">
-        <v>8</v>
-      </c>
-      <c r="BE29">
-        <v>8.6</v>
-      </c>
       <c r="BF29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8016,22 +8016,22 @@
         <v>1.74</v>
       </c>
       <c r="G30">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H30">
         <v>4.8</v>
       </c>
       <c r="I30">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J30">
         <v>3.7</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M30">
         <v>1.06</v>
@@ -8049,22 +8049,22 @@
         <v>1.83</v>
       </c>
       <c r="R30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S30">
         <v>3</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W30">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8079,22 +8079,22 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC30">
+        <v>11.5</v>
+      </c>
+      <c r="AD30">
+        <v>27</v>
+      </c>
+      <c r="AE30">
+        <v>1000</v>
+      </c>
+      <c r="AF30">
         <v>13</v>
       </c>
-      <c r="AD30">
-        <v>28</v>
-      </c>
-      <c r="AE30">
-        <v>1000</v>
-      </c>
-      <c r="AF30">
-        <v>970</v>
-      </c>
       <c r="AG30">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH30">
         <v>1000</v>
@@ -8121,58 +8121,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR30">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AS30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AT30">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU30">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV30">
-        <v>1.77</v>
+        <v>14</v>
       </c>
       <c r="AW30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AX30">
         <v>8.199999999999999</v>
       </c>
       <c r="AY30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BB30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BC30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BD30">
         <v>21</v>
       </c>
       <c r="BE30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BF30">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="BG30">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8255,19 +8255,19 @@
         <v>194</v>
       </c>
       <c r="F31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G31">
         <v>110</v>
       </c>
       <c r="H31">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="I31">
         <v>110</v>
       </c>
       <c r="J31">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="K31">
         <v>950</v>
@@ -8303,10 +8303,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8363,52 +8363,52 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8497,7 +8497,7 @@
         <v>195</v>
       </c>
       <c r="F32">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="G32">
         <v>1.9</v>
@@ -8506,10 +8506,10 @@
         <v>4.4</v>
       </c>
       <c r="I32">
-        <v>110</v>
+        <v>5.1</v>
       </c>
       <c r="J32">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K32">
         <v>4</v>
@@ -8518,25 +8518,25 @@
         <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
         <v>1.26</v>
       </c>
       <c r="O32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S32">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8545,7 +8545,7 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="W32">
         <v>2.1</v>
@@ -8653,10 +8653,10 @@
         <v>1.03</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8739,7 +8739,7 @@
         <v>196</v>
       </c>
       <c r="F33">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G33">
         <v>1.31</v>
@@ -8766,7 +8766,7 @@
         <v>4.3</v>
       </c>
       <c r="O33">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P33">
         <v>2.18</v>
@@ -8781,7 +8781,7 @@
         <v>3</v>
       </c>
       <c r="T33">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U33">
         <v>1.67</v>
@@ -8802,7 +8802,7 @@
         <v>140</v>
       </c>
       <c r="AA33">
-        <v>780</v>
+        <v>880</v>
       </c>
       <c r="AB33">
         <v>7.6</v>
@@ -8811,7 +8811,7 @@
         <v>14</v>
       </c>
       <c r="AD33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE33">
         <v>300</v>
@@ -8820,7 +8820,7 @@
         <v>7.2</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH33">
         <v>40</v>
@@ -8841,22 +8841,22 @@
         <v>270</v>
       </c>
       <c r="AN33">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO33">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="AP33">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33">
         <v>29</v>
       </c>
       <c r="AR33">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS33">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT33">
         <v>7</v>
@@ -8868,7 +8868,7 @@
         <v>42</v>
       </c>
       <c r="AW33">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX33">
         <v>6.4</v>
@@ -8880,7 +8880,7 @@
         <v>32</v>
       </c>
       <c r="BA33">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB33">
         <v>8.6</v>
@@ -8889,16 +8889,16 @@
         <v>14</v>
       </c>
       <c r="BD33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE33">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF33">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG33">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH33">
         <v>3.85</v>
@@ -8987,82 +8987,82 @@
         <v>1.14</v>
       </c>
       <c r="H34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I34">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J34">
+        <v>11</v>
+      </c>
+      <c r="K34">
         <v>11.5</v>
       </c>
-      <c r="K34">
+      <c r="L34">
+        <v>1.17</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
         <v>12</v>
       </c>
-      <c r="L34">
-        <v>1.18</v>
-      </c>
-      <c r="M34">
-        <v>1.01</v>
-      </c>
-      <c r="N34">
-        <v>11.5</v>
-      </c>
       <c r="O34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P34">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S34">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T34">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U34">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V34">
         <v>1.03</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X34">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z34">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="AA34">
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC34">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AD34">
         <v>1000</v>
       </c>
       <c r="AE34">
-        <v>410</v>
+        <v>490</v>
       </c>
       <c r="AF34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG34">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
         <v>50</v>
@@ -9071,37 +9071,37 @@
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AK34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM34">
         <v>1000</v>
       </c>
       <c r="AN34">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AO34">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AP34">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AQ34">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AR34">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AS34">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AT34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU34">
         <v>25</v>
@@ -9110,19 +9110,19 @@
         <v>55</v>
       </c>
       <c r="AW34">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY34">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ34">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BA34">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB34">
         <v>8.800000000000001</v>
@@ -9131,16 +9131,16 @@
         <v>13</v>
       </c>
       <c r="BD34">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE34">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BF34">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BG34">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BH34">
         <v>7.6</v>
@@ -9149,7 +9149,7 @@
         <v>6</v>
       </c>
       <c r="BJ34">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BK34">
         <v>12.5</v>
@@ -9158,10 +9158,10 @@
         <v>150</v>
       </c>
       <c r="BM34">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BN34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO34">
         <v>3.8</v>
@@ -9173,31 +9173,31 @@
         <v>5</v>
       </c>
       <c r="BR34">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BS34">
         <v>16.5</v>
       </c>
       <c r="BT34">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BU34">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BX34">
         <v>110</v>
       </c>
       <c r="BY34">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BZ34">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="CA34">
         <v>4.6</v>
@@ -9223,10 +9223,10 @@
         <v>198</v>
       </c>
       <c r="F35">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G35">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H35">
         <v>2.82</v>
@@ -9250,13 +9250,13 @@
         <v>4.4</v>
       </c>
       <c r="O35">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P35">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q35">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R35">
         <v>1.45</v>
@@ -9265,7 +9265,7 @@
         <v>3.1</v>
       </c>
       <c r="T35">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U35">
         <v>2.42</v>
@@ -9277,37 +9277,37 @@
         <v>1.58</v>
       </c>
       <c r="X35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z35">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA35">
         <v>42</v>
       </c>
       <c r="AB35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC35">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD35">
         <v>12.5</v>
       </c>
       <c r="AE35">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF35">
         <v>18.5</v>
       </c>
       <c r="AG35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI35">
         <v>38</v>
@@ -9316,13 +9316,13 @@
         <v>38</v>
       </c>
       <c r="AK35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL35">
         <v>36</v>
       </c>
       <c r="AM35">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN35">
         <v>20</v>
@@ -9340,7 +9340,7 @@
         <v>18</v>
       </c>
       <c r="AS35">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT35">
         <v>12</v>
@@ -9358,19 +9358,19 @@
         <v>17</v>
       </c>
       <c r="AY35">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35">
         <v>14.5</v>
       </c>
       <c r="BA35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB35">
         <v>34</v>
       </c>
       <c r="BC35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD35">
         <v>32</v>
@@ -9379,10 +9379,10 @@
         <v>60</v>
       </c>
       <c r="BF35">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG35">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH35">
         <v>3.7</v>
@@ -9409,7 +9409,7 @@
         <v>5.3</v>
       </c>
       <c r="BP35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ35">
         <v>14</v>
@@ -9418,7 +9418,7 @@
         <v>29</v>
       </c>
       <c r="BS35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT35">
         <v>5.9</v>
@@ -9436,13 +9436,13 @@
         <v>30</v>
       </c>
       <c r="BY35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BZ35">
         <v>22</v>
       </c>
       <c r="CA35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CB35" t="s">
         <v>209</v>
@@ -9465,16 +9465,16 @@
         <v>199</v>
       </c>
       <c r="F36">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G36">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H36">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J36">
         <v>4.1</v>
@@ -9489,7 +9489,7 @@
         <v>1.04</v>
       </c>
       <c r="N36">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O36">
         <v>1.2</v>
@@ -9498,25 +9498,25 @@
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R36">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S36">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T36">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U36">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W36">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X36">
         <v>24</v>
@@ -9528,37 +9528,37 @@
         <v>36</v>
       </c>
       <c r="AA36">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC36">
         <v>9.800000000000001</v>
       </c>
       <c r="AD36">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE36">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF36">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH36">
         <v>16</v>
       </c>
       <c r="AI36">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ36">
         <v>22</v>
       </c>
       <c r="AK36">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL36">
         <v>27</v>
@@ -9567,7 +9567,7 @@
         <v>65</v>
       </c>
       <c r="AN36">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO36">
         <v>32</v>
@@ -9579,7 +9579,7 @@
         <v>19.5</v>
       </c>
       <c r="AR36">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS36">
         <v>36</v>
@@ -9588,13 +9588,13 @@
         <v>12</v>
       </c>
       <c r="AU36">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV36">
         <v>15.5</v>
       </c>
       <c r="AW36">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AX36">
         <v>13</v>
@@ -9603,10 +9603,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA36">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB36">
         <v>20</v>
@@ -9618,13 +9618,13 @@
         <v>23</v>
       </c>
       <c r="BE36">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF36">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG36">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9642,7 +9642,7 @@
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BN36">
         <v>6.2</v>
@@ -9660,31 +9660,31 @@
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BT36">
         <v>1000</v>
       </c>
       <c r="BU36">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>8.4</v>
+        <v>2.38</v>
       </c>
       <c r="CB36" t="s">
         <v>209</v>
@@ -9713,7 +9713,7 @@
         <v>3.35</v>
       </c>
       <c r="H37">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I37">
         <v>2.44</v>
@@ -9725,13 +9725,13 @@
         <v>3.65</v>
       </c>
       <c r="L37">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M37">
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O37">
         <v>1.34</v>
@@ -9749,16 +9749,16 @@
         <v>3.55</v>
       </c>
       <c r="T37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X37">
         <v>16</v>
@@ -9776,7 +9776,7 @@
         <v>13</v>
       </c>
       <c r="AC37">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD37">
         <v>12</v>
@@ -9785,10 +9785,10 @@
         <v>29</v>
       </c>
       <c r="AF37">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG37">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH37">
         <v>22</v>
@@ -9818,58 +9818,58 @@
         <v>12</v>
       </c>
       <c r="AQ37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR37">
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AT37">
         <v>11</v>
       </c>
       <c r="AU37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV37">
         <v>10</v>
       </c>
       <c r="AW37">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX37">
         <v>19.5</v>
       </c>
       <c r="AY37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ37">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BA37">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BB37">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BC37">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BD37">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE37">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF37">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG37">
         <v>17</v>
       </c>
       <c r="BH37">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BI37">
         <v>3.05</v>
@@ -9878,31 +9878,31 @@
         <v>11.5</v>
       </c>
       <c r="BK37">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BN37">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO37">
         <v>5.5</v>
       </c>
       <c r="BP37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ37">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BR37">
         <v>48</v>
       </c>
       <c r="BS37">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BT37">
         <v>6.2</v>
@@ -9914,19 +9914,19 @@
         <v>22</v>
       </c>
       <c r="BW37">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BX37">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY37">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BZ37">
         <v>34</v>
       </c>
       <c r="CA37">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="CB37" t="s">
         <v>209</v>
@@ -9955,76 +9955,76 @@
         <v>1.13</v>
       </c>
       <c r="H38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I38">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J38">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="K38">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L38">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="M38">
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="O38">
         <v>1.05</v>
       </c>
       <c r="P38">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Q38">
         <v>1.15</v>
       </c>
       <c r="R38">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S38">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U38">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W38">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="Z38">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="AA38">
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC38">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AD38">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AE38">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AF38">
         <v>18</v>
@@ -10033,13 +10033,13 @@
         <v>18.5</v>
       </c>
       <c r="AH38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AI38">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AJ38">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK38">
         <v>15</v>
@@ -10048,28 +10048,28 @@
         <v>32</v>
       </c>
       <c r="AM38">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN38">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AO38">
         <v>190</v>
       </c>
       <c r="AP38">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AQ38">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AR38">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS38">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="AT38">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AU38">
         <v>36</v>
@@ -10078,22 +10078,22 @@
         <v>38</v>
       </c>
       <c r="AW38">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX38">
         <v>15.5</v>
       </c>
       <c r="AY38">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ38">
         <v>36</v>
       </c>
       <c r="BA38">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="BB38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC38">
         <v>13</v>
@@ -10102,10 +10102,10 @@
         <v>21</v>
       </c>
       <c r="BE38">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BF38">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="BG38">
         <v>85</v>
@@ -10117,19 +10117,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BJ38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK38">
         <v>11</v>
       </c>
       <c r="BL38">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM38">
         <v>21</v>
       </c>
       <c r="BN38">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO38">
         <v>4.6</v>
@@ -10141,13 +10141,13 @@
         <v>5.2</v>
       </c>
       <c r="BR38">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BS38">
         <v>8.199999999999999</v>
       </c>
       <c r="BT38">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BU38">
         <v>19.5</v>
@@ -10156,7 +10156,7 @@
         <v>120</v>
       </c>
       <c r="BW38">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BX38">
         <v>65</v>
@@ -10168,7 +10168,7 @@
         <v>4</v>
       </c>
       <c r="CA38">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CB38" t="s">
         <v>209</v>
@@ -10191,25 +10191,25 @@
         <v>202</v>
       </c>
       <c r="F39">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G39">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="I39">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J39">
         <v>4</v>
       </c>
       <c r="K39">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L39">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M39">
         <v>1.07</v>
@@ -10221,10 +10221,10 @@
         <v>1.33</v>
       </c>
       <c r="P39">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q39">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R39">
         <v>1.36</v>
@@ -10239,25 +10239,25 @@
         <v>1.99</v>
       </c>
       <c r="V39">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
         <v>15</v>
       </c>
       <c r="Y39">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z39">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA39">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AB39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC39">
         <v>9</v>
@@ -10269,7 +10269,7 @@
         <v>19</v>
       </c>
       <c r="AF39">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG39">
         <v>22</v>
@@ -10281,10 +10281,10 @@
         <v>44</v>
       </c>
       <c r="AJ39">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AK39">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL39">
         <v>85</v>
@@ -10299,19 +10299,19 @@
         <v>11.5</v>
       </c>
       <c r="AP39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR39">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS39">
+        <v>15.5</v>
+      </c>
+      <c r="AT39">
         <v>16</v>
-      </c>
-      <c r="AT39">
-        <v>15.5</v>
       </c>
       <c r="AU39">
         <v>8</v>
@@ -10323,31 +10323,31 @@
         <v>16.5</v>
       </c>
       <c r="AX39">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY39">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA39">
         <v>32</v>
       </c>
       <c r="BB39">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC39">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="BD39">
+        <v>15.5</v>
+      </c>
+      <c r="BE39">
         <v>16</v>
       </c>
-      <c r="BE39">
-        <v>17</v>
-      </c>
       <c r="BF39">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="BG39">
         <v>10</v>
@@ -10439,13 +10439,13 @@
         <v>1.47</v>
       </c>
       <c r="H40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>15</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K40">
         <v>5.2</v>
@@ -10454,25 +10454,25 @@
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N40">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O40">
         <v>1.36</v>
       </c>
       <c r="P40">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q40">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S40">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="T40">
         <v>2.36</v>
@@ -10541,58 +10541,58 @@
         <v>620</v>
       </c>
       <c r="AP40">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ40">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AR40">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS40">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT40">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU40">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV40">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW40">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX40">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AY40">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ40">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA40">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB40">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BC40">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD40">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE40">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF40">
         <v>6.6</v>
       </c>
       <c r="BG40">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10681,13 +10681,13 @@
         <v>1000</v>
       </c>
       <c r="H41">
-        <v>2.1</v>
+        <v>1.05</v>
       </c>
       <c r="I41">
         <v>1000</v>
       </c>
       <c r="J41">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K41">
         <v>950</v>
@@ -10699,22 +10699,22 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O41">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R41">
         <v>1.18</v>
       </c>
       <c r="S41">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10726,7 +10726,7 @@
         <v>1.02</v>
       </c>
       <c r="W41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10783,58 +10783,58 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10917,25 +10917,25 @@
         <v>205</v>
       </c>
       <c r="F42">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G42">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H42">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I42">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J42">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K42">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L42">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M42">
         <v>1.14</v>
@@ -10947,10 +10947,10 @@
         <v>1.59</v>
       </c>
       <c r="P42">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q42">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R42">
         <v>1.16</v>
@@ -10959,16 +10959,16 @@
         <v>6</v>
       </c>
       <c r="T42">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U42">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -10980,7 +10980,7 @@
         <v>27</v>
       </c>
       <c r="AA42">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AB42">
         <v>8.199999999999999</v>
@@ -11004,10 +11004,10 @@
         <v>27</v>
       </c>
       <c r="AI42">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ42">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK42">
         <v>46</v>
@@ -11019,64 +11019,64 @@
         <v>270</v>
       </c>
       <c r="AN42">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO42">
         <v>130</v>
       </c>
       <c r="AP42">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="AQ42">
-        <v>8.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AR42">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS42">
         <v>4.8</v>
       </c>
       <c r="AT42">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AU42">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AV42">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="AW42">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX42">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="AY42">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AZ42">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BA42">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB42">
         <v>4.5</v>
       </c>
       <c r="BC42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD42">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE42">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF42">
         <v>4.6</v>
       </c>
       <c r="BG42">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11159,64 +11159,64 @@
         <v>206</v>
       </c>
       <c r="F43">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="G43">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="J43">
         <v>3.55</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N43">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O43">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P43">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q43">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R43">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S43">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="T43">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U43">
         <v>1.89</v>
       </c>
       <c r="V43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W43">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="X43">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y43">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z43">
         <v>55</v>
@@ -11225,10 +11225,10 @@
         <v>170</v>
       </c>
       <c r="AB43">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC43">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD43">
         <v>26</v>
@@ -11237,7 +11237,7 @@
         <v>90</v>
       </c>
       <c r="AF43">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG43">
         <v>11.5</v>
@@ -11267,118 +11267,118 @@
         <v>110</v>
       </c>
       <c r="AP43">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ43">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR43">
+        <v>5.6</v>
+      </c>
+      <c r="AS43">
+        <v>6</v>
+      </c>
+      <c r="AT43">
+        <v>3.75</v>
+      </c>
+      <c r="AU43">
+        <v>3.95</v>
+      </c>
+      <c r="AV43">
         <v>5</v>
       </c>
-      <c r="AS43">
+      <c r="AW43">
+        <v>5.9</v>
+      </c>
+      <c r="AX43">
+        <v>4</v>
+      </c>
+      <c r="AY43">
+        <v>4</v>
+      </c>
+      <c r="AZ43">
+        <v>5</v>
+      </c>
+      <c r="BA43">
+        <v>5.8</v>
+      </c>
+      <c r="BB43">
+        <v>4.7</v>
+      </c>
+      <c r="BC43">
+        <v>4.8</v>
+      </c>
+      <c r="BD43">
         <v>5.4</v>
       </c>
-      <c r="AT43">
-        <v>3.55</v>
-      </c>
-      <c r="AU43">
-        <v>3.7</v>
-      </c>
-      <c r="AV43">
-        <v>4.6</v>
-      </c>
-      <c r="AW43">
-        <v>5.2</v>
-      </c>
-      <c r="AX43">
-        <v>3.8</v>
-      </c>
-      <c r="AY43">
-        <v>3.75</v>
-      </c>
-      <c r="AZ43">
-        <v>4.5</v>
-      </c>
-      <c r="BA43">
-        <v>5.2</v>
-      </c>
-      <c r="BB43">
-        <v>4.3</v>
-      </c>
-      <c r="BC43">
-        <v>4.3</v>
-      </c>
-      <c r="BD43">
-        <v>4.9</v>
-      </c>
       <c r="BE43">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF43">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BG43">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH43">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BI43">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BJ43">
         <v>12</v>
       </c>
       <c r="BK43">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BN43">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO43">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BP43">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ43">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BR43">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS43">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BT43">
         <v>11</v>
       </c>
       <c r="BU43">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV43">
         <v>60</v>
       </c>
       <c r="BW43">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BZ43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CA43">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="CB43" t="s">
         <v>209</v>
@@ -11401,7 +11401,7 @@
         <v>207</v>
       </c>
       <c r="F44">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G44">
         <v>1.9</v>
@@ -11416,7 +11416,7 @@
         <v>3.5</v>
       </c>
       <c r="K44">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L44">
         <v>1.45</v>
@@ -11566,22 +11566,22 @@
         <v>1000</v>
       </c>
       <c r="BI44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BJ44">
         <v>1000</v>
       </c>
       <c r="BK44">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BL44">
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BN44">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO44">
         <v>1.42</v>
@@ -11590,37 +11590,37 @@
         <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BR44">
         <v>1000</v>
       </c>
       <c r="BS44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BT44">
         <v>1000</v>
       </c>
       <c r="BU44">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BV44">
         <v>1000</v>
       </c>
       <c r="BW44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BX44">
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BZ44">
         <v>1000</v>
       </c>
       <c r="CA44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CB44" t="s">
         <v>209</v>
@@ -11685,10 +11685,10 @@
         <v>5.5</v>
       </c>
       <c r="T45">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U45">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V45">
         <v>1.25</v>
@@ -11715,7 +11715,7 @@
         <v>7.4</v>
       </c>
       <c r="AD45">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE45">
         <v>110</v>
@@ -11757,7 +11757,7 @@
         <v>11</v>
       </c>
       <c r="AR45">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS45">
         <v>9.4</v>
@@ -11772,7 +11772,7 @@
         <v>18.5</v>
       </c>
       <c r="AW45">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX45">
         <v>10</v>
@@ -11784,16 +11784,16 @@
         <v>20</v>
       </c>
       <c r="BA45">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB45">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC45">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD45">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE45">
         <v>9.6</v>
@@ -11802,7 +11802,7 @@
         <v>18.5</v>
       </c>
       <c r="BG45">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH45">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -574,7 +574,7 @@
     <t>Cobreloa Calama</t>
   </si>
   <si>
-    <t>2026-09-10 03:33:39</t>
+    <t>2026-09-10 05:51:16</t>
   </si>
 </sst>
 </file>
@@ -1168,22 +1168,22 @@
         <v>152</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G2">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I2">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.43</v>
@@ -1192,22 +1192,22 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
         <v>1.77</v>
@@ -1216,82 +1216,82 @@
         <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W2">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X2">
         <v>14</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC2">
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2">
+        <v>24</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>18.5</v>
+      </c>
+      <c r="AI2">
+        <v>40</v>
+      </c>
+      <c r="AJ2">
+        <v>65</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>200</v>
+      </c>
+      <c r="AN2">
+        <v>40</v>
+      </c>
+      <c r="AO2">
         <v>23</v>
       </c>
-      <c r="AG2">
+      <c r="AP2">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2">
         <v>14</v>
       </c>
-      <c r="AH2">
-        <v>18</v>
-      </c>
-      <c r="AI2">
-        <v>42</v>
-      </c>
-      <c r="AJ2">
-        <v>60</v>
-      </c>
-      <c r="AK2">
-        <v>38</v>
-      </c>
-      <c r="AL2">
-        <v>46</v>
-      </c>
-      <c r="AM2">
-        <v>390</v>
-      </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>25</v>
       </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <v>9</v>
-      </c>
-      <c r="AR2">
-        <v>14.5</v>
-      </c>
-      <c r="AS2">
-        <v>26</v>
-      </c>
       <c r="AT2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1300,94 +1300,94 @@
         <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC2">
         <v>27</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2">
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>186</v>
@@ -1410,22 +1410,22 @@
         <v>153</v>
       </c>
       <c r="F3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I3">
         <v>1.33</v>
       </c>
       <c r="J3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L3">
         <v>1.2</v>
@@ -1434,40 +1434,40 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
         <v>4</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>13</v>
@@ -1488,148 +1488,148 @@
         <v>14</v>
       </c>
       <c r="AF3">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AG3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AH3">
         <v>28</v>
       </c>
       <c r="AI3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ3">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AK3">
         <v>190</v>
       </c>
       <c r="AL3">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AN3">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AO3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AP3">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>46</v>
       </c>
       <c r="AU3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV3">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX3">
         <v>80</v>
       </c>
       <c r="AY3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>22</v>
       </c>
       <c r="BB3">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="BC3">
         <v>75</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BG3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BH3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BN3">
         <v>15.5</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU3">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BV3">
         <v>8.4</v>
       </c>
       <c r="BW3">
+        <v>5.8</v>
+      </c>
+      <c r="BX3">
+        <v>19</v>
+      </c>
+      <c r="BY3">
+        <v>4.6</v>
+      </c>
+      <c r="BZ3">
+        <v>8.4</v>
+      </c>
+      <c r="CA3">
         <v>5.7</v>
-      </c>
-      <c r="BX3">
-        <v>17.5</v>
-      </c>
-      <c r="BY3">
-        <v>4.7</v>
-      </c>
-      <c r="BZ3">
-        <v>8.6</v>
-      </c>
-      <c r="CA3">
-        <v>3.65</v>
       </c>
       <c r="CB3" t="s">
         <v>186</v>
@@ -1655,49 +1655,49 @@
         <v>1.53</v>
       </c>
       <c r="G4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K4">
         <v>5.4</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="O4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P4">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="Q4">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R4">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="S4">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="T4">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1706,7 +1706,7 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y4">
         <v>32</v>
@@ -1715,112 +1715,112 @@
         <v>55</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB4">
+        <v>12.5</v>
+      </c>
+      <c r="AC4">
         <v>13</v>
       </c>
-      <c r="AC4">
-        <v>13.5</v>
-      </c>
       <c r="AD4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
         <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
         <v>15.5</v>
       </c>
       <c r="AL4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM4">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP4">
+        <v>23</v>
+      </c>
+      <c r="AQ4">
         <v>25</v>
       </c>
-      <c r="AQ4">
-        <v>26</v>
-      </c>
       <c r="AR4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU4">
         <v>11</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4">
         <v>46</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC4">
         <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE4">
         <v>55</v>
       </c>
       <c r="BF4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BH4">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BI4">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK4">
         <v>5.1</v>
@@ -1829,22 +1829,22 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS4">
         <v>7</v>
@@ -1853,25 +1853,25 @@
         <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BW4">
         <v>8.6</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CA4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="s">
         <v>186</v>
@@ -1894,28 +1894,28 @@
         <v>155</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="G5">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="H5">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
         <v>6.2</v>
@@ -1927,139 +1927,139 @@
         <v>2.72</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S5">
         <v>2.34</v>
       </c>
       <c r="T5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U5">
         <v>2.76</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="X5">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AJ5">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AL5">
+        <v>26</v>
+      </c>
+      <c r="AM5">
         <v>55</v>
       </c>
-      <c r="AM5">
-        <v>580</v>
-      </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS5">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AT5">
         <v>14.5</v>
       </c>
       <c r="AU5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AX5">
+        <v>16.5</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>13</v>
+      </c>
+      <c r="BA5">
+        <v>27</v>
+      </c>
+      <c r="BB5">
+        <v>26</v>
+      </c>
+      <c r="BC5">
         <v>17.5</v>
       </c>
-      <c r="AY5">
-        <v>11</v>
-      </c>
-      <c r="AZ5">
-        <v>12.5</v>
-      </c>
-      <c r="BA5">
+      <c r="BD5">
+        <v>22</v>
+      </c>
+      <c r="BE5">
+        <v>44</v>
+      </c>
+      <c r="BF5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG5">
         <v>16</v>
-      </c>
-      <c r="BB5">
-        <v>15</v>
-      </c>
-      <c r="BC5">
-        <v>10.5</v>
-      </c>
-      <c r="BD5">
-        <v>14.5</v>
-      </c>
-      <c r="BE5">
-        <v>10.5</v>
-      </c>
-      <c r="BF5">
-        <v>11</v>
-      </c>
-      <c r="BG5">
-        <v>13</v>
       </c>
       <c r="BH5">
         <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BJ5">
         <v>8.4</v>
@@ -2071,49 +2071,49 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="s">
         <v>186</v>
@@ -2136,22 +2136,22 @@
         <v>156</v>
       </c>
       <c r="F6">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2163,7 +2163,7 @@
         <v>5.5</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
         <v>2.54</v>
@@ -2172,43 +2172,43 @@
         <v>1.59</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
         <v>1.11</v>
       </c>
       <c r="W6">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z6">
         <v>450</v>
       </c>
       <c r="AA6">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="AB6">
         <v>11</v>
       </c>
       <c r="AC6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE6">
         <v>400</v>
@@ -2220,25 +2220,25 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AJ6">
         <v>13</v>
       </c>
       <c r="AK6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AO6">
         <v>160</v>
@@ -2247,37 +2247,37 @@
         <v>20</v>
       </c>
       <c r="AQ6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AR6">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6">
         <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AW6">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="AX6">
         <v>7.8</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BB6">
         <v>9.800000000000001</v>
@@ -2286,25 +2286,25 @@
         <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BH6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
         <v>7.8</v>
@@ -2313,49 +2313,49 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BS6">
         <v>4.9</v>
       </c>
       <c r="BT6">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BU6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BV6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BW6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BZ6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA6">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>186</v>
@@ -2378,7 +2378,7 @@
         <v>157</v>
       </c>
       <c r="F7">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
         <v>2.4</v>
@@ -2387,217 +2387,217 @@
         <v>3.05</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="P7">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
         <v>1.73</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AD7">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH7">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AP7">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="AR7">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="AS7">
         <v>4.9</v>
       </c>
       <c r="AT7">
-        <v>1.32</v>
+        <v>3.65</v>
       </c>
       <c r="AU7">
-        <v>1.24</v>
+        <v>3.4</v>
       </c>
       <c r="AV7">
-        <v>1.34</v>
+        <v>4</v>
       </c>
       <c r="AW7">
-        <v>1.34</v>
+        <v>4.7</v>
       </c>
       <c r="AX7">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="AY7">
-        <v>1.32</v>
+        <v>3.75</v>
       </c>
       <c r="AZ7">
-        <v>1.33</v>
+        <v>4.1</v>
       </c>
       <c r="BA7">
         <v>4.9</v>
       </c>
       <c r="BB7">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="BC7">
-        <v>1.33</v>
+        <v>4.4</v>
       </c>
       <c r="BD7">
-        <v>1.34</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>1.36</v>
+        <v>5</v>
       </c>
       <c r="BF7">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>4.7</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB7" t="s">
         <v>186</v>
@@ -2620,22 +2620,22 @@
         <v>158</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="G8">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="H8">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2644,202 +2644,202 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
         <v>4</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="U8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="X8">
         <v>12</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA8">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
+        <v>32</v>
+      </c>
+      <c r="AO8">
+        <v>55</v>
+      </c>
+      <c r="AP8">
+        <v>9.6</v>
+      </c>
+      <c r="AQ8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR8">
+        <v>18</v>
+      </c>
+      <c r="AS8">
+        <v>40</v>
+      </c>
+      <c r="AT8">
+        <v>8</v>
+      </c>
+      <c r="AU8">
+        <v>6.4</v>
+      </c>
+      <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
+        <v>26</v>
+      </c>
+      <c r="AX8">
+        <v>13.5</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>16</v>
+      </c>
+      <c r="BA8">
         <v>36</v>
       </c>
-      <c r="AO8">
-        <v>40</v>
-      </c>
-      <c r="AP8">
-        <v>5.1</v>
-      </c>
-      <c r="AQ8">
-        <v>4.9</v>
-      </c>
-      <c r="AR8">
-        <v>6</v>
-      </c>
-      <c r="AS8">
-        <v>7.6</v>
-      </c>
-      <c r="AT8">
-        <v>4.8</v>
-      </c>
-      <c r="AU8">
-        <v>4.2</v>
-      </c>
-      <c r="AV8">
-        <v>5.5</v>
-      </c>
-      <c r="AW8">
-        <v>7.2</v>
-      </c>
-      <c r="AX8">
-        <v>6</v>
-      </c>
-      <c r="AY8">
-        <v>5.3</v>
-      </c>
-      <c r="AZ8">
-        <v>6</v>
-      </c>
-      <c r="BA8">
-        <v>7.6</v>
-      </c>
       <c r="BB8">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BC8">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>8.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BG8">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BH8">
         <v>3.2</v>
       </c>
       <c r="BI8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
         <v>7</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BW8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8">
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>186</v>
@@ -2862,43 +2862,43 @@
         <v>159</v>
       </c>
       <c r="F9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
         <v>1.83</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>3.15</v>
@@ -2907,46 +2907,46 @@
         <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X9">
         <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z9">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
+        <v>15</v>
+      </c>
+      <c r="AE9">
+        <v>120</v>
+      </c>
+      <c r="AF9">
         <v>15.5</v>
-      </c>
-      <c r="AE9">
-        <v>90</v>
-      </c>
-      <c r="AF9">
-        <v>15</v>
       </c>
       <c r="AG9">
         <v>11</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>150</v>
@@ -2955,19 +2955,19 @@
         <v>32</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL9">
         <v>44</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP9">
         <v>15</v>
@@ -2976,13 +2976,13 @@
         <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9">
         <v>7.6</v>
@@ -3003,64 +3003,64 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE9">
         <v>60</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH9">
         <v>3.75</v>
       </c>
       <c r="BI9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BK9">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU9">
         <v>6</v>
@@ -3069,19 +3069,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>186</v>
@@ -3104,94 +3104,94 @@
         <v>160</v>
       </c>
       <c r="F10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="G10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>1.09</v>
       </c>
       <c r="P10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="T10">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V10">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z10">
         <v>12.5</v>
       </c>
       <c r="AA10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB10">
         <v>90</v>
       </c>
       <c r="AC10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD10">
         <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF10">
         <v>210</v>
       </c>
       <c r="AG10">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3200,130 +3200,130 @@
         <v>250</v>
       </c>
       <c r="AL10">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AM10">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AN10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AO10">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AP10">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR10">
         <v>10</v>
       </c>
       <c r="AS10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX10">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY10">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AZ10">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
         <v>23</v>
       </c>
       <c r="BB10">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC10">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD10">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE10">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="BH10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BI10">
         <v>4.8</v>
       </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BK10">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BL10">
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BN10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BO10">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BQ10">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BR10">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BS10">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BT10">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BU10">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BV10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BW10">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BX10">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BY10">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BZ10">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CA10">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB10" t="s">
         <v>186</v>
@@ -3346,52 +3346,52 @@
         <v>161</v>
       </c>
       <c r="F11">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G11">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="H11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I11">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
         <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S11">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3400,13 +3400,13 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA11">
         <v>900</v>
@@ -3418,37 +3418,37 @@
         <v>11.5</v>
       </c>
       <c r="AD11">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL11">
         <v>27</v>
       </c>
       <c r="AM11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN11">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO11">
         <v>55</v>
@@ -3457,115 +3457,115 @@
         <v>20</v>
       </c>
       <c r="AQ11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
         <v>9</v>
       </c>
       <c r="AZ11">
+        <v>15.5</v>
+      </c>
+      <c r="BA11">
+        <v>32</v>
+      </c>
+      <c r="BB11">
         <v>15</v>
-      </c>
-      <c r="BA11">
-        <v>30</v>
-      </c>
-      <c r="BB11">
-        <v>16.5</v>
       </c>
       <c r="BC11">
         <v>14</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BH11">
         <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO11">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ11">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU11">
         <v>5.4</v>
       </c>
       <c r="BV11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW11">
         <v>10</v>
       </c>
       <c r="BX11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>14.5</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
         <v>186</v>
@@ -3588,16 +3588,16 @@
         <v>162</v>
       </c>
       <c r="F12">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G12">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H12">
+        <v>6.4</v>
+      </c>
+      <c r="I12">
         <v>6.6</v>
-      </c>
-      <c r="I12">
-        <v>6.8</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -3612,34 +3612,34 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O12">
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R12">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
         <v>1.63</v>
       </c>
       <c r="U12">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X12">
         <v>32</v>
@@ -3651,7 +3651,7 @@
         <v>60</v>
       </c>
       <c r="AA12">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12">
         <v>13.5</v>
@@ -3660,13 +3660,13 @@
         <v>12</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -3678,31 +3678,31 @@
         <v>60</v>
       </c>
       <c r="AJ12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK12">
         <v>14</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN12">
         <v>5</v>
       </c>
       <c r="AO12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP12">
         <v>30</v>
       </c>
       <c r="AQ12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS12">
         <v>110</v>
@@ -3717,16 +3717,16 @@
         <v>22</v>
       </c>
       <c r="AW12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
         <v>50</v>
@@ -3753,49 +3753,49 @@
         <v>4.8</v>
       </c>
       <c r="BI12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK12">
         <v>8.6</v>
       </c>
       <c r="BL12">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BM12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BN12">
         <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BS12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BT12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU12">
         <v>9.199999999999999</v>
       </c>
       <c r="BV12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW12">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX12">
         <v>40</v>
@@ -3804,7 +3804,7 @@
         <v>34</v>
       </c>
       <c r="BZ12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA12">
         <v>9.800000000000001</v>
@@ -3830,46 +3830,46 @@
         <v>163</v>
       </c>
       <c r="F13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
         <v>2.16</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S13">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="T13">
         <v>1.6</v>
@@ -3878,13 +3878,13 @@
         <v>2.6</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W13">
         <v>1.37</v>
       </c>
       <c r="X13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y13">
         <v>13</v>
@@ -3899,13 +3899,13 @@
         <v>18</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF13">
         <v>28</v>
@@ -3932,34 +3932,34 @@
         <v>65</v>
       </c>
       <c r="AN13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR13">
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13">
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX13">
         <v>26</v>
@@ -3974,7 +3974,7 @@
         <v>26</v>
       </c>
       <c r="BB13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC13">
         <v>34</v>
@@ -3986,19 +3986,19 @@
         <v>60</v>
       </c>
       <c r="BF13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BG13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK13">
         <v>7.8</v>
@@ -4007,28 +4007,28 @@
         <v>100</v>
       </c>
       <c r="BM13">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BN13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BQ13">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BT13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU13">
         <v>4.8</v>
@@ -4037,16 +4037,16 @@
         <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA13">
         <v>15.5</v>
@@ -4072,28 +4072,28 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="H14">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L14">
         <v>1.39</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
         <v>4.1</v>
@@ -4114,82 +4114,82 @@
         <v>3.35</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="X14">
+        <v>16</v>
+      </c>
+      <c r="Y14">
         <v>16.5</v>
       </c>
-      <c r="Y14">
-        <v>19</v>
-      </c>
       <c r="Z14">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AA14">
         <v>300</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE14">
         <v>140</v>
       </c>
       <c r="AF14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI14">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AJ14">
+        <v>23</v>
+      </c>
+      <c r="AK14">
         <v>21</v>
       </c>
-      <c r="AK14">
-        <v>20</v>
-      </c>
       <c r="AL14">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM14">
         <v>190</v>
       </c>
       <c r="AN14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO14">
-        <v>590</v>
+        <v>330</v>
       </c>
       <c r="AP14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS14">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AT14">
         <v>8.6</v>
@@ -4198,52 +4198,52 @@
         <v>7.8</v>
       </c>
       <c r="AV14">
+        <v>15</v>
+      </c>
+      <c r="AW14">
+        <v>42</v>
+      </c>
+      <c r="AX14">
+        <v>11</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
         <v>16</v>
       </c>
-      <c r="AW14">
-        <v>40</v>
-      </c>
-      <c r="AX14">
-        <v>10.5</v>
-      </c>
-      <c r="AY14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14">
-        <v>16.5</v>
-      </c>
       <c r="BA14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB14">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD14">
         <v>28</v>
       </c>
       <c r="BE14">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF14">
         <v>10.5</v>
       </c>
       <c r="BG14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH14">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BI14">
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4252,43 +4252,43 @@
         <v>10</v>
       </c>
       <c r="BN14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO14">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP14">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU14">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX14">
+        <v>42</v>
+      </c>
+      <c r="BY14">
         <v>8.6</v>
       </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>9</v>
-      </c>
       <c r="BZ14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA14">
         <v>7.4</v>
@@ -4314,28 +4314,28 @@
         <v>165</v>
       </c>
       <c r="F15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I15">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
         <v>5</v>
@@ -4344,34 +4344,34 @@
         <v>1.23</v>
       </c>
       <c r="P15">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U15">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z15">
         <v>15.5</v>
@@ -4380,19 +4380,19 @@
         <v>26</v>
       </c>
       <c r="AB15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD15">
         <v>11</v>
       </c>
       <c r="AE15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG15">
         <v>15.5</v>
@@ -4401,49 +4401,49 @@
         <v>16</v>
       </c>
       <c r="AI15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ15">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK15">
         <v>38</v>
       </c>
       <c r="AL15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM15">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AN15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR15">
         <v>13.5</v>
       </c>
       <c r="AS15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT15">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU15">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV15">
         <v>9.800000000000001</v>
       </c>
       <c r="AW15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX15">
         <v>23</v>
@@ -4470,70 +4470,70 @@
         <v>32</v>
       </c>
       <c r="BF15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG15">
+        <v>10</v>
+      </c>
+      <c r="BH15">
+        <v>4.8</v>
+      </c>
+      <c r="BI15">
+        <v>3.7</v>
+      </c>
+      <c r="BJ15">
         <v>10.5</v>
       </c>
-      <c r="BH15">
-        <v>4.7</v>
-      </c>
-      <c r="BI15">
-        <v>3.65</v>
-      </c>
-      <c r="BJ15">
-        <v>9</v>
-      </c>
       <c r="BK15">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="BL15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM15">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BN15">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BO15">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BQ15">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BR15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS15">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BT15">
         <v>6.2</v>
       </c>
       <c r="BU15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BW15">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BX15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY15">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="BZ15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="CA15">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="CB15" t="s">
         <v>186</v>
@@ -4556,22 +4556,22 @@
         <v>166</v>
       </c>
       <c r="F16">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="G16">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I16">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K16">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>1.38</v>
@@ -4589,145 +4589,145 @@
         <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
         <v>3.2</v>
       </c>
       <c r="T16">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="W16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
         <v>11</v>
       </c>
       <c r="Z16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
         <v>11</v>
       </c>
       <c r="AE16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF16">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AG16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK16">
+        <v>100</v>
+      </c>
+      <c r="AL16">
+        <v>110</v>
+      </c>
+      <c r="AM16">
         <v>190</v>
       </c>
-      <c r="AL16">
-        <v>250</v>
-      </c>
-      <c r="AM16">
-        <v>580</v>
-      </c>
       <c r="AN16">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AO16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS16">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT16">
         <v>13.5</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX16">
         <v>24</v>
       </c>
       <c r="AY16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ16">
         <v>15</v>
       </c>
       <c r="BA16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB16">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BC16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD16">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE16">
-        <v>9.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BF16">
         <v>27</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16">
         <v>9.6</v>
       </c>
       <c r="BK16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4739,7 +4739,7 @@
         <v>7.6</v>
       </c>
       <c r="BO16">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BP16">
         <v>32</v>
@@ -4748,7 +4748,7 @@
         <v>8</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS16">
         <v>8.4</v>
@@ -4760,22 +4760,22 @@
         <v>4.3</v>
       </c>
       <c r="BV16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW16">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY16">
         <v>7.6</v>
       </c>
       <c r="BZ16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA16">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>186</v>
@@ -4798,67 +4798,67 @@
         <v>167</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G17">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="H17">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="I17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="J17">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K17">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O17">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="S17">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U17">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="V17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Y17">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z17">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA17">
         <v>10.5</v>
@@ -4867,154 +4867,154 @@
         <v>55</v>
       </c>
       <c r="AC17">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD17">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE17">
         <v>14.5</v>
       </c>
       <c r="AF17">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AG17">
         <v>55</v>
       </c>
       <c r="AH17">
+        <v>32</v>
+      </c>
+      <c r="AI17">
+        <v>38</v>
+      </c>
+      <c r="AJ17">
+        <v>600</v>
+      </c>
+      <c r="AK17">
+        <v>230</v>
+      </c>
+      <c r="AL17">
+        <v>170</v>
+      </c>
+      <c r="AM17">
+        <v>200</v>
+      </c>
+      <c r="AN17">
+        <v>270</v>
+      </c>
+      <c r="AO17">
+        <v>4.7</v>
+      </c>
+      <c r="AP17">
+        <v>23</v>
+      </c>
+      <c r="AQ17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR17">
+        <v>7</v>
+      </c>
+      <c r="AS17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT17">
         <v>36</v>
       </c>
-      <c r="AI17">
-        <v>44</v>
-      </c>
-      <c r="AJ17">
-        <v>520</v>
-      </c>
-      <c r="AK17">
-        <v>220</v>
-      </c>
-      <c r="AL17">
-        <v>160</v>
-      </c>
-      <c r="AM17">
-        <v>180</v>
-      </c>
-      <c r="AN17">
-        <v>290</v>
-      </c>
-      <c r="AO17">
-        <v>4.2</v>
-      </c>
-      <c r="AP17">
-        <v>11</v>
-      </c>
-      <c r="AQ17">
-        <v>9.6</v>
-      </c>
-      <c r="AR17">
-        <v>7.2</v>
-      </c>
-      <c r="AS17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT17">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV17">
         <v>10</v>
       </c>
       <c r="AW17">
+        <v>12</v>
+      </c>
+      <c r="AX17">
         <v>11</v>
       </c>
-      <c r="AX17">
-        <v>7.6</v>
-      </c>
       <c r="AY17">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AZ17">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA17">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BB17">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BC17">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BD17">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="BE17">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BF17">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BG17">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BH17">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BI17">
         <v>3.65</v>
       </c>
       <c r="BJ17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BO17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP17">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BS17">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT17">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BU17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV17">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BW17">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BX17">
         <v>23</v>
       </c>
       <c r="BY17">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BZ17">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CA17">
         <v>7</v>
@@ -5040,91 +5040,91 @@
         <v>168</v>
       </c>
       <c r="F18">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="G18">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>2.12</v>
       </c>
       <c r="I18">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L18">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q18">
+        <v>1.95</v>
+      </c>
+      <c r="R18">
+        <v>1.4</v>
+      </c>
+      <c r="S18">
+        <v>3.2</v>
+      </c>
+      <c r="T18">
+        <v>1.75</v>
+      </c>
+      <c r="U18">
+        <v>1.96</v>
+      </c>
+      <c r="V18">
         <v>1.83</v>
       </c>
-      <c r="R18">
-        <v>1.44</v>
-      </c>
-      <c r="S18">
-        <v>3.05</v>
-      </c>
-      <c r="T18">
-        <v>1.68</v>
-      </c>
-      <c r="U18">
-        <v>2.24</v>
-      </c>
-      <c r="V18">
-        <v>1.81</v>
-      </c>
       <c r="W18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X18">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z18">
         <v>16.5</v>
       </c>
       <c r="AA18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB18">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AC18">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18">
         <v>12.5</v>
       </c>
       <c r="AE18">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI18">
         <v>38</v>
@@ -5133,7 +5133,7 @@
         <v>75</v>
       </c>
       <c r="AK18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL18">
         <v>55</v>
@@ -5148,118 +5148,118 @@
         <v>15</v>
       </c>
       <c r="AP18">
+        <v>14</v>
+      </c>
+      <c r="AQ18">
+        <v>9.4</v>
+      </c>
+      <c r="AR18">
+        <v>12</v>
+      </c>
+      <c r="AS18">
+        <v>15.5</v>
+      </c>
+      <c r="AT18">
+        <v>12.5</v>
+      </c>
+      <c r="AU18">
+        <v>7</v>
+      </c>
+      <c r="AV18">
+        <v>9.6</v>
+      </c>
+      <c r="AW18">
+        <v>19.5</v>
+      </c>
+      <c r="AX18">
+        <v>15</v>
+      </c>
+      <c r="AY18">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18">
         <v>14.5</v>
       </c>
-      <c r="AQ18">
-        <v>9.6</v>
-      </c>
-      <c r="AR18">
-        <v>12.5</v>
-      </c>
-      <c r="AS18">
-        <v>5.2</v>
-      </c>
-      <c r="AT18">
-        <v>13</v>
-      </c>
-      <c r="AU18">
-        <v>7.4</v>
-      </c>
-      <c r="AV18">
-        <v>9.4</v>
-      </c>
-      <c r="AW18">
-        <v>18.5</v>
-      </c>
-      <c r="AX18">
-        <v>10.5</v>
-      </c>
-      <c r="AY18">
-        <v>13</v>
-      </c>
-      <c r="AZ18">
-        <v>14</v>
-      </c>
       <c r="BA18">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BB18">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC18">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BD18">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BE18">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF18">
         <v>9.800000000000001</v>
       </c>
       <c r="BG18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BL18">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BN18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO18">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP18">
         <v>32</v>
       </c>
       <c r="BQ18">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR18">
         <v>42</v>
       </c>
       <c r="BS18">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BT18">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU18">
         <v>4.1</v>
       </c>
       <c r="BV18">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW18">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BX18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY18">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BZ18">
         <v>25</v>
       </c>
       <c r="CA18">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB18" t="s">
         <v>186</v>
@@ -5282,19 +5282,19 @@
         <v>169</v>
       </c>
       <c r="F19">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="H19">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I19">
+        <v>4.3</v>
+      </c>
+      <c r="J19">
         <v>3.95</v>
-      </c>
-      <c r="J19">
-        <v>3.9</v>
       </c>
       <c r="K19">
         <v>4.1</v>
@@ -5303,49 +5303,49 @@
         <v>1.34</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
         <v>4.9</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R19">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S19">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="X19">
         <v>22</v>
       </c>
       <c r="Y19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z19">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA19">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB19">
         <v>12</v>
@@ -5354,52 +5354,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD19">
+        <v>17.5</v>
+      </c>
+      <c r="AE19">
+        <v>46</v>
+      </c>
+      <c r="AF19">
+        <v>13.5</v>
+      </c>
+      <c r="AG19">
+        <v>10.5</v>
+      </c>
+      <c r="AH19">
         <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>42</v>
-      </c>
-      <c r="AF19">
-        <v>14.5</v>
-      </c>
-      <c r="AG19">
-        <v>11</v>
-      </c>
-      <c r="AH19">
-        <v>16.5</v>
       </c>
       <c r="AI19">
         <v>46</v>
       </c>
       <c r="AJ19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL19">
         <v>30</v>
       </c>
       <c r="AM19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN19">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO19">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AP19">
         <v>18</v>
       </c>
       <c r="AQ19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS19">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT19">
         <v>10.5</v>
@@ -5408,10 +5408,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX19">
         <v>12</v>
@@ -5420,7 +5420,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
         <v>34</v>
@@ -5429,79 +5429,79 @@
         <v>20</v>
       </c>
       <c r="BC19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD19">
         <v>24</v>
       </c>
       <c r="BE19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF19">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BH19">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI19">
         <v>3.6</v>
       </c>
       <c r="BJ19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK19">
         <v>5.4</v>
       </c>
       <c r="BL19">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM19">
         <v>11</v>
       </c>
       <c r="BN19">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ19">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR19">
         <v>25</v>
       </c>
       <c r="BS19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU19">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW19">
         <v>9</v>
       </c>
       <c r="BX19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY19">
         <v>9.4</v>
       </c>
       <c r="BZ19">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA19">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="s">
         <v>186</v>
@@ -5524,220 +5524,220 @@
         <v>170</v>
       </c>
       <c r="F20">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G20">
         <v>3.15</v>
       </c>
       <c r="H20">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="I20">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M20">
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="Q20">
+        <v>1.56</v>
+      </c>
+      <c r="R20">
+        <v>1.58</v>
+      </c>
+      <c r="S20">
+        <v>2.4</v>
+      </c>
+      <c r="T20">
+        <v>1.52</v>
+      </c>
+      <c r="U20">
+        <v>2.38</v>
+      </c>
+      <c r="V20">
         <v>1.62</v>
-      </c>
-      <c r="R20">
-        <v>1.51</v>
-      </c>
-      <c r="S20">
-        <v>2.56</v>
-      </c>
-      <c r="T20">
-        <v>1.11</v>
-      </c>
-      <c r="U20">
-        <v>1.11</v>
-      </c>
-      <c r="V20">
-        <v>1.59</v>
       </c>
       <c r="W20">
         <v>1.48</v>
       </c>
       <c r="X20">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Z20">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB20">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AC20">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AE20">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AF20">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AG20">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AH20">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK20">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL20">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AM20">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN20">
-        <v>600</v>
+        <v>19.5</v>
       </c>
       <c r="AO20">
-        <v>600</v>
+        <v>14.5</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="AR20">
-        <v>1.31</v>
+        <v>4.3</v>
       </c>
       <c r="AS20">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="AT20">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="AU20">
         <v>5.1</v>
       </c>
       <c r="AV20">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="AW20">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="AX20">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="AY20">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="AZ20">
-        <v>1.27</v>
+        <v>4.1</v>
       </c>
       <c r="BA20">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="BB20">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="BC20">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="BD20">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="BE20">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="BF20">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BG20">
-        <v>1.55</v>
+        <v>3.95</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5766,172 +5766,172 @@
         <v>171</v>
       </c>
       <c r="F21">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G21">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I21">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J21">
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L21">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N21">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T21">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="V21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X21">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="Y21">
         <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AA21">
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE21">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AF21">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AG21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI21">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ21">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK21">
         <v>26</v>
       </c>
       <c r="AL21">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AM21">
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO21">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP21">
+        <v>8.4</v>
+      </c>
+      <c r="AQ21">
+        <v>12.5</v>
+      </c>
+      <c r="AR21">
+        <v>18</v>
+      </c>
+      <c r="AS21">
+        <v>13</v>
+      </c>
+      <c r="AT21">
+        <v>6.4</v>
+      </c>
+      <c r="AU21">
+        <v>7</v>
+      </c>
+      <c r="AV21">
+        <v>18.5</v>
+      </c>
+      <c r="AW21">
+        <v>12.5</v>
+      </c>
+      <c r="AX21">
         <v>9</v>
       </c>
-      <c r="AQ21">
-        <v>12</v>
-      </c>
-      <c r="AR21">
-        <v>5.8</v>
-      </c>
-      <c r="AS21">
-        <v>6.2</v>
-      </c>
-      <c r="AT21">
-        <v>6.2</v>
-      </c>
-      <c r="AU21">
-        <v>6.6</v>
-      </c>
-      <c r="AV21">
-        <v>17.5</v>
-      </c>
-      <c r="AW21">
-        <v>6</v>
-      </c>
-      <c r="AX21">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AY21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ21">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA21">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB21">
         <v>20</v>
       </c>
       <c r="BC21">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BD21">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="BE21">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BF21">
         <v>17</v>
       </c>
       <c r="BG21">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BH21">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI21">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
@@ -5967,13 +5967,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX21">
         <v>1000</v>
@@ -6011,19 +6011,19 @@
         <v>1.28</v>
       </c>
       <c r="G22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H22">
         <v>14</v>
       </c>
       <c r="I22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J22">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L22">
         <v>1.32</v>
@@ -6032,49 +6032,49 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S22">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T22">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U22">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y22">
         <v>42</v>
       </c>
       <c r="Z22">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA22">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="AB22">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC22">
         <v>15</v>
@@ -6083,10 +6083,10 @@
         <v>55</v>
       </c>
       <c r="AE22">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AF22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG22">
         <v>11</v>
@@ -6098,7 +6098,7 @@
         <v>220</v>
       </c>
       <c r="AJ22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK22">
         <v>15</v>
@@ -6107,25 +6107,25 @@
         <v>48</v>
       </c>
       <c r="AM22">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN22">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AO22">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AP22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ22">
         <v>36</v>
       </c>
       <c r="AR22">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AS22">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AT22">
         <v>7.6</v>
@@ -6134,10 +6134,10 @@
         <v>13</v>
       </c>
       <c r="AV22">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AW22">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AX22">
         <v>6.6</v>
@@ -6149,7 +6149,7 @@
         <v>32</v>
       </c>
       <c r="BA22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB22">
         <v>8.6</v>
@@ -6158,43 +6158,43 @@
         <v>13</v>
       </c>
       <c r="BD22">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BF22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG22">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ22">
         <v>14</v>
       </c>
       <c r="BK22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BO22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ22">
         <v>6</v>
@@ -6203,31 +6203,31 @@
         <v>26</v>
       </c>
       <c r="BS22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BU22">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA22">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB22" t="s">
         <v>186</v>
@@ -6250,10 +6250,10 @@
         <v>173</v>
       </c>
       <c r="F23">
+        <v>1.12</v>
+      </c>
+      <c r="G23">
         <v>1.13</v>
-      </c>
-      <c r="G23">
-        <v>1.14</v>
       </c>
       <c r="H23">
         <v>32</v>
@@ -6262,10 +6262,10 @@
         <v>34</v>
       </c>
       <c r="J23">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L23">
         <v>1.16</v>
@@ -6274,7 +6274,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="O23">
         <v>1.07</v>
@@ -6289,10 +6289,10 @@
         <v>2.54</v>
       </c>
       <c r="S23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U23">
         <v>1.86</v>
@@ -6301,43 +6301,43 @@
         <v>1.03</v>
       </c>
       <c r="W23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X23">
         <v>70</v>
       </c>
       <c r="Y23">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="Z23">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC23">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AD23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AE23">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AF23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI23">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AJ23">
         <v>9.199999999999999</v>
@@ -6346,22 +6346,22 @@
         <v>14</v>
       </c>
       <c r="AL23">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM23">
         <v>190</v>
       </c>
       <c r="AN23">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AO23">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AP23">
         <v>55</v>
       </c>
       <c r="AQ23">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AR23">
         <v>100</v>
@@ -6370,13 +6370,13 @@
         <v>100</v>
       </c>
       <c r="AT23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU23">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AV23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AW23">
         <v>120</v>
@@ -6388,10 +6388,10 @@
         <v>15</v>
       </c>
       <c r="AZ23">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BA23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BB23">
         <v>8.800000000000001</v>
@@ -6406,28 +6406,28 @@
         <v>100</v>
       </c>
       <c r="BF23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BG23">
         <v>120</v>
       </c>
       <c r="BH23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BI23">
         <v>6.4</v>
       </c>
       <c r="BJ23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK23">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BL23">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="BM23">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN23">
         <v>4.2</v>
@@ -6439,34 +6439,34 @@
         <v>5.2</v>
       </c>
       <c r="BQ23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
         <v>19</v>
       </c>
       <c r="BS23">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT23">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BU23">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BV23">
         <v>210</v>
       </c>
       <c r="BW23">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BX23">
         <v>140</v>
       </c>
       <c r="BY23">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BZ23">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="CA23">
         <v>4.2</v>
@@ -6492,10 +6492,10 @@
         <v>174</v>
       </c>
       <c r="F24">
+        <v>1.1</v>
+      </c>
+      <c r="G24">
         <v>1.11</v>
-      </c>
-      <c r="G24">
-        <v>1.12</v>
       </c>
       <c r="H24">
         <v>32</v>
@@ -6504,13 +6504,13 @@
         <v>34</v>
       </c>
       <c r="J24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="K24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="M24">
         <v>1.01</v>
@@ -6522,82 +6522,82 @@
         <v>1.04</v>
       </c>
       <c r="P24">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Q24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R24">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="V24">
         <v>1.03</v>
       </c>
       <c r="W24">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="Z24">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AC24">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AD24">
         <v>130</v>
       </c>
       <c r="AE24">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="AF24">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG24">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI24">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AJ24">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL24">
         <v>32</v>
       </c>
       <c r="AM24">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN24">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP24">
         <v>95</v>
@@ -6606,112 +6606,112 @@
         <v>90</v>
       </c>
       <c r="AR24">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AS24">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AT24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU24">
+        <v>38</v>
+      </c>
+      <c r="AV24">
+        <v>75</v>
+      </c>
+      <c r="AW24">
+        <v>85</v>
+      </c>
+      <c r="AX24">
+        <v>16.5</v>
+      </c>
+      <c r="AY24">
+        <v>16.5</v>
+      </c>
+      <c r="AZ24">
         <v>40</v>
       </c>
-      <c r="AV24">
-        <v>42</v>
-      </c>
-      <c r="AW24">
-        <v>70</v>
-      </c>
-      <c r="AX24">
-        <v>18</v>
-      </c>
-      <c r="AY24">
-        <v>18</v>
-      </c>
-      <c r="AZ24">
-        <v>36</v>
-      </c>
       <c r="BA24">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BB24">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BC24">
+        <v>14</v>
+      </c>
+      <c r="BD24">
+        <v>28</v>
+      </c>
+      <c r="BE24">
+        <v>85</v>
+      </c>
+      <c r="BF24">
+        <v>1.74</v>
+      </c>
+      <c r="BG24">
+        <v>130</v>
+      </c>
+      <c r="BH24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BJ24">
         <v>13.5</v>
-      </c>
-      <c r="BD24">
-        <v>27</v>
-      </c>
-      <c r="BE24">
-        <v>60</v>
-      </c>
-      <c r="BF24">
-        <v>1.71</v>
-      </c>
-      <c r="BG24">
-        <v>75</v>
-      </c>
-      <c r="BH24">
-        <v>11</v>
-      </c>
-      <c r="BI24">
-        <v>9.4</v>
-      </c>
-      <c r="BJ24">
-        <v>13</v>
       </c>
       <c r="BK24">
         <v>11.5</v>
       </c>
       <c r="BL24">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BM24">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BN24">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BO24">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP24">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BQ24">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BR24">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BS24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BU24">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BV24">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BW24">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BX24">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BY24">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="BZ24">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="CA24">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="CB24" t="s">
         <v>186</v>
@@ -6734,22 +6734,22 @@
         <v>175</v>
       </c>
       <c r="F25">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G25">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H25">
         <v>2.72</v>
       </c>
       <c r="I25">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L25">
         <v>1.35</v>
@@ -6764,13 +6764,13 @@
         <v>1.23</v>
       </c>
       <c r="P25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S25">
         <v>2.74</v>
@@ -6779,10 +6779,10 @@
         <v>1.59</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V25">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
         <v>1.56</v>
@@ -6794,7 +6794,7 @@
         <v>15</v>
       </c>
       <c r="Z25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA25">
         <v>38</v>
@@ -6803,13 +6803,13 @@
         <v>14.5</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD25">
         <v>12.5</v>
       </c>
       <c r="AE25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF25">
         <v>21</v>
@@ -6818,10 +6818,10 @@
         <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ25">
         <v>40</v>
@@ -6830,10 +6830,10 @@
         <v>26</v>
       </c>
       <c r="AL25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN25">
         <v>17.5</v>
@@ -6857,7 +6857,7 @@
         <v>13.5</v>
       </c>
       <c r="AU25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25">
         <v>11.5</v>
@@ -6866,22 +6866,22 @@
         <v>23</v>
       </c>
       <c r="AX25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY25">
         <v>11.5</v>
       </c>
       <c r="AZ25">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB25">
         <v>34</v>
       </c>
       <c r="BC25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD25">
         <v>30</v>
@@ -6890,13 +6890,13 @@
         <v>48</v>
       </c>
       <c r="BF25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH25">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI25">
         <v>3.6</v>
@@ -6905,22 +6905,22 @@
         <v>8.6</v>
       </c>
       <c r="BK25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL25">
         <v>85</v>
       </c>
       <c r="BM25">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN25">
         <v>6</v>
       </c>
       <c r="BO25">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ25">
         <v>17</v>
@@ -6938,22 +6938,22 @@
         <v>5.5</v>
       </c>
       <c r="BV25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX25">
         <v>27</v>
       </c>
       <c r="BY25">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BZ25">
         <v>19</v>
       </c>
       <c r="CA25">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="CB25" t="s">
         <v>186</v>
@@ -6979,10 +6979,10 @@
         <v>3.25</v>
       </c>
       <c r="G26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H26">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I26">
         <v>2.38</v>
@@ -6994,13 +6994,13 @@
         <v>3.65</v>
       </c>
       <c r="L26">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M26">
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O26">
         <v>1.32</v>
@@ -7009,13 +7009,13 @@
         <v>2</v>
       </c>
       <c r="Q26">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R26">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S26">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
         <v>1.77</v>
@@ -7027,19 +7027,19 @@
         <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y26">
         <v>11</v>
       </c>
       <c r="Z26">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA26">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB26">
         <v>13</v>
@@ -7048,22 +7048,22 @@
         <v>8</v>
       </c>
       <c r="AD26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF26">
         <v>23</v>
       </c>
       <c r="AG26">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI26">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AJ26">
         <v>60</v>
@@ -7075,7 +7075,7 @@
         <v>46</v>
       </c>
       <c r="AM26">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN26">
         <v>34</v>
@@ -7087,7 +7087,7 @@
         <v>13</v>
       </c>
       <c r="AQ26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR26">
         <v>13.5</v>
@@ -7096,13 +7096,13 @@
         <v>29</v>
       </c>
       <c r="AT26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU26">
         <v>7.4</v>
       </c>
       <c r="AV26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW26">
         <v>22</v>
@@ -7126,13 +7126,13 @@
         <v>32</v>
       </c>
       <c r="BD26">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE26">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF26">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BG26">
         <v>17</v>
@@ -7141,40 +7141,40 @@
         <v>4</v>
       </c>
       <c r="BI26">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ26">
         <v>11.5</v>
       </c>
       <c r="BK26">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN26">
         <v>6.8</v>
       </c>
       <c r="BO26">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BR26">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BT26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU26">
         <v>4.8</v>
@@ -7183,19 +7183,19 @@
         <v>21</v>
       </c>
       <c r="BW26">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BX26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="CB26" t="s">
         <v>186</v>
@@ -7218,22 +7218,22 @@
         <v>177</v>
       </c>
       <c r="F27">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="G27">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H27">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I27">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L27">
         <v>1.28</v>
@@ -7242,49 +7242,49 @@
         <v>1.03</v>
       </c>
       <c r="N27">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O27">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q27">
+        <v>1.51</v>
+      </c>
+      <c r="R27">
+        <v>1.78</v>
+      </c>
+      <c r="S27">
+        <v>2.26</v>
+      </c>
+      <c r="T27">
         <v>1.54</v>
       </c>
-      <c r="R27">
-        <v>1.74</v>
-      </c>
-      <c r="S27">
-        <v>2.32</v>
-      </c>
-      <c r="T27">
-        <v>1.55</v>
-      </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="V27">
         <v>1.27</v>
       </c>
       <c r="W27">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="X27">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z27">
         <v>42</v>
       </c>
       <c r="AA27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -7293,58 +7293,58 @@
         <v>18.5</v>
       </c>
       <c r="AE27">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG27">
         <v>10</v>
       </c>
       <c r="AH27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ27">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM27">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN27">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR27">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS27">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AT27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU27">
         <v>9.6</v>
       </c>
       <c r="AV27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW27">
         <v>40</v>
@@ -7362,28 +7362,28 @@
         <v>38</v>
       </c>
       <c r="BB27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE27">
         <v>46</v>
       </c>
       <c r="BF27">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG27">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ27">
         <v>8.6</v>
@@ -7395,7 +7395,7 @@
         <v>75</v>
       </c>
       <c r="BM27">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BN27">
         <v>5</v>
@@ -7404,40 +7404,40 @@
         <v>4.6</v>
       </c>
       <c r="BP27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS27">
         <v>17</v>
       </c>
       <c r="BT27">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU27">
+        <v>7.4</v>
+      </c>
+      <c r="BV27">
+        <v>32</v>
+      </c>
+      <c r="BW27">
+        <v>26</v>
+      </c>
+      <c r="BX27">
+        <v>34</v>
+      </c>
+      <c r="BY27">
+        <v>28</v>
+      </c>
+      <c r="BZ27">
+        <v>13</v>
+      </c>
+      <c r="CA27">
         <v>7.2</v>
-      </c>
-      <c r="BV27">
-        <v>30</v>
-      </c>
-      <c r="BW27">
-        <v>24</v>
-      </c>
-      <c r="BX27">
-        <v>32</v>
-      </c>
-      <c r="BY27">
-        <v>27</v>
-      </c>
-      <c r="BZ27">
-        <v>13.5</v>
-      </c>
-      <c r="CA27">
-        <v>11</v>
       </c>
       <c r="CB27" t="s">
         <v>186</v>
@@ -7460,16 +7460,16 @@
         <v>178</v>
       </c>
       <c r="F28">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H28">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I28">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="J28">
         <v>4</v>
@@ -7484,79 +7484,79 @@
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O28">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q28">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R28">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S28">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T28">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U28">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W28">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z28">
         <v>9.6</v>
       </c>
       <c r="AA28">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB28">
+        <v>18.5</v>
+      </c>
+      <c r="AC28">
+        <v>9</v>
+      </c>
+      <c r="AD28">
+        <v>9.6</v>
+      </c>
+      <c r="AE28">
         <v>18</v>
-      </c>
-      <c r="AC28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE28">
-        <v>19</v>
       </c>
       <c r="AF28">
         <v>55</v>
       </c>
       <c r="AG28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28">
         <v>40</v>
       </c>
       <c r="AJ28">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AK28">
         <v>100</v>
       </c>
       <c r="AL28">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM28">
         <v>130</v>
@@ -7565,25 +7565,25 @@
         <v>120</v>
       </c>
       <c r="AO28">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR28">
         <v>8.800000000000001</v>
       </c>
       <c r="AS28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT28">
         <v>17</v>
       </c>
       <c r="AU28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28">
         <v>9.199999999999999</v>
@@ -7598,13 +7598,13 @@
         <v>19.5</v>
       </c>
       <c r="AZ28">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB28">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="BC28">
         <v>60</v>
@@ -7613,73 +7613,73 @@
         <v>70</v>
       </c>
       <c r="BE28">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BF28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG28">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI28">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK28">
-        <v>2.18</v>
+        <v>5.4</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM28">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO28">
         <v>5.6</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ28">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS28">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BU28">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW28">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY28">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA28">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="CB28" t="s">
         <v>186</v>
@@ -7702,88 +7702,88 @@
         <v>179</v>
       </c>
       <c r="F29">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G29">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="H29">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L29">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M29">
         <v>1.11</v>
       </c>
       <c r="N29">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="O29">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P29">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q29">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R29">
         <v>1.21</v>
       </c>
       <c r="S29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T29">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V29">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W29">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="X29">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y29">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z29">
         <v>110</v>
       </c>
       <c r="AA29">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="AB29">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AC29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AE29">
         <v>320</v>
       </c>
       <c r="AF29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH29">
         <v>42</v>
@@ -7792,115 +7792,115 @@
         <v>310</v>
       </c>
       <c r="AJ29">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AK29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL29">
         <v>190</v>
       </c>
       <c r="AM29">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN29">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AO29">
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR29">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS29">
         <v>10</v>
       </c>
       <c r="AT29">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU29">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW29">
+        <v>10</v>
+      </c>
+      <c r="AX29">
+        <v>6.4</v>
+      </c>
+      <c r="AY29">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AX29">
-        <v>6.2</v>
-      </c>
-      <c r="AY29">
-        <v>9.6</v>
       </c>
       <c r="AZ29">
         <v>8.199999999999999</v>
       </c>
       <c r="BA29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC29">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
         <v>9</v>
       </c>
       <c r="BE29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF29">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG29">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH29">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BI29">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BJ29">
         <v>15</v>
       </c>
       <c r="BK29">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN29">
         <v>3.75</v>
       </c>
       <c r="BO29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ29">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR29">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS29">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU29">
         <v>6.2</v>
@@ -7909,19 +7909,19 @@
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ29">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA29">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="s">
         <v>186</v>
@@ -7944,226 +7944,226 @@
         <v>180</v>
       </c>
       <c r="F30">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G30">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H30">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I30">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J30">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L30">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N30">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="O30">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P30">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S30">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="T30">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="U30">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="V30">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X30">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y30">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z30">
+        <v>28</v>
+      </c>
+      <c r="AA30">
         <v>500</v>
       </c>
-      <c r="AA30">
-        <v>900</v>
-      </c>
       <c r="AB30">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE30">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF30">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG30">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AI30">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ30">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK30">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL30">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM30">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN30">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO30">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP30">
-        <v>1.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="AR30">
-        <v>1.41</v>
+        <v>6.2</v>
       </c>
       <c r="AS30">
-        <v>1.43</v>
+        <v>7.4</v>
       </c>
       <c r="AT30">
-        <v>1.44</v>
+        <v>6.6</v>
       </c>
       <c r="AU30">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV30">
-        <v>1.41</v>
+        <v>14</v>
       </c>
       <c r="AW30">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="AX30">
-        <v>1.44</v>
+        <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>1.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30">
-        <v>1.39</v>
+        <v>18</v>
       </c>
       <c r="BA30">
-        <v>1.43</v>
+        <v>7.4</v>
       </c>
       <c r="BB30">
-        <v>1.42</v>
+        <v>6.6</v>
       </c>
       <c r="BC30">
-        <v>1.42</v>
+        <v>6.4</v>
       </c>
       <c r="BD30">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="BE30">
-        <v>1.44</v>
+        <v>7.8</v>
       </c>
       <c r="BF30">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG30">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BH30">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BI30">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK30">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.49</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO30">
-        <v>1.49</v>
+        <v>3.95</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ30">
-        <v>1.49</v>
+        <v>6.8</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS30">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU30">
-        <v>1.49</v>
+        <v>5.4</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW30">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY30">
-        <v>1.49</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA30">
-        <v>1.49</v>
+        <v>8.4</v>
       </c>
       <c r="CB30" t="s">
         <v>186</v>
@@ -8186,217 +8186,217 @@
         <v>181</v>
       </c>
       <c r="F31">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="G31">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="H31">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="I31">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J31">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L31">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M31">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N31">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O31">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="P31">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q31">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="R31">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S31">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="T31">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U31">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W31">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="X31">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z31">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA31">
         <v>900</v>
       </c>
       <c r="AB31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC31">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE31">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF31">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG31">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI31">
         <v>500</v>
       </c>
       <c r="AJ31">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AK31">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AL31">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AM31">
         <v>500</v>
       </c>
       <c r="AN31">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AO31">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AP31">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ31">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR31">
-        <v>19.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS31">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT31">
+        <v>5.7</v>
+      </c>
+      <c r="AU31">
+        <v>6.4</v>
+      </c>
+      <c r="AV31">
+        <v>17.5</v>
+      </c>
+      <c r="AW31">
+        <v>5.7</v>
+      </c>
+      <c r="AX31">
+        <v>9</v>
+      </c>
+      <c r="AY31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31">
+        <v>21</v>
+      </c>
+      <c r="BA31">
+        <v>5.8</v>
+      </c>
+      <c r="BB31">
+        <v>21</v>
+      </c>
+      <c r="BC31">
+        <v>23</v>
+      </c>
+      <c r="BD31">
+        <v>5.8</v>
+      </c>
+      <c r="BE31">
         <v>6</v>
       </c>
-      <c r="AU31">
-        <v>6.2</v>
-      </c>
-      <c r="AV31">
-        <v>15.5</v>
-      </c>
-      <c r="AW31">
-        <v>5.5</v>
-      </c>
-      <c r="AX31">
-        <v>11</v>
-      </c>
-      <c r="AY31">
-        <v>10.5</v>
-      </c>
-      <c r="AZ31">
-        <v>18.5</v>
-      </c>
-      <c r="BA31">
-        <v>5.3</v>
-      </c>
-      <c r="BB31">
-        <v>5.1</v>
-      </c>
-      <c r="BC31">
-        <v>5.1</v>
-      </c>
-      <c r="BD31">
-        <v>5.4</v>
-      </c>
-      <c r="BE31">
-        <v>5.7</v>
-      </c>
       <c r="BF31">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BG31">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH31">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BI31">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ31">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BK31">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO31">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP31">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
         <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV31">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
         <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
         <v>1.01</v>
@@ -8428,76 +8428,76 @@
         <v>182</v>
       </c>
       <c r="F32">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="G32">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="H32">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="I32">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J32">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>1.4</v>
       </c>
       <c r="M32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P32">
+        <v>1.98</v>
+      </c>
+      <c r="Q32">
         <v>1.94</v>
       </c>
-      <c r="Q32">
-        <v>1.98</v>
-      </c>
       <c r="R32">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T32">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="U32">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V32">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W32">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="X32">
         <v>17</v>
       </c>
       <c r="Y32">
-        <v>19.5</v>
+        <v>110</v>
       </c>
       <c r="Z32">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AA32">
         <v>900</v>
       </c>
       <c r="AB32">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD32">
         <v>26</v>
@@ -8506,22 +8506,22 @@
         <v>700</v>
       </c>
       <c r="AF32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH32">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI32">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ32">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AK32">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AL32">
         <v>500</v>
@@ -8530,7 +8530,7 @@
         <v>580</v>
       </c>
       <c r="AN32">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AO32">
         <v>700</v>
@@ -8539,67 +8539,67 @@
         <v>12.5</v>
       </c>
       <c r="AQ32">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AR32">
+        <v>8.6</v>
+      </c>
+      <c r="AS32">
+        <v>7.8</v>
+      </c>
+      <c r="AT32">
+        <v>7</v>
+      </c>
+      <c r="AU32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>13</v>
+      </c>
+      <c r="AW32">
         <v>7.6</v>
       </c>
-      <c r="AS32">
-        <v>8.4</v>
-      </c>
-      <c r="AT32">
-        <v>7.2</v>
-      </c>
-      <c r="AU32">
+      <c r="AX32">
         <v>8</v>
       </c>
-      <c r="AV32">
-        <v>17.5</v>
-      </c>
-      <c r="AW32">
-        <v>8</v>
-      </c>
-      <c r="AX32">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AY32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ32">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA32">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB32">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC32">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE32">
+        <v>7.8</v>
+      </c>
+      <c r="BF32">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF32">
-        <v>9.6</v>
-      </c>
       <c r="BG32">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH32">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI32">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK32">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8608,13 +8608,13 @@
         <v>5.7</v>
       </c>
       <c r="BN32">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO32">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ32">
         <v>4</v>
@@ -8623,31 +8623,31 @@
         <v>32</v>
       </c>
       <c r="BS32">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BT32">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU32">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BV32">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
         <v>5.4</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY32">
         <v>5.4</v>
       </c>
       <c r="BZ32">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CA32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB32" t="s">
         <v>186</v>
@@ -8670,64 +8670,64 @@
         <v>183</v>
       </c>
       <c r="F33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G33">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H33">
         <v>4.6</v>
       </c>
       <c r="I33">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J33">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M33">
         <v>1.14</v>
       </c>
       <c r="N33">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="O33">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P33">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q33">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="R33">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S33">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T33">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U33">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V33">
         <v>1.26</v>
       </c>
       <c r="W33">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X33">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z33">
         <v>42</v>
@@ -8745,7 +8745,7 @@
         <v>26</v>
       </c>
       <c r="AE33">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF33">
         <v>11.5</v>
@@ -8754,7 +8754,7 @@
         <v>11.5</v>
       </c>
       <c r="AH33">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI33">
         <v>140</v>
@@ -8772,25 +8772,25 @@
         <v>500</v>
       </c>
       <c r="AN33">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO33">
         <v>500</v>
       </c>
       <c r="AP33">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ33">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR33">
         <v>13</v>
       </c>
       <c r="AS33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT33">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU33">
         <v>6.6</v>
@@ -8799,7 +8799,7 @@
         <v>18.5</v>
       </c>
       <c r="AW33">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8811,7 +8811,7 @@
         <v>19.5</v>
       </c>
       <c r="BA33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB33">
         <v>11.5</v>
@@ -8820,76 +8820,76 @@
         <v>25</v>
       </c>
       <c r="BD33">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE33">
         <v>10</v>
       </c>
       <c r="BF33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH33">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI33">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="BJ33">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BK33">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BN33">
         <v>5.4</v>
       </c>
       <c r="BO33">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP33">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BQ33">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR33">
         <v>55</v>
       </c>
       <c r="BS33">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT33">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU33">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="BV33">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW33">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BX33">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BY33">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BZ33">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA33">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="CB33" t="s">
         <v>186</v>
@@ -8912,19 +8912,19 @@
         <v>184</v>
       </c>
       <c r="F34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G34">
         <v>1.83</v>
       </c>
       <c r="H34">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I34">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K34">
         <v>3.75</v>
@@ -8933,7 +8933,7 @@
         <v>1.46</v>
       </c>
       <c r="M34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
         <v>3.4</v>
@@ -8957,7 +8957,7 @@
         <v>2</v>
       </c>
       <c r="U34">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V34">
         <v>1.22</v>
@@ -8975,7 +8975,7 @@
         <v>40</v>
       </c>
       <c r="AA34">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB34">
         <v>7.6</v>
@@ -8987,7 +8987,7 @@
         <v>21</v>
       </c>
       <c r="AE34">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF34">
         <v>10</v>
@@ -9005,7 +9005,7 @@
         <v>19.5</v>
       </c>
       <c r="AK34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL34">
         <v>44</v>
@@ -9029,7 +9029,7 @@
         <v>36</v>
       </c>
       <c r="AS34">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT34">
         <v>7</v>
@@ -9041,7 +9041,7 @@
         <v>18.5</v>
       </c>
       <c r="AW34">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AX34">
         <v>9.199999999999999</v>
@@ -9059,79 +9059,79 @@
         <v>17.5</v>
       </c>
       <c r="BC34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD34">
         <v>38</v>
       </c>
       <c r="BE34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BF34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG34">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH34">
         <v>3.2</v>
       </c>
       <c r="BI34">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ34">
         <v>11</v>
       </c>
       <c r="BK34">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN34">
         <v>4.3</v>
       </c>
       <c r="BO34">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP34">
         <v>13</v>
       </c>
       <c r="BQ34">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BR34">
         <v>32</v>
       </c>
       <c r="BS34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT34">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU34">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW34">
+        <v>11.5</v>
+      </c>
+      <c r="BX34">
+        <v>65</v>
+      </c>
+      <c r="BY34">
         <v>12</v>
-      </c>
-      <c r="BX34">
-        <v>1000</v>
-      </c>
-      <c r="BY34">
-        <v>12.5</v>
       </c>
       <c r="BZ34">
         <v>28</v>
       </c>
       <c r="CA34">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB34" t="s">
         <v>186</v>
@@ -9157,19 +9157,19 @@
         <v>1.9</v>
       </c>
       <c r="G35">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H35">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>4.6</v>
       </c>
       <c r="J35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K35">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L35">
         <v>1.37</v>
@@ -9178,43 +9178,43 @@
         <v>1.06</v>
       </c>
       <c r="N35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>1.28</v>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q35">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R35">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S35">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T35">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U35">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
         <v>1.28</v>
       </c>
       <c r="W35">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X35">
+        <v>20</v>
+      </c>
+      <c r="Y35">
         <v>19.5</v>
       </c>
-      <c r="Y35">
-        <v>17</v>
-      </c>
       <c r="Z35">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA35">
         <v>110</v>
@@ -9223,7 +9223,7 @@
         <v>10.5</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35">
         <v>18</v>
@@ -9238,7 +9238,7 @@
         <v>11</v>
       </c>
       <c r="AH35">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI35">
         <v>60</v>
@@ -9247,7 +9247,7 @@
         <v>24</v>
       </c>
       <c r="AK35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL35">
         <v>36</v>
@@ -9262,70 +9262,70 @@
         <v>60</v>
       </c>
       <c r="AP35">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ35">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR35">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT35">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU35">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV35">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY35">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ35">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB35">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC35">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD35">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH35">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI35">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ35">
         <v>10</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL35">
         <v>1000</v>
@@ -9337,16 +9337,16 @@
         <v>4.9</v>
       </c>
       <c r="BO35">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP35">
         <v>14</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS35">
         <v>1.01</v>
@@ -9355,7 +9355,7 @@
         <v>8</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV35">
         <v>36</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -574,7 +574,7 @@
     <t>Cobreloa Calama</t>
   </si>
   <si>
-    <t>2026-09-10 05:51:16</t>
+    <t>2026-09-10 08:10:17</t>
   </si>
 </sst>
 </file>
@@ -1168,169 +1168,169 @@
         <v>152</v>
       </c>
       <c r="F2">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H2">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
+        <v>3.35</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.1</v>
+      </c>
+      <c r="N2">
         <v>3.5</v>
       </c>
-      <c r="L2">
-        <v>1.43</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.55</v>
-      </c>
       <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.83</v>
+      </c>
+      <c r="Q2">
+        <v>2.14</v>
+      </c>
+      <c r="R2">
+        <v>1.33</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>1.81</v>
+      </c>
+      <c r="U2">
+        <v>2.1</v>
+      </c>
+      <c r="V2">
+        <v>1.68</v>
+      </c>
+      <c r="W2">
         <v>1.35</v>
       </c>
-      <c r="P2">
-        <v>1.87</v>
-      </c>
-      <c r="Q2">
-        <v>1.98</v>
-      </c>
-      <c r="R2">
-        <v>1.34</v>
-      </c>
-      <c r="S2">
-        <v>3.75</v>
-      </c>
-      <c r="T2">
-        <v>1.77</v>
-      </c>
-      <c r="U2">
-        <v>2.14</v>
-      </c>
-      <c r="V2">
-        <v>1.64</v>
-      </c>
-      <c r="W2">
-        <v>1.41</v>
-      </c>
       <c r="X2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>200</v>
       </c>
       <c r="AN2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO2">
         <v>23</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS2">
         <v>25</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX2">
         <v>19.5</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BB2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BC2">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF2">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="BG2">
         <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
         <v>2.9</v>
@@ -1339,55 +1339,55 @@
         <v>10</v>
       </c>
       <c r="BK2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
         <v>6.6</v>
       </c>
       <c r="BO2">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
         <v>34</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>186</v>
@@ -1410,19 +1410,19 @@
         <v>153</v>
       </c>
       <c r="F3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="H3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K3">
         <v>7.2</v>
@@ -1431,7 +1431,7 @@
         <v>1.2</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
         <v>9</v>
@@ -1440,31 +1440,31 @@
         <v>1.1</v>
       </c>
       <c r="P3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
         <v>1.88</v>
       </c>
       <c r="T3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
         <v>2.34</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="Y3">
         <v>17.5</v>
@@ -1476,10 +1476,10 @@
         <v>13</v>
       </c>
       <c r="AB3">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AC3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1488,31 +1488,31 @@
         <v>14</v>
       </c>
       <c r="AF3">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AG3">
         <v>44</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ3">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AK3">
         <v>190</v>
       </c>
       <c r="AL3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM3">
         <v>95</v>
       </c>
       <c r="AN3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AO3">
         <v>3.4</v>
@@ -1527,7 +1527,7 @@
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT3">
         <v>46</v>
@@ -1536,7 +1536,7 @@
         <v>15</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW3">
         <v>11.5</v>
@@ -1554,7 +1554,7 @@
         <v>22</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="BC3">
         <v>75</v>
@@ -1569,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="BG3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH3">
         <v>6.8</v>
@@ -1602,16 +1602,16 @@
         <v>5.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
         <v>5.5</v>
       </c>
       <c r="BT3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
         <v>8.4</v>
@@ -1620,16 +1620,16 @@
         <v>5.8</v>
       </c>
       <c r="BX3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BY3">
         <v>4.6</v>
       </c>
       <c r="BZ3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CA3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="s">
         <v>186</v>
@@ -1652,52 +1652,52 @@
         <v>154</v>
       </c>
       <c r="F4">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="G4">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
+        <v>5.8</v>
+      </c>
+      <c r="I4">
         <v>6.2</v>
       </c>
-      <c r="I4">
-        <v>6.6</v>
-      </c>
       <c r="J4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K4">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4">
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S4">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1706,10 +1706,10 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z4">
         <v>55</v>
@@ -1718,28 +1718,28 @@
         <v>180</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH4">
         <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>15.5</v>
@@ -1751,55 +1751,55 @@
         <v>28</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN4">
         <v>6.2</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ4">
         <v>25</v>
       </c>
       <c r="AR4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS4">
         <v>100</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV4">
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB4">
+        <v>13.5</v>
+      </c>
+      <c r="BC4">
         <v>13</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
       </c>
       <c r="BD4">
         <v>23</v>
@@ -1808,70 +1808,70 @@
         <v>55</v>
       </c>
       <c r="BF4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
         <v>21</v>
       </c>
       <c r="BS4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <v>46</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>186</v>
@@ -1894,22 +1894,22 @@
         <v>155</v>
       </c>
       <c r="F5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1924,28 +1924,28 @@
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q5">
         <v>1.53</v>
       </c>
       <c r="R5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S5">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T5">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1972,22 +1972,22 @@
         <v>32</v>
       </c>
       <c r="AF5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AK5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5">
         <v>26</v>
@@ -2011,49 +2011,49 @@
         <v>24</v>
       </c>
       <c r="AS5">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU5">
         <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX5">
         <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>13</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB5">
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD5">
         <v>22</v>
       </c>
       <c r="BE5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH5">
         <v>4.6</v>
@@ -2062,34 +2062,34 @@
         <v>4.1</v>
       </c>
       <c r="BJ5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP5">
         <v>15</v>
       </c>
       <c r="BQ5">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
@@ -2101,19 +2101,19 @@
         <v>21</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>186</v>
@@ -2136,25 +2136,25 @@
         <v>156</v>
       </c>
       <c r="F6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="G6">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="K6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="L6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -2163,199 +2163,199 @@
         <v>5.5</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T6">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
         <v>1.11</v>
       </c>
       <c r="W6">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="Y6">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="Z6">
         <v>450</v>
       </c>
       <c r="AA6">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC6">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD6">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AE6">
         <v>400</v>
       </c>
       <c r="AF6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AJ6">
-        <v>13</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL6">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
+        <v>29</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.58</v>
+      </c>
+      <c r="AQ6">
+        <v>4.2</v>
+      </c>
+      <c r="AR6">
+        <v>4.2</v>
+      </c>
+      <c r="AS6">
+        <v>4.2</v>
+      </c>
+      <c r="AT6">
+        <v>4.9</v>
+      </c>
+      <c r="AU6">
+        <v>5.2</v>
+      </c>
+      <c r="AV6">
+        <v>4.2</v>
+      </c>
+      <c r="AW6">
+        <v>4.2</v>
+      </c>
+      <c r="AX6">
+        <v>3.95</v>
+      </c>
+      <c r="AY6">
+        <v>4.4</v>
+      </c>
+      <c r="AZ6">
+        <v>1.62</v>
+      </c>
+      <c r="BA6">
+        <v>4.2</v>
+      </c>
+      <c r="BB6">
+        <v>5.5</v>
+      </c>
+      <c r="BC6">
         <v>5.7</v>
       </c>
-      <c r="AO6">
-        <v>160</v>
-      </c>
-      <c r="AP6">
-        <v>20</v>
-      </c>
-      <c r="AQ6">
-        <v>27</v>
-      </c>
-      <c r="AR6">
-        <v>55</v>
-      </c>
-      <c r="AS6">
-        <v>8</v>
-      </c>
-      <c r="AT6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU6">
+      <c r="BD6">
+        <v>1.59</v>
+      </c>
+      <c r="BE6">
+        <v>1.6</v>
+      </c>
+      <c r="BF6">
+        <v>1.27</v>
+      </c>
+      <c r="BG6">
         <v>10.5</v>
       </c>
-      <c r="AV6">
-        <v>24</v>
-      </c>
-      <c r="AW6">
-        <v>60</v>
-      </c>
-      <c r="AX6">
-        <v>7.8</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
-      </c>
-      <c r="AZ6">
-        <v>19</v>
-      </c>
-      <c r="BA6">
-        <v>46</v>
-      </c>
-      <c r="BB6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC6">
-        <v>11.5</v>
-      </c>
-      <c r="BD6">
-        <v>22</v>
-      </c>
-      <c r="BE6">
-        <v>65</v>
-      </c>
-      <c r="BF6">
-        <v>4.6</v>
-      </c>
-      <c r="BG6">
-        <v>55</v>
-      </c>
       <c r="BH6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BP6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ6">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="BR6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BT6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BX6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BZ6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="CB6" t="s">
         <v>186</v>
@@ -2378,91 +2378,91 @@
         <v>157</v>
       </c>
       <c r="F7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
         <v>2.4</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
         <v>3.9</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U7">
         <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X7">
         <v>17</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
         <v>9</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI7">
         <v>60</v>
@@ -2471,10 +2471,10 @@
         <v>34</v>
       </c>
       <c r="AK7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2489,55 +2489,55 @@
         <v>6</v>
       </c>
       <c r="AQ7">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR7">
+        <v>4.9</v>
+      </c>
+      <c r="AS7">
+        <v>5.5</v>
+      </c>
+      <c r="AT7">
         <v>4.4</v>
       </c>
-      <c r="AS7">
+      <c r="AU7">
+        <v>3.6</v>
+      </c>
+      <c r="AV7">
+        <v>6.2</v>
+      </c>
+      <c r="AW7">
+        <v>5.3</v>
+      </c>
+      <c r="AX7">
+        <v>6.6</v>
+      </c>
+      <c r="AY7">
         <v>4.9</v>
       </c>
-      <c r="AT7">
-        <v>3.65</v>
-      </c>
-      <c r="AU7">
-        <v>3.4</v>
-      </c>
-      <c r="AV7">
-        <v>4</v>
-      </c>
-      <c r="AW7">
-        <v>4.7</v>
-      </c>
-      <c r="AX7">
-        <v>4</v>
-      </c>
-      <c r="AY7">
-        <v>3.75</v>
-      </c>
       <c r="AZ7">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA7">
+        <v>5.4</v>
+      </c>
+      <c r="BB7">
+        <v>5.1</v>
+      </c>
+      <c r="BC7">
         <v>4.9</v>
       </c>
-      <c r="BB7">
-        <v>4.5</v>
-      </c>
-      <c r="BC7">
-        <v>4.4</v>
-      </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE7">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF7">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG7">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH7">
         <v>3.85</v>
@@ -2620,100 +2620,100 @@
         <v>158</v>
       </c>
       <c r="F8">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G8">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="H8">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="I8">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="X8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y8">
+        <v>10.5</v>
+      </c>
+      <c r="Z8">
+        <v>17</v>
+      </c>
+      <c r="AA8">
+        <v>42</v>
+      </c>
+      <c r="AB8">
         <v>11.5</v>
-      </c>
-      <c r="Z8">
-        <v>23</v>
-      </c>
-      <c r="AA8">
-        <v>65</v>
-      </c>
-      <c r="AB8">
-        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ8">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL8">
         <v>75</v>
@@ -2722,124 +2722,124 @@
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO8">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AP8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR8">
+        <v>13.5</v>
+      </c>
+      <c r="AS8">
+        <v>27</v>
+      </c>
+      <c r="AT8">
         <v>9.6</v>
-      </c>
-      <c r="AQ8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR8">
-        <v>18</v>
-      </c>
-      <c r="AS8">
-        <v>40</v>
-      </c>
-      <c r="AT8">
-        <v>8</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
+        <v>22</v>
+      </c>
+      <c r="AX8">
+        <v>17.5</v>
+      </c>
+      <c r="AY8">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8">
+        <v>15.5</v>
+      </c>
+      <c r="BA8">
+        <v>32</v>
+      </c>
+      <c r="BB8">
+        <v>36</v>
+      </c>
+      <c r="BC8">
         <v>26</v>
       </c>
-      <c r="AX8">
-        <v>13.5</v>
-      </c>
-      <c r="AY8">
-        <v>10</v>
-      </c>
-      <c r="AZ8">
-        <v>16</v>
-      </c>
-      <c r="BA8">
-        <v>36</v>
-      </c>
-      <c r="BB8">
-        <v>26</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
       <c r="BD8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF8">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BG8">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="BH8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN8">
+        <v>6.4</v>
+      </c>
+      <c r="BO8">
+        <v>4.9</v>
+      </c>
+      <c r="BP8">
+        <v>26</v>
+      </c>
+      <c r="BQ8">
+        <v>7.8</v>
+      </c>
+      <c r="BR8">
+        <v>40</v>
+      </c>
+      <c r="BS8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT8">
         <v>5.6</v>
       </c>
-      <c r="BO8">
-        <v>4.3</v>
-      </c>
-      <c r="BP8">
-        <v>22</v>
-      </c>
-      <c r="BQ8">
-        <v>7</v>
-      </c>
-      <c r="BR8">
+      <c r="BU8">
+        <v>4.4</v>
+      </c>
+      <c r="BV8">
+        <v>21</v>
+      </c>
+      <c r="BW8">
+        <v>7.2</v>
+      </c>
+      <c r="BX8">
         <v>38</v>
       </c>
-      <c r="BS8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8">
-        <v>6.4</v>
-      </c>
-      <c r="BU8">
-        <v>4.9</v>
-      </c>
-      <c r="BV8">
-        <v>28</v>
-      </c>
-      <c r="BW8">
-        <v>7.6</v>
-      </c>
-      <c r="BX8">
-        <v>44</v>
-      </c>
       <c r="BY8">
+        <v>8.6</v>
+      </c>
+      <c r="BZ8">
+        <v>34</v>
+      </c>
+      <c r="CA8">
         <v>8.4</v>
-      </c>
-      <c r="BZ8">
-        <v>38</v>
-      </c>
-      <c r="CA8">
-        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>186</v>
@@ -2862,19 +2862,19 @@
         <v>159</v>
       </c>
       <c r="F9">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I9">
         <v>3.55</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
         <v>3.95</v>
@@ -2895,28 +2895,28 @@
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
         <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>15</v>
@@ -2925,7 +2925,7 @@
         <v>32</v>
       </c>
       <c r="AA9">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="AB9">
         <v>11.5</v>
@@ -2940,13 +2940,13 @@
         <v>120</v>
       </c>
       <c r="AF9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
         <v>150</v>
@@ -2964,22 +2964,22 @@
         <v>320</v>
       </c>
       <c r="AN9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP9">
         <v>15</v>
       </c>
       <c r="AQ9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR9">
         <v>20</v>
       </c>
       <c r="AS9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT9">
         <v>9.800000000000001</v>
@@ -2988,10 +2988,10 @@
         <v>7.6</v>
       </c>
       <c r="AV9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX9">
         <v>12.5</v>
@@ -3003,7 +3003,7 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB9">
         <v>24</v>
@@ -3012,19 +3012,19 @@
         <v>17</v>
       </c>
       <c r="BD9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF9">
         <v>13</v>
       </c>
       <c r="BG9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH9">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI9">
         <v>3.4</v>
@@ -3039,7 +3039,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -3048,16 +3048,16 @@
         <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>6.8</v>
@@ -3069,19 +3069,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>186</v>
@@ -3107,7 +3107,7 @@
         <v>16.5</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>1.18</v>
@@ -3116,7 +3116,7 @@
         <v>1.2</v>
       </c>
       <c r="J10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>10.5</v>
@@ -3128,7 +3128,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O10">
         <v>1.09</v>
@@ -3149,7 +3149,7 @@
         <v>1.89</v>
       </c>
       <c r="U10">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -3164,10 +3164,10 @@
         <v>18.5</v>
       </c>
       <c r="Z10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB10">
         <v>90</v>
@@ -3185,13 +3185,13 @@
         <v>210</v>
       </c>
       <c r="AG10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ10">
         <v>1000</v>
@@ -3200,16 +3200,16 @@
         <v>250</v>
       </c>
       <c r="AL10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AM10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN10">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AO10">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AP10">
         <v>20</v>
@@ -3221,10 +3221,10 @@
         <v>10</v>
       </c>
       <c r="AS10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT10">
         <v>9</v>
-      </c>
-      <c r="AT10">
-        <v>8.6</v>
       </c>
       <c r="AU10">
         <v>20</v>
@@ -3236,82 +3236,82 @@
         <v>12</v>
       </c>
       <c r="AX10">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AZ10">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
         <v>23</v>
       </c>
       <c r="BB10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC10">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BI10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ10">
         <v>15</v>
       </c>
       <c r="BK10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BL10">
         <v>130</v>
       </c>
       <c r="BM10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN10">
         <v>25</v>
       </c>
       <c r="BO10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
+        <v>5</v>
+      </c>
+      <c r="BR10">
+        <v>90</v>
+      </c>
+      <c r="BS10">
+        <v>4.9</v>
+      </c>
+      <c r="BT10">
         <v>5.1</v>
       </c>
-      <c r="BR10">
-        <v>95</v>
-      </c>
-      <c r="BS10">
-        <v>5.1</v>
-      </c>
-      <c r="BT10">
-        <v>5</v>
-      </c>
       <c r="BU10">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BV10">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BW10">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX10">
         <v>21</v>
@@ -3320,10 +3320,10 @@
         <v>4.2</v>
       </c>
       <c r="BZ10">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="CA10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="s">
         <v>186</v>
@@ -3346,7 +3346,7 @@
         <v>161</v>
       </c>
       <c r="F11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G11">
         <v>1.74</v>
@@ -3361,37 +3361,37 @@
         <v>4.4</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q11">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T11">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U11">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3400,10 +3400,10 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z11">
         <v>50</v>
@@ -3412,28 +3412,28 @@
         <v>900</v>
       </c>
       <c r="AB11">
+        <v>13</v>
+      </c>
+      <c r="AC11">
         <v>12</v>
       </c>
-      <c r="AC11">
-        <v>11.5</v>
-      </c>
       <c r="AD11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE11">
         <v>75</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
         <v>17.5</v>
@@ -3442,28 +3442,28 @@
         <v>16</v>
       </c>
       <c r="AL11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM11">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3475,7 +3475,7 @@
         <v>17</v>
       </c>
       <c r="AW11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3499,73 +3499,73 @@
         <v>22</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN11">
         <v>4.7</v>
       </c>
       <c r="BO11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP11">
         <v>11</v>
       </c>
       <c r="BQ11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB11" t="s">
         <v>186</v>
@@ -3588,16 +3588,16 @@
         <v>162</v>
       </c>
       <c r="F12">
+        <v>1.53</v>
+      </c>
+      <c r="G12">
         <v>1.55</v>
       </c>
-      <c r="G12">
-        <v>1.56</v>
-      </c>
       <c r="H12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -3618,28 +3618,28 @@
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R12">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U12">
         <v>2.58</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X12">
         <v>32</v>
@@ -3651,7 +3651,7 @@
         <v>60</v>
       </c>
       <c r="AA12">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB12">
         <v>13.5</v>
@@ -3660,10 +3660,10 @@
         <v>12</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF12">
         <v>12.5</v>
@@ -3672,7 +3672,7 @@
         <v>10</v>
       </c>
       <c r="AH12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI12">
         <v>60</v>
@@ -3681,7 +3681,7 @@
         <v>15.5</v>
       </c>
       <c r="AK12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL12">
         <v>23</v>
@@ -3693,7 +3693,7 @@
         <v>5</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP12">
         <v>30</v>
@@ -3702,28 +3702,28 @@
         <v>32</v>
       </c>
       <c r="AR12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS12">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AT12">
         <v>13</v>
       </c>
       <c r="AU12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV12">
         <v>22</v>
       </c>
       <c r="AW12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
       </c>
       <c r="AY12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
         <v>16.5</v>
@@ -3735,10 +3735,10 @@
         <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE12">
         <v>55</v>
@@ -3753,19 +3753,19 @@
         <v>4.8</v>
       </c>
       <c r="BI12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
         <v>8.6</v>
       </c>
       <c r="BL12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN12">
         <v>4.5</v>
@@ -3774,7 +3774,7 @@
         <v>4.2</v>
       </c>
       <c r="BP12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ12">
         <v>8.199999999999999</v>
@@ -3783,7 +3783,7 @@
         <v>18</v>
       </c>
       <c r="BS12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BT12">
         <v>10</v>
@@ -3795,10 +3795,10 @@
         <v>42</v>
       </c>
       <c r="BW12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BY12">
         <v>34</v>
@@ -3836,49 +3836,49 @@
         <v>3.7</v>
       </c>
       <c r="H13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
+        <v>3.7</v>
+      </c>
+      <c r="K13">
         <v>3.75</v>
       </c>
-      <c r="K13">
-        <v>3.8</v>
-      </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O13">
         <v>1.22</v>
       </c>
       <c r="P13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q13">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S13">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V13">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3887,7 +3887,7 @@
         <v>19.5</v>
       </c>
       <c r="Y13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z13">
         <v>15.5</v>
@@ -3896,16 +3896,16 @@
         <v>28</v>
       </c>
       <c r="AB13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF13">
         <v>28</v>
@@ -3944,13 +3944,13 @@
         <v>12.5</v>
       </c>
       <c r="AR13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS13">
         <v>26</v>
       </c>
       <c r="AT13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU13">
         <v>8.199999999999999</v>
@@ -3965,13 +3965,13 @@
         <v>26</v>
       </c>
       <c r="AY13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ13">
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB13">
         <v>60</v>
@@ -3989,13 +3989,13 @@
         <v>25</v>
       </c>
       <c r="BG13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
@@ -4007,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="BM13">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN13">
         <v>7</v>
@@ -4016,16 +4016,16 @@
         <v>6.4</v>
       </c>
       <c r="BP13">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BQ13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BR13">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BS13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
@@ -4040,10 +4040,10 @@
         <v>12.5</v>
       </c>
       <c r="BX13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BY13">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BZ13">
         <v>17.5</v>
@@ -4072,28 +4072,28 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="G14">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
         <v>1.39</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
         <v>4.1</v>
@@ -4108,88 +4108,88 @@
         <v>1.9</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14">
         <v>3.35</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U14">
         <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="X14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA14">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="AB14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC14">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE14">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
         <v>60</v>
       </c>
       <c r="AJ14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AN14">
         <v>12.5</v>
       </c>
       <c r="AO14">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="AP14">
         <v>14</v>
       </c>
       <c r="AQ14">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AS14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT14">
         <v>8.6</v>
@@ -4198,22 +4198,22 @@
         <v>7.8</v>
       </c>
       <c r="AV14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX14">
         <v>11</v>
       </c>
       <c r="AY14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB14">
         <v>19.5</v>
@@ -4222,76 +4222,76 @@
         <v>18</v>
       </c>
       <c r="BD14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG14">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH14">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI14">
         <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK14">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BN14">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BO14">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BP14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BR14">
         <v>28</v>
       </c>
       <c r="BS14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT14">
         <v>7.8</v>
       </c>
-      <c r="BT14">
-        <v>7.6</v>
-      </c>
       <c r="BU14">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW14">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY14">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BZ14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA14">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB14" t="s">
         <v>186</v>
@@ -4332,34 +4332,34 @@
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q15">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R15">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S15">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V15">
         <v>1.88</v>
@@ -4389,37 +4389,37 @@
         <v>11</v>
       </c>
       <c r="AE15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG15">
         <v>15.5</v>
       </c>
       <c r="AH15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ15">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL15">
         <v>40</v>
       </c>
       <c r="AM15">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AN15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP15">
         <v>19</v>
@@ -4431,7 +4431,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT15">
         <v>15.5</v>
@@ -4446,10 +4446,10 @@
         <v>17.5</v>
       </c>
       <c r="AX15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ15">
         <v>14</v>
@@ -4458,58 +4458,58 @@
         <v>24</v>
       </c>
       <c r="BB15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC15">
         <v>30</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE15">
         <v>32</v>
       </c>
       <c r="BF15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15">
         <v>4.8</v>
       </c>
       <c r="BI15">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ15">
         <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BL15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM15">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN15">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO15">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BP15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR15">
         <v>38</v>
       </c>
       <c r="BS15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT15">
         <v>6.2</v>
@@ -4521,19 +4521,19 @@
         <v>17</v>
       </c>
       <c r="BW15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BX15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BZ15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="s">
         <v>186</v>
@@ -4556,52 +4556,52 @@
         <v>166</v>
       </c>
       <c r="F16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I16">
         <v>2.12</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R16">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V16">
         <v>1.89</v>
@@ -4610,22 +4610,22 @@
         <v>1.33</v>
       </c>
       <c r="X16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z16">
         <v>13.5</v>
       </c>
       <c r="AA16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16">
         <v>11</v>
@@ -4634,7 +4634,7 @@
         <v>22</v>
       </c>
       <c r="AF16">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AG16">
         <v>16</v>
@@ -4643,40 +4643,40 @@
         <v>17.5</v>
       </c>
       <c r="AI16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ16">
         <v>160</v>
       </c>
       <c r="AK16">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AL16">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM16">
         <v>190</v>
       </c>
       <c r="AN16">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AO16">
+        <v>15</v>
+      </c>
+      <c r="AP16">
         <v>13.5</v>
       </c>
-      <c r="AP16">
-        <v>14.5</v>
-      </c>
       <c r="AQ16">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS16">
         <v>18.5</v>
       </c>
       <c r="AT16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU16">
         <v>7.4</v>
@@ -4685,25 +4685,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX16">
         <v>24</v>
       </c>
       <c r="AY16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ16">
         <v>15</v>
       </c>
       <c r="BA16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB16">
         <v>60</v>
       </c>
       <c r="BC16">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD16">
         <v>40</v>
@@ -4712,49 +4712,49 @@
         <v>65</v>
       </c>
       <c r="BF16">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BI16">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN16">
         <v>7.6</v>
       </c>
       <c r="BO16">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ16">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BR16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS16">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BT16">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU16">
         <v>4.3</v>
@@ -4763,19 +4763,19 @@
         <v>15</v>
       </c>
       <c r="BW16">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BX16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY16">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="CB16" t="s">
         <v>186</v>
@@ -4801,10 +4801,10 @@
         <v>11.5</v>
       </c>
       <c r="G17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I17">
         <v>1.31</v>
@@ -4816,7 +4816,7 @@
         <v>7.4</v>
       </c>
       <c r="L17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M17">
         <v>1.03</v>
@@ -4825,37 +4825,37 @@
         <v>5.7</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
         <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
         <v>1.64</v>
       </c>
       <c r="S17">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T17">
         <v>2.04</v>
       </c>
       <c r="U17">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y17">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17">
         <v>8.199999999999999</v>
@@ -4864,7 +4864,7 @@
         <v>10.5</v>
       </c>
       <c r="AB17">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AC17">
         <v>15.5</v>
@@ -4879,145 +4879,145 @@
         <v>140</v>
       </c>
       <c r="AG17">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AH17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ17">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="AK17">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AL17">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN17">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AO17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AP17">
         <v>23</v>
       </c>
       <c r="AQ17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
         <v>7</v>
       </c>
       <c r="AS17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU17">
         <v>12.5</v>
       </c>
       <c r="AV17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17">
         <v>12</v>
       </c>
       <c r="AX17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AZ17">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="BA17">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BB17">
         <v>12</v>
       </c>
       <c r="BC17">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BD17">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="BE17">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="BF17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH17">
         <v>5.2</v>
       </c>
       <c r="BI17">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BJ17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK17">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BN17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BO17">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BP17">
         <v>110</v>
       </c>
       <c r="BQ17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BR17">
         <v>95</v>
       </c>
       <c r="BS17">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BT17">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BU17">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV17">
         <v>7.6</v>
       </c>
       <c r="BW17">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BX17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BY17">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA17">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="s">
         <v>186</v>
@@ -5046,25 +5046,25 @@
         <v>4</v>
       </c>
       <c r="H18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I18">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J18">
         <v>3.45</v>
       </c>
       <c r="K18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L18">
         <v>1.39</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O18">
         <v>1.32</v>
@@ -5076,46 +5076,46 @@
         <v>1.95</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
         <v>1.75</v>
       </c>
       <c r="U18">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="V18">
         <v>1.83</v>
       </c>
       <c r="W18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z18">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AA18">
         <v>32</v>
       </c>
       <c r="AB18">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD18">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF18">
         <v>29</v>
@@ -5124,142 +5124,142 @@
         <v>18</v>
       </c>
       <c r="AH18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18">
         <v>38</v>
       </c>
       <c r="AJ18">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AK18">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL18">
         <v>55</v>
       </c>
       <c r="AM18">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN18">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO18">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AP18">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR18">
+        <v>11.5</v>
+      </c>
+      <c r="AS18">
+        <v>23</v>
+      </c>
+      <c r="AT18">
         <v>12</v>
-      </c>
-      <c r="AS18">
-        <v>15.5</v>
-      </c>
-      <c r="AT18">
-        <v>12.5</v>
       </c>
       <c r="AU18">
         <v>7</v>
       </c>
       <c r="AV18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AY18">
         <v>13.5</v>
       </c>
       <c r="AZ18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BB18">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="BC18">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BD18">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BE18">
-        <v>6.6</v>
+        <v>65</v>
       </c>
       <c r="BF18">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG18">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI18">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BN18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO18">
         <v>5.6</v>
       </c>
       <c r="BP18">
+        <v>34</v>
+      </c>
+      <c r="BQ18">
+        <v>5.1</v>
+      </c>
+      <c r="BR18">
+        <v>46</v>
+      </c>
+      <c r="BS18">
+        <v>5.3</v>
+      </c>
+      <c r="BT18">
+        <v>5.6</v>
+      </c>
+      <c r="BU18">
+        <v>4</v>
+      </c>
+      <c r="BV18">
+        <v>17.5</v>
+      </c>
+      <c r="BW18">
+        <v>4.4</v>
+      </c>
+      <c r="BX18">
         <v>32</v>
       </c>
-      <c r="BQ18">
-        <v>5.4</v>
-      </c>
-      <c r="BR18">
-        <v>42</v>
-      </c>
-      <c r="BS18">
-        <v>5.6</v>
-      </c>
-      <c r="BT18">
-        <v>5.7</v>
-      </c>
-      <c r="BU18">
-        <v>4.1</v>
-      </c>
-      <c r="BV18">
-        <v>16.5</v>
-      </c>
-      <c r="BW18">
-        <v>4.6</v>
-      </c>
-      <c r="BX18">
-        <v>30</v>
-      </c>
       <c r="BY18">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BZ18">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CA18">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB18" t="s">
         <v>186</v>
@@ -5285,7 +5285,7 @@
         <v>1.93</v>
       </c>
       <c r="G19">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -5297,7 +5297,7 @@
         <v>3.95</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.34</v>
@@ -5306,22 +5306,22 @@
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q19">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
         <v>1.53</v>
       </c>
       <c r="S19">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T19">
         <v>1.65</v>
@@ -5345,16 +5345,16 @@
         <v>36</v>
       </c>
       <c r="AA19">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB19">
         <v>12</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE19">
         <v>46</v>
@@ -5441,7 +5441,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>3.95</v>
@@ -5450,16 +5450,16 @@
         <v>3.6</v>
       </c>
       <c r="BJ19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN19">
         <v>4.9</v>
@@ -5471,37 +5471,37 @@
         <v>13.5</v>
       </c>
       <c r="BQ19">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT19">
         <v>8</v>
       </c>
       <c r="BU19">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV19">
         <v>32</v>
       </c>
       <c r="BW19">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX19">
         <v>38</v>
       </c>
       <c r="BY19">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA19">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB19" t="s">
         <v>186</v>
@@ -5536,7 +5536,7 @@
         <v>2.64</v>
       </c>
       <c r="J20">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
         <v>4.7</v>
@@ -5548,19 +5548,19 @@
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
         <v>1.56</v>
       </c>
       <c r="R20">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S20">
         <v>2.4</v>
@@ -5569,7 +5569,7 @@
         <v>1.52</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V20">
         <v>1.62</v>
@@ -5581,13 +5581,13 @@
         <v>28</v>
       </c>
       <c r="Y20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z20">
         <v>22</v>
       </c>
       <c r="AA20">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AB20">
         <v>20</v>
@@ -5611,16 +5611,16 @@
         <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ20">
         <v>55</v>
       </c>
       <c r="AK20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM20">
         <v>200</v>
@@ -5632,19 +5632,19 @@
         <v>14.5</v>
       </c>
       <c r="AP20">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ20">
         <v>4.3</v>
       </c>
       <c r="AR20">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS20">
         <v>5.5</v>
       </c>
       <c r="AT20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU20">
         <v>5.1</v>
@@ -5653,16 +5653,16 @@
         <v>5.1</v>
       </c>
       <c r="AW20">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX20">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY20">
         <v>5.5</v>
       </c>
       <c r="AZ20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA20">
         <v>5.5</v>
@@ -5671,19 +5671,19 @@
         <v>5.5</v>
       </c>
       <c r="BC20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD20">
         <v>5.5</v>
       </c>
       <c r="BE20">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG20">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH20">
         <v>4.9</v>
@@ -5766,40 +5766,40 @@
         <v>171</v>
       </c>
       <c r="F21">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H21">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M21">
         <v>1.12</v>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O21">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P21">
         <v>1.62</v>
       </c>
       <c r="Q21">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R21">
         <v>1.23</v>
@@ -5808,16 +5808,16 @@
         <v>4.8</v>
       </c>
       <c r="T21">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U21">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X21">
         <v>10.5</v>
@@ -5826,7 +5826,7 @@
         <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA21">
         <v>900</v>
@@ -5835,82 +5835,82 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE21">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AF21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
         <v>25</v>
       </c>
       <c r="AI21">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AJ21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21">
         <v>60</v>
       </c>
       <c r="AM21">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO21">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR21">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AS21">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="AT21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU21">
         <v>7</v>
       </c>
       <c r="AV21">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW21">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AX21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21">
         <v>10</v>
       </c>
       <c r="AZ21">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA21">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC21">
         <v>21</v>
@@ -5919,73 +5919,73 @@
         <v>42</v>
       </c>
       <c r="BE21">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="BF21">
         <v>17</v>
       </c>
       <c r="BG21">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="BH21">
         <v>2.98</v>
       </c>
       <c r="BI21">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO21">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT21">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU21">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB21" t="s">
         <v>186</v>
@@ -6008,16 +6008,16 @@
         <v>172</v>
       </c>
       <c r="F22">
+        <v>1.27</v>
+      </c>
+      <c r="G22">
         <v>1.28</v>
       </c>
-      <c r="G22">
-        <v>1.29</v>
-      </c>
       <c r="H22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J22">
         <v>6.4</v>
@@ -6029,10 +6029,10 @@
         <v>1.32</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O22">
         <v>1.23</v>
@@ -6041,37 +6041,37 @@
         <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
         <v>1.53</v>
       </c>
       <c r="S22">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U22">
         <v>1.73</v>
       </c>
       <c r="V22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z22">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA22">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="AB22">
         <v>8.6</v>
@@ -6083,19 +6083,19 @@
         <v>55</v>
       </c>
       <c r="AE22">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="AF22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH22">
         <v>38</v>
       </c>
       <c r="AI22">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AJ22">
         <v>9.199999999999999</v>
@@ -6104,13 +6104,13 @@
         <v>15</v>
       </c>
       <c r="AL22">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM22">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN22">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO22">
         <v>390</v>
@@ -6119,16 +6119,16 @@
         <v>20</v>
       </c>
       <c r="AQ22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR22">
         <v>28</v>
       </c>
       <c r="AS22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT22">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU22">
         <v>13</v>
@@ -6137,7 +6137,7 @@
         <v>25</v>
       </c>
       <c r="AW22">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX22">
         <v>6.6</v>
@@ -6149,43 +6149,43 @@
         <v>32</v>
       </c>
       <c r="BA22">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC22">
         <v>13</v>
       </c>
       <c r="BD22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE22">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="BF22">
         <v>4.6</v>
       </c>
       <c r="BG22">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH22">
         <v>4.2</v>
       </c>
       <c r="BI22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ22">
         <v>14</v>
       </c>
       <c r="BK22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN22">
         <v>3.6</v>
@@ -6203,31 +6203,31 @@
         <v>26</v>
       </c>
       <c r="BS22">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BU22">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ22">
         <v>11.5</v>
       </c>
       <c r="CA22">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="s">
         <v>186</v>
@@ -6250,25 +6250,25 @@
         <v>173</v>
       </c>
       <c r="F23">
+        <v>1.11</v>
+      </c>
+      <c r="G23">
         <v>1.12</v>
       </c>
-      <c r="G23">
-        <v>1.13</v>
-      </c>
       <c r="H23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="K23">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6280,49 +6280,49 @@
         <v>1.07</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="R23">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="T23">
         <v>2.14</v>
       </c>
       <c r="U23">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="X23">
         <v>70</v>
       </c>
       <c r="Y23">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="Z23">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AD23">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AE23">
         <v>590</v>
@@ -6331,13 +6331,13 @@
         <v>12</v>
       </c>
       <c r="AG23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH23">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI23">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AJ23">
         <v>9.199999999999999</v>
@@ -6349,85 +6349,85 @@
         <v>40</v>
       </c>
       <c r="AM23">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN23">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AO23">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AQ23">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AR23">
+        <v>110</v>
+      </c>
+      <c r="AS23">
+        <v>110</v>
+      </c>
+      <c r="AT23">
+        <v>18.5</v>
+      </c>
+      <c r="AU23">
+        <v>32</v>
+      </c>
+      <c r="AV23">
         <v>100</v>
       </c>
-      <c r="AS23">
-        <v>100</v>
-      </c>
-      <c r="AT23">
-        <v>18</v>
-      </c>
-      <c r="AU23">
-        <v>28</v>
-      </c>
-      <c r="AV23">
-        <v>90</v>
-      </c>
       <c r="AW23">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AX23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ23">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BA23">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BB23">
         <v>8.800000000000001</v>
       </c>
       <c r="BC23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD23">
         <v>36</v>
       </c>
       <c r="BE23">
+        <v>140</v>
+      </c>
+      <c r="BF23">
+        <v>2.04</v>
+      </c>
+      <c r="BG23">
         <v>100</v>
       </c>
-      <c r="BF23">
-        <v>2.1</v>
-      </c>
-      <c r="BG23">
-        <v>120</v>
-      </c>
       <c r="BH23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BJ23">
         <v>15</v>
       </c>
       <c r="BK23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BL23">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM23">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN23">
         <v>4.2</v>
@@ -6445,31 +6445,31 @@
         <v>19</v>
       </c>
       <c r="BS23">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BT23">
         <v>28</v>
       </c>
       <c r="BU23">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BV23">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BW23">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="BX23">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BY23">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BZ23">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CA23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB23" t="s">
         <v>186</v>
@@ -6504,10 +6504,10 @@
         <v>34</v>
       </c>
       <c r="J24">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="K24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="L24">
         <v>1.11</v>
@@ -6522,16 +6522,16 @@
         <v>1.04</v>
       </c>
       <c r="P24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Q24">
         <v>1.14</v>
       </c>
       <c r="R24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
         <v>1.75</v>
@@ -6552,7 +6552,7 @@
         <v>210</v>
       </c>
       <c r="Z24">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AA24">
         <v>1000</v>
@@ -6561,13 +6561,13 @@
         <v>34</v>
       </c>
       <c r="AC24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD24">
         <v>130</v>
       </c>
       <c r="AE24">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="AF24">
         <v>17.5</v>
@@ -6579,55 +6579,55 @@
         <v>44</v>
       </c>
       <c r="AI24">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ24">
         <v>12.5</v>
       </c>
       <c r="AK24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM24">
         <v>120</v>
       </c>
       <c r="AN24">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AO24">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP24">
         <v>95</v>
       </c>
       <c r="AQ24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AR24">
         <v>55</v>
       </c>
       <c r="AS24">
+        <v>130</v>
+      </c>
+      <c r="AT24">
+        <v>30</v>
+      </c>
+      <c r="AU24">
+        <v>42</v>
+      </c>
+      <c r="AV24">
+        <v>65</v>
+      </c>
+      <c r="AW24">
         <v>120</v>
-      </c>
-      <c r="AT24">
-        <v>29</v>
-      </c>
-      <c r="AU24">
-        <v>38</v>
-      </c>
-      <c r="AV24">
-        <v>75</v>
-      </c>
-      <c r="AW24">
-        <v>85</v>
       </c>
       <c r="AX24">
         <v>16.5</v>
       </c>
       <c r="AY24">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ24">
         <v>40</v>
@@ -6636,49 +6636,49 @@
         <v>95</v>
       </c>
       <c r="BB24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD24">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE24">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF24">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BG24">
         <v>130</v>
       </c>
       <c r="BH24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BI24">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BJ24">
         <v>13.5</v>
       </c>
       <c r="BK24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BL24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BN24">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BQ24">
         <v>5.1</v>
@@ -6690,28 +6690,28 @@
         <v>13</v>
       </c>
       <c r="BT24">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BU24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV24">
         <v>140</v>
       </c>
       <c r="BW24">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BX24">
         <v>80</v>
       </c>
       <c r="BY24">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BZ24">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="CA24">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="CB24" t="s">
         <v>186</v>
@@ -6734,22 +6734,22 @@
         <v>175</v>
       </c>
       <c r="F25">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G25">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H25">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I25">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J25">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K25">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L25">
         <v>1.35</v>
@@ -6758,7 +6758,7 @@
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O25">
         <v>1.23</v>
@@ -6773,7 +6773,7 @@
         <v>1.56</v>
       </c>
       <c r="S25">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T25">
         <v>1.59</v>
@@ -6782,10 +6782,10 @@
         <v>2.64</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X25">
         <v>19.5</v>
@@ -6794,25 +6794,25 @@
         <v>15</v>
       </c>
       <c r="Z25">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA25">
         <v>38</v>
       </c>
       <c r="AB25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC25">
         <v>8.6</v>
       </c>
       <c r="AD25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE25">
         <v>25</v>
       </c>
       <c r="AF25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG25">
         <v>12.5</v>
@@ -6836,25 +6836,25 @@
         <v>55</v>
       </c>
       <c r="AN25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ25">
         <v>14</v>
       </c>
       <c r="AR25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS25">
         <v>34</v>
       </c>
       <c r="AT25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU25">
         <v>8.199999999999999</v>
@@ -6872,13 +6872,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA25">
         <v>29</v>
       </c>
       <c r="BB25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC25">
         <v>25</v>
@@ -6890,16 +6890,16 @@
         <v>48</v>
       </c>
       <c r="BF25">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG25">
         <v>16</v>
       </c>
       <c r="BH25">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ25">
         <v>8.6</v>
@@ -6911,13 +6911,13 @@
         <v>85</v>
       </c>
       <c r="BM25">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN25">
         <v>6</v>
       </c>
       <c r="BO25">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP25">
         <v>19</v>
@@ -6947,13 +6947,13 @@
         <v>27</v>
       </c>
       <c r="BY25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25">
         <v>19</v>
       </c>
       <c r="CA25">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="CB25" t="s">
         <v>186</v>
@@ -6976,61 +6976,61 @@
         <v>176</v>
       </c>
       <c r="F26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G26">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I26">
         <v>2.38</v>
       </c>
       <c r="J26">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K26">
         <v>3.65</v>
       </c>
       <c r="L26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M26">
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O26">
         <v>1.32</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R26">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U26">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V26">
         <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X26">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y26">
         <v>11</v>
@@ -7051,7 +7051,7 @@
         <v>11</v>
       </c>
       <c r="AE26">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AF26">
         <v>23</v>
@@ -7060,31 +7060,31 @@
         <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI26">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ26">
         <v>60</v>
       </c>
       <c r="AK26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM26">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN26">
         <v>34</v>
       </c>
       <c r="AO26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7099,7 +7099,7 @@
         <v>12</v>
       </c>
       <c r="AU26">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
         <v>10.5</v>
@@ -7117,7 +7117,7 @@
         <v>15.5</v>
       </c>
       <c r="BA26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB26">
         <v>50</v>
@@ -7132,70 +7132,70 @@
         <v>65</v>
       </c>
       <c r="BF26">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BG26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH26">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI26">
         <v>3.2</v>
       </c>
       <c r="BJ26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK26">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BN26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BO26">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BT26">
         <v>6.2</v>
       </c>
       <c r="BU26">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV26">
         <v>21</v>
       </c>
       <c r="BW26">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="CB26" t="s">
         <v>186</v>
@@ -7218,16 +7218,16 @@
         <v>177</v>
       </c>
       <c r="F27">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G27">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H27">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I27">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J27">
         <v>4.3</v>
@@ -7236,7 +7236,7 @@
         <v>4.4</v>
       </c>
       <c r="L27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M27">
         <v>1.03</v>
@@ -7248,55 +7248,55 @@
         <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q27">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R27">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S27">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T27">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U27">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="V27">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA27">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -7308,40 +7308,40 @@
         <v>40</v>
       </c>
       <c r="AJ27">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK27">
         <v>16</v>
       </c>
       <c r="AL27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27">
         <v>50</v>
       </c>
       <c r="AN27">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR27">
         <v>38</v>
       </c>
       <c r="AS27">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT27">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV27">
         <v>17</v>
@@ -7350,7 +7350,7 @@
         <v>40</v>
       </c>
       <c r="AX27">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY27">
         <v>9.6</v>
@@ -7359,16 +7359,16 @@
         <v>14</v>
       </c>
       <c r="BA27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC27">
         <v>15</v>
       </c>
       <c r="BD27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE27">
         <v>46</v>
@@ -7383,61 +7383,61 @@
         <v>4.7</v>
       </c>
       <c r="BI27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ27">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK27">
         <v>8</v>
       </c>
       <c r="BL27">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BM27">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BN27">
         <v>5</v>
       </c>
       <c r="BO27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR27">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BS27">
         <v>17</v>
       </c>
       <c r="BT27">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV27">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BX27">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BY27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BZ27">
         <v>13</v>
       </c>
       <c r="CA27">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB27" t="s">
         <v>186</v>
@@ -7460,46 +7460,46 @@
         <v>178</v>
       </c>
       <c r="F28">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H28">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="I28">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L28">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M28">
         <v>1.07</v>
       </c>
       <c r="N28">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O28">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P28">
+        <v>2.02</v>
+      </c>
+      <c r="Q28">
         <v>1.96</v>
       </c>
-      <c r="Q28">
-        <v>1.99</v>
-      </c>
       <c r="R28">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S28">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T28">
         <v>1.95</v>
@@ -7508,52 +7508,52 @@
         <v>2</v>
       </c>
       <c r="V28">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="W28">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y28">
         <v>8.4</v>
       </c>
       <c r="Z28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE28">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF28">
         <v>55</v>
       </c>
       <c r="AG28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI28">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ28">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AK28">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL28">
         <v>85</v>
@@ -7565,82 +7565,82 @@
         <v>120</v>
       </c>
       <c r="AO28">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AP28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR28">
         <v>8.800000000000001</v>
       </c>
       <c r="AS28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV28">
         <v>9.199999999999999</v>
       </c>
       <c r="AW28">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX28">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AY28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ28">
         <v>19</v>
       </c>
       <c r="BA28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB28">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BC28">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BD28">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BE28">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="BF28">
         <v>70</v>
       </c>
       <c r="BG28">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK28">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL28">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM28">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BN28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO28">
         <v>5.6</v>
@@ -7649,13 +7649,13 @@
         <v>65</v>
       </c>
       <c r="BQ28">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR28">
         <v>70</v>
       </c>
       <c r="BS28">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28">
         <v>4.2</v>
@@ -7664,22 +7664,22 @@
         <v>3.8</v>
       </c>
       <c r="BV28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BW28">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX28">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BY28">
         <v>6.8</v>
       </c>
       <c r="BZ28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB28" t="s">
         <v>186</v>
@@ -7702,223 +7702,223 @@
         <v>179</v>
       </c>
       <c r="F29">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="G29">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I29">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M29">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N29">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="O29">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="P29">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="Q29">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="R29">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S29">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="U29">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V29">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W29">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="X29">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y29">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z29">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AA29">
-        <v>600</v>
+        <v>490</v>
       </c>
       <c r="AB29">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD29">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE29">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AF29">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG29">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH29">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI29">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AJ29">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AK29">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL29">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AM29">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN29">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AO29">
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ29">
+        <v>14.5</v>
+      </c>
+      <c r="AR29">
+        <v>9</v>
+      </c>
+      <c r="AS29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT29">
+        <v>4.6</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>16.5</v>
+      </c>
+      <c r="AW29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX29">
+        <v>6.6</v>
+      </c>
+      <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
         <v>17.5</v>
       </c>
-      <c r="AR29">
-        <v>9.4</v>
-      </c>
-      <c r="AS29">
-        <v>10</v>
-      </c>
-      <c r="AT29">
-        <v>4.7</v>
-      </c>
-      <c r="AU29">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV29">
-        <v>9</v>
-      </c>
-      <c r="AW29">
-        <v>10</v>
-      </c>
-      <c r="AX29">
-        <v>6.4</v>
-      </c>
-      <c r="AY29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BA29">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC29">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD29">
         <v>9</v>
       </c>
       <c r="BE29">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF29">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG29">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BH29">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="BI29">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="BJ29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK29">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
+        <v>11</v>
+      </c>
+      <c r="BN29">
+        <v>3.9</v>
+      </c>
+      <c r="BO29">
+        <v>3.3</v>
+      </c>
+      <c r="BP29">
+        <v>13.5</v>
+      </c>
+      <c r="BQ29">
+        <v>6</v>
+      </c>
+      <c r="BR29">
+        <v>48</v>
+      </c>
+      <c r="BS29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT29">
         <v>12</v>
       </c>
-      <c r="BN29">
-        <v>3.75</v>
-      </c>
-      <c r="BO29">
-        <v>3.2</v>
-      </c>
-      <c r="BP29">
-        <v>11.5</v>
-      </c>
-      <c r="BQ29">
-        <v>5.9</v>
-      </c>
-      <c r="BR29">
-        <v>42</v>
-      </c>
-      <c r="BS29">
-        <v>9.6</v>
-      </c>
-      <c r="BT29">
-        <v>13</v>
-      </c>
       <c r="BU29">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ29">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="CA29">
         <v>8.800000000000001</v>
@@ -7944,22 +7944,22 @@
         <v>180</v>
       </c>
       <c r="F30">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H30">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I30">
         <v>4.1</v>
       </c>
       <c r="J30">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L30">
         <v>1.52</v>
@@ -7968,7 +7968,7 @@
         <v>1.1</v>
       </c>
       <c r="N30">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O30">
         <v>1.46</v>
@@ -7995,7 +7995,7 @@
         <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X30">
         <v>10.5</v>
@@ -8013,7 +8013,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC30">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30">
         <v>17.5</v>
@@ -8058,10 +8058,10 @@
         <v>9.4</v>
       </c>
       <c r="AR30">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AS30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT30">
         <v>6.6</v>
@@ -8073,7 +8073,7 @@
         <v>14</v>
       </c>
       <c r="AW30">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8085,25 +8085,25 @@
         <v>18</v>
       </c>
       <c r="BA30">
+        <v>7.6</v>
+      </c>
+      <c r="BB30">
+        <v>14.5</v>
+      </c>
+      <c r="BC30">
+        <v>13.5</v>
+      </c>
+      <c r="BD30">
         <v>7.4</v>
       </c>
-      <c r="BB30">
+      <c r="BE30">
+        <v>8</v>
+      </c>
+      <c r="BF30">
         <v>6.6</v>
       </c>
-      <c r="BC30">
-        <v>6.4</v>
-      </c>
-      <c r="BD30">
-        <v>7.2</v>
-      </c>
-      <c r="BE30">
-        <v>7.8</v>
-      </c>
-      <c r="BF30">
-        <v>6.4</v>
-      </c>
       <c r="BG30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH30">
         <v>2.96</v>
@@ -8115,7 +8115,7 @@
         <v>11.5</v>
       </c>
       <c r="BK30">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8186,64 +8186,64 @@
         <v>181</v>
       </c>
       <c r="F31">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="G31">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I31">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J31">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K31">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L31">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N31">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O31">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q31">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S31">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T31">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U31">
         <v>1.66</v>
       </c>
       <c r="V31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W31">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Y31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z31">
         <v>40</v>
@@ -8255,31 +8255,31 @@
         <v>7.6</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD31">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE31">
         <v>500</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG31">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI31">
         <v>500</v>
       </c>
       <c r="AJ31">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK31">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL31">
         <v>200</v>
@@ -8288,118 +8288,118 @@
         <v>500</v>
       </c>
       <c r="AN31">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO31">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="AP31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR31">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AS31">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT31">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AU31">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW31">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX31">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AY31">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31">
+        <v>4.9</v>
+      </c>
+      <c r="BA31">
+        <v>4.9</v>
+      </c>
+      <c r="BB31">
+        <v>18</v>
+      </c>
+      <c r="BC31">
         <v>21</v>
       </c>
-      <c r="BA31">
-        <v>5.8</v>
-      </c>
-      <c r="BB31">
-        <v>21</v>
-      </c>
-      <c r="BC31">
-        <v>23</v>
-      </c>
       <c r="BD31">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BE31">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BF31">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG31">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH31">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI31">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="BJ31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BN31">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO31">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BP31">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR31">
         <v>1000</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BT31">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU31">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8437,10 +8437,10 @@
         <v>6.4</v>
       </c>
       <c r="I32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
         <v>4.5</v>
@@ -8458,25 +8458,25 @@
         <v>1.31</v>
       </c>
       <c r="P32">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S32">
         <v>3.4</v>
       </c>
       <c r="T32">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U32">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W32">
         <v>2.6</v>
@@ -8485,13 +8485,13 @@
         <v>17</v>
       </c>
       <c r="Y32">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="Z32">
         <v>65</v>
       </c>
       <c r="AA32">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -8500,7 +8500,7 @@
         <v>10.5</v>
       </c>
       <c r="AD32">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AE32">
         <v>700</v>
@@ -8530,22 +8530,22 @@
         <v>580</v>
       </c>
       <c r="AN32">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO32">
         <v>700</v>
       </c>
       <c r="AP32">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ32">
         <v>10.5</v>
       </c>
       <c r="AR32">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AS32">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT32">
         <v>7</v>
@@ -8557,7 +8557,7 @@
         <v>13</v>
       </c>
       <c r="AW32">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32">
         <v>8</v>
@@ -8566,58 +8566,58 @@
         <v>8.6</v>
       </c>
       <c r="AZ32">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BA32">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BB32">
         <v>13</v>
       </c>
       <c r="BC32">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD32">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE32">
         <v>7.8</v>
       </c>
       <c r="BF32">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG32">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH32">
         <v>3.95</v>
       </c>
       <c r="BI32">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ32">
         <v>12.5</v>
       </c>
       <c r="BK32">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BN32">
         <v>4.6</v>
       </c>
       <c r="BO32">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ32">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR32">
         <v>32</v>
@@ -8629,13 +8629,13 @@
         <v>11.5</v>
       </c>
       <c r="BU32">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW32">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX32">
         <v>75</v>
@@ -8644,7 +8644,7 @@
         <v>5.4</v>
       </c>
       <c r="BZ32">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA32">
         <v>4.6</v>
@@ -8682,37 +8682,37 @@
         <v>4.8</v>
       </c>
       <c r="J33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K33">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L33">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M33">
         <v>1.14</v>
       </c>
       <c r="N33">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P33">
         <v>1.5</v>
       </c>
       <c r="Q33">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S33">
         <v>6.2</v>
       </c>
       <c r="T33">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U33">
         <v>1.69</v>
@@ -8721,61 +8721,61 @@
         <v>1.26</v>
       </c>
       <c r="W33">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z33">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA33">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="AB33">
         <v>6.4</v>
       </c>
       <c r="AC33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD33">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE33">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AF33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
       </c>
       <c r="AH33">
+        <v>27</v>
+      </c>
+      <c r="AI33">
+        <v>130</v>
+      </c>
+      <c r="AJ33">
         <v>28</v>
       </c>
-      <c r="AI33">
-        <v>140</v>
-      </c>
-      <c r="AJ33">
-        <v>34</v>
-      </c>
       <c r="AK33">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL33">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM33">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AN33">
         <v>32</v>
       </c>
       <c r="AO33">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AP33">
         <v>7</v>
@@ -8784,88 +8784,88 @@
         <v>10.5</v>
       </c>
       <c r="AR33">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AS33">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AT33">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU33">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW33">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AX33">
         <v>10</v>
       </c>
       <c r="AY33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ33">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA33">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB33">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BC33">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BD33">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BE33">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BF33">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BG33">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BH33">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="BI33">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ33">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BN33">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ33">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BR33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS33">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT33">
         <v>7.8</v>
@@ -8877,19 +8877,19 @@
         <v>55</v>
       </c>
       <c r="BW33">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BX33">
         <v>95</v>
       </c>
       <c r="BY33">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ33">
         <v>55</v>
       </c>
       <c r="CA33">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="CB33" t="s">
         <v>186</v>
@@ -8912,31 +8912,31 @@
         <v>184</v>
       </c>
       <c r="F34">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G34">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H34">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I34">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J34">
         <v>3.7</v>
       </c>
       <c r="K34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L34">
         <v>1.46</v>
       </c>
       <c r="M34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N34">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O34">
         <v>1.39</v>
@@ -8954,16 +8954,16 @@
         <v>4.1</v>
       </c>
       <c r="T34">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U34">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V34">
         <v>1.22</v>
       </c>
       <c r="W34">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X34">
         <v>12</v>
@@ -8975,22 +8975,22 @@
         <v>40</v>
       </c>
       <c r="AA34">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB34">
         <v>7.6</v>
       </c>
       <c r="AC34">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD34">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG34">
         <v>10.5</v>
@@ -9026,10 +9026,10 @@
         <v>14</v>
       </c>
       <c r="AR34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS34">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="AT34">
         <v>7</v>
@@ -9041,7 +9041,7 @@
         <v>18.5</v>
       </c>
       <c r="AW34">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AX34">
         <v>9.199999999999999</v>
@@ -9053,10 +9053,10 @@
         <v>20</v>
       </c>
       <c r="BA34">
+        <v>55</v>
+      </c>
+      <c r="BB34">
         <v>17</v>
-      </c>
-      <c r="BB34">
-        <v>17.5</v>
       </c>
       <c r="BC34">
         <v>18.5</v>
@@ -9065,16 +9065,16 @@
         <v>38</v>
       </c>
       <c r="BE34">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="BF34">
         <v>12.5</v>
       </c>
       <c r="BG34">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH34">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI34">
         <v>2.9</v>
@@ -9089,13 +9089,13 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN34">
         <v>4.3</v>
       </c>
       <c r="BO34">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP34">
         <v>13</v>
@@ -9107,31 +9107,31 @@
         <v>32</v>
       </c>
       <c r="BS34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT34">
         <v>8.800000000000001</v>
       </c>
       <c r="BU34">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV34">
         <v>55</v>
       </c>
       <c r="BW34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX34">
         <v>65</v>
       </c>
       <c r="BY34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ34">
         <v>28</v>
       </c>
       <c r="CA34">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB34" t="s">
         <v>186</v>
@@ -9154,10 +9154,10 @@
         <v>185</v>
       </c>
       <c r="F35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G35">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H35">
         <v>4</v>
@@ -9169,7 +9169,7 @@
         <v>3.65</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L35">
         <v>1.37</v>
@@ -9184,16 +9184,16 @@
         <v>1.28</v>
       </c>
       <c r="P35">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
         <v>1.83</v>
       </c>
       <c r="R35">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S35">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T35">
         <v>1.73</v>
@@ -9205,13 +9205,13 @@
         <v>1.28</v>
       </c>
       <c r="W35">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X35">
         <v>20</v>
       </c>
       <c r="Y35">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z35">
         <v>34</v>
@@ -9271,7 +9271,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT35">
         <v>8.4</v>
@@ -9283,7 +9283,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX35">
         <v>10.5</v>
@@ -9295,7 +9295,7 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB35">
         <v>19</v>
@@ -9307,13 +9307,13 @@
         <v>16</v>
       </c>
       <c r="BE35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF35">
         <v>10.5</v>
       </c>
       <c r="BG35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH35">
         <v>3.75</v>
@@ -9331,7 +9331,7 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN35">
         <v>4.9</v>
@@ -9349,7 +9349,7 @@
         <v>27</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT35">
         <v>8</v>
@@ -9361,13 +9361,13 @@
         <v>36</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX35">
         <v>44</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ35">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-10.xlsx
@@ -574,7 +574,7 @@
     <t>Cobreloa Calama</t>
   </si>
   <si>
-    <t>2026-09-10 08:10:17</t>
+    <t>2026-09-10 10:31:41</t>
   </si>
 </sst>
 </file>
@@ -1168,226 +1168,226 @@
         <v>152</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="G2">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>2.32</v>
       </c>
       <c r="I2">
-        <v>2.46</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>1.21</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="Q2">
+        <v>4.8</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>50</v>
+      </c>
+      <c r="T2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="U2">
+        <v>1.12</v>
+      </c>
+      <c r="V2">
+        <v>1.6</v>
+      </c>
+      <c r="W2">
+        <v>1.15</v>
+      </c>
+      <c r="X2">
+        <v>2.58</v>
+      </c>
+      <c r="Y2">
+        <v>3.9</v>
+      </c>
+      <c r="Z2">
+        <v>20</v>
+      </c>
+      <c r="AA2">
+        <v>210</v>
+      </c>
+      <c r="AB2">
+        <v>8.4</v>
+      </c>
+      <c r="AC2">
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <v>95</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>310</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.24</v>
+      </c>
+      <c r="AQ2">
+        <v>2.98</v>
+      </c>
+      <c r="AR2">
+        <v>4.1</v>
+      </c>
+      <c r="AS2">
+        <v>3.95</v>
+      </c>
+      <c r="AT2">
+        <v>5</v>
+      </c>
+      <c r="AU2">
+        <v>4.2</v>
+      </c>
+      <c r="AV2">
+        <v>3.95</v>
+      </c>
+      <c r="AW2">
+        <v>6</v>
+      </c>
+      <c r="AX2">
+        <v>3.25</v>
+      </c>
+      <c r="AY2">
+        <v>3.95</v>
+      </c>
+      <c r="AZ2">
         <v>2.14</v>
       </c>
-      <c r="R2">
-        <v>1.33</v>
-      </c>
-      <c r="S2">
-        <v>3.7</v>
-      </c>
-      <c r="T2">
-        <v>1.81</v>
-      </c>
-      <c r="U2">
-        <v>2.1</v>
-      </c>
-      <c r="V2">
-        <v>1.68</v>
-      </c>
-      <c r="W2">
-        <v>1.35</v>
-      </c>
-      <c r="X2">
-        <v>12</v>
-      </c>
-      <c r="Y2">
-        <v>10.5</v>
-      </c>
-      <c r="Z2">
-        <v>15.5</v>
-      </c>
-      <c r="AA2">
-        <v>34</v>
-      </c>
-      <c r="AB2">
-        <v>14</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
-      </c>
-      <c r="AD2">
-        <v>12</v>
-      </c>
-      <c r="AE2">
-        <v>27</v>
-      </c>
-      <c r="AF2">
-        <v>26</v>
-      </c>
-      <c r="AG2">
-        <v>15.5</v>
-      </c>
-      <c r="AH2">
-        <v>17.5</v>
-      </c>
-      <c r="AI2">
-        <v>42</v>
-      </c>
-      <c r="AJ2">
-        <v>100</v>
-      </c>
-      <c r="AK2">
-        <v>85</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>200</v>
-      </c>
-      <c r="AN2">
-        <v>55</v>
-      </c>
-      <c r="AO2">
-        <v>23</v>
-      </c>
-      <c r="AP2">
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR2">
-        <v>13</v>
-      </c>
-      <c r="AS2">
-        <v>25</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>21</v>
-      </c>
-      <c r="AX2">
-        <v>19.5</v>
-      </c>
-      <c r="AY2">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
       <c r="BA2">
-        <v>23</v>
+        <v>2.14</v>
       </c>
       <c r="BB2">
-        <v>23</v>
+        <v>3.95</v>
       </c>
       <c r="BC2">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>2.14</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>2.14</v>
       </c>
       <c r="BF2">
-        <v>8.6</v>
+        <v>2.14</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>186</v>
@@ -1410,226 +1410,226 @@
         <v>153</v>
       </c>
       <c r="F3">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G3">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="I3">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="J3">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="K3">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M3">
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="O3">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P3">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="R3">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="S3">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="T3">
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB3">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AC3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3">
         <v>14</v>
       </c>
       <c r="AF3">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AG3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ3">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AK3">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AO3">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AP3">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
         <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AU3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AY3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3">
         <v>22</v>
       </c>
       <c r="BB3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BC3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BD3">
+        <v>50</v>
+      </c>
+      <c r="BE3">
+        <v>60</v>
+      </c>
+      <c r="BF3">
+        <v>55</v>
+      </c>
+      <c r="BG3">
+        <v>4.1</v>
+      </c>
+      <c r="BH3">
+        <v>6</v>
+      </c>
+      <c r="BI3">
+        <v>4.8</v>
+      </c>
+      <c r="BJ3">
+        <v>10.5</v>
+      </c>
+      <c r="BK3">
+        <v>4.7</v>
+      </c>
+      <c r="BL3">
+        <v>90</v>
+      </c>
+      <c r="BM3">
+        <v>6.8</v>
+      </c>
+      <c r="BN3">
+        <v>12</v>
+      </c>
+      <c r="BO3">
+        <v>10</v>
+      </c>
+      <c r="BP3">
+        <v>55</v>
+      </c>
+      <c r="BQ3">
+        <v>6.6</v>
+      </c>
+      <c r="BR3">
         <v>46</v>
       </c>
-      <c r="BE3">
-        <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>50</v>
-      </c>
-      <c r="BG3">
-        <v>3.15</v>
-      </c>
-      <c r="BH3">
-        <v>6.8</v>
-      </c>
-      <c r="BI3">
-        <v>4.7</v>
-      </c>
-      <c r="BJ3">
-        <v>12</v>
-      </c>
-      <c r="BK3">
+      <c r="BS3">
+        <v>7</v>
+      </c>
+      <c r="BT3">
+        <v>4.9</v>
+      </c>
+      <c r="BU3">
         <v>4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>5.7</v>
-      </c>
-      <c r="BN3">
-        <v>15.5</v>
-      </c>
-      <c r="BO3">
-        <v>4.4</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>5.6</v>
-      </c>
-      <c r="BR3">
-        <v>55</v>
-      </c>
-      <c r="BS3">
-        <v>5.5</v>
-      </c>
-      <c r="BT3">
-        <v>4.7</v>
-      </c>
-      <c r="BU3">
-        <v>4.1</v>
       </c>
       <c r="BV3">
         <v>8.4</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BZ3">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="CA3">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>186</v>
@@ -1652,28 +1652,28 @@
         <v>154</v>
       </c>
       <c r="F4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
         <v>1.29</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>5.8</v>
@@ -1682,7 +1682,7 @@
         <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q4">
         <v>1.58</v>
@@ -1694,31 +1694,31 @@
         <v>2.48</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4">
         <v>12</v>
@@ -1727,46 +1727,46 @@
         <v>23</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI4">
         <v>65</v>
       </c>
       <c r="AJ4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL4">
         <v>28</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN4">
         <v>6.2</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS4">
         <v>100</v>
@@ -1775,103 +1775,103 @@
         <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB4">
+        <v>13</v>
+      </c>
+      <c r="BC4">
         <v>13.5</v>
       </c>
-      <c r="BC4">
-        <v>13</v>
-      </c>
       <c r="BD4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BJ4">
         <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ4">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR4">
         <v>21</v>
       </c>
       <c r="BS4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT4">
         <v>10</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>46</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>46</v>
       </c>
       <c r="BY4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>13.5</v>
       </c>
       <c r="CA4">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="s">
         <v>186</v>
@@ -1894,16 +1894,16 @@
         <v>155</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H5">
         <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1912,7 +1912,7 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1924,28 +1924,28 @@
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S5">
         <v>2.32</v>
       </c>
       <c r="T5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1954,37 +1954,37 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5">
+        <v>29</v>
+      </c>
+      <c r="AF5">
+        <v>19</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
         <v>14.5</v>
-      </c>
-      <c r="AE5">
-        <v>32</v>
-      </c>
-      <c r="AF5">
-        <v>19.5</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>14</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AK5">
         <v>20</v>
@@ -2002,7 +2002,7 @@
         <v>18</v>
       </c>
       <c r="AP5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ5">
         <v>18.5</v>
@@ -2017,7 +2017,7 @@
         <v>15</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5">
         <v>12.5</v>
@@ -2026,10 +2026,10 @@
         <v>25</v>
       </c>
       <c r="AX5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
         <v>13</v>
@@ -2038,19 +2038,19 @@
         <v>28</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC5">
         <v>18</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG5">
         <v>15.5</v>
@@ -2059,7 +2059,7 @@
         <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ5">
         <v>8.199999999999999</v>
@@ -2071,7 +2071,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN5">
         <v>5.7</v>
@@ -2089,22 +2089,22 @@
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW5">
         <v>10</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BY5">
         <v>11</v>
@@ -2113,7 +2113,7 @@
         <v>14.5</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="s">
         <v>186</v>
@@ -2136,226 +2136,226 @@
         <v>156</v>
       </c>
       <c r="F6">
+        <v>1.35</v>
+      </c>
+      <c r="G6">
         <v>1.38</v>
       </c>
-      <c r="G6">
-        <v>1.41</v>
-      </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L6">
         <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S6">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
+        <v>2.02</v>
+      </c>
+      <c r="U6">
         <v>1.92</v>
       </c>
-      <c r="U6">
-        <v>1.88</v>
-      </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="X6">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="Y6">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="Z6">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB6">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD6">
+        <v>40</v>
+      </c>
+      <c r="AE6">
+        <v>190</v>
+      </c>
+      <c r="AF6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>29</v>
+      </c>
+      <c r="AI6">
+        <v>160</v>
+      </c>
+      <c r="AJ6">
+        <v>10.5</v>
+      </c>
+      <c r="AK6">
+        <v>14.5</v>
+      </c>
+      <c r="AL6">
+        <v>38</v>
+      </c>
+      <c r="AM6">
+        <v>160</v>
+      </c>
+      <c r="AN6">
+        <v>5.2</v>
+      </c>
+      <c r="AO6">
+        <v>200</v>
+      </c>
+      <c r="AP6">
+        <v>20</v>
+      </c>
+      <c r="AQ6">
+        <v>32</v>
+      </c>
+      <c r="AR6">
+        <v>75</v>
+      </c>
+      <c r="AS6">
+        <v>15</v>
+      </c>
+      <c r="AT6">
+        <v>9</v>
+      </c>
+      <c r="AU6">
+        <v>11.5</v>
+      </c>
+      <c r="AV6">
+        <v>32</v>
+      </c>
+      <c r="AW6">
         <v>85</v>
       </c>
-      <c r="AE6">
-        <v>400</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>320</v>
-      </c>
-      <c r="AJ6">
-        <v>900</v>
-      </c>
-      <c r="AK6">
-        <v>970</v>
-      </c>
-      <c r="AL6">
-        <v>85</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>29</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.58</v>
-      </c>
-      <c r="AQ6">
-        <v>4.2</v>
-      </c>
-      <c r="AR6">
-        <v>4.2</v>
-      </c>
-      <c r="AS6">
-        <v>4.2</v>
-      </c>
-      <c r="AT6">
-        <v>4.9</v>
-      </c>
-      <c r="AU6">
-        <v>5.2</v>
-      </c>
-      <c r="AV6">
-        <v>4.2</v>
-      </c>
-      <c r="AW6">
-        <v>4.2</v>
-      </c>
       <c r="AX6">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="AY6">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.62</v>
+        <v>22</v>
       </c>
       <c r="BA6">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="BB6">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>1.59</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>1.6</v>
+        <v>75</v>
       </c>
       <c r="BF6">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>95</v>
       </c>
       <c r="BH6">
         <v>5</v>
       </c>
       <c r="BI6">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6">
         <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BN6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO6">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP6">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ6">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
         <v>27</v>
       </c>
       <c r="BS6">
+        <v>4.6</v>
+      </c>
+      <c r="BT6">
+        <v>16</v>
+      </c>
+      <c r="BU6">
         <v>4</v>
-      </c>
-      <c r="BT6">
-        <v>14.5</v>
-      </c>
-      <c r="BU6">
-        <v>3.6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CA6">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="CB6" t="s">
         <v>186</v>
@@ -2378,19 +2378,19 @@
         <v>157</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -2402,88 +2402,88 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="T7">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="X7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
         <v>27</v>
       </c>
       <c r="AA7">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
         <v>34</v>
       </c>
       <c r="AK7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL7">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AP7">
         <v>6</v>
@@ -2492,16 +2492,16 @@
         <v>5.7</v>
       </c>
       <c r="AR7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT7">
         <v>4.4</v>
       </c>
       <c r="AU7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AV7">
         <v>6.2</v>
@@ -2516,88 +2516,88 @@
         <v>4.9</v>
       </c>
       <c r="AZ7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA7">
         <v>5.4</v>
       </c>
       <c r="BB7">
+        <v>5.2</v>
+      </c>
+      <c r="BC7">
+        <v>5</v>
+      </c>
+      <c r="BD7">
+        <v>5.3</v>
+      </c>
+      <c r="BE7">
+        <v>5.7</v>
+      </c>
+      <c r="BF7">
+        <v>4.4</v>
+      </c>
+      <c r="BG7">
         <v>5.1</v>
       </c>
-      <c r="BC7">
-        <v>4.9</v>
-      </c>
-      <c r="BD7">
-        <v>5.2</v>
-      </c>
-      <c r="BE7">
-        <v>5.6</v>
-      </c>
-      <c r="BF7">
-        <v>4.6</v>
-      </c>
-      <c r="BG7">
-        <v>5.3</v>
-      </c>
       <c r="BH7">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="BP7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>186</v>
@@ -2620,139 +2620,139 @@
         <v>158</v>
       </c>
       <c r="F8">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="G8">
+        <v>2.8</v>
+      </c>
+      <c r="H8">
+        <v>2.86</v>
+      </c>
+      <c r="I8">
+        <v>3.05</v>
+      </c>
+      <c r="J8">
         <v>3.25</v>
       </c>
-      <c r="H8">
-        <v>2.48</v>
-      </c>
-      <c r="I8">
-        <v>2.66</v>
-      </c>
-      <c r="J8">
-        <v>3.3</v>
-      </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S8">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T8">
         <v>1.8</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA8">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
+        <v>50</v>
+      </c>
+      <c r="AJ8">
+        <v>46</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
         <v>65</v>
-      </c>
-      <c r="AJ8">
-        <v>65</v>
-      </c>
-      <c r="AK8">
-        <v>40</v>
-      </c>
-      <c r="AL8">
-        <v>75</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS8">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AT8">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
@@ -2761,79 +2761,79 @@
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD8">
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG8">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BH8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI8">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
+        <v>38</v>
+      </c>
+      <c r="BS8">
+        <v>8.6</v>
+      </c>
+      <c r="BT8">
+        <v>6</v>
+      </c>
+      <c r="BU8">
+        <v>4.6</v>
+      </c>
+      <c r="BV8">
+        <v>24</v>
+      </c>
+      <c r="BW8">
+        <v>7.6</v>
+      </c>
+      <c r="BX8">
         <v>40</v>
       </c>
-      <c r="BS8">
+      <c r="BY8">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BT8">
-        <v>5.6</v>
-      </c>
-      <c r="BU8">
-        <v>4.4</v>
-      </c>
-      <c r="BV8">
-        <v>21</v>
-      </c>
-      <c r="BW8">
-        <v>7.2</v>
-      </c>
-      <c r="BX8">
-        <v>38</v>
-      </c>
-      <c r="BY8">
-        <v>8.6</v>
       </c>
       <c r="BZ8">
         <v>34</v>
@@ -2862,22 +2862,22 @@
         <v>159</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="G9">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H9">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
         <v>3.75</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.37</v>
@@ -2889,58 +2889,58 @@
         <v>4.3</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
         <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA9">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AB9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE9">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
@@ -2949,25 +2949,25 @@
         <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ9">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AK9">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AP9">
         <v>15</v>
@@ -2976,25 +2976,25 @@
         <v>12.5</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AT9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
         <v>7.6</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY9">
         <v>9.6</v>
@@ -3003,34 +3003,34 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF9">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG9">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI9">
         <v>3.4</v>
       </c>
       <c r="BJ9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK9">
         <v>6.8</v>
@@ -3039,37 +3039,37 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
         <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -3081,7 +3081,7 @@
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="s">
         <v>186</v>
@@ -3104,31 +3104,31 @@
         <v>160</v>
       </c>
       <c r="F10">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="H10">
+        <v>1.23</v>
+      </c>
+      <c r="I10">
+        <v>1.25</v>
+      </c>
+      <c r="J10">
+        <v>7.8</v>
+      </c>
+      <c r="K10">
+        <v>9</v>
+      </c>
+      <c r="L10">
         <v>1.18</v>
-      </c>
-      <c r="I10">
-        <v>1.2</v>
-      </c>
-      <c r="J10">
-        <v>9</v>
-      </c>
-      <c r="K10">
-        <v>10.5</v>
-      </c>
-      <c r="L10">
-        <v>1.17</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>1.09</v>
@@ -3137,193 +3137,193 @@
         <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R10">
         <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="T10">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Y10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z10">
         <v>13</v>
       </c>
       <c r="AA10">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AB10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AC10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE10">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AF10">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AG10">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AH10">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI10">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AK10">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AL10">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AM10">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AN10">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AO10">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="AP10">
         <v>20</v>
       </c>
       <c r="AQ10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR10">
+        <v>10.5</v>
+      </c>
+      <c r="AS10">
+        <v>9.4</v>
+      </c>
+      <c r="AT10">
+        <v>32</v>
+      </c>
+      <c r="AU10">
+        <v>18.5</v>
+      </c>
+      <c r="AV10">
+        <v>11.5</v>
+      </c>
+      <c r="AW10">
+        <v>11.5</v>
+      </c>
+      <c r="AX10">
+        <v>10.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10">
+        <v>12.5</v>
+      </c>
+      <c r="BA10">
+        <v>18.5</v>
+      </c>
+      <c r="BB10">
+        <v>11</v>
+      </c>
+      <c r="BC10">
+        <v>10.5</v>
+      </c>
+      <c r="BD10">
         <v>10</v>
       </c>
-      <c r="AS10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT10">
-        <v>9</v>
-      </c>
-      <c r="AU10">
-        <v>20</v>
-      </c>
-      <c r="AV10">
-        <v>12</v>
-      </c>
-      <c r="AW10">
-        <v>12</v>
-      </c>
-      <c r="AX10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>30</v>
-      </c>
-      <c r="AZ10">
-        <v>19.5</v>
-      </c>
-      <c r="BA10">
-        <v>23</v>
-      </c>
-      <c r="BB10">
-        <v>9</v>
-      </c>
-      <c r="BC10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD10">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BH10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BI10">
+        <v>5.7</v>
+      </c>
+      <c r="BJ10">
+        <v>11.5</v>
+      </c>
+      <c r="BK10">
+        <v>4.3</v>
+      </c>
+      <c r="BL10">
+        <v>100</v>
+      </c>
+      <c r="BM10">
+        <v>6.4</v>
+      </c>
+      <c r="BN10">
+        <v>18</v>
+      </c>
+      <c r="BO10">
         <v>4.9</v>
       </c>
-      <c r="BJ10">
-        <v>15</v>
-      </c>
-      <c r="BK10">
-        <v>3.9</v>
-      </c>
-      <c r="BL10">
-        <v>130</v>
-      </c>
-      <c r="BM10">
-        <v>5</v>
-      </c>
-      <c r="BN10">
-        <v>25</v>
-      </c>
-      <c r="BO10">
-        <v>4.3</v>
-      </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BQ10">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BR10">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="BS10">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BT10">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BU10">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BV10">
         <v>7.4</v>
       </c>
       <c r="BW10">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX10">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BY10">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BZ10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="CA10">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="s">
         <v>186</v>
@@ -3346,52 +3346,52 @@
         <v>161</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="G11">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="H11">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="I11">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R11">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S11">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T11">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="U11">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3400,46 +3400,46 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z11">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AK11">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL11">
         <v>26</v>
@@ -3448,76 +3448,76 @@
         <v>200</v>
       </c>
       <c r="AN11">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AO11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AP11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
+        <v>18</v>
+      </c>
+      <c r="AR11">
+        <v>25</v>
+      </c>
+      <c r="AS11">
+        <v>46</v>
+      </c>
+      <c r="AT11">
+        <v>12</v>
+      </c>
+      <c r="AU11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV11">
+        <v>13.5</v>
+      </c>
+      <c r="AW11">
+        <v>30</v>
+      </c>
+      <c r="AX11">
+        <v>12</v>
+      </c>
+      <c r="AY11">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11">
+        <v>28</v>
+      </c>
+      <c r="BB11">
         <v>20</v>
       </c>
-      <c r="AR11">
-        <v>34</v>
-      </c>
-      <c r="AS11">
-        <v>65</v>
-      </c>
-      <c r="AT11">
-        <v>10.5</v>
-      </c>
-      <c r="AU11">
-        <v>10</v>
-      </c>
-      <c r="AV11">
-        <v>17</v>
-      </c>
-      <c r="AW11">
-        <v>36</v>
-      </c>
-      <c r="AX11">
-        <v>10.5</v>
-      </c>
-      <c r="AY11">
-        <v>9</v>
-      </c>
-      <c r="AZ11">
-        <v>15.5</v>
-      </c>
-      <c r="BA11">
-        <v>32</v>
-      </c>
-      <c r="BB11">
-        <v>15</v>
-      </c>
       <c r="BC11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD11">
         <v>22</v>
       </c>
       <c r="BE11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF11">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="BH11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BJ11">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3526,46 +3526,46 @@
         <v>13</v>
       </c>
       <c r="BN11">
+        <v>5.2</v>
+      </c>
+      <c r="BO11">
         <v>4.7</v>
       </c>
-      <c r="BO11">
-        <v>3.8</v>
-      </c>
       <c r="BP11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BQ11">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX11">
+        <v>32</v>
+      </c>
+      <c r="BY11">
         <v>10.5</v>
       </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>11</v>
-      </c>
       <c r="BZ11">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA11">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="s">
         <v>186</v>
@@ -3591,7 +3591,7 @@
         <v>1.53</v>
       </c>
       <c r="G12">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H12">
         <v>6.6</v>
@@ -3600,40 +3600,40 @@
         <v>6.8</v>
       </c>
       <c r="J12">
+        <v>4.9</v>
+      </c>
+      <c r="K12">
         <v>5</v>
       </c>
-      <c r="K12">
-        <v>5.1</v>
-      </c>
       <c r="L12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R12">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T12">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
         <v>1.17</v>
@@ -3654,22 +3654,22 @@
         <v>160</v>
       </c>
       <c r="AB12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE12">
         <v>70</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH12">
         <v>17</v>
@@ -3687,13 +3687,13 @@
         <v>23</v>
       </c>
       <c r="AM12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AP12">
         <v>30</v>
@@ -3717,13 +3717,13 @@
         <v>22</v>
       </c>
       <c r="AW12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
         <v>16.5</v>
@@ -3744,31 +3744,31 @@
         <v>55</v>
       </c>
       <c r="BF12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH12">
         <v>4.8</v>
       </c>
       <c r="BI12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK12">
         <v>8.6</v>
       </c>
       <c r="BL12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BM12">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BN12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO12">
         <v>4.2</v>
@@ -3795,19 +3795,19 @@
         <v>42</v>
       </c>
       <c r="BW12">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BX12">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BY12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BZ12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
         <v>186</v>
@@ -3830,61 +3830,61 @@
         <v>163</v>
       </c>
       <c r="F13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H13">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q13">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R13">
+        <v>1.59</v>
+      </c>
+      <c r="S13">
+        <v>2.64</v>
+      </c>
+      <c r="T13">
         <v>1.58</v>
-      </c>
-      <c r="S13">
-        <v>2.66</v>
-      </c>
-      <c r="T13">
-        <v>1.59</v>
       </c>
       <c r="U13">
         <v>2.66</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="W13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y13">
         <v>13.5</v>
@@ -3893,34 +3893,34 @@
         <v>15.5</v>
       </c>
       <c r="AA13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
       </c>
       <c r="AE13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ13">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK13">
         <v>36</v>
@@ -3929,28 +3929,28 @@
         <v>38</v>
       </c>
       <c r="AM13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR13">
         <v>15</v>
       </c>
       <c r="AS13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU13">
         <v>8.199999999999999</v>
@@ -3959,19 +3959,19 @@
         <v>10</v>
       </c>
       <c r="AW13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX13">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AY13">
         <v>14</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB13">
         <v>60</v>
@@ -3983,19 +3983,19 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG13">
         <v>10.5</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13">
         <v>8.6</v>
@@ -4004,19 +4004,19 @@
         <v>7.8</v>
       </c>
       <c r="BL13">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM13">
-        <v>15.5</v>
+        <v>65</v>
       </c>
       <c r="BN13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
         <v>22</v>
@@ -4025,16 +4025,16 @@
         <v>30</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BT13">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU13">
         <v>4.8</v>
       </c>
       <c r="BV13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BW13">
         <v>12.5</v>
@@ -4046,10 +4046,10 @@
         <v>20</v>
       </c>
       <c r="BZ13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CB13" t="s">
         <v>186</v>
@@ -4072,226 +4072,226 @@
         <v>164</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="G14">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="H14">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P14">
+        <v>1.97</v>
+      </c>
+      <c r="Q14">
+        <v>1.98</v>
+      </c>
+      <c r="R14">
+        <v>1.37</v>
+      </c>
+      <c r="S14">
+        <v>3.5</v>
+      </c>
+      <c r="T14">
+        <v>1.9</v>
+      </c>
+      <c r="U14">
         <v>2.04</v>
       </c>
-      <c r="Q14">
-        <v>1.9</v>
-      </c>
-      <c r="R14">
-        <v>1.41</v>
-      </c>
-      <c r="S14">
-        <v>3.35</v>
-      </c>
-      <c r="T14">
-        <v>1.79</v>
-      </c>
-      <c r="U14">
-        <v>2.18</v>
-      </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W14">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y14">
         <v>17</v>
       </c>
       <c r="Z14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA14">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB14">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ14">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN14">
         <v>12.5</v>
       </c>
       <c r="AO14">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14">
         <v>15.5</v>
       </c>
       <c r="AR14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT14">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AX14">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB14">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE14">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BF14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG14">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BH14">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BI14">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14">
         <v>10</v>
       </c>
       <c r="BK14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BN14">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO14">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP14">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ14">
         <v>7.2</v>
       </c>
       <c r="BR14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS14">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT14">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU14">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BV14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BW14">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BY14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA14">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="s">
         <v>186</v>
@@ -4314,118 +4314,118 @@
         <v>165</v>
       </c>
       <c r="F15">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H15">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I15">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P15">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R15">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T15">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U15">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V15">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15">
         <v>15.5</v>
       </c>
       <c r="AA15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>11</v>
       </c>
       <c r="AE15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF15">
+        <v>27</v>
+      </c>
+      <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>16</v>
+      </c>
+      <c r="AI15">
+        <v>30</v>
+      </c>
+      <c r="AJ15">
+        <v>80</v>
+      </c>
+      <c r="AK15">
+        <v>38</v>
+      </c>
+      <c r="AL15">
+        <v>42</v>
+      </c>
+      <c r="AM15">
+        <v>70</v>
+      </c>
+      <c r="AN15">
         <v>29</v>
       </c>
-      <c r="AG15">
-        <v>15.5</v>
-      </c>
-      <c r="AH15">
-        <v>15.5</v>
-      </c>
-      <c r="AI15">
-        <v>28</v>
-      </c>
-      <c r="AJ15">
-        <v>65</v>
-      </c>
-      <c r="AK15">
-        <v>36</v>
-      </c>
-      <c r="AL15">
-        <v>40</v>
-      </c>
-      <c r="AM15">
-        <v>65</v>
-      </c>
-      <c r="AN15">
-        <v>28</v>
-      </c>
       <c r="AO15">
+        <v>12.5</v>
+      </c>
+      <c r="AP15">
+        <v>17.5</v>
+      </c>
+      <c r="AQ15">
         <v>11</v>
-      </c>
-      <c r="AP15">
-        <v>19</v>
-      </c>
-      <c r="AQ15">
-        <v>11.5</v>
       </c>
       <c r="AR15">
         <v>13.5</v>
@@ -4434,10 +4434,10 @@
         <v>22</v>
       </c>
       <c r="AT15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU15">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV15">
         <v>9.800000000000001</v>
@@ -4446,70 +4446,70 @@
         <v>17.5</v>
       </c>
       <c r="AX15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ15">
         <v>14</v>
       </c>
       <c r="BA15">
+        <v>25</v>
+      </c>
+      <c r="BB15">
+        <v>50</v>
+      </c>
+      <c r="BC15">
+        <v>32</v>
+      </c>
+      <c r="BD15">
+        <v>34</v>
+      </c>
+      <c r="BE15">
+        <v>55</v>
+      </c>
+      <c r="BF15">
         <v>24</v>
       </c>
-      <c r="BB15">
-        <v>46</v>
-      </c>
-      <c r="BC15">
-        <v>30</v>
-      </c>
-      <c r="BD15">
-        <v>30</v>
-      </c>
-      <c r="BE15">
-        <v>32</v>
-      </c>
-      <c r="BF15">
-        <v>23</v>
-      </c>
       <c r="BG15">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH15">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BI15">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK15">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="BL15">
         <v>95</v>
       </c>
       <c r="BM15">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BN15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO15">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BP15">
         <v>30</v>
       </c>
       <c r="BQ15">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BR15">
         <v>38</v>
       </c>
       <c r="BS15">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BT15">
         <v>6.2</v>
@@ -4521,19 +4521,19 @@
         <v>17</v>
       </c>
       <c r="BW15">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX15">
         <v>28</v>
       </c>
       <c r="BY15">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BZ15">
         <v>20</v>
       </c>
       <c r="CA15">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="CB15" t="s">
         <v>186</v>
@@ -4556,25 +4556,25 @@
         <v>166</v>
       </c>
       <c r="F16">
+        <v>3.65</v>
+      </c>
+      <c r="G16">
+        <v>3.75</v>
+      </c>
+      <c r="H16">
+        <v>2.12</v>
+      </c>
+      <c r="I16">
+        <v>2.16</v>
+      </c>
+      <c r="J16">
+        <v>3.7</v>
+      </c>
+      <c r="K16">
         <v>3.85</v>
       </c>
-      <c r="G16">
-        <v>4</v>
-      </c>
-      <c r="H16">
-        <v>2.08</v>
-      </c>
-      <c r="I16">
-        <v>2.12</v>
-      </c>
-      <c r="J16">
-        <v>3.65</v>
-      </c>
-      <c r="K16">
-        <v>3.75</v>
-      </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
         <v>1.07</v>
@@ -4583,46 +4583,46 @@
         <v>4</v>
       </c>
       <c r="O16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P16">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q16">
         <v>1.94</v>
       </c>
       <c r="R16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
         <v>3.4</v>
       </c>
       <c r="T16">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U16">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z16">
         <v>13.5</v>
       </c>
       <c r="AA16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC16">
         <v>8.199999999999999</v>
@@ -4634,58 +4634,58 @@
         <v>22</v>
       </c>
       <c r="AF16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
         <v>17.5</v>
       </c>
       <c r="AI16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ16">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL16">
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AN16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO16">
         <v>15</v>
       </c>
       <c r="AP16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ16">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR16">
         <v>12</v>
       </c>
       <c r="AS16">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AT16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV16">
         <v>9.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX16">
         <v>24</v>
@@ -4694,28 +4694,28 @@
         <v>14</v>
       </c>
       <c r="AZ16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB16">
         <v>60</v>
       </c>
       <c r="BC16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE16">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH16">
         <v>3.5</v>
@@ -4727,55 +4727,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN16">
+        <v>7</v>
+      </c>
+      <c r="BO16">
+        <v>6.2</v>
+      </c>
+      <c r="BP16">
+        <v>30</v>
+      </c>
+      <c r="BQ16">
+        <v>10</v>
+      </c>
+      <c r="BR16">
+        <v>40</v>
+      </c>
+      <c r="BS16">
+        <v>11</v>
+      </c>
+      <c r="BT16">
+        <v>5</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>15.5</v>
+      </c>
+      <c r="BW16">
         <v>7.6</v>
-      </c>
-      <c r="BO16">
-        <v>4.9</v>
-      </c>
-      <c r="BP16">
-        <v>34</v>
-      </c>
-      <c r="BQ16">
-        <v>9.6</v>
-      </c>
-      <c r="BR16">
-        <v>42</v>
-      </c>
-      <c r="BS16">
-        <v>10</v>
-      </c>
-      <c r="BT16">
-        <v>4.9</v>
-      </c>
-      <c r="BU16">
-        <v>4.3</v>
-      </c>
-      <c r="BV16">
-        <v>15</v>
-      </c>
-      <c r="BW16">
-        <v>7</v>
       </c>
       <c r="BX16">
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ16">
         <v>25</v>
       </c>
       <c r="CA16">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB16" t="s">
         <v>186</v>
@@ -4798,25 +4798,25 @@
         <v>167</v>
       </c>
       <c r="F17">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="G17">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="H17">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="I17">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="J17">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M17">
         <v>1.03</v>
@@ -4828,85 +4828,85 @@
         <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R17">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S17">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T17">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U17">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V17">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Y17">
+        <v>10</v>
+      </c>
+      <c r="Z17">
+        <v>8</v>
+      </c>
+      <c r="AA17">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA17">
-        <v>10.5</v>
-      </c>
       <c r="AB17">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AC17">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF17">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AG17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AH17">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AI17">
         <v>36</v>
       </c>
       <c r="AJ17">
-        <v>620</v>
+        <v>880</v>
       </c>
       <c r="AK17">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="AL17">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AM17">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="AN17">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="AO17">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AP17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ17">
         <v>8.800000000000001</v>
@@ -4915,13 +4915,13 @@
         <v>7</v>
       </c>
       <c r="AS17">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AU17">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV17">
         <v>9.800000000000001</v>
@@ -4930,31 +4930,31 @@
         <v>12</v>
       </c>
       <c r="AX17">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AY17">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AZ17">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB17">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BC17">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE17">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG17">
         <v>4</v>
@@ -4963,7 +4963,7 @@
         <v>5.2</v>
       </c>
       <c r="BI17">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BJ17">
         <v>12</v>
@@ -4975,49 +4975,49 @@
         <v>1000</v>
       </c>
       <c r="BM17">
+        <v>11</v>
+      </c>
+      <c r="BN17">
+        <v>18.5</v>
+      </c>
+      <c r="BO17">
         <v>7.2</v>
-      </c>
-      <c r="BN17">
-        <v>18</v>
-      </c>
-      <c r="BO17">
-        <v>5.3</v>
       </c>
       <c r="BP17">
         <v>110</v>
       </c>
       <c r="BQ17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BR17">
         <v>95</v>
       </c>
       <c r="BS17">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BT17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU17">
         <v>3.5</v>
       </c>
       <c r="BV17">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BW17">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX17">
         <v>20</v>
       </c>
       <c r="BY17">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ17">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="CA17">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB17" t="s">
         <v>186</v>
@@ -5040,97 +5040,97 @@
         <v>168</v>
       </c>
       <c r="F18">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H18">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="I18">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="J18">
         <v>3.45</v>
       </c>
       <c r="K18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L18">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M18">
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P18">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R18">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U18">
         <v>2.12</v>
       </c>
       <c r="V18">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AA18">
         <v>32</v>
       </c>
       <c r="AB18">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD18">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG18">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH18">
         <v>21</v>
       </c>
       <c r="AI18">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AJ18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK18">
         <v>55</v>
@@ -5142,46 +5142,46 @@
         <v>110</v>
       </c>
       <c r="AN18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO18">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AP18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
         <v>8.6</v>
       </c>
       <c r="AR18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS18">
         <v>23</v>
       </c>
       <c r="AT18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW18">
         <v>20</v>
       </c>
       <c r="AX18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY18">
         <v>13.5</v>
       </c>
       <c r="AZ18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB18">
         <v>46</v>
@@ -5190,37 +5190,37 @@
         <v>30</v>
       </c>
       <c r="BD18">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF18">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BG18">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI18">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ18">
         <v>11</v>
       </c>
       <c r="BK18">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BN18">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO18">
         <v>5.6</v>
@@ -5229,37 +5229,37 @@
         <v>34</v>
       </c>
       <c r="BQ18">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BR18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS18">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BT18">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU18">
         <v>4</v>
       </c>
       <c r="BV18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW18">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX18">
         <v>32</v>
       </c>
       <c r="BY18">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA18">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB18" t="s">
         <v>186</v>
@@ -5282,10 +5282,10 @@
         <v>169</v>
       </c>
       <c r="F19">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="G19">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -5294,73 +5294,73 @@
         <v>4.3</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M19">
         <v>1.04</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O19">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R19">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S19">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="T19">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U19">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.3</v>
       </c>
       <c r="W19">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z19">
         <v>36</v>
       </c>
       <c r="AA19">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5369,61 +5369,61 @@
         <v>16</v>
       </c>
       <c r="AI19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ19">
         <v>23</v>
       </c>
       <c r="AK19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL19">
+        <v>27</v>
+      </c>
+      <c r="AM19">
+        <v>65</v>
+      </c>
+      <c r="AN19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO19">
+        <v>34</v>
+      </c>
+      <c r="AP19">
+        <v>20</v>
+      </c>
+      <c r="AQ19">
+        <v>19</v>
+      </c>
+      <c r="AR19">
         <v>30</v>
-      </c>
-      <c r="AM19">
-        <v>70</v>
-      </c>
-      <c r="AN19">
-        <v>10.5</v>
-      </c>
-      <c r="AO19">
-        <v>40</v>
-      </c>
-      <c r="AP19">
-        <v>18</v>
-      </c>
-      <c r="AQ19">
-        <v>16</v>
-      </c>
-      <c r="AR19">
-        <v>28</v>
       </c>
       <c r="AS19">
         <v>55</v>
       </c>
       <c r="AT19">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU19">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY19">
         <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB19">
         <v>20</v>
@@ -5438,70 +5438,70 @@
         <v>48</v>
       </c>
       <c r="BF19">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH19">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI19">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BJ19">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK19">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL19">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BM19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN19">
         <v>4.9</v>
       </c>
       <c r="BO19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ19">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BR19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS19">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT19">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU19">
         <v>6.8</v>
       </c>
       <c r="BV19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW19">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ19">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA19">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="CB19" t="s">
         <v>186</v>
@@ -5524,10 +5524,10 @@
         <v>170</v>
       </c>
       <c r="F20">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G20">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H20">
         <v>2.3</v>
@@ -5536,10 +5536,10 @@
         <v>2.64</v>
       </c>
       <c r="J20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.28</v>
@@ -5551,31 +5551,31 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
+        <v>2.52</v>
+      </c>
+      <c r="Q20">
+        <v>1.57</v>
+      </c>
+      <c r="R20">
+        <v>1.59</v>
+      </c>
+      <c r="S20">
+        <v>2.44</v>
+      </c>
+      <c r="T20">
+        <v>1.56</v>
+      </c>
+      <c r="U20">
         <v>2.5</v>
-      </c>
-      <c r="Q20">
-        <v>1.56</v>
-      </c>
-      <c r="R20">
-        <v>1.64</v>
-      </c>
-      <c r="S20">
-        <v>2.4</v>
-      </c>
-      <c r="T20">
-        <v>1.52</v>
-      </c>
-      <c r="U20">
-        <v>2.42</v>
       </c>
       <c r="V20">
         <v>1.62</v>
       </c>
       <c r="W20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X20">
         <v>28</v>
@@ -5635,7 +5635,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR20">
         <v>4.5</v>
@@ -5766,58 +5766,58 @@
         <v>171</v>
       </c>
       <c r="F21">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I21">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J21">
+        <v>3.15</v>
+      </c>
+      <c r="K21">
         <v>3.3</v>
       </c>
-      <c r="K21">
-        <v>3.5</v>
-      </c>
       <c r="L21">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M21">
         <v>1.12</v>
       </c>
       <c r="N21">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O21">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P21">
         <v>1.62</v>
       </c>
       <c r="Q21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
         <v>1.23</v>
       </c>
       <c r="S21">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T21">
         <v>2.1</v>
       </c>
       <c r="U21">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="X21">
         <v>10.5</v>
@@ -5826,79 +5826,79 @@
         <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA21">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB21">
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE21">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG21">
         <v>11</v>
       </c>
       <c r="AH21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ21">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AK21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM21">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN21">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="AO21">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP21">
         <v>8.6</v>
       </c>
       <c r="AQ21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS21">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="AT21">
         <v>6.2</v>
       </c>
       <c r="AU21">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW21">
-        <v>55</v>
+        <v>9.4</v>
       </c>
       <c r="AX21">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY21">
         <v>10</v>
@@ -5907,7 +5907,7 @@
         <v>22</v>
       </c>
       <c r="BA21">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="BB21">
         <v>19</v>
@@ -5919,67 +5919,67 @@
         <v>42</v>
       </c>
       <c r="BE21">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="BF21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG21">
-        <v>90</v>
+        <v>9.4</v>
       </c>
       <c r="BH21">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI21">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BN21">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO21">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP21">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT21">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU21">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
@@ -6008,22 +6008,22 @@
         <v>172</v>
       </c>
       <c r="F22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I22">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="J22">
         <v>6.4</v>
       </c>
       <c r="K22">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L22">
         <v>1.32</v>
@@ -6032,7 +6032,7 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>1.23</v>
@@ -6041,85 +6041,85 @@
         <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S22">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U22">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W22">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="X22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z22">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA22">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="AB22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD22">
         <v>55</v>
       </c>
       <c r="AE22">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AF22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI22">
+        <v>210</v>
+      </c>
+      <c r="AJ22">
+        <v>9.4</v>
+      </c>
+      <c r="AK22">
+        <v>14.5</v>
+      </c>
+      <c r="AL22">
+        <v>44</v>
+      </c>
+      <c r="AM22">
         <v>270</v>
       </c>
-      <c r="AJ22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK22">
-        <v>15</v>
-      </c>
-      <c r="AL22">
-        <v>46</v>
-      </c>
-      <c r="AM22">
-        <v>250</v>
-      </c>
       <c r="AN22">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AP22">
         <v>20</v>
       </c>
       <c r="AQ22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR22">
         <v>28</v>
@@ -6128,19 +6128,19 @@
         <v>20</v>
       </c>
       <c r="AT22">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU22">
         <v>13</v>
       </c>
       <c r="AV22">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AW22">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY22">
         <v>10</v>
@@ -6149,16 +6149,16 @@
         <v>32</v>
       </c>
       <c r="BA22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB22">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC22">
         <v>13</v>
       </c>
       <c r="BD22">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BE22">
         <v>38</v>
@@ -6167,7 +6167,7 @@
         <v>4.6</v>
       </c>
       <c r="BG22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH22">
         <v>4.2</v>
@@ -6176,58 +6176,58 @@
         <v>3.85</v>
       </c>
       <c r="BJ22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK22">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN22">
         <v>3.6</v>
       </c>
       <c r="BO22">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP22">
         <v>7.2</v>
       </c>
       <c r="BQ22">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR22">
         <v>26</v>
       </c>
       <c r="BS22">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU22">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY22">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ22">
         <v>11.5</v>
       </c>
       <c r="CA22">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
         <v>186</v>
@@ -6268,34 +6268,34 @@
         <v>14</v>
       </c>
       <c r="L23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M23">
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="O23">
         <v>1.07</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q23">
         <v>1.23</v>
       </c>
       <c r="R23">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="S23">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T23">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U23">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V23">
         <v>1.02</v>
@@ -6304,10 +6304,10 @@
         <v>9.6</v>
       </c>
       <c r="X23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y23">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="Z23">
         <v>440</v>
@@ -6316,7 +6316,7 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC23">
         <v>34</v>
@@ -6325,7 +6325,7 @@
         <v>120</v>
       </c>
       <c r="AE23">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AF23">
         <v>12</v>
@@ -6340,7 +6340,7 @@
         <v>300</v>
       </c>
       <c r="AJ23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AK23">
         <v>14</v>
@@ -6352,25 +6352,25 @@
         <v>200</v>
       </c>
       <c r="AN23">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AQ23">
         <v>120</v>
       </c>
       <c r="AR23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AS23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU23">
         <v>32</v>
@@ -6379,10 +6379,10 @@
         <v>100</v>
       </c>
       <c r="AW23">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AX23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY23">
         <v>15.5</v>
@@ -6391,10 +6391,10 @@
         <v>48</v>
       </c>
       <c r="BA23">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="BB23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC23">
         <v>13.5</v>
@@ -6403,10 +6403,10 @@
         <v>36</v>
       </c>
       <c r="BE23">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="BF23">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BG23">
         <v>100</v>
@@ -6418,7 +6418,7 @@
         <v>6.6</v>
       </c>
       <c r="BJ23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK23">
         <v>13</v>
@@ -6427,22 +6427,22 @@
         <v>150</v>
       </c>
       <c r="BM23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN23">
         <v>4.2</v>
       </c>
       <c r="BO23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP23">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BQ23">
         <v>4.9</v>
       </c>
       <c r="BR23">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS23">
         <v>15.5</v>
@@ -6451,19 +6451,19 @@
         <v>28</v>
       </c>
       <c r="BU23">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="BV23">
         <v>200</v>
       </c>
       <c r="BW23">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BX23">
         <v>130</v>
       </c>
       <c r="BY23">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ23">
         <v>4.6</v>
@@ -6510,127 +6510,127 @@
         <v>15.5</v>
       </c>
       <c r="L24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M24">
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O24">
         <v>1.04</v>
       </c>
       <c r="P24">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q24">
         <v>1.14</v>
       </c>
       <c r="R24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U24">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V24">
         <v>1.03</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="X24">
         <v>130</v>
       </c>
       <c r="Y24">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="Z24">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AD24">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AE24">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="AF24">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH24">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI24">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AJ24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK24">
         <v>14</v>
       </c>
       <c r="AL24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM24">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN24">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AO24">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP24">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AQ24">
         <v>100</v>
       </c>
       <c r="AR24">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AS24">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AT24">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AU24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AV24">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AW24">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AX24">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ24">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BA24">
         <v>95</v>
@@ -6645,46 +6645,46 @@
         <v>30</v>
       </c>
       <c r="BE24">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="BF24">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BG24">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="BH24">
         <v>10.5</v>
       </c>
       <c r="BI24">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BJ24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK24">
         <v>12</v>
       </c>
       <c r="BL24">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BM24">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="BN24">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO24">
         <v>4.7</v>
       </c>
       <c r="BP24">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BQ24">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BS24">
         <v>13</v>
@@ -6693,25 +6693,25 @@
         <v>29</v>
       </c>
       <c r="BU24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV24">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="BW24">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BY24">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BZ24">
         <v>3.7</v>
       </c>
       <c r="CA24">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="CB24" t="s">
         <v>186</v>
@@ -6752,34 +6752,34 @@
         <v>3.75</v>
       </c>
       <c r="L25">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M25">
         <v>1.05</v>
       </c>
       <c r="N25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O25">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P25">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q25">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R25">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S25">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="T25">
         <v>1.59</v>
       </c>
       <c r="U25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V25">
         <v>1.59</v>
@@ -6788,10 +6788,10 @@
         <v>1.54</v>
       </c>
       <c r="X25">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z25">
         <v>19.5</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="AC25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25">
         <v>12</v>
       </c>
       <c r="AE25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25">
         <v>22</v>
@@ -6818,10 +6818,10 @@
         <v>12.5</v>
       </c>
       <c r="AH25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ25">
         <v>40</v>
@@ -6839,22 +6839,22 @@
         <v>18</v>
       </c>
       <c r="AO25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP25">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU25">
         <v>8.199999999999999</v>
@@ -6869,7 +6869,7 @@
         <v>20</v>
       </c>
       <c r="AY25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
         <v>13</v>
@@ -6893,7 +6893,7 @@
         <v>16.5</v>
       </c>
       <c r="BG25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH25">
         <v>3.9</v>
@@ -6902,16 +6902,16 @@
         <v>3.7</v>
       </c>
       <c r="BJ25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK25">
         <v>7.8</v>
       </c>
       <c r="BL25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM25">
-        <v>18.5</v>
+        <v>65</v>
       </c>
       <c r="BN25">
         <v>6</v>
@@ -6947,10 +6947,10 @@
         <v>27</v>
       </c>
       <c r="BY25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA25">
         <v>16.5</v>
@@ -6976,40 +6976,40 @@
         <v>176</v>
       </c>
       <c r="F26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G26">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="H26">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="I26">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="J26">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L26">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M26">
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P26">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q26">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R26">
         <v>1.39</v>
@@ -7021,28 +7021,28 @@
         <v>1.76</v>
       </c>
       <c r="U26">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V26">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="W26">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X26">
         <v>15.5</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA26">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -7054,148 +7054,148 @@
         <v>23</v>
       </c>
       <c r="AF26">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH26">
         <v>17</v>
       </c>
       <c r="AI26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AK26">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL26">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM26">
         <v>85</v>
       </c>
       <c r="AN26">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO26">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ26">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR26">
         <v>13.5</v>
       </c>
       <c r="AS26">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ26">
         <v>15.5</v>
       </c>
       <c r="BA26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB26">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BC26">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD26">
+        <v>40</v>
+      </c>
+      <c r="BE26">
+        <v>70</v>
+      </c>
+      <c r="BF26">
         <v>34</v>
       </c>
-      <c r="BE26">
-        <v>65</v>
-      </c>
-      <c r="BF26">
-        <v>30</v>
-      </c>
       <c r="BG26">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH26">
         <v>4.2</v>
       </c>
       <c r="BI26">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>5.2</v>
+        <v>85</v>
       </c>
       <c r="BN26">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO26">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ26">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BT26">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BU26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV26">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BW26">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY26">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB26" t="s">
         <v>186</v>
@@ -7242,22 +7242,22 @@
         <v>1.03</v>
       </c>
       <c r="N27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P27">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q27">
         <v>1.5</v>
       </c>
       <c r="R27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S27">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T27">
         <v>1.52</v>
@@ -7266,13 +7266,13 @@
         <v>2.86</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W27">
         <v>2.2</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y27">
         <v>27</v>
@@ -7287,7 +7287,7 @@
         <v>15</v>
       </c>
       <c r="AC27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>18</v>
@@ -7296,13 +7296,13 @@
         <v>44</v>
       </c>
       <c r="AF27">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG27">
         <v>10</v>
       </c>
       <c r="AH27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI27">
         <v>40</v>
@@ -7311,16 +7311,16 @@
         <v>21</v>
       </c>
       <c r="AK27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL27">
         <v>23</v>
       </c>
       <c r="AM27">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN27">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO27">
         <v>32</v>
@@ -7335,7 +7335,7 @@
         <v>38</v>
       </c>
       <c r="AS27">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT27">
         <v>14.5</v>
@@ -7344,19 +7344,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW27">
         <v>40</v>
       </c>
       <c r="AX27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA27">
         <v>36</v>
@@ -7365,19 +7365,19 @@
         <v>20</v>
       </c>
       <c r="BC27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF27">
         <v>6.4</v>
       </c>
       <c r="BG27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH27">
         <v>4.7</v>
@@ -7395,7 +7395,7 @@
         <v>65</v>
       </c>
       <c r="BM27">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BN27">
         <v>5</v>
@@ -7425,7 +7425,7 @@
         <v>29</v>
       </c>
       <c r="BW27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BX27">
         <v>30</v>
@@ -7460,226 +7460,226 @@
         <v>178</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G28">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H28">
+        <v>1.66</v>
+      </c>
+      <c r="I28">
         <v>1.67</v>
       </c>
-      <c r="I28">
-        <v>1.68</v>
-      </c>
       <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28">
         <v>4.1</v>
       </c>
-      <c r="K28">
-        <v>4.2</v>
-      </c>
       <c r="L28">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
+        <v>1.38</v>
+      </c>
+      <c r="P28">
+        <v>1.81</v>
+      </c>
+      <c r="Q28">
+        <v>2.2</v>
+      </c>
+      <c r="R28">
         <v>1.31</v>
       </c>
-      <c r="P28">
-        <v>2.02</v>
-      </c>
-      <c r="Q28">
-        <v>1.96</v>
-      </c>
-      <c r="R28">
-        <v>1.4</v>
-      </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="T28">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="V28">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X28">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y28">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z28">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA28">
         <v>16</v>
       </c>
       <c r="AB28">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC28">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF28">
         <v>55</v>
       </c>
       <c r="AG28">
+        <v>25</v>
+      </c>
+      <c r="AH28">
         <v>24</v>
       </c>
-      <c r="AH28">
-        <v>22</v>
-      </c>
       <c r="AI28">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ28">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AK28">
         <v>110</v>
       </c>
       <c r="AL28">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM28">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AN28">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AO28">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AP28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AR28">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AS28">
         <v>14.5</v>
       </c>
       <c r="AT28">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AU28">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX28">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AY28">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ28">
+        <v>22</v>
+      </c>
+      <c r="BA28">
+        <v>36</v>
+      </c>
+      <c r="BB28">
+        <v>22</v>
+      </c>
+      <c r="BC28">
+        <v>85</v>
+      </c>
+      <c r="BD28">
+        <v>70</v>
+      </c>
+      <c r="BE28">
         <v>19</v>
       </c>
-      <c r="BA28">
-        <v>32</v>
-      </c>
-      <c r="BB28">
+      <c r="BF28">
         <v>120</v>
       </c>
-      <c r="BC28">
-        <v>70</v>
-      </c>
-      <c r="BD28">
-        <v>55</v>
-      </c>
-      <c r="BE28">
-        <v>85</v>
-      </c>
-      <c r="BF28">
-        <v>70</v>
-      </c>
       <c r="BG28">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH28">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BI28">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK28">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BL28">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="BM28">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BN28">
         <v>11.5</v>
       </c>
       <c r="BO28">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BP28">
         <v>65</v>
       </c>
       <c r="BQ28">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BR28">
         <v>70</v>
       </c>
       <c r="BS28">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BU28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV28">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BW28">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY28">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BZ28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA28">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="CB28" t="s">
         <v>186</v>
@@ -7702,109 +7702,109 @@
         <v>179</v>
       </c>
       <c r="F29">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G29">
         <v>1.69</v>
       </c>
       <c r="H29">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29">
         <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L29">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M29">
         <v>1.14</v>
       </c>
       <c r="N29">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="O29">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P29">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q29">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R29">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S29">
         <v>6.2</v>
       </c>
       <c r="T29">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
         <v>1.5</v>
       </c>
       <c r="V29">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W29">
         <v>2.44</v>
       </c>
       <c r="X29">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y29">
         <v>18</v>
       </c>
       <c r="Z29">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA29">
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="AB29">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AC29">
         <v>9.4</v>
       </c>
       <c r="AD29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE29">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AF29">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG29">
         <v>12.5</v>
       </c>
       <c r="AH29">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AI29">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="AJ29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK29">
         <v>28</v>
       </c>
       <c r="AL29">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM29">
         <v>700</v>
       </c>
       <c r="AN29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO29">
         <v>1000</v>
@@ -7816,22 +7816,22 @@
         <v>14.5</v>
       </c>
       <c r="AR29">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AS29">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT29">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU29">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV29">
         <v>16.5</v>
       </c>
       <c r="AW29">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX29">
         <v>6.6</v>
@@ -7840,10 +7840,10 @@
         <v>10</v>
       </c>
       <c r="AZ29">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BA29">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB29">
         <v>13.5</v>
@@ -7852,76 +7852,76 @@
         <v>21</v>
       </c>
       <c r="BD29">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE29">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG29">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BH29">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BI29">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ29">
         <v>15.5</v>
       </c>
       <c r="BK29">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN29">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO29">
         <v>3.3</v>
       </c>
       <c r="BP29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ29">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR29">
         <v>48</v>
       </c>
       <c r="BS29">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT29">
         <v>12</v>
       </c>
       <c r="BU29">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ29">
         <v>40</v>
       </c>
       <c r="CA29">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB29" t="s">
         <v>186</v>
@@ -7944,94 +7944,94 @@
         <v>180</v>
       </c>
       <c r="F30">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="G30">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H30">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I30">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J30">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M30">
         <v>1.1</v>
       </c>
       <c r="N30">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O30">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P30">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R30">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S30">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T30">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="U30">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="X30">
         <v>10.5</v>
       </c>
       <c r="Y30">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z30">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA30">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB30">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC30">
         <v>7.6</v>
       </c>
       <c r="AD30">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF30">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG30">
         <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI30">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AJ30">
         <v>36</v>
@@ -8040,7 +8040,7 @@
         <v>32</v>
       </c>
       <c r="AL30">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM30">
         <v>580</v>
@@ -8049,121 +8049,121 @@
         <v>32</v>
       </c>
       <c r="AO30">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="AP30">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ30">
         <v>9.4</v>
       </c>
       <c r="AR30">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AS30">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="AT30">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU30">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BB30">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BC30">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BD30">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE30">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="BF30">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BG30">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BH30">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI30">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK30">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN30">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO30">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP30">
         <v>20</v>
       </c>
       <c r="BQ30">
+        <v>7.8</v>
+      </c>
+      <c r="BR30">
+        <v>40</v>
+      </c>
+      <c r="BS30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT30">
         <v>6.8</v>
       </c>
-      <c r="BR30">
-        <v>42</v>
-      </c>
-      <c r="BS30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT30">
-        <v>7.2</v>
-      </c>
       <c r="BU30">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV30">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BW30">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ30">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA30">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB30" t="s">
         <v>186</v>
@@ -8186,64 +8186,64 @@
         <v>181</v>
       </c>
       <c r="F31">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H31">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I31">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L31">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M31">
         <v>1.13</v>
       </c>
       <c r="N31">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O31">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P31">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q31">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R31">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S31">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U31">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="V31">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X31">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z31">
         <v>40</v>
@@ -8252,31 +8252,31 @@
         <v>900</v>
       </c>
       <c r="AB31">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC31">
         <v>8.4</v>
       </c>
       <c r="AD31">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE31">
         <v>500</v>
       </c>
       <c r="AF31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI31">
         <v>500</v>
       </c>
       <c r="AJ31">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK31">
         <v>65</v>
@@ -8288,70 +8288,70 @@
         <v>500</v>
       </c>
       <c r="AN31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO31">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AP31">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR31">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AS31">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT31">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU31">
         <v>6.6</v>
       </c>
       <c r="AV31">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AW31">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX31">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY31">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BA31">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB31">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC31">
         <v>21</v>
       </c>
       <c r="BD31">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BE31">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF31">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG31">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH31">
         <v>2.94</v>
       </c>
       <c r="BI31">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ31">
         <v>14</v>
@@ -8363,19 +8363,19 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN31">
+        <v>4.6</v>
+      </c>
+      <c r="BO31">
+        <v>3.55</v>
+      </c>
+      <c r="BP31">
+        <v>17.5</v>
+      </c>
+      <c r="BQ31">
         <v>4.9</v>
-      </c>
-      <c r="BO31">
-        <v>3.6</v>
-      </c>
-      <c r="BP31">
-        <v>17</v>
-      </c>
-      <c r="BQ31">
-        <v>4.8</v>
       </c>
       <c r="BR31">
         <v>1000</v>
@@ -8384,22 +8384,22 @@
         <v>5.9</v>
       </c>
       <c r="BT31">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW31">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ31">
         <v>0</v>
@@ -8437,7 +8437,7 @@
         <v>6.4</v>
       </c>
       <c r="I32">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>4.3</v>
@@ -8455,7 +8455,7 @@
         <v>3.85</v>
       </c>
       <c r="O32">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P32">
         <v>2</v>
@@ -8464,7 +8464,7 @@
         <v>1.93</v>
       </c>
       <c r="R32">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S32">
         <v>3.4</v>
@@ -8473,10 +8473,10 @@
         <v>1.98</v>
       </c>
       <c r="U32">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V32">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W32">
         <v>2.6</v>
@@ -8506,7 +8506,7 @@
         <v>700</v>
       </c>
       <c r="AF32">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8518,7 +8518,7 @@
         <v>320</v>
       </c>
       <c r="AJ32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK32">
         <v>18</v>
@@ -8539,13 +8539,13 @@
         <v>14</v>
       </c>
       <c r="AQ32">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AR32">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AS32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32">
         <v>7</v>
@@ -8557,19 +8557,19 @@
         <v>13</v>
       </c>
       <c r="AW32">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX32">
         <v>8</v>
       </c>
       <c r="AY32">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ32">
         <v>21</v>
       </c>
       <c r="BA32">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB32">
         <v>13</v>
@@ -8578,16 +8578,16 @@
         <v>15</v>
       </c>
       <c r="BD32">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BE32">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32">
         <v>8</v>
       </c>
       <c r="BG32">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH32">
         <v>3.95</v>
@@ -8682,40 +8682,40 @@
         <v>4.8</v>
       </c>
       <c r="J33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
         <v>3.15</v>
       </c>
       <c r="L33">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N33">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q33">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R33">
         <v>1.17</v>
       </c>
       <c r="S33">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T33">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U33">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V33">
         <v>1.26</v>
@@ -8724,7 +8724,7 @@
         <v>1.86</v>
       </c>
       <c r="X33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y33">
         <v>11.5</v>
@@ -8742,19 +8742,19 @@
         <v>7.4</v>
       </c>
       <c r="AD33">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE33">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="AF33">
         <v>11</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH33">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI33">
         <v>130</v>
@@ -8766,10 +8766,10 @@
         <v>32</v>
       </c>
       <c r="AL33">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM33">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN33">
         <v>32</v>
@@ -8787,10 +8787,10 @@
         <v>29</v>
       </c>
       <c r="AS33">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AT33">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU33">
         <v>6.8</v>
@@ -8799,7 +8799,7 @@
         <v>19</v>
       </c>
       <c r="AW33">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AX33">
         <v>10</v>
@@ -8808,10 +8808,10 @@
         <v>11</v>
       </c>
       <c r="AZ33">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA33">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB33">
         <v>24</v>
@@ -8823,13 +8823,13 @@
         <v>60</v>
       </c>
       <c r="BE33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BF33">
         <v>27</v>
       </c>
       <c r="BG33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH33">
         <v>2.82</v>
@@ -8841,13 +8841,13 @@
         <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BN33">
         <v>5.3</v>
@@ -8856,16 +8856,16 @@
         <v>4.1</v>
       </c>
       <c r="BP33">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BQ33">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR33">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS33">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BT33">
         <v>7.8</v>
@@ -8877,19 +8877,19 @@
         <v>55</v>
       </c>
       <c r="BW33">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BX33">
         <v>95</v>
       </c>
       <c r="BY33">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BZ33">
         <v>55</v>
       </c>
       <c r="CA33">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="CB33" t="s">
         <v>186</v>
@@ -8912,31 +8912,31 @@
         <v>184</v>
       </c>
       <c r="F34">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="G34">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H34">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I34">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J34">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K34">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L34">
         <v>1.46</v>
       </c>
       <c r="M34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O34">
         <v>1.39</v>
@@ -8948,7 +8948,7 @@
         <v>2.18</v>
       </c>
       <c r="R34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
         <v>4.1</v>
@@ -8960,16 +8960,16 @@
         <v>1.88</v>
       </c>
       <c r="V34">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W34">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="X34">
         <v>12</v>
       </c>
       <c r="Y34">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z34">
         <v>40</v>
@@ -8981,7 +8981,7 @@
         <v>7.6</v>
       </c>
       <c r="AC34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD34">
         <v>22</v>
@@ -8990,7 +8990,7 @@
         <v>85</v>
       </c>
       <c r="AF34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>10.5</v>
@@ -8999,22 +8999,22 @@
         <v>23</v>
       </c>
       <c r="AI34">
-        <v>370</v>
+        <v>95</v>
       </c>
       <c r="AJ34">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK34">
         <v>21</v>
       </c>
       <c r="AL34">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AM34">
         <v>150</v>
       </c>
       <c r="AN34">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO34">
         <v>110</v>
@@ -9026,37 +9026,37 @@
         <v>14</v>
       </c>
       <c r="AR34">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS34">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AT34">
         <v>7</v>
       </c>
       <c r="AU34">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV34">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW34">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY34">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY34">
-        <v>9.6</v>
       </c>
       <c r="AZ34">
         <v>20</v>
       </c>
       <c r="BA34">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BB34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC34">
         <v>18.5</v>
@@ -9065,70 +9065,70 @@
         <v>38</v>
       </c>
       <c r="BE34">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG34">
-        <v>16.5</v>
+        <v>48</v>
       </c>
       <c r="BH34">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI34">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ34">
         <v>11</v>
       </c>
       <c r="BK34">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN34">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO34">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ34">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR34">
         <v>32</v>
       </c>
       <c r="BS34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU34">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV34">
         <v>55</v>
       </c>
       <c r="BW34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX34">
         <v>65</v>
       </c>
       <c r="BY34">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA34">
         <v>10</v>
@@ -9154,7 +9154,7 @@
         <v>185</v>
       </c>
       <c r="F35">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G35">
         <v>2.02</v>
@@ -9178,7 +9178,7 @@
         <v>1.06</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O35">
         <v>1.28</v>
@@ -9187,13 +9187,13 @@
         <v>2.06</v>
       </c>
       <c r="Q35">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R35">
         <v>1.41</v>
       </c>
       <c r="S35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T35">
         <v>1.73</v>
@@ -9202,13 +9202,13 @@
         <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W35">
         <v>1.98</v>
       </c>
       <c r="X35">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y35">
         <v>17.5</v>
@@ -9268,10 +9268,10 @@
         <v>14</v>
       </c>
       <c r="AR35">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AS35">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AT35">
         <v>8.4</v>
@@ -9283,7 +9283,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AX35">
         <v>10.5</v>
@@ -9295,7 +9295,7 @@
         <v>15</v>
       </c>
       <c r="BA35">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BB35">
         <v>19</v>
@@ -9304,16 +9304,16 @@
         <v>17</v>
       </c>
       <c r="BD35">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BE35">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BF35">
         <v>10.5</v>
       </c>
       <c r="BG35">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BH35">
         <v>3.75</v>
